--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B16A0B7-8D75-4743-AF6B-FF2B0CF71CE0}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937BB337-B783-4FDE-B0AF-53CF6C8A0708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38290" yWindow="-2070" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -34,7 +34,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="12">其他芯片!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">贴片电容!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">贴片电阻!$A$1:$J$1</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4">贴片结构料!$A$1:$J$54</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4">贴片结构料!$A$1:$J$55</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="11">振荡晶体!$A$1:$J$17</definedName>
     <definedName name="TMPPRTS">TMPPRTS!$A$1:$B$1</definedName>
   </definedNames>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4518" uniqueCount="2557">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4535" uniqueCount="2567">
   <si>
     <t>Part Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9653,10 +9653,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>PH2.0-2PWB</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>8mmx7.6mmx5.6mm</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -9816,10 +9812,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SOP-8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>SPI-FLASH</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -9921,6 +9913,54 @@
   </si>
   <si>
     <t>RC0402FR-0720K5L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PH2_0-2PWB</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3015140013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZIF 连接器;40pin;pitch 0.5mm;24.4*6mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AFC01-S40FCC-00</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>con40p_0d5mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24.4*6mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ZIF-40PIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2082700002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TXB0104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TXB0104PWR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOP-14</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TXB0104 带自动方向感应和 ±15kV ESD 保护功能的 4 位双向电压电平转换器</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10425,21 +10465,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J153"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="70.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="14.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10471,7 +10511,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>774</v>
       </c>
@@ -10488,7 +10528,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -10514,7 +10554,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>336</v>
       </c>
@@ -10540,7 +10580,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>568</v>
       </c>
@@ -10566,7 +10606,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1084</v>
       </c>
@@ -10592,7 +10632,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1548</v>
       </c>
@@ -10618,7 +10658,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1629</v>
       </c>
@@ -10644,7 +10684,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1630</v>
       </c>
@@ -10670,7 +10710,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1665</v>
       </c>
@@ -10696,7 +10736,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>128</v>
       </c>
@@ -10722,7 +10762,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>448</v>
       </c>
@@ -10748,7 +10788,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2457</v>
       </c>
@@ -10774,7 +10814,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1134</v>
       </c>
@@ -10800,7 +10840,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>889</v>
       </c>
@@ -10814,7 +10854,7 @@
         <v>892</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>891</v>
@@ -10826,7 +10866,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1500</v>
       </c>
@@ -10852,7 +10892,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>286</v>
       </c>
@@ -10878,7 +10918,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1032</v>
       </c>
@@ -10904,7 +10944,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1459</v>
       </c>
@@ -10930,7 +10970,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1849</v>
       </c>
@@ -10956,7 +10996,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>291</v>
       </c>
@@ -10982,7 +11022,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>369</v>
       </c>
@@ -11008,7 +11048,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>830</v>
       </c>
@@ -11034,7 +11074,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1422</v>
       </c>
@@ -11060,7 +11100,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>177</v>
       </c>
@@ -11086,7 +11126,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>418</v>
       </c>
@@ -11112,7 +11152,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>1210</v>
       </c>
@@ -11138,7 +11178,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>2312</v>
       </c>
@@ -11164,7 +11204,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>711</v>
       </c>
@@ -11190,7 +11230,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>964</v>
       </c>
@@ -11216,7 +11256,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1320</v>
       </c>
@@ -11242,7 +11282,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>2350</v>
       </c>
@@ -11268,33 +11308,33 @@
         <v>339</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>2521</v>
+        <v>2520</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2520</v>
+        <v>2519</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
+        <v>2522</v>
+      </c>
+      <c r="G33" s="1" t="s">
         <v>2523</v>
-      </c>
-      <c r="G33" s="1" t="s">
-        <v>2524</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1841</v>
       </c>
@@ -11320,7 +11360,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>722</v>
       </c>
@@ -11346,7 +11386,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>473</v>
       </c>
@@ -11372,7 +11412,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1669</v>
       </c>
@@ -11398,7 +11438,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1258</v>
       </c>
@@ -11424,7 +11464,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>425</v>
       </c>
@@ -11450,7 +11490,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>1337</v>
       </c>
@@ -11476,7 +11516,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>2134</v>
       </c>
@@ -11502,7 +11542,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>1889</v>
       </c>
@@ -11528,7 +11568,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>1100</v>
       </c>
@@ -11554,7 +11594,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>1207</v>
       </c>
@@ -11580,7 +11620,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>2156</v>
       </c>
@@ -11606,7 +11646,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>776</v>
       </c>
@@ -11632,7 +11672,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>953</v>
       </c>
@@ -11658,7 +11698,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>1473</v>
       </c>
@@ -11684,24 +11724,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>2507</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>2508</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>2505</v>
+        <v>2504</v>
       </c>
       <c r="G49" t="s">
         <v>91</v>
@@ -11710,24 +11750,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>2509</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>2510</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>2511</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="G50" t="s">
         <v>91</v>
@@ -11736,7 +11776,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>1923</v>
       </c>
@@ -11762,7 +11802,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>1611</v>
       </c>
@@ -11788,7 +11828,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>1978</v>
       </c>
@@ -11814,7 +11854,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>1162</v>
       </c>
@@ -11840,7 +11880,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>1313</v>
       </c>
@@ -11866,7 +11906,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>1396</v>
       </c>
@@ -11892,7 +11932,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>409</v>
       </c>
@@ -11918,7 +11958,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>1587</v>
       </c>
@@ -11944,7 +11984,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>294</v>
       </c>
@@ -11970,7 +12010,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>643</v>
       </c>
@@ -11996,7 +12036,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>1633</v>
       </c>
@@ -12022,7 +12062,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>1685</v>
       </c>
@@ -12048,7 +12088,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>2303</v>
       </c>
@@ -12074,24 +12114,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>2551</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>2553</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>2555</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="G64" t="s">
         <v>91</v>
@@ -12100,7 +12140,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>1852</v>
       </c>
@@ -12126,7 +12166,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>1342</v>
       </c>
@@ -12152,7 +12192,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>357</v>
       </c>
@@ -12178,7 +12218,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>361</v>
       </c>
@@ -12204,7 +12244,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>899</v>
       </c>
@@ -12230,7 +12270,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>1677</v>
       </c>
@@ -12256,7 +12296,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>2296</v>
       </c>
@@ -12282,7 +12322,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>412</v>
       </c>
@@ -12308,7 +12348,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>2139</v>
       </c>
@@ -12334,7 +12374,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>1028</v>
       </c>
@@ -12360,7 +12400,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>2337</v>
       </c>
@@ -12386,7 +12426,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>1462</v>
       </c>
@@ -12412,7 +12452,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>180</v>
       </c>
@@ -12438,7 +12478,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>2175</v>
       </c>
@@ -12464,7 +12504,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>2435</v>
       </c>
@@ -12490,7 +12530,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>1293</v>
       </c>
@@ -12516,7 +12556,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>1165</v>
       </c>
@@ -12542,7 +12582,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>480</v>
       </c>
@@ -12568,7 +12608,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>1532</v>
       </c>
@@ -12594,7 +12634,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>958</v>
       </c>
@@ -12620,24 +12660,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>2543</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>2545</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>2547</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="G85" t="s">
         <v>19</v>
@@ -12646,7 +12686,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>1690</v>
       </c>
@@ -12672,7 +12712,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>1691</v>
       </c>
@@ -12698,7 +12738,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>789</v>
       </c>
@@ -12724,7 +12764,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>1932</v>
       </c>
@@ -12750,7 +12790,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>1892</v>
       </c>
@@ -12776,7 +12816,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>1927</v>
       </c>
@@ -12802,7 +12842,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>1709</v>
       </c>
@@ -12828,7 +12868,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>1521</v>
       </c>
@@ -12854,7 +12894,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>130</v>
       </c>
@@ -12880,7 +12920,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>697</v>
       </c>
@@ -12906,7 +12946,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>1076</v>
       </c>
@@ -12932,7 +12972,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>1526</v>
       </c>
@@ -12958,24 +12998,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="G98" t="s">
         <v>19</v>
@@ -12984,7 +13024,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>1170</v>
       </c>
@@ -13010,7 +13050,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>1054</v>
       </c>
@@ -13036,7 +13076,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>1542</v>
       </c>
@@ -13062,7 +13102,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>408</v>
       </c>
@@ -13088,7 +13128,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>470</v>
       </c>
@@ -13114,7 +13154,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>482</v>
       </c>
@@ -13140,7 +13180,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>428</v>
       </c>
@@ -13166,7 +13206,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>1087</v>
       </c>
@@ -13192,7 +13232,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>1439</v>
       </c>
@@ -13218,7 +13258,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>163</v>
       </c>
@@ -13244,7 +13284,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>367</v>
       </c>
@@ -13270,7 +13310,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>368</v>
       </c>
@@ -13296,7 +13336,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>1096</v>
       </c>
@@ -13322,7 +13362,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>153</v>
       </c>
@@ -13348,7 +13388,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>157</v>
       </c>
@@ -13374,7 +13414,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>450</v>
       </c>
@@ -13400,7 +13440,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>1030</v>
       </c>
@@ -13426,7 +13466,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>1453</v>
       </c>
@@ -13452,7 +13492,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>1042</v>
       </c>
@@ -13478,7 +13518,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>1456</v>
       </c>
@@ -13504,7 +13544,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>944</v>
       </c>
@@ -13530,7 +13570,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>1287</v>
       </c>
@@ -13556,7 +13596,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>1158</v>
       </c>
@@ -13582,7 +13622,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>1575</v>
       </c>
@@ -13608,7 +13648,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>1681</v>
       </c>
@@ -13634,7 +13674,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>2235</v>
       </c>
@@ -13660,7 +13700,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>1475</v>
       </c>
@@ -13686,7 +13726,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>679</v>
       </c>
@@ -13712,7 +13752,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>687</v>
       </c>
@@ -13738,7 +13778,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>606</v>
       </c>
@@ -13764,7 +13804,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>400</v>
       </c>
@@ -13790,7 +13830,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>331</v>
       </c>
@@ -13816,7 +13856,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>338</v>
       </c>
@@ -13842,7 +13882,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>1154</v>
       </c>
@@ -13868,7 +13908,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>1703</v>
       </c>
@@ -13894,7 +13934,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>1816</v>
       </c>
@@ -13920,7 +13960,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>1079</v>
       </c>
@@ -13946,7 +13986,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>1675</v>
       </c>
@@ -13972,7 +14012,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>1883</v>
       </c>
@@ -13998,7 +14038,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>1272</v>
       </c>
@@ -14024,7 +14064,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>1103</v>
       </c>
@@ -14050,7 +14090,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>828</v>
       </c>
@@ -14076,7 +14116,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>1919</v>
       </c>
@@ -14102,7 +14142,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>1303</v>
       </c>
@@ -14128,7 +14168,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>2340</v>
       </c>
@@ -14154,7 +14194,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>2315</v>
       </c>
@@ -14180,7 +14220,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -14206,7 +14246,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>1388</v>
       </c>
@@ -14232,7 +14272,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>134</v>
       </c>
@@ -14258,7 +14298,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>1538</v>
       </c>
@@ -14284,7 +14324,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>690</v>
       </c>
@@ -14310,7 +14350,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>1053</v>
       </c>
@@ -14336,7 +14376,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>398</v>
       </c>
@@ -14362,7 +14402,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>694</v>
       </c>
@@ -14388,7 +14428,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>1649</v>
       </c>
@@ -14432,21 +14472,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A56977-BF1C-4909-8B1B-32F3873FBB32}">
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.58203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="78.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.875" customWidth="1"/>
     <col min="5" max="5" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14478,7 +14518,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>51</v>
       </c>
@@ -14504,7 +14544,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>681</v>
       </c>
@@ -14530,7 +14570,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>757</v>
       </c>
@@ -14556,7 +14596,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>759</v>
       </c>
@@ -14582,7 +14622,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>780</v>
       </c>
@@ -14608,7 +14648,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>866</v>
       </c>
@@ -14634,7 +14674,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>973</v>
       </c>
@@ -14660,7 +14700,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1035</v>
       </c>
@@ -14686,7 +14726,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1045</v>
       </c>
@@ -14712,7 +14752,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1425</v>
       </c>
@@ -14738,7 +14778,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1608</v>
       </c>
@@ -14764,7 +14804,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1731</v>
       </c>
@@ -14790,7 +14830,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1894</v>
       </c>
@@ -14816,7 +14856,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1897</v>
       </c>
@@ -14842,7 +14882,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1900</v>
       </c>
@@ -14868,7 +14908,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>2212</v>
       </c>
@@ -14894,7 +14934,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>65</v>
       </c>
@@ -14920,7 +14960,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>392</v>
       </c>
@@ -14946,7 +14986,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>421</v>
       </c>
@@ -14972,7 +15012,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>442</v>
       </c>
@@ -14998,7 +15038,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>461</v>
       </c>
@@ -15024,7 +15064,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>671</v>
       </c>
@@ -15050,7 +15090,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>799</v>
       </c>
@@ -15076,7 +15116,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>834</v>
       </c>
@@ -15102,7 +15142,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>1198</v>
       </c>
@@ -15131,7 +15171,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>1323</v>
       </c>
@@ -15157,7 +15197,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>1379</v>
       </c>
@@ -15183,7 +15223,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>1609</v>
       </c>
@@ -15209,7 +15249,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>1601</v>
       </c>
@@ -15235,7 +15275,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1926</v>
       </c>
@@ -15261,7 +15301,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>2128</v>
       </c>
@@ -15287,7 +15327,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>2226</v>
       </c>
@@ -15313,7 +15353,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>2306</v>
       </c>
@@ -15339,7 +15379,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1660</v>
       </c>
@@ -15365,7 +15405,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>2183</v>
       </c>
@@ -15391,7 +15431,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>2468</v>
       </c>
@@ -15414,27 +15454,27 @@
         <v>2472</v>
       </c>
       <c r="I37" t="s">
-        <v>2519</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2518</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="B38" t="s">
         <v>388</v>
       </c>
       <c r="C38" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="D38" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="E38" t="s">
         <v>2186</v>
       </c>
       <c r="F38" t="s">
-        <v>2535</v>
+        <v>2533</v>
       </c>
       <c r="G38" t="s">
         <v>2230</v>
@@ -15443,7 +15483,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>721</v>
       </c>
@@ -15469,7 +15509,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>1619</v>
       </c>
@@ -15495,33 +15535,33 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="B41" t="s">
         <v>716</v>
       </c>
       <c r="C41" t="s">
+        <v>2497</v>
+      </c>
+      <c r="D41" t="s">
         <v>2498</v>
-      </c>
-      <c r="D41" t="s">
-        <v>2499</v>
       </c>
       <c r="E41" t="s">
         <v>513</v>
       </c>
       <c r="F41" t="s">
-        <v>2500</v>
+        <v>2499</v>
       </c>
       <c r="G41" t="s">
         <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>2500</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2499</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>1643</v>
       </c>
@@ -15547,7 +15587,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>2249</v>
       </c>
@@ -15573,7 +15613,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>2368</v>
       </c>
@@ -15599,7 +15639,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>2379</v>
       </c>
@@ -15643,20 +15683,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013733C5-3D86-4F9A-8E9B-0FC55B649E0F}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="91.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.375" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15688,7 +15728,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>108</v>
       </c>
@@ -15714,7 +15754,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2385</v>
       </c>
@@ -15740,7 +15780,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2412</v>
       </c>
@@ -15766,7 +15806,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
@@ -15792,7 +15832,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1355</v>
       </c>
@@ -15818,7 +15858,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1356</v>
       </c>
@@ -15844,7 +15884,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>2019</v>
       </c>
@@ -15870,7 +15910,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1600</v>
       </c>
@@ -15896,24 +15936,24 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="B10" t="s">
         <v>1594</v>
       </c>
       <c r="C10" t="s">
+        <v>2535</v>
+      </c>
+      <c r="D10" t="s">
         <v>2537</v>
       </c>
-      <c r="D10" t="s">
-        <v>2539</v>
-      </c>
       <c r="E10" t="s">
+        <v>2536</v>
+      </c>
+      <c r="F10" t="s">
         <v>2538</v>
-      </c>
-      <c r="F10" t="s">
-        <v>2540</v>
       </c>
       <c r="G10" t="s">
         <v>129</v>
@@ -15934,20 +15974,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.58203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15979,7 +16019,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1743</v>
       </c>
@@ -16008,7 +16048,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>344</v>
       </c>
@@ -16037,7 +16077,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1562</v>
       </c>
@@ -16066,7 +16106,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>381</v>
       </c>
@@ -16095,7 +16135,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>881</v>
       </c>
@@ -16124,7 +16164,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1216</v>
       </c>
@@ -16153,7 +16193,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1742</v>
       </c>
@@ -16182,7 +16222,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1508</v>
       </c>
@@ -16211,7 +16251,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1748</v>
       </c>
@@ -16240,7 +16280,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1984</v>
       </c>
@@ -16269,7 +16309,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1961</v>
       </c>
@@ -16298,7 +16338,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1963</v>
       </c>
@@ -16327,7 +16367,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1744</v>
       </c>
@@ -16356,7 +16396,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1745</v>
       </c>
@@ -16385,7 +16425,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1746</v>
       </c>
@@ -16414,7 +16454,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1747</v>
       </c>
@@ -16443,7 +16483,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2177</v>
       </c>
@@ -16472,7 +16512,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>2193</v>
       </c>
@@ -16516,20 +16556,20 @@
 
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC4AD67-C776-4093-88E2-79BBC414D956}">
-  <dimension ref="A1:J42"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J43"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="118" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16561,7 +16601,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
@@ -16587,7 +16627,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>386</v>
       </c>
@@ -16610,10 +16650,10 @@
         <v>387</v>
       </c>
       <c r="I3" t="s">
-        <v>2531</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>2529</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>656</v>
       </c>
@@ -16639,7 +16679,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>984</v>
       </c>
@@ -16665,7 +16705,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1003</v>
       </c>
@@ -16691,7 +16731,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1007</v>
       </c>
@@ -16717,7 +16757,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1399</v>
       </c>
@@ -16743,7 +16783,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1513</v>
       </c>
@@ -16769,7 +16809,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1514</v>
       </c>
@@ -16795,7 +16835,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1753</v>
       </c>
@@ -16821,7 +16861,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1754</v>
       </c>
@@ -16847,7 +16887,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2207</v>
       </c>
@@ -16873,33 +16913,33 @@
         <v>658</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>2525</v>
+        <v>2524</v>
       </c>
       <c r="B14" t="s">
         <v>382</v>
       </c>
       <c r="C14" t="s">
+        <v>2525</v>
+      </c>
+      <c r="D14" t="s">
         <v>2526</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>2527</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>2528</v>
       </c>
-      <c r="F14" t="s">
+      <c r="G14" t="s">
+        <v>989</v>
+      </c>
+      <c r="I14" t="s">
         <v>2529</v>
       </c>
-      <c r="G14" t="s">
-        <v>2530</v>
-      </c>
-      <c r="I14" t="s">
-        <v>2531</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>593</v>
       </c>
@@ -16925,7 +16965,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>840</v>
       </c>
@@ -16951,7 +16991,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1634</v>
       </c>
@@ -16977,7 +17017,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1635</v>
       </c>
@@ -17003,7 +17043,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1636</v>
       </c>
@@ -17029,336 +17069,336 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>1637</v>
+        <v>2562</v>
       </c>
       <c r="B20" t="s">
-        <v>929</v>
+        <v>433</v>
       </c>
       <c r="C20" t="s">
-        <v>930</v>
-      </c>
-      <c r="D20" t="s">
-        <v>931</v>
+        <v>2563</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>2566</v>
       </c>
       <c r="E20" t="s">
         <v>844</v>
       </c>
       <c r="F20" t="s">
-        <v>933</v>
+        <v>2564</v>
       </c>
       <c r="G20" t="s">
-        <v>935</v>
+        <v>2565</v>
       </c>
       <c r="I20" t="s">
-        <v>930</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2563</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>1638</v>
+        <v>1637</v>
       </c>
       <c r="B21" t="s">
         <v>929</v>
       </c>
       <c r="C21" t="s">
-        <v>932</v>
+        <v>930</v>
       </c>
       <c r="D21" t="s">
-        <v>961</v>
+        <v>931</v>
       </c>
       <c r="E21" t="s">
         <v>844</v>
       </c>
       <c r="F21" t="s">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="G21" t="s">
         <v>935</v>
       </c>
       <c r="I21" t="s">
+        <v>930</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A22" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="B22" t="s">
+        <v>929</v>
+      </c>
+      <c r="C22" t="s">
         <v>932</v>
       </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A22" s="2" t="s">
+      <c r="D22" t="s">
+        <v>961</v>
+      </c>
+      <c r="E22" t="s">
+        <v>844</v>
+      </c>
+      <c r="F22" t="s">
+        <v>934</v>
+      </c>
+      <c r="G22" t="s">
+        <v>935</v>
+      </c>
+      <c r="I22" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A23" s="2" t="s">
         <v>457</v>
-      </c>
-      <c r="B22" t="s">
-        <v>453</v>
-      </c>
-      <c r="C22" t="s">
-        <v>456</v>
-      </c>
-      <c r="D22" t="s">
-        <v>454</v>
-      </c>
-      <c r="E22" t="s">
-        <v>455</v>
-      </c>
-      <c r="F22" t="s">
-        <v>456</v>
-      </c>
-      <c r="G22" t="s">
-        <v>458</v>
-      </c>
-      <c r="I22" t="s">
-        <v>456</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A23" s="2" t="s">
-        <v>562</v>
       </c>
       <c r="B23" t="s">
         <v>453</v>
       </c>
       <c r="C23" t="s">
-        <v>559</v>
+        <v>456</v>
       </c>
       <c r="D23" t="s">
-        <v>561</v>
+        <v>454</v>
       </c>
       <c r="E23" t="s">
-        <v>560</v>
+        <v>455</v>
       </c>
       <c r="F23" t="s">
-        <v>559</v>
+        <v>456</v>
       </c>
       <c r="G23" t="s">
-        <v>558</v>
+        <v>458</v>
       </c>
       <c r="I23" t="s">
-        <v>559</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>456</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>566</v>
+        <v>562</v>
       </c>
       <c r="B24" t="s">
         <v>453</v>
       </c>
       <c r="C24" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="D24" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E24" t="s">
-        <v>565</v>
+        <v>560</v>
       </c>
       <c r="F24" t="s">
-        <v>563</v>
+        <v>559</v>
       </c>
       <c r="G24" t="s">
-        <v>563</v>
+        <v>558</v>
       </c>
       <c r="I24" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>559</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>726</v>
+        <v>566</v>
       </c>
       <c r="B25" t="s">
         <v>453</v>
       </c>
       <c r="C25" t="s">
-        <v>727</v>
+        <v>563</v>
       </c>
       <c r="D25" t="s">
-        <v>561</v>
+        <v>564</v>
       </c>
       <c r="E25" t="s">
-        <v>728</v>
+        <v>565</v>
       </c>
       <c r="F25" t="s">
-        <v>727</v>
+        <v>563</v>
       </c>
       <c r="G25" t="s">
-        <v>732</v>
+        <v>563</v>
       </c>
       <c r="I25" t="s">
-        <v>727</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>729</v>
+        <v>726</v>
       </c>
       <c r="B26" t="s">
         <v>453</v>
       </c>
       <c r="C26" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="D26" t="s">
-        <v>564</v>
+        <v>561</v>
       </c>
       <c r="E26" t="s">
-        <v>731</v>
+        <v>728</v>
       </c>
       <c r="F26" t="s">
-        <v>730</v>
+        <v>727</v>
       </c>
       <c r="G26" t="s">
-        <v>563</v>
+        <v>732</v>
       </c>
       <c r="I26" t="s">
-        <v>563</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>733</v>
+        <v>729</v>
       </c>
       <c r="B27" t="s">
         <v>453</v>
       </c>
       <c r="C27" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="D27" t="s">
-        <v>735</v>
+        <v>564</v>
       </c>
       <c r="E27" t="s">
-        <v>736</v>
+        <v>731</v>
       </c>
       <c r="F27" t="s">
-        <v>734</v>
+        <v>730</v>
       </c>
       <c r="G27" t="s">
-        <v>734</v>
+        <v>563</v>
       </c>
       <c r="I27" t="s">
-        <v>734</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>563</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>738</v>
+        <v>733</v>
       </c>
       <c r="B28" t="s">
         <v>453</v>
       </c>
       <c r="C28" t="s">
-        <v>737</v>
-      </c>
-      <c r="D28" s="6" t="s">
-        <v>739</v>
+        <v>734</v>
+      </c>
+      <c r="D28" t="s">
+        <v>735</v>
       </c>
       <c r="E28" t="s">
-        <v>740</v>
+        <v>736</v>
       </c>
       <c r="F28" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="G28" t="s">
-        <v>737</v>
+        <v>734</v>
       </c>
       <c r="I28" t="s">
-        <v>737</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>734</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>913</v>
+        <v>738</v>
       </c>
       <c r="B29" t="s">
         <v>453</v>
       </c>
       <c r="C29" t="s">
+        <v>737</v>
+      </c>
+      <c r="D29" s="6" t="s">
+        <v>739</v>
+      </c>
+      <c r="E29" t="s">
+        <v>740</v>
+      </c>
+      <c r="F29" t="s">
+        <v>737</v>
+      </c>
+      <c r="G29" t="s">
+        <v>737</v>
+      </c>
+      <c r="I29" t="s">
+        <v>737</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A30" s="2" t="s">
+        <v>913</v>
+      </c>
+      <c r="B30" t="s">
+        <v>453</v>
+      </c>
+      <c r="C30" t="s">
         <v>914</v>
       </c>
-      <c r="D29" t="s">
+      <c r="D30" t="s">
         <v>915</v>
       </c>
-      <c r="E29" t="s">
+      <c r="E30" t="s">
         <v>916</v>
       </c>
-      <c r="F29" t="s">
+      <c r="F30" t="s">
         <v>914</v>
       </c>
-      <c r="G29" t="s">
+      <c r="G30" t="s">
         <v>914</v>
       </c>
-      <c r="I29" t="s">
+      <c r="I30" t="s">
         <v>914</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A30" s="2" t="s">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A31" s="2" t="s">
         <v>1639</v>
-      </c>
-      <c r="B30" t="s">
-        <v>1265</v>
-      </c>
-      <c r="C30" t="s">
-        <v>1267</v>
-      </c>
-      <c r="D30" t="s">
-        <v>1269</v>
-      </c>
-      <c r="E30" t="s">
-        <v>1268</v>
-      </c>
-      <c r="F30" t="s">
-        <v>1267</v>
-      </c>
-      <c r="G30" t="s">
-        <v>1266</v>
-      </c>
-      <c r="I30" t="s">
-        <v>1270</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A31" s="2" t="s">
-        <v>2065</v>
       </c>
       <c r="B31" t="s">
         <v>1265</v>
       </c>
       <c r="C31" t="s">
-        <v>2066</v>
+        <v>1267</v>
       </c>
       <c r="D31" t="s">
-        <v>2071</v>
+        <v>1269</v>
       </c>
       <c r="E31" t="s">
         <v>1268</v>
       </c>
       <c r="F31" t="s">
-        <v>2066</v>
+        <v>1267</v>
       </c>
       <c r="G31" t="s">
-        <v>2066</v>
+        <v>1266</v>
       </c>
       <c r="I31" t="s">
-        <v>2068</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1270</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>2069</v>
+        <v>2065</v>
       </c>
       <c r="B32" t="s">
         <v>1265</v>
       </c>
       <c r="C32" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
       <c r="D32" t="s">
-        <v>2067</v>
+        <v>2071</v>
       </c>
       <c r="E32" t="s">
         <v>1268</v>
       </c>
       <c r="F32" t="s">
-        <v>2070</v>
+        <v>2066</v>
       </c>
       <c r="G32" t="s">
         <v>2066</v>
@@ -17367,160 +17407,160 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>2072</v>
+        <v>2069</v>
       </c>
       <c r="B33" t="s">
         <v>1265</v>
       </c>
       <c r="C33" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="D33" t="s">
-        <v>2074</v>
+        <v>2067</v>
       </c>
       <c r="E33" t="s">
         <v>1268</v>
       </c>
       <c r="F33" t="s">
-        <v>2073</v>
+        <v>2070</v>
       </c>
       <c r="G33" t="s">
-        <v>2073</v>
+        <v>2066</v>
       </c>
       <c r="I33" t="s">
-        <v>2075</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2068</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>2254</v>
+        <v>2072</v>
       </c>
       <c r="B34" t="s">
         <v>1265</v>
       </c>
       <c r="C34" t="s">
+        <v>2073</v>
+      </c>
+      <c r="D34" t="s">
+        <v>2074</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1268</v>
+      </c>
+      <c r="F34" t="s">
+        <v>2073</v>
+      </c>
+      <c r="G34" t="s">
+        <v>2073</v>
+      </c>
+      <c r="I34" t="s">
+        <v>2075</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A35" s="2" t="s">
+        <v>2254</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1265</v>
+      </c>
+      <c r="C35" t="s">
         <v>2256</v>
       </c>
-      <c r="D34" t="s">
+      <c r="D35" t="s">
         <v>2267</v>
       </c>
-      <c r="E34" t="s">
+      <c r="E35" t="s">
         <v>2259</v>
       </c>
-      <c r="F34" t="s">
+      <c r="F35" t="s">
         <v>2255</v>
       </c>
-      <c r="G34" t="s">
+      <c r="G35" t="s">
         <v>2257</v>
       </c>
-      <c r="I34" t="s">
+      <c r="I35" t="s">
         <v>2258</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A35" s="2" t="s">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A36" s="2" t="s">
         <v>1760</v>
-      </c>
-      <c r="B35" t="s">
-        <v>1759</v>
-      </c>
-      <c r="C35" t="s">
-        <v>1762</v>
-      </c>
-      <c r="D35" t="s">
-        <v>1772</v>
-      </c>
-      <c r="E35" t="s">
-        <v>1763</v>
-      </c>
-      <c r="F35" t="s">
-        <v>1770</v>
-      </c>
-      <c r="G35" t="s">
-        <v>1765</v>
-      </c>
-      <c r="H35" t="s">
-        <v>1773</v>
-      </c>
-      <c r="I35" t="s">
-        <v>1766</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A36" s="2" t="s">
-        <v>1761</v>
       </c>
       <c r="B36" t="s">
         <v>1759</v>
       </c>
       <c r="C36" t="s">
-        <v>1768</v>
+        <v>1762</v>
       </c>
       <c r="D36" t="s">
-        <v>1771</v>
+        <v>1772</v>
       </c>
       <c r="E36" t="s">
         <v>1763</v>
       </c>
       <c r="F36" t="s">
-        <v>1769</v>
+        <v>1770</v>
       </c>
       <c r="G36" t="s">
-        <v>1764</v>
+        <v>1765</v>
       </c>
       <c r="H36" t="s">
         <v>1773</v>
       </c>
       <c r="I36" t="s">
+        <v>1766</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>1761</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1759</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1768</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1771</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1763</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1769</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1764</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1773</v>
+      </c>
+      <c r="I37" t="s">
         <v>1767</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>1775</v>
-      </c>
-      <c r="B37" t="s">
-        <v>1774</v>
-      </c>
-      <c r="C37" t="s">
-        <v>1777</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>1782</v>
-      </c>
-      <c r="E37" t="s">
-        <v>1781</v>
-      </c>
-      <c r="F37" t="s">
-        <v>1777</v>
-      </c>
-      <c r="G37" t="s">
-        <v>1780</v>
-      </c>
-      <c r="I37" t="s">
-        <v>1779</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>1776</v>
       </c>
       <c r="B38" t="s">
         <v>1774</v>
       </c>
       <c r="C38" t="s">
-        <v>1783</v>
-      </c>
-      <c r="D38" t="s">
-        <v>1784</v>
+        <v>1777</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>1782</v>
       </c>
       <c r="E38" t="s">
         <v>1781</v>
       </c>
       <c r="F38" t="s">
-        <v>1778</v>
+        <v>1777</v>
       </c>
       <c r="G38" t="s">
         <v>1780</v>
@@ -17529,50 +17569,50 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
+        <v>1776</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1774</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1783</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1784</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1781</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1778</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1780</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1779</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A40" s="2" t="s">
         <v>1786</v>
-      </c>
-      <c r="B39" t="s">
-        <v>1785</v>
-      </c>
-      <c r="C39" t="s">
-        <v>1787</v>
-      </c>
-      <c r="D39" t="s">
-        <v>1790</v>
-      </c>
-      <c r="E39" t="s">
-        <v>1788</v>
-      </c>
-      <c r="F39" t="s">
-        <v>1789</v>
-      </c>
-      <c r="G39" t="s">
-        <v>1791</v>
-      </c>
-      <c r="I39" t="s">
-        <v>1789</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="2" t="s">
-        <v>1870</v>
       </c>
       <c r="B40" t="s">
         <v>1785</v>
       </c>
       <c r="C40" t="s">
-        <v>2171</v>
+        <v>1787</v>
       </c>
       <c r="D40" t="s">
-        <v>2170</v>
+        <v>1790</v>
       </c>
       <c r="E40" t="s">
         <v>1788</v>
       </c>
       <c r="F40" t="s">
-        <v>2171</v>
+        <v>1789</v>
       </c>
       <c r="G40" t="s">
         <v>1791</v>
@@ -17581,55 +17621,81 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
+        <v>1870</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1785</v>
+      </c>
+      <c r="C41" t="s">
+        <v>2171</v>
+      </c>
+      <c r="D41" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1788</v>
+      </c>
+      <c r="F41" t="s">
+        <v>2171</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1791</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1789</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
         <v>2440</v>
       </c>
-      <c r="B41" t="s">
+      <c r="B42" t="s">
         <v>2439</v>
       </c>
-      <c r="C41" t="s">
+      <c r="C42" t="s">
         <v>2443</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>2442</v>
       </c>
-      <c r="E41" t="s">
+      <c r="E42" t="s">
         <v>2441</v>
       </c>
-      <c r="F41" t="s">
+      <c r="F42" t="s">
         <v>2443</v>
       </c>
-      <c r="G41" t="s">
+      <c r="G42" t="s">
         <v>989</v>
       </c>
-      <c r="I41" t="s">
+      <c r="I42" t="s">
         <v>2443</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A43" s="2" t="s">
         <v>2462</v>
       </c>
-      <c r="B42" t="s">
+      <c r="B43" t="s">
         <v>2461</v>
       </c>
-      <c r="C42" t="s">
+      <c r="C43" t="s">
         <v>2463</v>
       </c>
-      <c r="D42" t="s">
+      <c r="D43" t="s">
         <v>2464</v>
       </c>
-      <c r="E42" t="s">
+      <c r="E43" t="s">
         <v>2467</v>
       </c>
-      <c r="F42" t="s">
+      <c r="F43" t="s">
         <v>2463</v>
       </c>
-      <c r="G42" t="s">
+      <c r="G43" t="s">
         <v>2466</v>
       </c>
-      <c r="I42" t="s">
+      <c r="I43" t="s">
         <v>2463</v>
       </c>
     </row>
@@ -17651,9 +17717,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
         <v>2477</v>
       </c>
@@ -17670,20 +17736,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CB78C2-2208-4DF0-8ABB-0CE48BD26296}">
   <dimension ref="A1:J76"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17715,7 +17781,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1876</v>
       </c>
@@ -17741,7 +17807,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1811</v>
       </c>
@@ -17767,7 +17833,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1737</v>
       </c>
@@ -17793,7 +17859,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1820</v>
       </c>
@@ -17819,7 +17885,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1833</v>
       </c>
@@ -17845,7 +17911,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1834</v>
       </c>
@@ -17871,7 +17937,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1805</v>
       </c>
@@ -17897,7 +17963,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1845</v>
       </c>
@@ -17923,7 +17989,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1806</v>
       </c>
@@ -17949,7 +18015,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>2050</v>
       </c>
@@ -17975,7 +18041,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1860</v>
       </c>
@@ -18001,7 +18067,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2046</v>
       </c>
@@ -18027,7 +18093,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>2041</v>
       </c>
@@ -18053,7 +18119,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1632</v>
       </c>
@@ -18079,7 +18145,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1631</v>
       </c>
@@ -18105,7 +18171,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1812</v>
       </c>
@@ -18131,7 +18197,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2015</v>
       </c>
@@ -18157,7 +18223,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -18183,7 +18249,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1856</v>
       </c>
@@ -18209,7 +18275,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>2334</v>
       </c>
@@ -18235,7 +18301,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>174</v>
       </c>
@@ -18261,7 +18327,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>653</v>
       </c>
@@ -18287,7 +18353,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1985</v>
       </c>
@@ -18313,7 +18379,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>2076</v>
       </c>
@@ -18339,33 +18405,33 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>2492</v>
+        <v>2491</v>
       </c>
       <c r="D26" t="s">
-        <v>2496</v>
+        <v>2495</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F26" t="s">
+        <v>2493</v>
+      </c>
+      <c r="G26" t="s">
         <v>2494</v>
-      </c>
-      <c r="G26" t="s">
-        <v>2495</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2330</v>
       </c>
@@ -18391,7 +18457,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>1264</v>
       </c>
@@ -18417,7 +18483,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>2300</v>
       </c>
@@ -18443,7 +18509,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>72</v>
       </c>
@@ -18469,7 +18535,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>327</v>
       </c>
@@ -18495,7 +18561,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>194</v>
       </c>
@@ -18521,7 +18587,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>1483</v>
       </c>
@@ -18547,7 +18613,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1484</v>
       </c>
@@ -18573,7 +18639,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1867</v>
       </c>
@@ -18599,7 +18665,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>2220</v>
       </c>
@@ -18625,7 +18691,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>205</v>
       </c>
@@ -18651,7 +18717,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>810</v>
       </c>
@@ -18677,7 +18743,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>2232</v>
       </c>
@@ -18703,7 +18769,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>815</v>
       </c>
@@ -18732,7 +18798,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>1120</v>
       </c>
@@ -18761,7 +18827,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>2027</v>
       </c>
@@ -18790,7 +18856,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>1250</v>
       </c>
@@ -18816,7 +18882,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>349</v>
       </c>
@@ -18842,7 +18908,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>2038</v>
       </c>
@@ -18868,7 +18934,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>417</v>
       </c>
@@ -18894,7 +18960,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>887</v>
       </c>
@@ -18920,7 +18986,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>197</v>
       </c>
@@ -18946,7 +19012,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>1091</v>
       </c>
@@ -18972,7 +19038,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>167</v>
       </c>
@@ -18998,7 +19064,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>1487</v>
       </c>
@@ -19024,7 +19090,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>1130</v>
       </c>
@@ -19050,7 +19116,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>1385</v>
       </c>
@@ -19076,7 +19142,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -19102,7 +19168,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>1591</v>
       </c>
@@ -19128,7 +19194,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>1905</v>
       </c>
@@ -19154,7 +19220,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>121</v>
       </c>
@@ -19180,7 +19246,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>1117</v>
       </c>
@@ -19206,7 +19272,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>1434</v>
       </c>
@@ -19232,7 +19298,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>2219</v>
       </c>
@@ -19258,7 +19324,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>2223</v>
       </c>
@@ -19284,7 +19350,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>1149</v>
       </c>
@@ -19313,7 +19379,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>2023</v>
       </c>
@@ -19339,7 +19405,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>2031</v>
       </c>
@@ -19368,7 +19434,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>161</v>
       </c>
@@ -19394,7 +19460,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>979</v>
       </c>
@@ -19420,7 +19486,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>2239</v>
       </c>
@@ -19446,7 +19512,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>1144</v>
       </c>
@@ -19475,7 +19541,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>58</v>
       </c>
@@ -19501,7 +19567,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>67</v>
       </c>
@@ -19527,7 +19593,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>1452</v>
       </c>
@@ -19553,7 +19619,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>548</v>
       </c>
@@ -19579,7 +19645,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>2325</v>
       </c>
@@ -19605,7 +19671,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>1110</v>
       </c>
@@ -19634,7 +19700,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
         <v>17</v>
       </c>
@@ -19649,7 +19715,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>17</v>
       </c>
@@ -19681,21 +19747,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C302E28E-61B5-45F2-9EED-9E658F066E8B}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="133.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="133.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19727,7 +19793,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>307</v>
       </c>
@@ -19747,7 +19813,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>306</v>
       </c>
@@ -19776,7 +19842,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>311</v>
       </c>
@@ -19805,7 +19871,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>634</v>
       </c>
@@ -19834,7 +19900,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2479</v>
       </c>
@@ -19860,7 +19926,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>869</v>
       </c>
@@ -19889,7 +19955,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1010</v>
       </c>
@@ -19918,7 +19984,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1019</v>
       </c>
@@ -19947,7 +20013,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1067</v>
       </c>
@@ -19973,7 +20039,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1192</v>
       </c>
@@ -20002,7 +20068,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1225</v>
       </c>
@@ -20031,7 +20097,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1964</v>
       </c>
@@ -20060,7 +20126,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1970</v>
       </c>
@@ -20089,7 +20155,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1971</v>
       </c>
@@ -20118,30 +20184,30 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="B16" t="s">
         <v>1223</v>
       </c>
       <c r="D16" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
       <c r="E16" t="s">
         <v>1966</v>
       </c>
       <c r="F16" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="G16" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="I16" t="s">
-        <v>2513</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2512</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1238</v>
       </c>
@@ -20167,7 +20233,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1465</v>
       </c>
@@ -20193,7 +20259,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1717</v>
       </c>
@@ -20219,7 +20285,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1720</v>
       </c>
@@ -20245,7 +20311,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1721</v>
       </c>
@@ -20271,7 +20337,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>2320</v>
       </c>
@@ -20310,21 +20376,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F61549-8124-4EE7-A218-E5BC471FD40D}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.58203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20356,7 +20422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>7001100000</v>
       </c>
@@ -20382,7 +20448,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>543</v>
       </c>
@@ -20405,7 +20471,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1507</v>
       </c>
@@ -20431,7 +20497,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1556</v>
       </c>
@@ -20469,21 +20535,21 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77DF9D1-733F-4622-A5B9-9F6937E4842B}">
-  <dimension ref="A1:J67"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:J68"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="57.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.08203125" customWidth="1"/>
-    <col min="8" max="8" width="18.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
+    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20515,7 +20581,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>135</v>
       </c>
@@ -20544,7 +20610,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>141</v>
       </c>
@@ -20573,7 +20639,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -20602,7 +20668,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>295</v>
       </c>
@@ -20631,7 +20697,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>516</v>
       </c>
@@ -20660,7 +20726,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
@@ -20689,7 +20755,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>45</v>
       </c>
@@ -20718,7 +20784,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -20747,7 +20813,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>569</v>
       </c>
@@ -20776,7 +20842,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>582</v>
       </c>
@@ -20805,7 +20871,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>629</v>
       </c>
@@ -20834,7 +20900,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>700</v>
       </c>
@@ -20863,7 +20929,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>917</v>
       </c>
@@ -20892,7 +20958,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>922</v>
       </c>
@@ -20921,7 +20987,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>2283</v>
       </c>
@@ -20950,7 +21016,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>2348</v>
       </c>
@@ -20979,7 +21045,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2399</v>
       </c>
@@ -21008,1422 +21074,1451 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
+        <v>2556</v>
+      </c>
+      <c r="B19" s="3" t="s">
+        <v>33</v>
+      </c>
+      <c r="C19" t="s">
+        <v>2558</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2557</v>
+      </c>
+      <c r="E19" t="s">
+        <v>864</v>
+      </c>
+      <c r="F19" t="s">
+        <v>2558</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2559</v>
+      </c>
+      <c r="H19" t="s">
+        <v>2560</v>
+      </c>
+      <c r="I19" t="s">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A20" s="2" t="s">
         <v>105</v>
-      </c>
-      <c r="B19" s="3" t="s">
-        <v>101</v>
-      </c>
-      <c r="C19" t="s">
-        <v>103</v>
-      </c>
-      <c r="D19" t="s">
-        <v>100</v>
-      </c>
-      <c r="E19" t="s">
-        <v>102</v>
-      </c>
-      <c r="F19" t="s">
-        <v>103</v>
-      </c>
-      <c r="G19" t="s">
-        <v>103</v>
-      </c>
-      <c r="H19" t="s">
-        <v>104</v>
-      </c>
-      <c r="I19" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A20" s="2" t="s">
-        <v>226</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C20" t="s">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="D20" t="s">
-        <v>227</v>
+        <v>100</v>
       </c>
       <c r="E20" t="s">
-        <v>35</v>
+        <v>102</v>
       </c>
       <c r="F20" t="s">
-        <v>228</v>
+        <v>103</v>
       </c>
       <c r="G20" t="s">
-        <v>237</v>
+        <v>103</v>
       </c>
       <c r="H20" t="s">
-        <v>233</v>
+        <v>104</v>
       </c>
       <c r="I20" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>106</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="D21" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
       <c r="E21" t="s">
         <v>35</v>
       </c>
       <c r="F21" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="G21" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="H21" t="s">
-        <v>232</v>
+        <v>233</v>
       </c>
       <c r="I21" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C22" t="s">
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="D22" t="s">
-        <v>322</v>
+        <v>231</v>
       </c>
       <c r="E22" t="s">
         <v>35</v>
       </c>
       <c r="F22" t="s">
-        <v>320</v>
+        <v>230</v>
       </c>
       <c r="G22" t="s">
-        <v>321</v>
+        <v>236</v>
       </c>
       <c r="H22" t="s">
-        <v>323</v>
+        <v>232</v>
       </c>
       <c r="I22" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
-        <v>519</v>
+        <v>238</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C23" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
       <c r="D23" t="s">
-        <v>240</v>
+        <v>322</v>
       </c>
       <c r="E23" t="s">
         <v>35</v>
       </c>
       <c r="F23" t="s">
-        <v>239</v>
+        <v>320</v>
       </c>
       <c r="G23" t="s">
-        <v>242</v>
+        <v>321</v>
       </c>
       <c r="H23" t="s">
-        <v>241</v>
+        <v>323</v>
       </c>
       <c r="I23" t="s">
-        <v>235</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
-        <v>574</v>
+        <v>519</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C24" t="s">
-        <v>520</v>
+        <v>239</v>
       </c>
       <c r="D24" t="s">
-        <v>521</v>
+        <v>240</v>
       </c>
       <c r="E24" t="s">
         <v>35</v>
       </c>
       <c r="F24" t="s">
-        <v>520</v>
+        <v>239</v>
       </c>
       <c r="G24" t="s">
-        <v>523</v>
+        <v>242</v>
       </c>
       <c r="H24" t="s">
-        <v>522</v>
+        <v>241</v>
       </c>
       <c r="I24" t="s">
-        <v>524</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+        <v>235</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
-        <v>580</v>
+        <v>574</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C25" t="s">
-        <v>575</v>
+        <v>520</v>
       </c>
       <c r="D25" t="s">
-        <v>576</v>
+        <v>521</v>
       </c>
       <c r="E25" t="s">
         <v>35</v>
       </c>
       <c r="F25" t="s">
-        <v>575</v>
+        <v>520</v>
       </c>
       <c r="G25" t="s">
-        <v>577</v>
+        <v>523</v>
       </c>
       <c r="H25" t="s">
-        <v>578</v>
+        <v>522</v>
       </c>
       <c r="I25" t="s">
-        <v>579</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+        <v>524</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>623</v>
+        <v>580</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C26" t="s">
-        <v>624</v>
+        <v>575</v>
       </c>
       <c r="D26" t="s">
-        <v>625</v>
+        <v>576</v>
       </c>
       <c r="E26" t="s">
         <v>35</v>
       </c>
       <c r="F26" t="s">
-        <v>624</v>
+        <v>575</v>
       </c>
       <c r="G26" t="s">
-        <v>626</v>
+        <v>577</v>
       </c>
       <c r="H26" t="s">
-        <v>627</v>
+        <v>578</v>
       </c>
       <c r="I26" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+        <v>579</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
-        <v>659</v>
+        <v>623</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C27" t="s">
-        <v>660</v>
+        <v>624</v>
       </c>
       <c r="D27" t="s">
-        <v>661</v>
+        <v>625</v>
       </c>
       <c r="E27" t="s">
-        <v>529</v>
+        <v>35</v>
       </c>
       <c r="F27" t="s">
-        <v>664</v>
+        <v>624</v>
       </c>
       <c r="G27" t="s">
-        <v>664</v>
+        <v>626</v>
       </c>
       <c r="H27" t="s">
-        <v>662</v>
+        <v>627</v>
       </c>
       <c r="I27" t="s">
-        <v>663</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
-        <v>790</v>
+        <v>659</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C28" t="s">
-        <v>791</v>
+        <v>660</v>
       </c>
       <c r="D28" t="s">
-        <v>792</v>
+        <v>661</v>
       </c>
       <c r="E28" t="s">
-        <v>35</v>
+        <v>529</v>
       </c>
       <c r="F28" t="s">
-        <v>791</v>
+        <v>664</v>
       </c>
       <c r="G28" t="s">
-        <v>794</v>
+        <v>664</v>
       </c>
       <c r="H28" t="s">
-        <v>793</v>
+        <v>662</v>
       </c>
       <c r="I28" t="s">
-        <v>234</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
-        <v>893</v>
+        <v>790</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C29" t="s">
-        <v>895</v>
+        <v>791</v>
       </c>
       <c r="D29" t="s">
-        <v>894</v>
+        <v>792</v>
       </c>
       <c r="E29" t="s">
         <v>35</v>
       </c>
       <c r="F29" t="s">
-        <v>895</v>
+        <v>791</v>
       </c>
       <c r="G29" t="s">
-        <v>897</v>
+        <v>794</v>
       </c>
       <c r="H29" t="s">
-        <v>233</v>
+        <v>793</v>
       </c>
       <c r="I29" t="s">
-        <v>896</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+        <v>234</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>901</v>
+        <v>893</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C30" t="s">
-        <v>903</v>
+        <v>895</v>
       </c>
       <c r="D30" t="s">
-        <v>904</v>
+        <v>894</v>
       </c>
       <c r="E30" t="s">
         <v>35</v>
       </c>
       <c r="F30" t="s">
-        <v>902</v>
+        <v>895</v>
       </c>
       <c r="G30" t="s">
-        <v>907</v>
+        <v>897</v>
       </c>
       <c r="H30" t="s">
-        <v>905</v>
+        <v>233</v>
       </c>
       <c r="I30" t="s">
-        <v>906</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+        <v>896</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
-        <v>965</v>
+        <v>901</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C31" t="s">
-        <v>967</v>
+        <v>903</v>
       </c>
       <c r="D31" t="s">
-        <v>1001</v>
+        <v>904</v>
       </c>
       <c r="E31" t="s">
-        <v>968</v>
+        <v>35</v>
       </c>
       <c r="F31" t="s">
-        <v>967</v>
+        <v>902</v>
       </c>
       <c r="G31" t="s">
-        <v>966</v>
+        <v>907</v>
       </c>
       <c r="H31" t="s">
-        <v>970</v>
+        <v>905</v>
       </c>
       <c r="I31" t="s">
-        <v>969</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+        <v>906</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
-        <v>997</v>
+        <v>965</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C32" t="s">
-        <v>999</v>
+        <v>967</v>
       </c>
       <c r="D32" t="s">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="E32" t="s">
         <v>968</v>
       </c>
       <c r="F32" t="s">
-        <v>998</v>
+        <v>967</v>
       </c>
       <c r="G32" t="s">
-        <v>999</v>
+        <v>966</v>
       </c>
       <c r="H32" t="s">
-        <v>1000</v>
+        <v>970</v>
       </c>
       <c r="I32" t="s">
-        <v>996</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+        <v>969</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>1913</v>
+        <v>997</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C33" t="s">
-        <v>1914</v>
+        <v>999</v>
       </c>
       <c r="D33" t="s">
-        <v>1938</v>
+        <v>1002</v>
       </c>
       <c r="E33" t="s">
-        <v>1917</v>
+        <v>968</v>
       </c>
       <c r="F33" t="s">
-        <v>1914</v>
+        <v>998</v>
       </c>
       <c r="G33" t="s">
-        <v>1915</v>
+        <v>999</v>
       </c>
       <c r="H33" t="s">
-        <v>1939</v>
+        <v>1000</v>
       </c>
       <c r="I33" t="s">
-        <v>1916</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+        <v>996</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
-        <v>1933</v>
+        <v>1913</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C34" t="s">
-        <v>1934</v>
+        <v>1914</v>
       </c>
       <c r="D34" t="s">
-        <v>1935</v>
+        <v>1938</v>
       </c>
       <c r="E34" t="s">
         <v>1917</v>
       </c>
       <c r="F34" t="s">
-        <v>1934</v>
+        <v>1914</v>
       </c>
       <c r="G34" t="s">
-        <v>1934</v>
+        <v>1915</v>
       </c>
       <c r="H34" t="s">
-        <v>1937</v>
+        <v>1939</v>
       </c>
       <c r="I34" t="s">
-        <v>1936</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1916</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
-        <v>2116</v>
+        <v>1933</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C35" t="s">
-        <v>2126</v>
+        <v>1934</v>
       </c>
       <c r="D35" t="s">
-        <v>2118</v>
+        <v>1935</v>
       </c>
       <c r="E35" t="s">
-        <v>35</v>
+        <v>1917</v>
       </c>
       <c r="F35" t="s">
-        <v>2117</v>
+        <v>1934</v>
       </c>
       <c r="G35" t="s">
-        <v>2127</v>
+        <v>1934</v>
       </c>
       <c r="H35" t="s">
-        <v>2119</v>
+        <v>1937</v>
       </c>
       <c r="I35" t="s">
-        <v>2120</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1936</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>2121</v>
+        <v>2116</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>101</v>
       </c>
       <c r="C36" t="s">
+        <v>2126</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2118</v>
+      </c>
+      <c r="E36" t="s">
+        <v>35</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2117</v>
+      </c>
+      <c r="G36" t="s">
+        <v>2127</v>
+      </c>
+      <c r="H36" t="s">
+        <v>2119</v>
+      </c>
+      <c r="I36" t="s">
+        <v>2120</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A37" s="2" t="s">
+        <v>2121</v>
+      </c>
+      <c r="B37" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="C37" t="s">
         <v>2123</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>2124</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E37" t="s">
         <v>968</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F37" t="s">
         <v>2123</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G37" t="s">
         <v>2122</v>
       </c>
-      <c r="H36" t="s">
+      <c r="H37" t="s">
         <v>2125</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I37" t="s">
         <v>2122</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A37" s="2" t="s">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A38" s="2" t="s">
         <v>253</v>
-      </c>
-      <c r="B37" t="s">
-        <v>284</v>
-      </c>
-      <c r="C37" t="s">
-        <v>243</v>
-      </c>
-      <c r="D37" t="s">
-        <v>249</v>
-      </c>
-      <c r="E37" t="s">
-        <v>245</v>
-      </c>
-      <c r="F37" t="s">
-        <v>243</v>
-      </c>
-      <c r="G37" t="s">
-        <v>243</v>
-      </c>
-      <c r="H37" t="s">
-        <v>246</v>
-      </c>
-      <c r="I37" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A38" s="2" t="s">
-        <v>254</v>
       </c>
       <c r="B38" t="s">
         <v>284</v>
       </c>
       <c r="C38" t="s">
-        <v>248</v>
+        <v>243</v>
       </c>
       <c r="D38" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="E38" t="s">
         <v>245</v>
       </c>
       <c r="F38" t="s">
+        <v>243</v>
+      </c>
+      <c r="G38" t="s">
+        <v>243</v>
+      </c>
+      <c r="H38" t="s">
+        <v>246</v>
+      </c>
+      <c r="I38" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A39" s="2" t="s">
+        <v>254</v>
+      </c>
+      <c r="B39" t="s">
+        <v>284</v>
+      </c>
+      <c r="C39" t="s">
         <v>248</v>
       </c>
-      <c r="G38" t="s">
-        <v>248</v>
-      </c>
-      <c r="H38" t="s">
-        <v>251</v>
-      </c>
-      <c r="I38" t="s">
-        <v>252</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A39" s="2" t="s">
-        <v>255</v>
-      </c>
-      <c r="B39" t="s">
-        <v>244</v>
-      </c>
-      <c r="C39" t="s">
-        <v>319</v>
-      </c>
       <c r="D39" t="s">
-        <v>256</v>
+        <v>250</v>
       </c>
       <c r="E39" t="s">
         <v>245</v>
       </c>
       <c r="F39" t="s">
-        <v>319</v>
+        <v>248</v>
       </c>
       <c r="G39" t="s">
-        <v>319</v>
+        <v>248</v>
       </c>
       <c r="H39" t="s">
         <v>251</v>
       </c>
       <c r="I39" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+        <v>252</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
-        <v>497</v>
+        <v>255</v>
       </c>
       <c r="B40" t="s">
         <v>244</v>
       </c>
       <c r="C40" t="s">
-        <v>498</v>
+        <v>319</v>
       </c>
       <c r="D40" t="s">
-        <v>499</v>
+        <v>256</v>
       </c>
       <c r="E40" t="s">
         <v>245</v>
       </c>
       <c r="F40" t="s">
-        <v>498</v>
+        <v>319</v>
       </c>
       <c r="G40" t="s">
-        <v>498</v>
+        <v>319</v>
       </c>
       <c r="H40" t="s">
-        <v>500</v>
+        <v>251</v>
       </c>
       <c r="I40" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>492</v>
+        <v>497</v>
       </c>
       <c r="B41" t="s">
         <v>244</v>
       </c>
       <c r="C41" t="s">
+        <v>498</v>
+      </c>
+      <c r="D41" t="s">
+        <v>499</v>
+      </c>
+      <c r="E41" t="s">
+        <v>245</v>
+      </c>
+      <c r="F41" t="s">
+        <v>498</v>
+      </c>
+      <c r="G41" t="s">
+        <v>498</v>
+      </c>
+      <c r="H41" t="s">
+        <v>500</v>
+      </c>
+      <c r="I41" t="s">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A42" s="2" t="s">
+        <v>492</v>
+      </c>
+      <c r="B42" t="s">
+        <v>244</v>
+      </c>
+      <c r="C42" t="s">
         <v>493</v>
       </c>
-      <c r="D41" t="s">
+      <c r="D42" t="s">
         <v>494</v>
-      </c>
-      <c r="E41" t="s">
-        <v>200</v>
-      </c>
-      <c r="F41" t="s">
-        <v>493</v>
-      </c>
-      <c r="G41" t="s">
-        <v>496</v>
-      </c>
-      <c r="H41" t="s">
-        <v>495</v>
-      </c>
-      <c r="I41" t="s">
-        <v>496</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A42" s="2" t="s">
-        <v>515</v>
-      </c>
-      <c r="B42" s="3" t="s">
-        <v>284</v>
-      </c>
-      <c r="C42" t="s">
-        <v>201</v>
-      </c>
-      <c r="D42" t="s">
-        <v>514</v>
       </c>
       <c r="E42" t="s">
         <v>200</v>
       </c>
       <c r="F42" t="s">
-        <v>201</v>
+        <v>493</v>
       </c>
       <c r="G42" t="s">
-        <v>201</v>
+        <v>496</v>
       </c>
       <c r="H42" t="s">
-        <v>50</v>
+        <v>495</v>
       </c>
       <c r="I42" t="s">
-        <v>202</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+        <v>496</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
-        <v>553</v>
+        <v>515</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C43" t="s">
-        <v>556</v>
+        <v>201</v>
       </c>
       <c r="D43" t="s">
-        <v>554</v>
+        <v>514</v>
       </c>
       <c r="E43" t="s">
         <v>200</v>
       </c>
       <c r="F43" t="s">
-        <v>555</v>
+        <v>201</v>
       </c>
       <c r="G43" t="s">
-        <v>556</v>
+        <v>201</v>
       </c>
       <c r="H43" t="s">
-        <v>557</v>
+        <v>50</v>
       </c>
       <c r="I43" t="s">
-        <v>556</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
-        <v>589</v>
+        <v>553</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C44" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="D44" t="s">
-        <v>590</v>
+        <v>554</v>
       </c>
       <c r="E44" t="s">
-        <v>245</v>
+        <v>200</v>
       </c>
       <c r="F44" t="s">
-        <v>588</v>
+        <v>555</v>
       </c>
       <c r="G44" t="s">
-        <v>588</v>
+        <v>556</v>
       </c>
       <c r="H44" t="s">
-        <v>591</v>
+        <v>557</v>
       </c>
       <c r="I44" t="s">
-        <v>605</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
-        <v>857</v>
+        <v>589</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C45" t="s">
-        <v>858</v>
+        <v>588</v>
       </c>
       <c r="D45" t="s">
-        <v>859</v>
+        <v>590</v>
       </c>
       <c r="E45" t="s">
         <v>245</v>
       </c>
       <c r="F45" t="s">
-        <v>858</v>
+        <v>588</v>
       </c>
       <c r="G45" t="s">
-        <v>858</v>
+        <v>588</v>
       </c>
       <c r="H45" t="s">
-        <v>860</v>
+        <v>591</v>
       </c>
       <c r="I45" t="s">
-        <v>501</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+        <v>605</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
-        <v>861</v>
+        <v>857</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C46" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="D46" t="s">
-        <v>863</v>
+        <v>859</v>
       </c>
       <c r="E46" t="s">
-        <v>864</v>
+        <v>245</v>
       </c>
       <c r="F46" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="G46" t="s">
-        <v>862</v>
+        <v>858</v>
       </c>
       <c r="H46" t="s">
-        <v>865</v>
+        <v>860</v>
       </c>
       <c r="I46" t="s">
         <v>501</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
-        <v>2429</v>
+        <v>861</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C47" t="s">
-        <v>2432</v>
+        <v>862</v>
       </c>
       <c r="D47" t="s">
-        <v>2430</v>
+        <v>863</v>
       </c>
       <c r="E47" t="s">
-        <v>2431</v>
+        <v>864</v>
       </c>
       <c r="F47" t="s">
-        <v>2432</v>
+        <v>862</v>
       </c>
       <c r="G47" t="s">
-        <v>2434</v>
+        <v>862</v>
       </c>
       <c r="H47" t="s">
-        <v>2433</v>
+        <v>865</v>
       </c>
       <c r="I47" t="s">
-        <v>247</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+        <v>501</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
-        <v>2485</v>
+        <v>2429</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C48" t="s">
+        <v>2432</v>
+      </c>
+      <c r="D48" t="s">
+        <v>2430</v>
+      </c>
+      <c r="E48" t="s">
+        <v>2431</v>
+      </c>
+      <c r="F48" t="s">
+        <v>2432</v>
+      </c>
+      <c r="G48" t="s">
+        <v>2434</v>
+      </c>
+      <c r="H48" t="s">
+        <v>2433</v>
+      </c>
+      <c r="I48" t="s">
+        <v>247</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A49" s="2" t="s">
+        <v>2485</v>
+      </c>
+      <c r="B49" s="3" t="s">
+        <v>284</v>
+      </c>
+      <c r="C49" t="s">
         <v>2486</v>
       </c>
-      <c r="D48" t="s">
+      <c r="D49" t="s">
         <v>2487</v>
       </c>
-      <c r="E48" t="s">
+      <c r="E49" t="s">
         <v>2488</v>
       </c>
-      <c r="F48" t="s">
+      <c r="F49" t="s">
         <v>2486</v>
       </c>
-      <c r="G48" t="s">
+      <c r="G49" t="s">
+        <v>2555</v>
+      </c>
+      <c r="H49" t="s">
         <v>2489</v>
       </c>
-      <c r="H48" t="s">
+      <c r="I49" t="s">
         <v>2490</v>
       </c>
-      <c r="I48" t="s">
-        <v>2491</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A49" s="2" t="s">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A50" s="2" t="s">
         <v>486</v>
-      </c>
-      <c r="B49" t="s">
-        <v>485</v>
-      </c>
-      <c r="C49" t="s">
-        <v>488</v>
-      </c>
-      <c r="D49" t="s">
-        <v>489</v>
-      </c>
-      <c r="E49" t="s">
-        <v>490</v>
-      </c>
-      <c r="F49" t="s">
-        <v>488</v>
-      </c>
-      <c r="G49" t="s">
-        <v>487</v>
-      </c>
-      <c r="H49" t="s">
-        <v>491</v>
-      </c>
-      <c r="I49" t="s">
-        <v>488</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A50" s="2" t="s">
-        <v>502</v>
       </c>
       <c r="B50" t="s">
         <v>485</v>
       </c>
       <c r="C50" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="D50" t="s">
-        <v>504</v>
+        <v>489</v>
       </c>
       <c r="E50" t="s">
-        <v>260</v>
+        <v>490</v>
       </c>
       <c r="F50" t="s">
-        <v>503</v>
+        <v>488</v>
       </c>
       <c r="G50" t="s">
-        <v>503</v>
+        <v>487</v>
       </c>
       <c r="H50" t="s">
-        <v>505</v>
+        <v>491</v>
       </c>
       <c r="I50" t="s">
-        <v>506</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+        <v>488</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
-        <v>525</v>
+        <v>502</v>
       </c>
       <c r="B51" t="s">
         <v>485</v>
       </c>
       <c r="C51" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="D51" t="s">
-        <v>527</v>
+        <v>504</v>
       </c>
       <c r="E51" t="s">
-        <v>529</v>
+        <v>260</v>
       </c>
       <c r="F51" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="G51" t="s">
-        <v>526</v>
+        <v>503</v>
       </c>
       <c r="H51" t="s">
-        <v>528</v>
+        <v>505</v>
       </c>
       <c r="I51" t="s">
-        <v>530</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+        <v>506</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
-        <v>2001</v>
+        <v>525</v>
       </c>
       <c r="B52" t="s">
         <v>485</v>
       </c>
       <c r="C52" t="s">
-        <v>2002</v>
+        <v>526</v>
       </c>
       <c r="D52" t="s">
-        <v>2003</v>
+        <v>527</v>
       </c>
       <c r="E52" t="s">
-        <v>2004</v>
+        <v>529</v>
       </c>
       <c r="F52" t="s">
-        <v>2002</v>
+        <v>526</v>
       </c>
       <c r="G52" t="s">
-        <v>2005</v>
+        <v>526</v>
       </c>
       <c r="H52" t="s">
-        <v>2006</v>
+        <v>528</v>
       </c>
       <c r="I52" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
-        <v>2373</v>
+        <v>2001</v>
       </c>
       <c r="B53" t="s">
         <v>485</v>
       </c>
       <c r="C53" t="s">
-        <v>2375</v>
+        <v>2002</v>
       </c>
       <c r="D53" t="s">
-        <v>2377</v>
+        <v>2003</v>
       </c>
       <c r="E53" t="s">
-        <v>2374</v>
+        <v>2004</v>
       </c>
       <c r="F53" t="s">
-        <v>2375</v>
+        <v>2002</v>
       </c>
       <c r="G53" t="s">
-        <v>2376</v>
+        <v>2005</v>
       </c>
       <c r="H53" t="s">
-        <v>2378</v>
+        <v>2006</v>
       </c>
       <c r="I53" t="s">
         <v>530</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
+        <v>2373</v>
+      </c>
+      <c r="B54" t="s">
+        <v>485</v>
+      </c>
+      <c r="C54" t="s">
+        <v>2375</v>
+      </c>
+      <c r="D54" t="s">
+        <v>2377</v>
+      </c>
+      <c r="E54" t="s">
+        <v>2374</v>
+      </c>
+      <c r="F54" t="s">
+        <v>2375</v>
+      </c>
+      <c r="G54" t="s">
+        <v>2376</v>
+      </c>
+      <c r="H54" t="s">
+        <v>2378</v>
+      </c>
+      <c r="I54" t="s">
+        <v>530</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A55" s="2" t="s">
         <v>220</v>
-      </c>
-      <c r="B54" s="3" t="s">
-        <v>219</v>
-      </c>
-      <c r="C54" t="s">
-        <v>222</v>
-      </c>
-      <c r="D54" t="s">
-        <v>223</v>
-      </c>
-      <c r="E54" t="s">
-        <v>221</v>
-      </c>
-      <c r="F54" t="s">
-        <v>222</v>
-      </c>
-      <c r="G54" t="s">
-        <v>222</v>
-      </c>
-      <c r="H54" t="s">
-        <v>224</v>
-      </c>
-      <c r="I54" t="s">
-        <v>225</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="2" t="s">
-        <v>876</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C55" t="s">
-        <v>877</v>
+        <v>222</v>
       </c>
       <c r="D55" t="s">
-        <v>878</v>
+        <v>223</v>
       </c>
       <c r="E55" t="s">
-        <v>879</v>
+        <v>221</v>
       </c>
       <c r="F55" t="s">
-        <v>877</v>
+        <v>222</v>
       </c>
       <c r="G55" t="s">
-        <v>877</v>
+        <v>222</v>
       </c>
       <c r="H55" t="s">
-        <v>880</v>
+        <v>224</v>
       </c>
       <c r="I55" t="s">
-        <v>877</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
-        <v>1296</v>
+        <v>876</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C56" t="s">
-        <v>1299</v>
+        <v>877</v>
       </c>
       <c r="D56" t="s">
-        <v>1298</v>
+        <v>878</v>
       </c>
       <c r="E56" t="s">
-        <v>938</v>
+        <v>879</v>
       </c>
       <c r="F56" t="s">
-        <v>1297</v>
+        <v>877</v>
       </c>
       <c r="G56" t="s">
-        <v>1299</v>
+        <v>877</v>
       </c>
       <c r="H56" t="s">
-        <v>1300</v>
+        <v>880</v>
       </c>
       <c r="I56" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+        <v>877</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
-        <v>2091</v>
+        <v>1296</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C57" t="s">
-        <v>2093</v>
+        <v>1299</v>
       </c>
       <c r="D57" t="s">
-        <v>2097</v>
+        <v>1298</v>
       </c>
       <c r="E57" t="s">
-        <v>2095</v>
+        <v>938</v>
       </c>
       <c r="F57" t="s">
-        <v>2094</v>
+        <v>1297</v>
       </c>
       <c r="G57" t="s">
-        <v>2092</v>
+        <v>1299</v>
       </c>
       <c r="H57" t="s">
-        <v>2098</v>
+        <v>1300</v>
       </c>
       <c r="I57" t="s">
-        <v>2096</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
-        <v>2100</v>
+        <v>2091</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C58" t="s">
-        <v>2099</v>
+        <v>2093</v>
       </c>
       <c r="D58" t="s">
-        <v>2102</v>
+        <v>2097</v>
       </c>
       <c r="E58" t="s">
-        <v>2103</v>
+        <v>2095</v>
       </c>
       <c r="F58" t="s">
-        <v>2099</v>
+        <v>2094</v>
       </c>
       <c r="G58" t="s">
-        <v>2101</v>
+        <v>2092</v>
+      </c>
+      <c r="H58" t="s">
+        <v>2098</v>
       </c>
       <c r="I58" t="s">
-        <v>2104</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2096</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
-        <v>2364</v>
+        <v>2100</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C59" t="s">
-        <v>2365</v>
+        <v>2099</v>
       </c>
       <c r="D59" t="s">
-        <v>2367</v>
+        <v>2102</v>
       </c>
       <c r="E59" t="s">
-        <v>938</v>
+        <v>2103</v>
       </c>
       <c r="F59" t="s">
-        <v>2366</v>
+        <v>2099</v>
       </c>
       <c r="G59" t="s">
-        <v>2365</v>
+        <v>2101</v>
       </c>
       <c r="I59" t="s">
-        <v>1301</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2104</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
-        <v>2406</v>
+        <v>2364</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C60" t="s">
+        <v>2365</v>
+      </c>
+      <c r="D60" t="s">
+        <v>2367</v>
+      </c>
+      <c r="E60" t="s">
+        <v>938</v>
+      </c>
+      <c r="F60" t="s">
+        <v>2366</v>
+      </c>
+      <c r="G60" t="s">
+        <v>2365</v>
+      </c>
+      <c r="I60" t="s">
+        <v>1301</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A61" s="2" t="s">
+        <v>2406</v>
+      </c>
+      <c r="B61" s="3" t="s">
+        <v>219</v>
+      </c>
+      <c r="C61" t="s">
         <v>2407</v>
       </c>
-      <c r="D60" t="s">
+      <c r="D61" t="s">
         <v>2408</v>
       </c>
-      <c r="E60" t="s">
+      <c r="E61" t="s">
         <v>2410</v>
       </c>
-      <c r="F60" t="s">
+      <c r="F61" t="s">
         <v>2407</v>
       </c>
-      <c r="G60" t="s">
+      <c r="G61" t="s">
         <v>2411</v>
       </c>
-      <c r="H60" t="s">
+      <c r="H61" t="s">
         <v>2409</v>
       </c>
-      <c r="I60" t="s">
+      <c r="I61" t="s">
         <v>2083</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A61" s="2" t="s">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A62" s="2" t="s">
         <v>936</v>
       </c>
-      <c r="B61" t="s">
+      <c r="B62" t="s">
         <v>943</v>
       </c>
-      <c r="C61" t="s">
+      <c r="C62" t="s">
         <v>941</v>
       </c>
-      <c r="D61" t="s">
+      <c r="D62" t="s">
         <v>939</v>
       </c>
-      <c r="E61" t="s">
+      <c r="E62" t="s">
         <v>938</v>
       </c>
-      <c r="F61" t="s">
+      <c r="F62" t="s">
         <v>937</v>
       </c>
-      <c r="G61" t="s">
+      <c r="G62" t="s">
         <v>942</v>
       </c>
-      <c r="H61" t="s">
+      <c r="H62" t="s">
         <v>940</v>
       </c>
-      <c r="I61" t="s">
+      <c r="I62" t="s">
         <v>941</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A62" s="2" t="s">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A63" s="2" t="s">
         <v>1242</v>
       </c>
-      <c r="B62" t="s">
+      <c r="B63" t="s">
         <v>1241</v>
       </c>
-      <c r="C62" t="s">
+      <c r="C63" t="s">
         <v>1245</v>
       </c>
-      <c r="D62" t="s">
+      <c r="D63" t="s">
         <v>1244</v>
       </c>
-      <c r="E62" t="s">
+      <c r="E63" t="s">
         <v>1243</v>
       </c>
-      <c r="F62" t="s">
+      <c r="F63" t="s">
         <v>1245</v>
       </c>
-      <c r="G62" t="s">
+      <c r="G63" t="s">
         <v>1247</v>
       </c>
-      <c r="H62" t="s">
+      <c r="H63" t="s">
         <v>1248</v>
       </c>
-      <c r="I62" t="s">
+      <c r="I63" t="s">
         <v>1246</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A63" s="2" t="s">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A64" s="2" t="s">
         <v>1361</v>
       </c>
-      <c r="B63" s="3" t="s">
+      <c r="B64" s="3" t="s">
         <v>1360</v>
       </c>
-      <c r="C63" s="2">
+      <c r="C64" s="2">
         <v>1704320001</v>
       </c>
-      <c r="D63" t="s">
+      <c r="D64" t="s">
         <v>1363</v>
       </c>
-      <c r="E63" t="s">
+      <c r="E64" t="s">
         <v>47</v>
       </c>
-      <c r="F63" t="s">
+      <c r="F64" t="s">
         <v>1362</v>
       </c>
-      <c r="G63" t="s">
+      <c r="G64" t="s">
         <v>1365</v>
       </c>
-      <c r="H63" t="s">
+      <c r="H64" t="s">
         <v>1364</v>
       </c>
-      <c r="I63" t="s">
+      <c r="I64" t="s">
         <v>1359</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A64" s="2" t="s">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A65" s="2" t="s">
         <v>1986</v>
       </c>
-      <c r="B64" s="3" t="s">
+      <c r="B65" s="3" t="s">
         <v>92</v>
       </c>
-      <c r="C64" t="s">
+      <c r="C65" t="s">
         <v>1824</v>
       </c>
-      <c r="D64" t="s">
+      <c r="D65" t="s">
         <v>1823</v>
       </c>
-      <c r="E64" t="s">
+      <c r="E65" t="s">
         <v>1825</v>
       </c>
-      <c r="F64" t="s">
+      <c r="F65" t="s">
         <v>1824</v>
       </c>
-      <c r="G64" t="s">
+      <c r="G65" t="s">
         <v>1826</v>
       </c>
-      <c r="H64" t="s">
+      <c r="H65" t="s">
         <v>297</v>
       </c>
-      <c r="I64" t="s">
+      <c r="I65" t="s">
         <v>1822</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A65" s="2" t="s">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A66" s="2" t="s">
         <v>2013</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B66" s="3" t="s">
         <v>2007</v>
       </c>
-      <c r="C65" t="s">
+      <c r="C66" t="s">
         <v>2009</v>
       </c>
-      <c r="D65" t="s">
+      <c r="D66" t="s">
         <v>2008</v>
       </c>
-      <c r="E65" t="s">
+      <c r="E66" t="s">
         <v>2010</v>
       </c>
-      <c r="F65" t="s">
+      <c r="F66" t="s">
         <v>2009</v>
       </c>
-      <c r="G65" t="s">
+      <c r="G66" t="s">
         <v>2014</v>
       </c>
-      <c r="H65" t="s">
+      <c r="H66" t="s">
         <v>2011</v>
       </c>
-      <c r="I65" t="s">
+      <c r="I66" t="s">
         <v>2012</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A66" s="2" t="s">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A67" s="2" t="s">
         <v>2243</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B67" s="3" t="s">
         <v>2242</v>
       </c>
-      <c r="C66" t="s">
+      <c r="C67" t="s">
         <v>2245</v>
       </c>
-      <c r="D66" t="s">
+      <c r="D67" t="s">
         <v>2246</v>
       </c>
-      <c r="E66" t="s">
+      <c r="E67" t="s">
         <v>2086</v>
       </c>
-      <c r="F66" t="s">
+      <c r="F67" t="s">
         <v>2244</v>
       </c>
-      <c r="G66" t="s">
+      <c r="G67" t="s">
         <v>2248</v>
       </c>
-      <c r="I66" t="s">
+      <c r="I67" t="s">
         <v>2247</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A67" s="2" t="s">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+      <c r="A68" s="2" t="s">
         <v>2356</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>2355</v>
       </c>
-      <c r="C67" t="s">
+      <c r="C68" t="s">
         <v>2357</v>
       </c>
-      <c r="D67" t="s">
+      <c r="D68" t="s">
         <v>2358</v>
       </c>
-      <c r="E67" t="s">
+      <c r="E68" t="s">
         <v>2359</v>
       </c>
-      <c r="F67" t="s">
+      <c r="F68" t="s">
         <v>2360</v>
       </c>
-      <c r="G67" t="s">
+      <c r="G68" t="s">
         <v>2361</v>
       </c>
-      <c r="H67" t="s">
+      <c r="H68" t="s">
         <v>2363</v>
       </c>
-      <c r="I67" t="s">
+      <c r="I68" t="s">
         <v>2362</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J54" xr:uid="{F77DF9D1-733F-4622-A5B9-9F6937E4842B}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J54">
-      <sortCondition ref="A1:A54"/>
+  <autoFilter ref="A1:J55" xr:uid="{F77DF9D1-733F-4622-A5B9-9F6937E4842B}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J55">
+      <sortCondition ref="A1:A55"/>
     </sortState>
   </autoFilter>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -22438,19 +22533,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61606E71-114A-4060-B4DA-26AC2BA8C44E}">
   <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.08203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.5" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -22482,7 +22577,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>257</v>
       </c>
@@ -22511,7 +22606,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>263</v>
       </c>
@@ -22540,7 +22635,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>908</v>
       </c>
@@ -22569,7 +22664,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>912</v>
       </c>
@@ -22598,7 +22693,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1276</v>
       </c>
@@ -22627,7 +22722,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1406</v>
       </c>
@@ -22656,7 +22751,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1614</v>
       </c>
@@ -22685,7 +22780,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1954</v>
       </c>
@@ -22714,7 +22809,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1989</v>
       </c>
@@ -22743,7 +22838,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1996</v>
       </c>
@@ -22772,7 +22867,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>2051</v>
       </c>
@@ -22801,7 +22896,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2052</v>
       </c>
@@ -22830,7 +22925,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>2053</v>
       </c>
@@ -22856,7 +22951,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>2268</v>
       </c>
@@ -22885,7 +22980,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>2277</v>
       </c>
@@ -22914,7 +23009,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>2391</v>
       </c>
@@ -22943,7 +23038,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2080</v>
       </c>
@@ -22969,7 +23064,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>2084</v>
       </c>
@@ -22995,24 +23090,24 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>2501</v>
+        <v>2500</v>
       </c>
       <c r="B20" t="s">
         <v>2079</v>
       </c>
       <c r="C20" t="s">
+        <v>2501</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>2503</v>
+      </c>
+      <c r="E20" t="s">
         <v>2502</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>2504</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2503</v>
-      </c>
       <c r="F20" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="G20" t="s">
         <v>2411</v>
@@ -23021,7 +23116,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>2111</v>
       </c>
@@ -23060,21 +23155,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CC079E-4192-4042-9084-101DC20DC760}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="90.25" customWidth="1"/>
-    <col min="5" max="5" width="18.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23106,7 +23201,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>81</v>
       </c>
@@ -23132,7 +23227,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>395</v>
       </c>
@@ -23158,7 +23253,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>612</v>
       </c>
@@ -23184,7 +23279,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2167</v>
       </c>
@@ -23210,7 +23305,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2166</v>
       </c>
@@ -23236,7 +23331,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2165</v>
       </c>
@@ -23262,7 +23357,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>465</v>
       </c>
@@ -23288,7 +23383,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1391</v>
       </c>
@@ -23314,7 +23409,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1430</v>
       </c>
@@ -23340,7 +23435,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1443</v>
       </c>
@@ -23366,7 +23461,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>2162</v>
       </c>
@@ -23392,7 +23487,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2189</v>
       </c>
@@ -23418,7 +23513,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1566</v>
       </c>
@@ -23444,7 +23539,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1140</v>
       </c>
@@ -23470,7 +23565,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>668</v>
       </c>
@@ -23496,7 +23591,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1202</v>
       </c>
@@ -23522,7 +23617,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>820</v>
       </c>
@@ -23548,7 +23643,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1699</v>
       </c>
@@ -23574,9 +23669,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>78</v>
@@ -23585,13 +23680,13 @@
         <v>821</v>
       </c>
       <c r="D20" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="G20" t="s">
         <v>1433</v>
@@ -23600,7 +23695,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1534</v>
       </c>
@@ -23626,7 +23721,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>1126</v>
       </c>
@@ -23652,7 +23747,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>1478</v>
       </c>
@@ -23678,7 +23773,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1987</v>
       </c>
@@ -23704,7 +23799,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>1137</v>
       </c>
@@ -23730,7 +23825,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>2143</v>
       </c>
@@ -23756,7 +23851,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2141</v>
       </c>
@@ -23773,7 +23868,7 @@
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="G27" t="s">
         <v>1433</v>
@@ -23782,7 +23877,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>2147</v>
       </c>
@@ -23808,7 +23903,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>2151</v>
       </c>
@@ -23834,7 +23929,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>2473</v>
       </c>
@@ -23860,7 +23955,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1421</v>
       </c>
@@ -23886,7 +23981,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>2105</v>
       </c>
@@ -23912,7 +24007,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>2260</v>
       </c>
@@ -23938,7 +24033,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1798</v>
       </c>
@@ -23964,7 +24059,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1799</v>
       </c>
@@ -23990,7 +24085,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>1829</v>
       </c>
@@ -24016,7 +24111,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1866</v>
       </c>
@@ -24042,7 +24137,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1873</v>
       </c>
@@ -24068,7 +24163,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>1881</v>
       </c>
@@ -24094,7 +24189,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>2447</v>
       </c>
@@ -24133,21 +24228,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F2426-BE64-4140-89D3-828BC4EE93FD}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24179,7 +24274,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>191</v>
       </c>
@@ -24205,7 +24300,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>648</v>
       </c>
@@ -24231,7 +24326,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1174</v>
       </c>
@@ -24257,7 +24352,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1182</v>
       </c>
@@ -24283,7 +24378,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>649</v>
       </c>
@@ -24309,7 +24404,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1176</v>
       </c>
@@ -24335,7 +24430,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1186</v>
       </c>
@@ -24361,7 +24456,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1981</v>
       </c>
@@ -24387,7 +24482,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2289</v>
       </c>
@@ -24413,7 +24508,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>650</v>
       </c>
@@ -24439,7 +24534,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>949</v>
       </c>
@@ -24465,7 +24560,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>995</v>
       </c>
@@ -24491,7 +24586,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1241700000</v>
       </c>
@@ -24530,19 +24625,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F28B83C-EC15-4DE5-B23D-95C2173BD368}">
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="101.83203125" customWidth="1"/>
+    <col min="4" max="4" width="101.875" customWidth="1"/>
     <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24574,7 +24669,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>88</v>
       </c>
@@ -24600,7 +24695,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>119</v>
       </c>
@@ -24626,7 +24721,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1493</v>
       </c>
@@ -24652,7 +24747,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1551</v>
       </c>
@@ -24678,7 +24773,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1570</v>
       </c>
@@ -24704,7 +24799,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>769</v>
       </c>
@@ -24730,7 +24825,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1953</v>
       </c>
@@ -24756,7 +24851,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>533</v>
       </c>
@@ -24785,7 +24880,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>743</v>
       </c>
@@ -24811,7 +24906,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>742</v>
       </c>
@@ -24837,7 +24932,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>750</v>
       </c>
@@ -24863,7 +24958,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>751</v>
       </c>
@@ -24889,7 +24984,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>755</v>
       </c>
@@ -24915,7 +25010,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1344</v>
       </c>
@@ -24941,7 +25036,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1366</v>
       </c>
@@ -24967,7 +25062,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1367</v>
       </c>
@@ -24993,7 +25088,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1372</v>
       </c>
@@ -25019,7 +25114,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1499</v>
       </c>
@@ -25045,7 +25140,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1941</v>
       </c>
@@ -25071,7 +25166,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>2416</v>
       </c>
@@ -25097,7 +25192,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>2424</v>
       </c>
@@ -25117,7 +25212,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>2425</v>
       </c>
@@ -25137,7 +25232,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>2426</v>
       </c>
@@ -25157,7 +25252,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>212</v>
       </c>
@@ -25183,7 +25278,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>216</v>
       </c>
@@ -25209,7 +25304,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>599</v>
       </c>
@@ -25235,7 +25330,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>770</v>
       </c>
@@ -25261,7 +25356,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>846</v>
       </c>
@@ -25287,7 +25382,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>850</v>
       </c>
@@ -25313,7 +25408,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1060</v>
       </c>
@@ -25339,7 +25434,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>1412</v>
       </c>
@@ -25365,7 +25460,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>1694</v>
       </c>
@@ -25391,7 +25486,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1714</v>
       </c>
@@ -25417,7 +25512,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>2293</v>
       </c>
@@ -25443,7 +25538,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>2453</v>
       </c>

--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{937BB337-B783-4FDE-B0AF-53CF6C8A0708}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F365C295-B49A-4E56-9215-3495A9D2EAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="12" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4535" uniqueCount="2567">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4543" uniqueCount="2571">
   <si>
     <t>Part Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9961,6 +9961,22 @@
   </si>
   <si>
     <t>TXB0104 带自动方向感应和 ±15kV ESD 保护功能的 4 位双向电压电平转换器</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6611600020</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>USB插件母座;Type-A;USB 3.0;卷边;1.5A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HC-USB3.0-L168-ZJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HC-USB3_0-L168-ZJ</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10465,21 +10481,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J153"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="70.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.58203125" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="14.125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.08203125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10511,7 +10527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>774</v>
       </c>
@@ -10528,7 +10544,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -10554,7 +10570,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>336</v>
       </c>
@@ -10580,7 +10596,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>568</v>
       </c>
@@ -10606,7 +10622,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1084</v>
       </c>
@@ -10632,7 +10648,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1548</v>
       </c>
@@ -10658,7 +10674,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1629</v>
       </c>
@@ -10684,7 +10700,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1630</v>
       </c>
@@ -10710,7 +10726,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1665</v>
       </c>
@@ -10736,7 +10752,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>128</v>
       </c>
@@ -10762,7 +10778,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>448</v>
       </c>
@@ -10788,7 +10804,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>2457</v>
       </c>
@@ -10814,7 +10830,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1134</v>
       </c>
@@ -10840,7 +10856,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>889</v>
       </c>
@@ -10866,7 +10882,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1500</v>
       </c>
@@ -10892,7 +10908,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>286</v>
       </c>
@@ -10918,7 +10934,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>1032</v>
       </c>
@@ -10944,7 +10960,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>1459</v>
       </c>
@@ -10970,7 +10986,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>1849</v>
       </c>
@@ -10996,7 +11012,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>291</v>
       </c>
@@ -11022,7 +11038,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>369</v>
       </c>
@@ -11048,7 +11064,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>830</v>
       </c>
@@ -11074,7 +11090,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>1422</v>
       </c>
@@ -11100,7 +11116,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>177</v>
       </c>
@@ -11126,7 +11142,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>418</v>
       </c>
@@ -11152,7 +11168,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>1210</v>
       </c>
@@ -11178,7 +11194,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>2312</v>
       </c>
@@ -11204,7 +11220,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>711</v>
       </c>
@@ -11230,7 +11246,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>964</v>
       </c>
@@ -11256,7 +11272,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1320</v>
       </c>
@@ -11282,7 +11298,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>2350</v>
       </c>
@@ -11308,7 +11324,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>2520</v>
       </c>
@@ -11334,7 +11350,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1841</v>
       </c>
@@ -11360,7 +11376,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>722</v>
       </c>
@@ -11386,7 +11402,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>473</v>
       </c>
@@ -11412,7 +11428,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>1669</v>
       </c>
@@ -11438,7 +11454,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>1258</v>
       </c>
@@ -11464,7 +11480,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>425</v>
       </c>
@@ -11490,7 +11506,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>1337</v>
       </c>
@@ -11516,7 +11532,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>2134</v>
       </c>
@@ -11542,7 +11558,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>1889</v>
       </c>
@@ -11568,7 +11584,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>1100</v>
       </c>
@@ -11594,7 +11610,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>1207</v>
       </c>
@@ -11620,7 +11636,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>2156</v>
       </c>
@@ -11646,7 +11662,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>776</v>
       </c>
@@ -11672,7 +11688,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>953</v>
       </c>
@@ -11698,7 +11714,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>1473</v>
       </c>
@@ -11724,7 +11740,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>2505</v>
       </c>
@@ -11750,7 +11766,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>2511</v>
       </c>
@@ -11776,7 +11792,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>1923</v>
       </c>
@@ -11802,7 +11818,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>1611</v>
       </c>
@@ -11828,7 +11844,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>1978</v>
       </c>
@@ -11854,7 +11870,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>1162</v>
       </c>
@@ -11880,7 +11896,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>1313</v>
       </c>
@@ -11906,7 +11922,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>1396</v>
       </c>
@@ -11932,7 +11948,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>409</v>
       </c>
@@ -11958,7 +11974,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>1587</v>
       </c>
@@ -11984,7 +12000,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>294</v>
       </c>
@@ -12010,7 +12026,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>643</v>
       </c>
@@ -12036,7 +12052,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>1633</v>
       </c>
@@ -12062,7 +12078,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>1685</v>
       </c>
@@ -12088,7 +12104,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>2303</v>
       </c>
@@ -12114,7 +12130,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>2552</v>
       </c>
@@ -12140,7 +12156,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>1852</v>
       </c>
@@ -12166,7 +12182,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>1342</v>
       </c>
@@ -12192,7 +12208,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>357</v>
       </c>
@@ -12218,7 +12234,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>361</v>
       </c>
@@ -12244,7 +12260,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>899</v>
       </c>
@@ -12270,7 +12286,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>1677</v>
       </c>
@@ -12296,7 +12312,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>2296</v>
       </c>
@@ -12322,7 +12338,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>412</v>
       </c>
@@ -12348,7 +12364,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>2139</v>
       </c>
@@ -12374,7 +12390,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>1028</v>
       </c>
@@ -12400,7 +12416,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
         <v>2337</v>
       </c>
@@ -12426,7 +12442,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
         <v>1462</v>
       </c>
@@ -12452,7 +12468,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
         <v>180</v>
       </c>
@@ -12478,7 +12494,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
         <v>2175</v>
       </c>
@@ -12504,7 +12520,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
         <v>2435</v>
       </c>
@@ -12530,7 +12546,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
         <v>1293</v>
       </c>
@@ -12556,7 +12572,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
         <v>1165</v>
       </c>
@@ -12582,7 +12598,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
         <v>480</v>
       </c>
@@ -12608,7 +12624,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
         <v>1532</v>
       </c>
@@ -12634,7 +12650,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
         <v>958</v>
       </c>
@@ -12660,7 +12676,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A85" s="2" t="s">
         <v>2544</v>
       </c>
@@ -12686,7 +12702,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
         <v>1690</v>
       </c>
@@ -12712,7 +12728,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A87" s="2" t="s">
         <v>1691</v>
       </c>
@@ -12738,7 +12754,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
         <v>789</v>
       </c>
@@ -12764,7 +12780,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
         <v>1932</v>
       </c>
@@ -12790,7 +12806,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
         <v>1892</v>
       </c>
@@ -12816,7 +12832,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
         <v>1927</v>
       </c>
@@ -12842,7 +12858,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
         <v>1709</v>
       </c>
@@ -12868,7 +12884,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
         <v>1521</v>
       </c>
@@ -12894,7 +12910,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
         <v>130</v>
       </c>
@@ -12920,7 +12936,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
         <v>697</v>
       </c>
@@ -12946,7 +12962,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
         <v>1076</v>
       </c>
@@ -12972,7 +12988,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
         <v>1526</v>
       </c>
@@ -12998,7 +13014,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
         <v>2547</v>
       </c>
@@ -13024,7 +13040,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
         <v>1170</v>
       </c>
@@ -13050,7 +13066,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
         <v>1054</v>
       </c>
@@ -13076,7 +13092,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
         <v>1542</v>
       </c>
@@ -13102,7 +13118,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
         <v>408</v>
       </c>
@@ -13128,7 +13144,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
         <v>470</v>
       </c>
@@ -13154,7 +13170,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
         <v>482</v>
       </c>
@@ -13180,7 +13196,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
         <v>428</v>
       </c>
@@ -13206,7 +13222,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
         <v>1087</v>
       </c>
@@ -13232,7 +13248,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
         <v>1439</v>
       </c>
@@ -13258,7 +13274,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
         <v>163</v>
       </c>
@@ -13284,7 +13300,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
         <v>367</v>
       </c>
@@ -13310,7 +13326,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
         <v>368</v>
       </c>
@@ -13336,7 +13352,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
         <v>1096</v>
       </c>
@@ -13362,7 +13378,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
         <v>153</v>
       </c>
@@ -13388,7 +13404,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
         <v>157</v>
       </c>
@@ -13414,7 +13430,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
         <v>450</v>
       </c>
@@ -13440,7 +13456,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
         <v>1030</v>
       </c>
@@ -13466,7 +13482,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
         <v>1453</v>
       </c>
@@ -13492,7 +13508,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
         <v>1042</v>
       </c>
@@ -13518,7 +13534,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
         <v>1456</v>
       </c>
@@ -13544,7 +13560,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
         <v>944</v>
       </c>
@@ -13570,7 +13586,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
         <v>1287</v>
       </c>
@@ -13596,7 +13612,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
         <v>1158</v>
       </c>
@@ -13622,7 +13638,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
         <v>1575</v>
       </c>
@@ -13648,7 +13664,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
         <v>1681</v>
       </c>
@@ -13674,7 +13690,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
         <v>2235</v>
       </c>
@@ -13700,7 +13716,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
         <v>1475</v>
       </c>
@@ -13726,7 +13742,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
         <v>679</v>
       </c>
@@ -13752,7 +13768,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
         <v>687</v>
       </c>
@@ -13778,7 +13794,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
         <v>606</v>
       </c>
@@ -13804,7 +13820,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
         <v>400</v>
       </c>
@@ -13830,7 +13846,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
         <v>331</v>
       </c>
@@ -13856,7 +13872,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
         <v>338</v>
       </c>
@@ -13882,7 +13898,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
         <v>1154</v>
       </c>
@@ -13908,7 +13924,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
         <v>1703</v>
       </c>
@@ -13934,7 +13950,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
         <v>1816</v>
       </c>
@@ -13960,7 +13976,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
         <v>1079</v>
       </c>
@@ -13986,7 +14002,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
         <v>1675</v>
       </c>
@@ -14012,7 +14028,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
         <v>1883</v>
       </c>
@@ -14038,7 +14054,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
         <v>1272</v>
       </c>
@@ -14064,7 +14080,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
         <v>1103</v>
       </c>
@@ -14090,7 +14106,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
         <v>828</v>
       </c>
@@ -14116,7 +14132,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
         <v>1919</v>
       </c>
@@ -14142,7 +14158,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
         <v>1303</v>
       </c>
@@ -14168,7 +14184,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
         <v>2340</v>
       </c>
@@ -14194,7 +14210,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
         <v>2315</v>
       </c>
@@ -14220,7 +14236,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -14246,7 +14262,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
         <v>1388</v>
       </c>
@@ -14272,7 +14288,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
         <v>134</v>
       </c>
@@ -14298,7 +14314,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
         <v>1538</v>
       </c>
@@ -14324,7 +14340,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
         <v>690</v>
       </c>
@@ -14350,7 +14366,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
         <v>1053</v>
       </c>
@@ -14376,7 +14392,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
         <v>398</v>
       </c>
@@ -14402,7 +14418,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
         <v>694</v>
       </c>
@@ -14428,7 +14444,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
         <v>1649</v>
       </c>
@@ -14472,21 +14488,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A56977-BF1C-4909-8B1B-32F3873FBB32}">
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="78.875" customWidth="1"/>
+    <col min="2" max="2" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.83203125" customWidth="1"/>
     <col min="5" max="5" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14518,7 +14534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>51</v>
       </c>
@@ -14544,7 +14560,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>681</v>
       </c>
@@ -14570,7 +14586,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>757</v>
       </c>
@@ -14596,7 +14612,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>759</v>
       </c>
@@ -14622,7 +14638,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>780</v>
       </c>
@@ -14648,7 +14664,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>866</v>
       </c>
@@ -14674,7 +14690,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>973</v>
       </c>
@@ -14700,7 +14716,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1035</v>
       </c>
@@ -14726,7 +14742,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1045</v>
       </c>
@@ -14752,7 +14768,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1425</v>
       </c>
@@ -14778,7 +14794,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1608</v>
       </c>
@@ -14804,7 +14820,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>1731</v>
       </c>
@@ -14830,7 +14846,7 @@
         <v>1733</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1894</v>
       </c>
@@ -14856,7 +14872,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1897</v>
       </c>
@@ -14882,7 +14898,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1900</v>
       </c>
@@ -14908,7 +14924,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>2212</v>
       </c>
@@ -14934,7 +14950,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>65</v>
       </c>
@@ -14960,7 +14976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>392</v>
       </c>
@@ -14986,7 +15002,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>421</v>
       </c>
@@ -15012,7 +15028,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>442</v>
       </c>
@@ -15038,7 +15054,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>461</v>
       </c>
@@ -15064,7 +15080,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>671</v>
       </c>
@@ -15090,7 +15106,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>799</v>
       </c>
@@ -15116,7 +15132,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>834</v>
       </c>
@@ -15142,7 +15158,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>1198</v>
       </c>
@@ -15171,7 +15187,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>1323</v>
       </c>
@@ -15197,7 +15213,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>1379</v>
       </c>
@@ -15223,7 +15239,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>1609</v>
       </c>
@@ -15249,7 +15265,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>1601</v>
       </c>
@@ -15275,7 +15291,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1926</v>
       </c>
@@ -15301,7 +15317,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>2128</v>
       </c>
@@ -15327,7 +15343,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>2226</v>
       </c>
@@ -15353,7 +15369,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>2306</v>
       </c>
@@ -15379,7 +15395,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>1660</v>
       </c>
@@ -15405,7 +15421,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>2183</v>
       </c>
@@ -15431,7 +15447,7 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>2468</v>
       </c>
@@ -15457,7 +15473,7 @@
         <v>2518</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>2530</v>
       </c>
@@ -15483,7 +15499,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>721</v>
       </c>
@@ -15509,7 +15525,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>1619</v>
       </c>
@@ -15535,7 +15551,7 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>2496</v>
       </c>
@@ -15561,7 +15577,7 @@
         <v>2499</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>1643</v>
       </c>
@@ -15587,7 +15603,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>2249</v>
       </c>
@@ -15613,7 +15629,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>2368</v>
       </c>
@@ -15639,7 +15655,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>2379</v>
       </c>
@@ -15683,20 +15699,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013733C5-3D86-4F9A-8E9B-0FC55B649E0F}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="91.375" customWidth="1"/>
-    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.33203125" customWidth="1"/>
+    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15728,7 +15744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>108</v>
       </c>
@@ -15754,7 +15770,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>2385</v>
       </c>
@@ -15780,7 +15796,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>2412</v>
       </c>
@@ -15806,7 +15822,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
@@ -15832,7 +15848,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1355</v>
       </c>
@@ -15858,7 +15874,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1356</v>
       </c>
@@ -15884,7 +15900,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>2019</v>
       </c>
@@ -15910,7 +15926,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1600</v>
       </c>
@@ -15936,7 +15952,7 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>2534</v>
       </c>
@@ -15974,20 +15990,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16019,7 +16035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1743</v>
       </c>
@@ -16048,7 +16064,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>344</v>
       </c>
@@ -16077,7 +16093,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1562</v>
       </c>
@@ -16106,7 +16122,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>381</v>
       </c>
@@ -16135,7 +16151,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>881</v>
       </c>
@@ -16164,7 +16180,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1216</v>
       </c>
@@ -16193,7 +16209,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1742</v>
       </c>
@@ -16222,7 +16238,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1508</v>
       </c>
@@ -16251,7 +16267,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1748</v>
       </c>
@@ -16280,7 +16296,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1984</v>
       </c>
@@ -16309,7 +16325,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1961</v>
       </c>
@@ -16338,7 +16354,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>1963</v>
       </c>
@@ -16367,7 +16383,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1744</v>
       </c>
@@ -16396,7 +16412,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1745</v>
       </c>
@@ -16425,7 +16441,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1746</v>
       </c>
@@ -16454,7 +16470,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1747</v>
       </c>
@@ -16483,7 +16499,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2177</v>
       </c>
@@ -16512,7 +16528,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>2193</v>
       </c>
@@ -16557,19 +16573,19 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC4AD67-C776-4093-88E2-79BBC414D956}">
   <dimension ref="A1:J43"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="118" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.58203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16601,7 +16617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
@@ -16627,7 +16643,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>386</v>
       </c>
@@ -16653,7 +16669,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>656</v>
       </c>
@@ -16679,7 +16695,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>984</v>
       </c>
@@ -16705,7 +16721,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1003</v>
       </c>
@@ -16731,7 +16747,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1007</v>
       </c>
@@ -16757,7 +16773,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1399</v>
       </c>
@@ -16783,7 +16799,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1513</v>
       </c>
@@ -16809,7 +16825,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1514</v>
       </c>
@@ -16835,7 +16851,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1753</v>
       </c>
@@ -16861,7 +16877,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1754</v>
       </c>
@@ -16887,7 +16903,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>2207</v>
       </c>
@@ -16913,7 +16929,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>2524</v>
       </c>
@@ -16939,7 +16955,7 @@
         <v>2529</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>593</v>
       </c>
@@ -16965,7 +16981,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>840</v>
       </c>
@@ -16991,7 +17007,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1634</v>
       </c>
@@ -17017,7 +17033,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>1635</v>
       </c>
@@ -17043,7 +17059,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>1636</v>
       </c>
@@ -17069,7 +17085,7 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>2562</v>
       </c>
@@ -17095,7 +17111,7 @@
         <v>2563</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>1637</v>
       </c>
@@ -17121,7 +17137,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>1638</v>
       </c>
@@ -17147,7 +17163,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>457</v>
       </c>
@@ -17173,7 +17189,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>562</v>
       </c>
@@ -17199,7 +17215,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>566</v>
       </c>
@@ -17225,7 +17241,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>726</v>
       </c>
@@ -17251,7 +17267,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>729</v>
       </c>
@@ -17277,7 +17293,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>733</v>
       </c>
@@ -17303,7 +17319,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>738</v>
       </c>
@@ -17329,7 +17345,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>913</v>
       </c>
@@ -17355,7 +17371,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1639</v>
       </c>
@@ -17381,7 +17397,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>2065</v>
       </c>
@@ -17407,7 +17423,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>2069</v>
       </c>
@@ -17433,7 +17449,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>2072</v>
       </c>
@@ -17459,7 +17475,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>2254</v>
       </c>
@@ -17485,7 +17501,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>1760</v>
       </c>
@@ -17514,7 +17530,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>1761</v>
       </c>
@@ -17543,7 +17559,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>1775</v>
       </c>
@@ -17569,7 +17585,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>1776</v>
       </c>
@@ -17595,7 +17611,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>1786</v>
       </c>
@@ -17621,7 +17637,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>1870</v>
       </c>
@@ -17647,7 +17663,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>2440</v>
       </c>
@@ -17673,7 +17689,7 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>2462</v>
       </c>
@@ -17717,9 +17733,9 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" s="8" t="s">
         <v>2477</v>
       </c>
@@ -17736,20 +17752,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CB78C2-2208-4DF0-8ABB-0CE48BD26296}">
   <dimension ref="A1:J76"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17781,7 +17797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>1876</v>
       </c>
@@ -17807,7 +17823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>1811</v>
       </c>
@@ -17833,7 +17849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1737</v>
       </c>
@@ -17859,7 +17875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1820</v>
       </c>
@@ -17885,7 +17901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1833</v>
       </c>
@@ -17911,7 +17927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1834</v>
       </c>
@@ -17937,7 +17953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1805</v>
       </c>
@@ -17963,7 +17979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1845</v>
       </c>
@@ -17989,7 +18005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1806</v>
       </c>
@@ -18015,7 +18031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>2050</v>
       </c>
@@ -18041,7 +18057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1860</v>
       </c>
@@ -18067,7 +18083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>2046</v>
       </c>
@@ -18093,7 +18109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>2041</v>
       </c>
@@ -18119,7 +18135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1632</v>
       </c>
@@ -18145,7 +18161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1631</v>
       </c>
@@ -18171,7 +18187,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1812</v>
       </c>
@@ -18197,7 +18213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2015</v>
       </c>
@@ -18223,7 +18239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -18249,7 +18265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>1856</v>
       </c>
@@ -18275,7 +18291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>2334</v>
       </c>
@@ -18301,7 +18317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>174</v>
       </c>
@@ -18327,7 +18343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>653</v>
       </c>
@@ -18353,7 +18369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>1985</v>
       </c>
@@ -18379,7 +18395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>2076</v>
       </c>
@@ -18405,7 +18421,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>2492</v>
       </c>
@@ -18431,7 +18447,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>2330</v>
       </c>
@@ -18457,7 +18473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>1264</v>
       </c>
@@ -18483,7 +18499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>2300</v>
       </c>
@@ -18509,7 +18525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>72</v>
       </c>
@@ -18535,7 +18551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>327</v>
       </c>
@@ -18561,7 +18577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>194</v>
       </c>
@@ -18587,7 +18603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>1483</v>
       </c>
@@ -18613,7 +18629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1484</v>
       </c>
@@ -18639,7 +18655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>1867</v>
       </c>
@@ -18665,7 +18681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>2220</v>
       </c>
@@ -18691,7 +18707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>205</v>
       </c>
@@ -18717,7 +18733,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>810</v>
       </c>
@@ -18743,7 +18759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>2232</v>
       </c>
@@ -18769,7 +18785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>815</v>
       </c>
@@ -18798,7 +18814,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>1120</v>
       </c>
@@ -18827,7 +18843,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>2027</v>
       </c>
@@ -18856,7 +18872,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>1250</v>
       </c>
@@ -18882,7 +18898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>349</v>
       </c>
@@ -18908,7 +18924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>2038</v>
       </c>
@@ -18934,7 +18950,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>417</v>
       </c>
@@ -18960,7 +18976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>887</v>
       </c>
@@ -18986,7 +19002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>197</v>
       </c>
@@ -19012,7 +19028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>1091</v>
       </c>
@@ -19038,7 +19054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>167</v>
       </c>
@@ -19064,7 +19080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>1487</v>
       </c>
@@ -19090,7 +19106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>1130</v>
       </c>
@@ -19116,7 +19132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>1385</v>
       </c>
@@ -19142,7 +19158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -19168,7 +19184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>1591</v>
       </c>
@@ -19194,7 +19210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>1905</v>
       </c>
@@ -19220,7 +19236,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>121</v>
       </c>
@@ -19246,7 +19262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>1117</v>
       </c>
@@ -19272,7 +19288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>1434</v>
       </c>
@@ -19298,7 +19314,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>2219</v>
       </c>
@@ -19324,7 +19340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>2223</v>
       </c>
@@ -19350,7 +19366,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>1149</v>
       </c>
@@ -19379,7 +19395,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>2023</v>
       </c>
@@ -19405,7 +19421,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>2031</v>
       </c>
@@ -19434,7 +19450,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>161</v>
       </c>
@@ -19460,7 +19476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>979</v>
       </c>
@@ -19486,7 +19502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>2239</v>
       </c>
@@ -19512,7 +19528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>1144</v>
       </c>
@@ -19541,7 +19557,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
         <v>58</v>
       </c>
@@ -19567,7 +19583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
         <v>67</v>
       </c>
@@ -19593,7 +19609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
         <v>1452</v>
       </c>
@@ -19619,7 +19635,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
         <v>548</v>
       </c>
@@ -19645,7 +19661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
         <v>2325</v>
       </c>
@@ -19671,7 +19687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
         <v>1110</v>
       </c>
@@ -19700,7 +19716,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B75" t="s">
         <v>17</v>
       </c>
@@ -19715,7 +19731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="B76" t="s">
         <v>17</v>
       </c>
@@ -19747,21 +19763,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C302E28E-61B5-45F2-9EED-9E658F066E8B}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="133.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="133.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.58203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19793,7 +19809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>307</v>
       </c>
@@ -19813,7 +19829,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>306</v>
       </c>
@@ -19842,7 +19858,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>311</v>
       </c>
@@ -19871,7 +19887,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>634</v>
       </c>
@@ -19900,7 +19916,7 @@
         <v>637</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2479</v>
       </c>
@@ -19926,7 +19942,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>869</v>
       </c>
@@ -19955,7 +19971,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1010</v>
       </c>
@@ -19984,7 +20000,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1019</v>
       </c>
@@ -20013,7 +20029,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1067</v>
       </c>
@@ -20039,7 +20055,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1192</v>
       </c>
@@ -20068,7 +20084,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>1225</v>
       </c>
@@ -20097,7 +20113,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>1964</v>
       </c>
@@ -20126,7 +20142,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1970</v>
       </c>
@@ -20155,7 +20171,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1971</v>
       </c>
@@ -20184,7 +20200,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>2514</v>
       </c>
@@ -20207,7 +20223,7 @@
         <v>2512</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1238</v>
       </c>
@@ -20233,7 +20249,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>1465</v>
       </c>
@@ -20259,7 +20275,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>1717</v>
       </c>
@@ -20285,7 +20301,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>1720</v>
       </c>
@@ -20311,7 +20327,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>1721</v>
       </c>
@@ -20337,7 +20353,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>2320</v>
       </c>
@@ -20376,21 +20392,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F61549-8124-4EE7-A218-E5BC471FD40D}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.58203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.83203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20422,7 +20438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>7001100000</v>
       </c>
@@ -20448,7 +20464,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>543</v>
       </c>
@@ -20471,7 +20487,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1507</v>
       </c>
@@ -20497,7 +20513,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1556</v>
       </c>
@@ -20536,20 +20552,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77DF9D1-733F-4622-A5B9-9F6937E4842B}">
   <dimension ref="A1:J68"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.58203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.08203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="57.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.125" customWidth="1"/>
-    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.08203125" customWidth="1"/>
+    <col min="8" max="8" width="18.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.58203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20581,7 +20597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>135</v>
       </c>
@@ -20610,7 +20626,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>141</v>
       </c>
@@ -20639,7 +20655,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -20668,7 +20684,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>295</v>
       </c>
@@ -20697,7 +20713,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>516</v>
       </c>
@@ -20726,7 +20742,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
@@ -20755,7 +20771,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>45</v>
       </c>
@@ -20784,7 +20800,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -20813,7 +20829,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>569</v>
       </c>
@@ -20842,7 +20858,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>582</v>
       </c>
@@ -20871,7 +20887,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>629</v>
       </c>
@@ -20900,7 +20916,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>700</v>
       </c>
@@ -20929,7 +20945,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>917</v>
       </c>
@@ -20958,7 +20974,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>922</v>
       </c>
@@ -20987,7 +21003,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>2283</v>
       </c>
@@ -21016,7 +21032,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>2348</v>
       </c>
@@ -21045,7 +21061,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2399</v>
       </c>
@@ -21074,7 +21090,7 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>2556</v>
       </c>
@@ -21103,7 +21119,7 @@
         <v>2561</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>105</v>
       </c>
@@ -21132,7 +21148,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>226</v>
       </c>
@@ -21161,7 +21177,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>229</v>
       </c>
@@ -21190,7 +21206,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -21219,7 +21235,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>519</v>
       </c>
@@ -21248,7 +21264,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>574</v>
       </c>
@@ -21277,7 +21293,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>580</v>
       </c>
@@ -21306,7 +21322,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>623</v>
       </c>
@@ -21335,7 +21351,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>659</v>
       </c>
@@ -21364,7 +21380,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>790</v>
       </c>
@@ -21393,7 +21409,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>893</v>
       </c>
@@ -21422,7 +21438,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>901</v>
       </c>
@@ -21451,7 +21467,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>965</v>
       </c>
@@ -21480,7 +21496,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>997</v>
       </c>
@@ -21509,7 +21525,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1913</v>
       </c>
@@ -21538,7 +21554,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>1933</v>
       </c>
@@ -21567,7 +21583,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>2116</v>
       </c>
@@ -21596,7 +21612,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>2121</v>
       </c>
@@ -21625,7 +21641,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>253</v>
       </c>
@@ -21654,7 +21670,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>254</v>
       </c>
@@ -21683,7 +21699,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>255</v>
       </c>
@@ -21712,7 +21728,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
         <v>497</v>
       </c>
@@ -21741,7 +21757,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
         <v>492</v>
       </c>
@@ -21770,7 +21786,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
         <v>515</v>
       </c>
@@ -21799,7 +21815,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
         <v>553</v>
       </c>
@@ -21828,7 +21844,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
         <v>589</v>
       </c>
@@ -21857,7 +21873,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
         <v>857</v>
       </c>
@@ -21886,7 +21902,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
         <v>861</v>
       </c>
@@ -21915,7 +21931,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
         <v>2429</v>
       </c>
@@ -21944,7 +21960,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
         <v>2485</v>
       </c>
@@ -21973,7 +21989,7 @@
         <v>2490</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
         <v>486</v>
       </c>
@@ -22002,7 +22018,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
         <v>502</v>
       </c>
@@ -22031,7 +22047,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
         <v>525</v>
       </c>
@@ -22060,7 +22076,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
         <v>2001</v>
       </c>
@@ -22089,7 +22105,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
         <v>2373</v>
       </c>
@@ -22118,7 +22134,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
         <v>220</v>
       </c>
@@ -22147,7 +22163,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
         <v>876</v>
       </c>
@@ -22176,7 +22192,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
         <v>1296</v>
       </c>
@@ -22205,7 +22221,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
         <v>2091</v>
       </c>
@@ -22234,7 +22250,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
         <v>2100</v>
       </c>
@@ -22260,7 +22276,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
         <v>2364</v>
       </c>
@@ -22286,7 +22302,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
         <v>2406</v>
       </c>
@@ -22315,7 +22331,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
         <v>936</v>
       </c>
@@ -22344,7 +22360,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
         <v>1242</v>
       </c>
@@ -22373,7 +22389,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
         <v>1361</v>
       </c>
@@ -22402,7 +22418,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
         <v>1986</v>
       </c>
@@ -22431,7 +22447,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
         <v>2013</v>
       </c>
@@ -22460,7 +22476,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
         <v>2243</v>
       </c>
@@ -22486,7 +22502,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
         <v>2356</v>
       </c>
@@ -22532,20 +22548,20 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61606E71-114A-4060-B4DA-26AC2BA8C44E}">
-  <dimension ref="A1:J21"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <dimension ref="A1:J22"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.5" customWidth="1"/>
-    <col min="5" max="5" width="17.375" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -22577,7 +22593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>257</v>
       </c>
@@ -22606,7 +22622,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>263</v>
       </c>
@@ -22635,7 +22651,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>908</v>
       </c>
@@ -22664,7 +22680,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>912</v>
       </c>
@@ -22693,7 +22709,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1276</v>
       </c>
@@ -22722,7 +22738,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1406</v>
       </c>
@@ -22751,7 +22767,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1614</v>
       </c>
@@ -22780,7 +22796,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1954</v>
       </c>
@@ -22809,7 +22825,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1989</v>
       </c>
@@ -22838,7 +22854,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1996</v>
       </c>
@@ -22867,7 +22883,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>2051</v>
       </c>
@@ -22896,7 +22912,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>2052</v>
       </c>
@@ -22925,7 +22941,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>2053</v>
       </c>
@@ -22951,7 +22967,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>2268</v>
       </c>
@@ -22980,7 +22996,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>2277</v>
       </c>
@@ -23009,7 +23025,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>2391</v>
       </c>
@@ -23038,7 +23054,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>2080</v>
       </c>
@@ -23064,7 +23080,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>2084</v>
       </c>
@@ -23090,7 +23106,7 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>2500</v>
       </c>
@@ -23116,29 +23132,55 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
+        <v>2567</v>
+      </c>
+      <c r="B21" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C21" t="s">
+        <v>2570</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>2568</v>
+      </c>
+      <c r="E21" t="s">
+        <v>2410</v>
+      </c>
+      <c r="F21" t="s">
+        <v>2569</v>
+      </c>
+      <c r="G21" t="s">
+        <v>2570</v>
+      </c>
+      <c r="I21" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
         <v>2111</v>
       </c>
-      <c r="B21" t="s">
+      <c r="B22" t="s">
         <v>2110</v>
       </c>
-      <c r="C21" t="s">
+      <c r="C22" t="s">
         <v>2112</v>
       </c>
-      <c r="D21" s="6" t="s">
+      <c r="D22" s="6" t="s">
         <v>2113</v>
       </c>
-      <c r="E21" t="s">
+      <c r="E22" t="s">
         <v>2114</v>
       </c>
-      <c r="F21" t="s">
+      <c r="F22" t="s">
         <v>2112</v>
       </c>
-      <c r="G21" t="s">
+      <c r="G22" t="s">
         <v>2112</v>
       </c>
-      <c r="I21" t="s">
+      <c r="I22" t="s">
         <v>2115</v>
       </c>
     </row>
@@ -23155,21 +23197,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CC079E-4192-4042-9084-101DC20DC760}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="90.25" customWidth="1"/>
-    <col min="5" max="5" width="18.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.875" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.83203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23201,7 +23243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>81</v>
       </c>
@@ -23227,7 +23269,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>395</v>
       </c>
@@ -23253,7 +23295,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>612</v>
       </c>
@@ -23279,7 +23321,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>2167</v>
       </c>
@@ -23305,7 +23347,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>2166</v>
       </c>
@@ -23331,7 +23373,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>2165</v>
       </c>
@@ -23357,7 +23399,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>465</v>
       </c>
@@ -23383,7 +23425,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1391</v>
       </c>
@@ -23409,7 +23451,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>1430</v>
       </c>
@@ -23435,7 +23477,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>1443</v>
       </c>
@@ -23461,7 +23503,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>2162</v>
       </c>
@@ -23487,7 +23529,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>2189</v>
       </c>
@@ -23513,7 +23555,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>1566</v>
       </c>
@@ -23539,7 +23581,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1140</v>
       </c>
@@ -23565,7 +23607,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>668</v>
       </c>
@@ -23591,7 +23633,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1202</v>
       </c>
@@ -23617,7 +23659,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>820</v>
       </c>
@@ -23643,7 +23685,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>1699</v>
       </c>
@@ -23669,7 +23711,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>2539</v>
       </c>
@@ -23695,7 +23737,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>1534</v>
       </c>
@@ -23721,7 +23763,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>1126</v>
       </c>
@@ -23747,7 +23789,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>1478</v>
       </c>
@@ -23773,7 +23815,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>1987</v>
       </c>
@@ -23799,7 +23841,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>1137</v>
       </c>
@@ -23825,7 +23867,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>2143</v>
       </c>
@@ -23851,7 +23893,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>2141</v>
       </c>
@@ -23877,7 +23919,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>2147</v>
       </c>
@@ -23903,7 +23945,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>2151</v>
       </c>
@@ -23929,7 +23971,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>2473</v>
       </c>
@@ -23955,7 +23997,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1421</v>
       </c>
@@ -23981,7 +24023,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>2105</v>
       </c>
@@ -24007,7 +24049,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>2260</v>
       </c>
@@ -24033,7 +24075,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1798</v>
       </c>
@@ -24059,7 +24101,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>1799</v>
       </c>
@@ -24085,7 +24127,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>1829</v>
       </c>
@@ -24111,7 +24153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A37" s="2" t="s">
         <v>1866</v>
       </c>
@@ -24137,7 +24179,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
         <v>1873</v>
       </c>
@@ -24163,7 +24205,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
         <v>1881</v>
       </c>
@@ -24189,7 +24231,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
         <v>2447</v>
       </c>
@@ -24228,21 +24270,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F2426-BE64-4140-89D3-828BC4EE93FD}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.08203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.08203125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.58203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24274,7 +24316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>191</v>
       </c>
@@ -24300,7 +24342,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>648</v>
       </c>
@@ -24326,7 +24368,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1174</v>
       </c>
@@ -24352,7 +24394,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1182</v>
       </c>
@@ -24378,7 +24420,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>649</v>
       </c>
@@ -24404,7 +24446,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>1176</v>
       </c>
@@ -24430,7 +24472,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1186</v>
       </c>
@@ -24456,7 +24498,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>1981</v>
       </c>
@@ -24482,7 +24524,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>2289</v>
       </c>
@@ -24508,7 +24550,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>650</v>
       </c>
@@ -24534,7 +24576,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>949</v>
       </c>
@@ -24560,7 +24602,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>995</v>
       </c>
@@ -24586,7 +24628,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>1241700000</v>
       </c>
@@ -24625,19 +24667,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F28B83C-EC15-4DE5-B23D-95C2173BD368}">
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="101.875" customWidth="1"/>
+    <col min="4" max="4" width="101.83203125" customWidth="1"/>
     <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24669,7 +24711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="2" t="s">
         <v>88</v>
       </c>
@@ -24695,7 +24737,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
         <v>119</v>
       </c>
@@ -24721,7 +24763,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
         <v>1493</v>
       </c>
@@ -24747,7 +24789,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
         <v>1551</v>
       </c>
@@ -24773,7 +24815,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
         <v>1570</v>
       </c>
@@ -24799,7 +24841,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
         <v>769</v>
       </c>
@@ -24825,7 +24867,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
         <v>1953</v>
       </c>
@@ -24851,7 +24893,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
         <v>533</v>
       </c>
@@ -24880,7 +24922,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
         <v>743</v>
       </c>
@@ -24906,7 +24948,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
         <v>742</v>
       </c>
@@ -24932,7 +24974,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
         <v>750</v>
       </c>
@@ -24958,7 +25000,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
         <v>751</v>
       </c>
@@ -24984,7 +25026,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
         <v>755</v>
       </c>
@@ -25010,7 +25052,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
         <v>1344</v>
       </c>
@@ -25036,7 +25078,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
         <v>1366</v>
       </c>
@@ -25062,7 +25104,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
         <v>1367</v>
       </c>
@@ -25088,7 +25130,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
         <v>1372</v>
       </c>
@@ -25114,7 +25156,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
         <v>1499</v>
       </c>
@@ -25140,7 +25182,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
         <v>1941</v>
       </c>
@@ -25166,7 +25208,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
         <v>2416</v>
       </c>
@@ -25192,7 +25234,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
         <v>2424</v>
       </c>
@@ -25212,7 +25254,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
         <v>2425</v>
       </c>
@@ -25232,7 +25274,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
         <v>2426</v>
       </c>
@@ -25252,7 +25294,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
         <v>212</v>
       </c>
@@ -25278,7 +25320,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
         <v>216</v>
       </c>
@@ -25304,7 +25346,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
         <v>599</v>
       </c>
@@ -25330,7 +25372,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
         <v>770</v>
       </c>
@@ -25356,7 +25398,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
         <v>846</v>
       </c>
@@ -25382,7 +25424,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
         <v>850</v>
       </c>
@@ -25408,7 +25450,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
         <v>1060</v>
       </c>
@@ -25434,7 +25476,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
         <v>1412</v>
       </c>
@@ -25460,7 +25502,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
         <v>1694</v>
       </c>
@@ -25486,7 +25528,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
         <v>1714</v>
       </c>
@@ -25512,7 +25554,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
         <v>2293</v>
       </c>
@@ -25538,7 +25580,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
         <v>2453</v>
       </c>

--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F365C295-B49A-4E56-9215-3495A9D2EAE3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1A63DFA2-A0B0-4A1D-BD1D-00170374E316}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="5" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -9495,10 +9495,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>LR80-52</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>某宝</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -9587,10 +9583,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>SOT23-6</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>1231475001</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -9977,6 +9969,14 @@
   </si>
   <si>
     <t>HC-USB3_0-L168-ZJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOT23_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>L0805_3pin</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10481,21 +10481,21 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:J153"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="13.75" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9" style="1"/>
-    <col min="4" max="4" width="70.58203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.58203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="70.625" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.625" style="1" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="20.25" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9" style="1"/>
-    <col min="9" max="9" width="14.08203125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" style="1" bestFit="1" customWidth="1"/>
     <col min="10" max="16384" width="9" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -10527,7 +10527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>774</v>
       </c>
@@ -10544,7 +10544,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -10570,7 +10570,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>336</v>
       </c>
@@ -10596,7 +10596,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>568</v>
       </c>
@@ -10622,7 +10622,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1084</v>
       </c>
@@ -10648,7 +10648,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1548</v>
       </c>
@@ -10674,7 +10674,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1629</v>
       </c>
@@ -10700,7 +10700,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1630</v>
       </c>
@@ -10726,7 +10726,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1665</v>
       </c>
@@ -10752,7 +10752,7 @@
         <v>1656</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>128</v>
       </c>
@@ -10778,7 +10778,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>448</v>
       </c>
@@ -10804,24 +10804,24 @@
         <v>447</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
-        <v>2457</v>
+        <v>2456</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>443</v>
       </c>
       <c r="C13" s="1" t="s">
+        <v>2457</v>
+      </c>
+      <c r="D13" s="1" t="s">
         <v>2458</v>
-      </c>
-      <c r="D13" s="1" t="s">
-        <v>2459</v>
       </c>
       <c r="E13" s="1" t="s">
         <v>713</v>
       </c>
       <c r="F13" s="1" t="s">
-        <v>2460</v>
+        <v>2459</v>
       </c>
       <c r="G13" s="1" t="s">
         <v>129</v>
@@ -10830,7 +10830,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1134</v>
       </c>
@@ -10856,7 +10856,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>889</v>
       </c>
@@ -10870,7 +10870,7 @@
         <v>892</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>891</v>
@@ -10882,7 +10882,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1500</v>
       </c>
@@ -10908,7 +10908,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>286</v>
       </c>
@@ -10934,7 +10934,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1032</v>
       </c>
@@ -10960,7 +10960,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1459</v>
       </c>
@@ -10986,7 +10986,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1849</v>
       </c>
@@ -11012,7 +11012,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>291</v>
       </c>
@@ -11038,7 +11038,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>369</v>
       </c>
@@ -11064,7 +11064,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>830</v>
       </c>
@@ -11090,7 +11090,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1422</v>
       </c>
@@ -11116,7 +11116,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>177</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>418</v>
       </c>
@@ -11168,7 +11168,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>1210</v>
       </c>
@@ -11194,7 +11194,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>2312</v>
       </c>
@@ -11220,7 +11220,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>711</v>
       </c>
@@ -11246,7 +11246,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>964</v>
       </c>
@@ -11272,7 +11272,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1320</v>
       </c>
@@ -11298,7 +11298,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>2350</v>
       </c>
@@ -11324,33 +11324,33 @@
         <v>339</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
+        <v>2517</v>
+      </c>
+      <c r="D33" s="1" t="s">
         <v>2519</v>
-      </c>
-      <c r="D33" s="1" t="s">
-        <v>2521</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2522</v>
+        <v>2520</v>
       </c>
       <c r="G33" s="1" t="s">
-        <v>2523</v>
+        <v>2521</v>
       </c>
       <c r="I33" s="1" t="s">
         <v>339</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1841</v>
       </c>
@@ -11376,7 +11376,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>722</v>
       </c>
@@ -11402,7 +11402,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>473</v>
       </c>
@@ -11428,7 +11428,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1669</v>
       </c>
@@ -11454,7 +11454,7 @@
         <v>1672</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1258</v>
       </c>
@@ -11480,7 +11480,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>425</v>
       </c>
@@ -11506,7 +11506,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>1337</v>
       </c>
@@ -11532,7 +11532,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>2134</v>
       </c>
@@ -11558,7 +11558,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>1889</v>
       </c>
@@ -11584,7 +11584,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>1100</v>
       </c>
@@ -11610,7 +11610,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>1207</v>
       </c>
@@ -11636,7 +11636,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>2156</v>
       </c>
@@ -11662,7 +11662,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>776</v>
       </c>
@@ -11688,7 +11688,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>953</v>
       </c>
@@ -11714,7 +11714,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>1473</v>
       </c>
@@ -11740,24 +11740,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>2505</v>
+        <v>2503</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
-        <v>2506</v>
+        <v>2504</v>
       </c>
       <c r="D49" s="1" t="s">
-        <v>2507</v>
+        <v>2505</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>2504</v>
+        <v>2502</v>
       </c>
       <c r="G49" t="s">
         <v>91</v>
@@ -11766,24 +11766,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
-        <v>2511</v>
+        <v>2509</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="1" t="s">
-        <v>2509</v>
+        <v>2507</v>
       </c>
       <c r="D50" s="1" t="s">
-        <v>2510</v>
+        <v>2508</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>2508</v>
+        <v>2506</v>
       </c>
       <c r="G50" t="s">
         <v>91</v>
@@ -11792,7 +11792,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>1923</v>
       </c>
@@ -11818,7 +11818,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>1611</v>
       </c>
@@ -11844,7 +11844,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>1978</v>
       </c>
@@ -11870,7 +11870,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>1162</v>
       </c>
@@ -11896,7 +11896,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>1313</v>
       </c>
@@ -11922,7 +11922,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>1396</v>
       </c>
@@ -11948,7 +11948,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>409</v>
       </c>
@@ -11974,7 +11974,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>1587</v>
       </c>
@@ -12000,7 +12000,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>294</v>
       </c>
@@ -12026,7 +12026,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>643</v>
       </c>
@@ -12052,7 +12052,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>1633</v>
       </c>
@@ -12078,7 +12078,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>1685</v>
       </c>
@@ -12104,7 +12104,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>2303</v>
       </c>
@@ -12130,24 +12130,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="B64" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C64" s="1" t="s">
+        <v>2549</v>
+      </c>
+      <c r="D64" s="1" t="s">
         <v>2551</v>
-      </c>
-      <c r="D64" s="1" t="s">
-        <v>2553</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F64" s="1" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="G64" t="s">
         <v>91</v>
@@ -12156,7 +12156,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>1852</v>
       </c>
@@ -12182,7 +12182,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>1342</v>
       </c>
@@ -12208,7 +12208,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>357</v>
       </c>
@@ -12234,7 +12234,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>361</v>
       </c>
@@ -12260,7 +12260,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>899</v>
       </c>
@@ -12286,7 +12286,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>1677</v>
       </c>
@@ -12312,7 +12312,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>2296</v>
       </c>
@@ -12338,7 +12338,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>412</v>
       </c>
@@ -12364,7 +12364,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>2139</v>
       </c>
@@ -12390,7 +12390,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>1028</v>
       </c>
@@ -12416,7 +12416,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A75" s="2" t="s">
         <v>2337</v>
       </c>
@@ -12442,7 +12442,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A76" s="2" t="s">
         <v>1462</v>
       </c>
@@ -12468,7 +12468,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A77" s="2" t="s">
         <v>180</v>
       </c>
@@ -12494,7 +12494,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A78" s="2" t="s">
         <v>2175</v>
       </c>
@@ -12520,7 +12520,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A79" s="2" t="s">
         <v>2435</v>
       </c>
@@ -12546,7 +12546,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="80" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A80" s="2" t="s">
         <v>1293</v>
       </c>
@@ -12572,7 +12572,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A81" s="2" t="s">
         <v>1165</v>
       </c>
@@ -12598,7 +12598,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A82" s="2" t="s">
         <v>480</v>
       </c>
@@ -12624,7 +12624,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A83" s="2" t="s">
         <v>1532</v>
       </c>
@@ -12650,7 +12650,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A84" s="2" t="s">
         <v>958</v>
       </c>
@@ -12676,24 +12676,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A85" s="2" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="B85" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C85" s="1" t="s">
+        <v>2541</v>
+      </c>
+      <c r="D85" s="1" t="s">
         <v>2543</v>
-      </c>
-      <c r="D85" s="1" t="s">
-        <v>2545</v>
       </c>
       <c r="E85" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F85" s="1" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="G85" t="s">
         <v>19</v>
@@ -12702,7 +12702,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A86" s="2" t="s">
         <v>1690</v>
       </c>
@@ -12728,7 +12728,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A87" s="2" t="s">
         <v>1691</v>
       </c>
@@ -12754,7 +12754,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A88" s="2" t="s">
         <v>789</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A89" s="2" t="s">
         <v>1932</v>
       </c>
@@ -12806,7 +12806,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A90" s="2" t="s">
         <v>1892</v>
       </c>
@@ -12832,7 +12832,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A91" s="2" t="s">
         <v>1927</v>
       </c>
@@ -12858,7 +12858,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A92" s="2" t="s">
         <v>1709</v>
       </c>
@@ -12884,7 +12884,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="93" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A93" s="2" t="s">
         <v>1521</v>
       </c>
@@ -12910,7 +12910,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="94" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A94" s="2" t="s">
         <v>130</v>
       </c>
@@ -12936,7 +12936,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="95" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A95" s="2" t="s">
         <v>697</v>
       </c>
@@ -12962,7 +12962,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="96" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A96" s="2" t="s">
         <v>1076</v>
       </c>
@@ -12988,7 +12988,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="97" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A97" s="2" t="s">
         <v>1526</v>
       </c>
@@ -13014,24 +13014,24 @@
         <v>339</v>
       </c>
     </row>
-    <row r="98" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A98" s="2" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>2548</v>
+        <v>2546</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>2550</v>
+        <v>2548</v>
       </c>
       <c r="G98" t="s">
         <v>19</v>
@@ -13040,7 +13040,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="99" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A99" s="2" t="s">
         <v>1170</v>
       </c>
@@ -13066,7 +13066,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="100" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A100" s="2" t="s">
         <v>1054</v>
       </c>
@@ -13092,7 +13092,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="101" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A101" s="2" t="s">
         <v>1542</v>
       </c>
@@ -13118,7 +13118,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="102" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A102" s="2" t="s">
         <v>408</v>
       </c>
@@ -13144,7 +13144,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="103" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A103" s="2" t="s">
         <v>470</v>
       </c>
@@ -13170,7 +13170,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="104" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A104" s="2" t="s">
         <v>482</v>
       </c>
@@ -13196,7 +13196,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A105" s="2" t="s">
         <v>428</v>
       </c>
@@ -13222,7 +13222,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="106" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A106" s="2" t="s">
         <v>1087</v>
       </c>
@@ -13248,7 +13248,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="107" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A107" s="2" t="s">
         <v>1439</v>
       </c>
@@ -13274,7 +13274,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="108" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A108" s="2" t="s">
         <v>163</v>
       </c>
@@ -13300,7 +13300,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="109" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A109" s="2" t="s">
         <v>367</v>
       </c>
@@ -13326,7 +13326,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="110" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A110" s="2" t="s">
         <v>368</v>
       </c>
@@ -13352,7 +13352,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="111" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A111" s="2" t="s">
         <v>1096</v>
       </c>
@@ -13378,7 +13378,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="112" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A112" s="2" t="s">
         <v>153</v>
       </c>
@@ -13404,7 +13404,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="113" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A113" s="2" t="s">
         <v>157</v>
       </c>
@@ -13430,7 +13430,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="114" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A114" s="2" t="s">
         <v>450</v>
       </c>
@@ -13456,7 +13456,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="115" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A115" s="2" t="s">
         <v>1030</v>
       </c>
@@ -13482,7 +13482,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="116" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A116" s="2" t="s">
         <v>1453</v>
       </c>
@@ -13508,7 +13508,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="117" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A117" s="2" t="s">
         <v>1042</v>
       </c>
@@ -13534,7 +13534,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="118" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A118" s="2" t="s">
         <v>1456</v>
       </c>
@@ -13560,7 +13560,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="119" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A119" s="2" t="s">
         <v>944</v>
       </c>
@@ -13586,7 +13586,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="120" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A120" s="2" t="s">
         <v>1287</v>
       </c>
@@ -13612,7 +13612,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="121" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A121" s="2" t="s">
         <v>1158</v>
       </c>
@@ -13638,7 +13638,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="122" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A122" s="2" t="s">
         <v>1575</v>
       </c>
@@ -13664,7 +13664,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="123" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A123" s="2" t="s">
         <v>1681</v>
       </c>
@@ -13690,7 +13690,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="124" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A124" s="2" t="s">
         <v>2235</v>
       </c>
@@ -13716,7 +13716,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="125" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A125" s="2" t="s">
         <v>1475</v>
       </c>
@@ -13742,7 +13742,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="126" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A126" s="2" t="s">
         <v>679</v>
       </c>
@@ -13768,7 +13768,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="127" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A127" s="2" t="s">
         <v>687</v>
       </c>
@@ -13794,7 +13794,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="128" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A128" s="2" t="s">
         <v>606</v>
       </c>
@@ -13820,7 +13820,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="129" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A129" s="2" t="s">
         <v>400</v>
       </c>
@@ -13846,7 +13846,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="130" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A130" s="2" t="s">
         <v>331</v>
       </c>
@@ -13872,7 +13872,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="131" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A131" s="2" t="s">
         <v>338</v>
       </c>
@@ -13898,7 +13898,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="132" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A132" s="2" t="s">
         <v>1154</v>
       </c>
@@ -13924,7 +13924,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="133" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A133" s="2" t="s">
         <v>1703</v>
       </c>
@@ -13950,7 +13950,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="134" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A134" s="2" t="s">
         <v>1816</v>
       </c>
@@ -13976,7 +13976,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="135" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A135" s="2" t="s">
         <v>1079</v>
       </c>
@@ -14002,7 +14002,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="136" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A136" s="2" t="s">
         <v>1675</v>
       </c>
@@ -14028,7 +14028,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="137" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A137" s="2" t="s">
         <v>1883</v>
       </c>
@@ -14054,7 +14054,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="138" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A138" s="2" t="s">
         <v>1272</v>
       </c>
@@ -14080,7 +14080,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="139" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A139" s="2" t="s">
         <v>1103</v>
       </c>
@@ -14106,7 +14106,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="140" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A140" s="2" t="s">
         <v>828</v>
       </c>
@@ -14132,7 +14132,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="141" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A141" s="2" t="s">
         <v>1919</v>
       </c>
@@ -14158,7 +14158,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="142" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A142" s="2" t="s">
         <v>1303</v>
       </c>
@@ -14184,7 +14184,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="143" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A143" s="2" t="s">
         <v>2340</v>
       </c>
@@ -14210,7 +14210,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="144" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A144" s="2" t="s">
         <v>2315</v>
       </c>
@@ -14236,7 +14236,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="145" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A145" s="2" t="s">
         <v>622</v>
       </c>
@@ -14262,7 +14262,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="146" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A146" s="2" t="s">
         <v>1388</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="147" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A147" s="2" t="s">
         <v>134</v>
       </c>
@@ -14314,7 +14314,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="148" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A148" s="2" t="s">
         <v>1538</v>
       </c>
@@ -14340,7 +14340,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="149" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A149" s="2" t="s">
         <v>690</v>
       </c>
@@ -14366,7 +14366,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="150" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A150" s="2" t="s">
         <v>1053</v>
       </c>
@@ -14392,7 +14392,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="151" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A151" s="2" t="s">
         <v>398</v>
       </c>
@@ -14418,7 +14418,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="152" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A152" s="2" t="s">
         <v>694</v>
       </c>
@@ -14444,7 +14444,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="153" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A153" s="2" t="s">
         <v>1649</v>
       </c>
@@ -14488,21 +14488,21 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{47A56977-BF1C-4909-8B1B-32F3873FBB32}">
   <dimension ref="A1:J45"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.58203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="78.83203125" customWidth="1"/>
+    <col min="2" max="2" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="78.875" customWidth="1"/>
     <col min="5" max="5" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="17.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="17.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -14534,7 +14534,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>51</v>
       </c>
@@ -14560,7 +14560,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>681</v>
       </c>
@@ -14586,7 +14586,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>757</v>
       </c>
@@ -14612,7 +14612,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>759</v>
       </c>
@@ -14638,7 +14638,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>780</v>
       </c>
@@ -14664,7 +14664,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>866</v>
       </c>
@@ -14690,7 +14690,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>973</v>
       </c>
@@ -14716,7 +14716,7 @@
         <v>978</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1035</v>
       </c>
@@ -14742,7 +14742,7 @@
         <v>1037</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1045</v>
       </c>
@@ -14768,7 +14768,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1425</v>
       </c>
@@ -14794,7 +14794,7 @@
         <v>1940</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1608</v>
       </c>
@@ -14820,7 +14820,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1731</v>
       </c>
@@ -14837,16 +14837,16 @@
         <v>1735</v>
       </c>
       <c r="F13" t="s">
+        <v>2464</v>
+      </c>
+      <c r="G13" t="s">
         <v>2465</v>
-      </c>
-      <c r="G13" t="s">
-        <v>2466</v>
       </c>
       <c r="I13" t="s">
         <v>1733</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1894</v>
       </c>
@@ -14872,7 +14872,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1897</v>
       </c>
@@ -14898,7 +14898,7 @@
         <v>684</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1900</v>
       </c>
@@ -14924,7 +14924,7 @@
         <v>1901</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>2212</v>
       </c>
@@ -14950,7 +14950,7 @@
         <v>2213</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>65</v>
       </c>
@@ -14976,7 +14976,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>392</v>
       </c>
@@ -15002,7 +15002,7 @@
         <v>391</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>421</v>
       </c>
@@ -15028,7 +15028,7 @@
         <v>424</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>442</v>
       </c>
@@ -15054,7 +15054,7 @@
         <v>440</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>461</v>
       </c>
@@ -15080,7 +15080,7 @@
         <v>459</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>671</v>
       </c>
@@ -15106,7 +15106,7 @@
         <v>670</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>799</v>
       </c>
@@ -15132,7 +15132,7 @@
         <v>825</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>834</v>
       </c>
@@ -15158,7 +15158,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>1198</v>
       </c>
@@ -15187,7 +15187,7 @@
         <v>1075</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>1323</v>
       </c>
@@ -15213,7 +15213,7 @@
         <v>1199</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>1379</v>
       </c>
@@ -15239,7 +15239,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>1609</v>
       </c>
@@ -15265,7 +15265,7 @@
         <v>1377</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>1601</v>
       </c>
@@ -15291,7 +15291,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1926</v>
       </c>
@@ -15317,7 +15317,7 @@
         <v>1908</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>2128</v>
       </c>
@@ -15343,7 +15343,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>2226</v>
       </c>
@@ -15369,7 +15369,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>2306</v>
       </c>
@@ -15395,7 +15395,7 @@
         <v>2307</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1660</v>
       </c>
@@ -15421,7 +15421,7 @@
         <v>1661</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>2183</v>
       </c>
@@ -15447,50 +15447,50 @@
         <v>2188</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
-        <v>2468</v>
+        <v>2467</v>
       </c>
       <c r="B37" t="s">
         <v>64</v>
       </c>
       <c r="C37" t="s">
+        <v>2469</v>
+      </c>
+      <c r="D37" t="s">
+        <v>2468</v>
+      </c>
+      <c r="E37" t="s">
         <v>2470</v>
       </c>
-      <c r="D37" t="s">
+      <c r="F37" t="s">
         <v>2469</v>
       </c>
-      <c r="E37" t="s">
-        <v>2471</v>
-      </c>
-      <c r="F37" t="s">
-        <v>2470</v>
-      </c>
       <c r="G37" t="s">
-        <v>2472</v>
+        <v>2569</v>
       </c>
       <c r="I37" t="s">
-        <v>2518</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2516</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="B38" t="s">
         <v>388</v>
       </c>
       <c r="C38" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="D38" t="s">
-        <v>2532</v>
+        <v>2530</v>
       </c>
       <c r="E38" t="s">
         <v>2186</v>
       </c>
       <c r="F38" t="s">
-        <v>2533</v>
+        <v>2531</v>
       </c>
       <c r="G38" t="s">
         <v>2230</v>
@@ -15499,7 +15499,7 @@
         <v>2231</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>721</v>
       </c>
@@ -15525,7 +15525,7 @@
         <v>720</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>1619</v>
       </c>
@@ -15551,33 +15551,33 @@
         <v>1310</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
-        <v>2496</v>
+        <v>2494</v>
       </c>
       <c r="B41" t="s">
         <v>716</v>
       </c>
       <c r="C41" t="s">
-        <v>2497</v>
+        <v>2495</v>
       </c>
       <c r="D41" t="s">
-        <v>2498</v>
+        <v>2496</v>
       </c>
       <c r="E41" t="s">
         <v>513</v>
       </c>
       <c r="F41" t="s">
-        <v>2499</v>
+        <v>2497</v>
       </c>
       <c r="G41" t="s">
         <v>63</v>
       </c>
       <c r="I41" t="s">
-        <v>2499</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2497</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>1643</v>
       </c>
@@ -15603,7 +15603,7 @@
         <v>1644</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>2249</v>
       </c>
@@ -15629,7 +15629,7 @@
         <v>2251</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>2368</v>
       </c>
@@ -15655,7 +15655,7 @@
         <v>2372</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>2379</v>
       </c>
@@ -15699,20 +15699,20 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013733C5-3D86-4F9A-8E9B-0FC55B649E0F}">
   <dimension ref="A1:J10"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="91.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.375" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="91.375" customWidth="1"/>
+    <col min="5" max="5" width="11.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -15744,7 +15744,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>108</v>
       </c>
@@ -15770,7 +15770,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>2385</v>
       </c>
@@ -15796,7 +15796,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>2412</v>
       </c>
@@ -15822,7 +15822,7 @@
         <v>2388</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>125</v>
       </c>
@@ -15848,7 +15848,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1355</v>
       </c>
@@ -15874,7 +15874,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1356</v>
       </c>
@@ -15900,7 +15900,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>2019</v>
       </c>
@@ -15926,7 +15926,7 @@
         <v>1260</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1600</v>
       </c>
@@ -15952,24 +15952,24 @@
         <v>1598</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
-        <v>2534</v>
+        <v>2532</v>
       </c>
       <c r="B10" t="s">
         <v>1594</v>
       </c>
       <c r="C10" t="s">
+        <v>2533</v>
+      </c>
+      <c r="D10" t="s">
         <v>2535</v>
       </c>
-      <c r="D10" t="s">
-        <v>2537</v>
-      </c>
       <c r="E10" t="s">
+        <v>2534</v>
+      </c>
+      <c r="F10" t="s">
         <v>2536</v>
-      </c>
-      <c r="F10" t="s">
-        <v>2538</v>
       </c>
       <c r="G10" t="s">
         <v>129</v>
@@ -15990,20 +15990,20 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
   <dimension ref="A1:J19"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="10.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="40.75" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="18.58203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16035,7 +16035,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1743</v>
       </c>
@@ -16064,7 +16064,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>344</v>
       </c>
@@ -16093,7 +16093,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1562</v>
       </c>
@@ -16122,7 +16122,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>381</v>
       </c>
@@ -16151,7 +16151,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>881</v>
       </c>
@@ -16180,7 +16180,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1216</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1742</v>
       </c>
@@ -16238,7 +16238,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1508</v>
       </c>
@@ -16267,7 +16267,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1748</v>
       </c>
@@ -16296,7 +16296,7 @@
         <v>346</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1984</v>
       </c>
@@ -16325,7 +16325,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1961</v>
       </c>
@@ -16354,7 +16354,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1963</v>
       </c>
@@ -16383,7 +16383,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1744</v>
       </c>
@@ -16412,7 +16412,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1745</v>
       </c>
@@ -16441,7 +16441,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1746</v>
       </c>
@@ -16470,7 +16470,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1747</v>
       </c>
@@ -16499,7 +16499,7 @@
         <v>1222</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2177</v>
       </c>
@@ -16528,7 +16528,7 @@
         <v>380</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>2193</v>
       </c>
@@ -16573,19 +16573,19 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9CC4AD67-C776-4093-88E2-79BBC414D956}">
   <dimension ref="A1:J43"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="19" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="118" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="25.25" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="23.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="27.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>181</v>
       </c>
@@ -16643,7 +16643,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>386</v>
       </c>
@@ -16666,10 +16666,10 @@
         <v>387</v>
       </c>
       <c r="I3" t="s">
-        <v>2529</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>656</v>
       </c>
@@ -16695,7 +16695,7 @@
         <v>658</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>984</v>
       </c>
@@ -16721,7 +16721,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1003</v>
       </c>
@@ -16747,7 +16747,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1007</v>
       </c>
@@ -16773,7 +16773,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1399</v>
       </c>
@@ -16799,7 +16799,7 @@
         <v>1405</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1513</v>
       </c>
@@ -16825,7 +16825,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1514</v>
       </c>
@@ -16851,7 +16851,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1753</v>
       </c>
@@ -16877,7 +16877,7 @@
         <v>1006</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1754</v>
       </c>
@@ -16903,7 +16903,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2207</v>
       </c>
@@ -16929,33 +16929,33 @@
         <v>658</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
-        <v>2524</v>
+        <v>2522</v>
       </c>
       <c r="B14" t="s">
         <v>382</v>
       </c>
       <c r="C14" t="s">
+        <v>2523</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2524</v>
+      </c>
+      <c r="E14" t="s">
         <v>2525</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>2526</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2527</v>
-      </c>
-      <c r="F14" t="s">
-        <v>2528</v>
       </c>
       <c r="G14" t="s">
         <v>989</v>
       </c>
       <c r="I14" t="s">
-        <v>2529</v>
-      </c>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+        <v>2527</v>
+      </c>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>593</v>
       </c>
@@ -16981,7 +16981,7 @@
         <v>594</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>840</v>
       </c>
@@ -17007,7 +17007,7 @@
         <v>841</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1634</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>299</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1635</v>
       </c>
@@ -17059,7 +17059,7 @@
         <v>434</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1636</v>
       </c>
@@ -17085,33 +17085,33 @@
         <v>1329</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="B20" t="s">
         <v>433</v>
       </c>
       <c r="C20" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="E20" t="s">
         <v>844</v>
       </c>
       <c r="F20" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="G20" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="I20" t="s">
-        <v>2563</v>
-      </c>
-    </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2561</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1637</v>
       </c>
@@ -17137,7 +17137,7 @@
         <v>930</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>1638</v>
       </c>
@@ -17163,7 +17163,7 @@
         <v>932</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>457</v>
       </c>
@@ -17189,7 +17189,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>562</v>
       </c>
@@ -17215,7 +17215,7 @@
         <v>559</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>566</v>
       </c>
@@ -17241,7 +17241,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>726</v>
       </c>
@@ -17267,7 +17267,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>729</v>
       </c>
@@ -17293,7 +17293,7 @@
         <v>563</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>733</v>
       </c>
@@ -17319,7 +17319,7 @@
         <v>734</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>738</v>
       </c>
@@ -17345,7 +17345,7 @@
         <v>737</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>913</v>
       </c>
@@ -17371,7 +17371,7 @@
         <v>914</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1639</v>
       </c>
@@ -17397,7 +17397,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>2065</v>
       </c>
@@ -17423,7 +17423,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>2069</v>
       </c>
@@ -17449,7 +17449,7 @@
         <v>2068</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>2072</v>
       </c>
@@ -17475,7 +17475,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>2254</v>
       </c>
@@ -17501,7 +17501,7 @@
         <v>2258</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>1760</v>
       </c>
@@ -17530,7 +17530,7 @@
         <v>1766</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1761</v>
       </c>
@@ -17559,7 +17559,7 @@
         <v>1767</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1775</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>1776</v>
       </c>
@@ -17611,7 +17611,7 @@
         <v>1779</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>1786</v>
       </c>
@@ -17637,7 +17637,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>1870</v>
       </c>
@@ -17663,7 +17663,7 @@
         <v>1789</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>2440</v>
       </c>
@@ -17689,30 +17689,30 @@
         <v>2443</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
+        <v>2461</v>
+      </c>
+      <c r="B43" t="s">
+        <v>2460</v>
+      </c>
+      <c r="C43" t="s">
         <v>2462</v>
       </c>
-      <c r="B43" t="s">
-        <v>2461</v>
-      </c>
-      <c r="C43" t="s">
+      <c r="D43" t="s">
         <v>2463</v>
       </c>
-      <c r="D43" t="s">
-        <v>2464</v>
-      </c>
       <c r="E43" t="s">
-        <v>2467</v>
+        <v>2466</v>
       </c>
       <c r="F43" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
       <c r="G43" t="s">
-        <v>2466</v>
+        <v>2465</v>
       </c>
       <c r="I43" t="s">
-        <v>2463</v>
+        <v>2462</v>
       </c>
     </row>
   </sheetData>
@@ -17733,14 +17733,14 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0D00-000000000000}">
   <dimension ref="A1:B1"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.2">
       <c r="A1" s="8" t="s">
-        <v>2477</v>
+        <v>2475</v>
       </c>
       <c r="B1" s="8" t="s">
-        <v>2478</v>
+        <v>2476</v>
       </c>
     </row>
   </sheetData>
@@ -17752,20 +17752,20 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CB78C2-2208-4DF0-8ABB-0CE48BD26296}">
   <dimension ref="A1:J76"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="11" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="36.83203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="36.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.58203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -17797,7 +17797,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>1876</v>
       </c>
@@ -17823,7 +17823,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>1811</v>
       </c>
@@ -17849,7 +17849,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1737</v>
       </c>
@@ -17875,7 +17875,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1820</v>
       </c>
@@ -17901,7 +17901,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1833</v>
       </c>
@@ -17927,7 +17927,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1834</v>
       </c>
@@ -17953,7 +17953,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1805</v>
       </c>
@@ -17979,7 +17979,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1845</v>
       </c>
@@ -18005,7 +18005,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1806</v>
       </c>
@@ -18031,7 +18031,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>2050</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1860</v>
       </c>
@@ -18083,7 +18083,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2046</v>
       </c>
@@ -18109,7 +18109,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>2041</v>
       </c>
@@ -18135,7 +18135,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1632</v>
       </c>
@@ -18161,7 +18161,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1631</v>
       </c>
@@ -18187,7 +18187,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1812</v>
       </c>
@@ -18213,7 +18213,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2015</v>
       </c>
@@ -18239,7 +18239,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>28</v>
       </c>
@@ -18265,7 +18265,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1856</v>
       </c>
@@ -18291,7 +18291,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>2334</v>
       </c>
@@ -18317,7 +18317,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>174</v>
       </c>
@@ -18343,7 +18343,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>653</v>
       </c>
@@ -18369,7 +18369,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1985</v>
       </c>
@@ -18395,7 +18395,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>2076</v>
       </c>
@@ -18421,33 +18421,33 @@
         <v>20</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
-        <v>2492</v>
+        <v>2490</v>
       </c>
       <c r="B26" t="s">
         <v>17</v>
       </c>
       <c r="C26" t="s">
-        <v>2491</v>
+        <v>2489</v>
       </c>
       <c r="D26" t="s">
-        <v>2495</v>
+        <v>2493</v>
       </c>
       <c r="E26" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F26" t="s">
-        <v>2493</v>
+        <v>2491</v>
       </c>
       <c r="G26" t="s">
-        <v>2494</v>
+        <v>2492</v>
       </c>
       <c r="I26" t="s">
         <v>20</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2330</v>
       </c>
@@ -18473,7 +18473,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>1264</v>
       </c>
@@ -18499,7 +18499,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>2300</v>
       </c>
@@ -18525,7 +18525,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>72</v>
       </c>
@@ -18551,7 +18551,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>327</v>
       </c>
@@ -18577,7 +18577,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>194</v>
       </c>
@@ -18603,7 +18603,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>1483</v>
       </c>
@@ -18629,7 +18629,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1484</v>
       </c>
@@ -18655,7 +18655,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1867</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>2220</v>
       </c>
@@ -18707,7 +18707,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>205</v>
       </c>
@@ -18733,7 +18733,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>810</v>
       </c>
@@ -18759,7 +18759,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>2232</v>
       </c>
@@ -18785,7 +18785,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>815</v>
       </c>
@@ -18814,7 +18814,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>1120</v>
       </c>
@@ -18843,7 +18843,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>2027</v>
       </c>
@@ -18872,7 +18872,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>1250</v>
       </c>
@@ -18898,7 +18898,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>349</v>
       </c>
@@ -18924,7 +18924,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>2038</v>
       </c>
@@ -18950,7 +18950,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>417</v>
       </c>
@@ -18976,7 +18976,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>887</v>
       </c>
@@ -19002,7 +19002,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>197</v>
       </c>
@@ -19028,7 +19028,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
         <v>1091</v>
       </c>
@@ -19054,7 +19054,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>167</v>
       </c>
@@ -19080,7 +19080,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>1487</v>
       </c>
@@ -19106,7 +19106,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>1130</v>
       </c>
@@ -19132,7 +19132,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>1385</v>
       </c>
@@ -19158,7 +19158,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>170</v>
       </c>
@@ -19184,7 +19184,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>1591</v>
       </c>
@@ -19210,7 +19210,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>1905</v>
       </c>
@@ -19236,7 +19236,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>121</v>
       </c>
@@ -19262,7 +19262,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>1117</v>
       </c>
@@ -19288,7 +19288,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>1434</v>
       </c>
@@ -19314,7 +19314,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>2219</v>
       </c>
@@ -19340,7 +19340,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>2223</v>
       </c>
@@ -19366,7 +19366,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>1149</v>
       </c>
@@ -19395,7 +19395,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>2023</v>
       </c>
@@ -19421,7 +19421,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>2031</v>
       </c>
@@ -19450,7 +19450,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>161</v>
       </c>
@@ -19476,7 +19476,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>979</v>
       </c>
@@ -19502,7 +19502,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>2239</v>
       </c>
@@ -19528,7 +19528,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>1144</v>
       </c>
@@ -19557,7 +19557,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="69" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A69" s="2" t="s">
         <v>58</v>
       </c>
@@ -19583,7 +19583,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="70" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A70" s="2" t="s">
         <v>67</v>
       </c>
@@ -19609,7 +19609,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="71" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A71" s="2" t="s">
         <v>1452</v>
       </c>
@@ -19635,7 +19635,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="72" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A72" s="2" t="s">
         <v>548</v>
       </c>
@@ -19661,7 +19661,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="73" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A73" s="2" t="s">
         <v>2325</v>
       </c>
@@ -19687,7 +19687,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="74" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A74" s="2" t="s">
         <v>1110</v>
       </c>
@@ -19716,7 +19716,7 @@
         <v>818</v>
       </c>
     </row>
-    <row r="75" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B75" t="s">
         <v>17</v>
       </c>
@@ -19731,7 +19731,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:9" x14ac:dyDescent="0.2">
       <c r="B76" t="s">
         <v>17</v>
       </c>
@@ -19763,21 +19763,21 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C302E28E-61B5-45F2-9EED-9E658F066E8B}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="21.08203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="133.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="20.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="23.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="21.125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="133.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="20.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="23.625" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="23" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="22" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -19809,7 +19809,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>307</v>
       </c>
@@ -19829,7 +19829,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>306</v>
       </c>
@@ -19858,7 +19858,7 @@
         <v>308</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>311</v>
       </c>
@@ -19887,7 +19887,7 @@
         <v>312</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>634</v>
       </c>
@@ -19916,33 +19916,33 @@
         <v>637</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
-        <v>2479</v>
+        <v>2477</v>
       </c>
       <c r="B6" t="s">
         <v>305</v>
       </c>
       <c r="C6" t="s">
-        <v>2484</v>
+        <v>2482</v>
       </c>
       <c r="E6" t="s">
+        <v>2479</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2478</v>
+      </c>
+      <c r="G6" t="s">
+        <v>2480</v>
+      </c>
+      <c r="H6" t="s">
         <v>2481</v>
       </c>
-      <c r="F6" t="s">
-        <v>2480</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="I6" t="s">
         <v>2482</v>
       </c>
-      <c r="H6" t="s">
-        <v>2483</v>
-      </c>
-      <c r="I6" t="s">
-        <v>2484</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>869</v>
       </c>
@@ -19971,7 +19971,7 @@
         <v>870</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1010</v>
       </c>
@@ -20000,7 +20000,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1019</v>
       </c>
@@ -20029,7 +20029,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1067</v>
       </c>
@@ -20055,7 +20055,7 @@
         <v>1068</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1192</v>
       </c>
@@ -20084,7 +20084,7 @@
         <v>1193</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>1225</v>
       </c>
@@ -20113,7 +20113,7 @@
         <v>1224</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>1964</v>
       </c>
@@ -20142,7 +20142,7 @@
         <v>1234</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1970</v>
       </c>
@@ -20171,7 +20171,7 @@
         <v>2064</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1971</v>
       </c>
@@ -20200,30 +20200,30 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="B16" t="s">
         <v>1223</v>
       </c>
       <c r="D16" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
       <c r="E16" t="s">
         <v>1966</v>
       </c>
       <c r="F16" t="s">
-        <v>2513</v>
+        <v>2511</v>
       </c>
       <c r="G16" t="s">
-        <v>2516</v>
+        <v>2514</v>
       </c>
       <c r="I16" t="s">
-        <v>2512</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+        <v>2510</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1238</v>
       </c>
@@ -20249,7 +20249,7 @@
         <v>1294</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1465</v>
       </c>
@@ -20275,7 +20275,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1717</v>
       </c>
@@ -20301,7 +20301,7 @@
         <v>1723</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1720</v>
       </c>
@@ -20327,7 +20327,7 @@
         <v>1725</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1721</v>
       </c>
@@ -20353,7 +20353,7 @@
         <v>1726</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>2320</v>
       </c>
@@ -20392,21 +20392,21 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B4F61549-8124-4EE7-A218-E5BC471FD40D}">
   <dimension ref="A1:J5"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="9.25" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.58203125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="66.83203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.625" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="66.875" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="17.75" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="24.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.08203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="24.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20438,7 +20438,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2">
         <v>7001100000</v>
       </c>
@@ -20464,7 +20464,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>543</v>
       </c>
@@ -20487,7 +20487,7 @@
         <v>544</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1507</v>
       </c>
@@ -20513,7 +20513,7 @@
         <v>1504</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1556</v>
       </c>
@@ -20552,20 +20552,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77DF9D1-733F-4622-A5B9-9F6937E4842B}">
   <dimension ref="A1:J68"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.58203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.08203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="30.08203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="30.125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="57.5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="16.08203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="25.83203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="27.08203125" customWidth="1"/>
-    <col min="8" max="8" width="18.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="29.58203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="16.125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="25.875" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="27.125" customWidth="1"/>
+    <col min="8" max="8" width="18.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="29.625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -20597,7 +20597,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>135</v>
       </c>
@@ -20626,7 +20626,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>141</v>
       </c>
@@ -20655,7 +20655,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>93</v>
       </c>
@@ -20684,7 +20684,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>295</v>
       </c>
@@ -20713,7 +20713,7 @@
         <v>298</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>516</v>
       </c>
@@ -20742,7 +20742,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>44</v>
       </c>
@@ -20771,7 +20771,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>45</v>
       </c>
@@ -20800,7 +20800,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>199</v>
       </c>
@@ -20829,7 +20829,7 @@
         <v>478</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>569</v>
       </c>
@@ -20858,7 +20858,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>582</v>
       </c>
@@ -20887,7 +20887,7 @@
         <v>586</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>629</v>
       </c>
@@ -20916,7 +20916,7 @@
         <v>633</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>700</v>
       </c>
@@ -20945,7 +20945,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>917</v>
       </c>
@@ -20974,7 +20974,7 @@
         <v>921</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>922</v>
       </c>
@@ -21003,7 +21003,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>2283</v>
       </c>
@@ -21032,7 +21032,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>2348</v>
       </c>
@@ -21061,7 +21061,7 @@
         <v>2344</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2399</v>
       </c>
@@ -21090,36 +21090,36 @@
         <v>2403</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
-        <v>2556</v>
+        <v>2554</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>2558</v>
+        <v>2556</v>
       </c>
       <c r="D19" t="s">
-        <v>2557</v>
+        <v>2555</v>
       </c>
       <c r="E19" t="s">
         <v>864</v>
       </c>
       <c r="F19" t="s">
+        <v>2556</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2557</v>
+      </c>
+      <c r="H19" t="s">
         <v>2558</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>2559</v>
       </c>
-      <c r="H19" t="s">
-        <v>2560</v>
-      </c>
-      <c r="I19" t="s">
-        <v>2561</v>
-      </c>
-    </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>105</v>
       </c>
@@ -21148,7 +21148,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>226</v>
       </c>
@@ -21177,7 +21177,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>229</v>
       </c>
@@ -21206,7 +21206,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>238</v>
       </c>
@@ -21235,7 +21235,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>519</v>
       </c>
@@ -21264,7 +21264,7 @@
         <v>235</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>574</v>
       </c>
@@ -21293,7 +21293,7 @@
         <v>524</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>580</v>
       </c>
@@ -21322,7 +21322,7 @@
         <v>579</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>623</v>
       </c>
@@ -21351,7 +21351,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>659</v>
       </c>
@@ -21380,7 +21380,7 @@
         <v>663</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>790</v>
       </c>
@@ -21409,7 +21409,7 @@
         <v>234</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>893</v>
       </c>
@@ -21438,7 +21438,7 @@
         <v>896</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>901</v>
       </c>
@@ -21467,7 +21467,7 @@
         <v>906</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>965</v>
       </c>
@@ -21496,7 +21496,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>997</v>
       </c>
@@ -21525,7 +21525,7 @@
         <v>996</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1913</v>
       </c>
@@ -21554,7 +21554,7 @@
         <v>1916</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1933</v>
       </c>
@@ -21583,7 +21583,7 @@
         <v>1936</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>2116</v>
       </c>
@@ -21612,7 +21612,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>2121</v>
       </c>
@@ -21641,7 +21641,7 @@
         <v>2122</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>253</v>
       </c>
@@ -21670,7 +21670,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>254</v>
       </c>
@@ -21699,7 +21699,7 @@
         <v>252</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>255</v>
       </c>
@@ -21728,7 +21728,7 @@
         <v>247</v>
       </c>
     </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A41" s="2" t="s">
         <v>497</v>
       </c>
@@ -21757,7 +21757,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="42" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A42" s="2" t="s">
         <v>492</v>
       </c>
@@ -21786,7 +21786,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="43" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A43" s="2" t="s">
         <v>515</v>
       </c>
@@ -21815,7 +21815,7 @@
         <v>202</v>
       </c>
     </row>
-    <row r="44" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A44" s="2" t="s">
         <v>553</v>
       </c>
@@ -21844,7 +21844,7 @@
         <v>556</v>
       </c>
     </row>
-    <row r="45" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A45" s="2" t="s">
         <v>589</v>
       </c>
@@ -21873,7 +21873,7 @@
         <v>605</v>
       </c>
     </row>
-    <row r="46" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A46" s="2" t="s">
         <v>857</v>
       </c>
@@ -21902,7 +21902,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A47" s="2" t="s">
         <v>861</v>
       </c>
@@ -21931,7 +21931,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A48" s="2" t="s">
         <v>2429</v>
       </c>
@@ -21960,36 +21960,36 @@
         <v>247</v>
       </c>
     </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A49" s="2" t="s">
-        <v>2485</v>
+        <v>2483</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C49" t="s">
+        <v>2484</v>
+      </c>
+      <c r="D49" t="s">
+        <v>2485</v>
+      </c>
+      <c r="E49" t="s">
         <v>2486</v>
       </c>
-      <c r="D49" t="s">
+      <c r="F49" t="s">
+        <v>2484</v>
+      </c>
+      <c r="G49" t="s">
+        <v>2553</v>
+      </c>
+      <c r="H49" t="s">
         <v>2487</v>
       </c>
-      <c r="E49" t="s">
+      <c r="I49" t="s">
         <v>2488</v>
       </c>
-      <c r="F49" t="s">
-        <v>2486</v>
-      </c>
-      <c r="G49" t="s">
-        <v>2555</v>
-      </c>
-      <c r="H49" t="s">
-        <v>2489</v>
-      </c>
-      <c r="I49" t="s">
-        <v>2490</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" x14ac:dyDescent="0.3">
+    </row>
+    <row r="50" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A50" s="2" t="s">
         <v>486</v>
       </c>
@@ -22018,7 +22018,7 @@
         <v>488</v>
       </c>
     </row>
-    <row r="51" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A51" s="2" t="s">
         <v>502</v>
       </c>
@@ -22047,7 +22047,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="52" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A52" s="2" t="s">
         <v>525</v>
       </c>
@@ -22076,7 +22076,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A53" s="2" t="s">
         <v>2001</v>
       </c>
@@ -22105,7 +22105,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A54" s="2" t="s">
         <v>2373</v>
       </c>
@@ -22134,7 +22134,7 @@
         <v>530</v>
       </c>
     </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A55" s="2" t="s">
         <v>220</v>
       </c>
@@ -22163,7 +22163,7 @@
         <v>225</v>
       </c>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A56" s="2" t="s">
         <v>876</v>
       </c>
@@ -22192,7 +22192,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A57" s="2" t="s">
         <v>1296</v>
       </c>
@@ -22221,7 +22221,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A58" s="2" t="s">
         <v>2091</v>
       </c>
@@ -22250,7 +22250,7 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A59" s="2" t="s">
         <v>2100</v>
       </c>
@@ -22276,7 +22276,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="60" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A60" s="2" t="s">
         <v>2364</v>
       </c>
@@ -22302,7 +22302,7 @@
         <v>1301</v>
       </c>
     </row>
-    <row r="61" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A61" s="2" t="s">
         <v>2406</v>
       </c>
@@ -22331,7 +22331,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="62" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A62" s="2" t="s">
         <v>936</v>
       </c>
@@ -22360,7 +22360,7 @@
         <v>941</v>
       </c>
     </row>
-    <row r="63" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A63" s="2" t="s">
         <v>1242</v>
       </c>
@@ -22389,7 +22389,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="64" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A64" s="2" t="s">
         <v>1361</v>
       </c>
@@ -22418,7 +22418,7 @@
         <v>1359</v>
       </c>
     </row>
-    <row r="65" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A65" s="2" t="s">
         <v>1986</v>
       </c>
@@ -22447,7 +22447,7 @@
         <v>1822</v>
       </c>
     </row>
-    <row r="66" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A66" s="2" t="s">
         <v>2013</v>
       </c>
@@ -22476,7 +22476,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="67" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A67" s="2" t="s">
         <v>2243</v>
       </c>
@@ -22502,7 +22502,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="68" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A68" s="2" t="s">
         <v>2356</v>
       </c>
@@ -22549,19 +22549,19 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61606E71-114A-4060-B4DA-26AC2BA8C44E}">
   <dimension ref="A1:J22"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.08203125" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="17.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.5" customWidth="1"/>
-    <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.08203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="17.375" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="16.875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="17.875" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -22593,7 +22593,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>257</v>
       </c>
@@ -22622,7 +22622,7 @@
         <v>262</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>263</v>
       </c>
@@ -22651,7 +22651,7 @@
         <v>268</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>908</v>
       </c>
@@ -22680,7 +22680,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>912</v>
       </c>
@@ -22709,7 +22709,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1276</v>
       </c>
@@ -22738,7 +22738,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1406</v>
       </c>
@@ -22767,7 +22767,7 @@
         <v>1407</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1614</v>
       </c>
@@ -22796,7 +22796,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1954</v>
       </c>
@@ -22825,7 +22825,7 @@
         <v>1958</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1989</v>
       </c>
@@ -22854,7 +22854,7 @@
         <v>1993</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1996</v>
       </c>
@@ -22883,7 +22883,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>2051</v>
       </c>
@@ -22912,7 +22912,7 @@
         <v>1282</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2052</v>
       </c>
@@ -22941,7 +22941,7 @@
         <v>2056</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>2053</v>
       </c>
@@ -22967,7 +22967,7 @@
         <v>2057</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>2268</v>
       </c>
@@ -22996,7 +22996,7 @@
         <v>2272</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>2277</v>
       </c>
@@ -23025,7 +23025,7 @@
         <v>2281</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>2391</v>
       </c>
@@ -23054,7 +23054,7 @@
         <v>2396</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>2080</v>
       </c>
@@ -23080,7 +23080,7 @@
         <v>2083</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>2084</v>
       </c>
@@ -23106,24 +23106,24 @@
         <v>2087</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>2500</v>
+        <v>2498</v>
       </c>
       <c r="B20" t="s">
         <v>2079</v>
       </c>
       <c r="C20" t="s">
+        <v>2499</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>2501</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>2503</v>
-      </c>
       <c r="E20" t="s">
-        <v>2502</v>
+        <v>2500</v>
       </c>
       <c r="F20" t="s">
-        <v>2501</v>
+        <v>2499</v>
       </c>
       <c r="G20" t="s">
         <v>2411</v>
@@ -23132,33 +23132,33 @@
         <v>2096</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="B21" t="s">
         <v>2079</v>
       </c>
       <c r="C21" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="E21" t="s">
         <v>2410</v>
       </c>
       <c r="F21" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="G21" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="I21" t="s">
         <v>2083</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>2111</v>
       </c>
@@ -23197,21 +23197,21 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{05CC079E-4192-4042-9084-101DC20DC760}">
   <dimension ref="A1:J40"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="12.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="12.375" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="90.25" customWidth="1"/>
-    <col min="5" max="5" width="18.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="22.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="18.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="22.875" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.25" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="18.75" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -23243,7 +23243,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>81</v>
       </c>
@@ -23269,7 +23269,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>395</v>
       </c>
@@ -23295,7 +23295,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>612</v>
       </c>
@@ -23321,7 +23321,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>2167</v>
       </c>
@@ -23347,7 +23347,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>2166</v>
       </c>
@@ -23373,7 +23373,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>2165</v>
       </c>
@@ -23399,7 +23399,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>465</v>
       </c>
@@ -23425,7 +23425,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1391</v>
       </c>
@@ -23451,7 +23451,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>1430</v>
       </c>
@@ -23477,7 +23477,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>1443</v>
       </c>
@@ -23503,7 +23503,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>2162</v>
       </c>
@@ -23529,7 +23529,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>2189</v>
       </c>
@@ -23555,7 +23555,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>1566</v>
       </c>
@@ -23581,7 +23581,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1140</v>
       </c>
@@ -23607,7 +23607,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>668</v>
       </c>
@@ -23633,7 +23633,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1202</v>
       </c>
@@ -23659,7 +23659,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>820</v>
       </c>
@@ -23685,7 +23685,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1699</v>
       </c>
@@ -23711,9 +23711,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="B20" s="2" t="s">
         <v>78</v>
@@ -23722,13 +23722,13 @@
         <v>821</v>
       </c>
       <c r="D20" t="s">
-        <v>2540</v>
+        <v>2538</v>
       </c>
       <c r="E20" t="s">
         <v>79</v>
       </c>
       <c r="F20" t="s">
-        <v>2542</v>
+        <v>2540</v>
       </c>
       <c r="G20" t="s">
         <v>1433</v>
@@ -23737,7 +23737,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>1534</v>
       </c>
@@ -23763,7 +23763,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>1126</v>
       </c>
@@ -23789,7 +23789,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>1478</v>
       </c>
@@ -23815,7 +23815,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>1987</v>
       </c>
@@ -23841,7 +23841,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>1137</v>
       </c>
@@ -23867,7 +23867,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>2143</v>
       </c>
@@ -23893,7 +23893,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>2141</v>
       </c>
@@ -23910,7 +23910,7 @@
         <v>79</v>
       </c>
       <c r="F27" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="G27" t="s">
         <v>1433</v>
@@ -23919,7 +23919,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>2147</v>
       </c>
@@ -23945,7 +23945,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>2151</v>
       </c>
@@ -23971,9 +23971,9 @@
         <v>76</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
-        <v>2473</v>
+        <v>2471</v>
       </c>
       <c r="B30" s="2" t="s">
         <v>78</v>
@@ -23982,13 +23982,13 @@
         <v>2140</v>
       </c>
       <c r="D30" t="s">
+        <v>2472</v>
+      </c>
+      <c r="E30" t="s">
+        <v>2473</v>
+      </c>
+      <c r="F30" t="s">
         <v>2474</v>
-      </c>
-      <c r="E30" t="s">
-        <v>2475</v>
-      </c>
-      <c r="F30" t="s">
-        <v>2476</v>
       </c>
       <c r="G30" t="s">
         <v>1701</v>
@@ -23997,7 +23997,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1421</v>
       </c>
@@ -24023,7 +24023,7 @@
         <v>1420</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>2105</v>
       </c>
@@ -24049,7 +24049,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>2260</v>
       </c>
@@ -24075,7 +24075,7 @@
         <v>2109</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1798</v>
       </c>
@@ -24101,7 +24101,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>1799</v>
       </c>
@@ -24127,7 +24127,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
         <v>1829</v>
       </c>
@@ -24153,7 +24153,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A37" s="2" t="s">
         <v>1866</v>
       </c>
@@ -24179,7 +24179,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="38" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A38" s="2" t="s">
         <v>1873</v>
       </c>
@@ -24205,7 +24205,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="39" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A39" s="2" t="s">
         <v>1881</v>
       </c>
@@ -24231,7 +24231,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A40" s="2" t="s">
         <v>2447</v>
       </c>
@@ -24245,13 +24245,13 @@
         <v>2446</v>
       </c>
       <c r="E40" t="s">
+        <v>2449</v>
+      </c>
+      <c r="F40" t="s">
         <v>2450</v>
       </c>
-      <c r="F40" t="s">
-        <v>2451</v>
-      </c>
       <c r="G40" t="s">
-        <v>2449</v>
+        <v>2570</v>
       </c>
       <c r="I40" t="s">
         <v>2448</v>
@@ -24270,21 +24270,21 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DF0F2426-BE64-4140-89D3-828BC4EE93FD}">
   <dimension ref="A1:J14"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
-    <col min="1" max="1" width="11.83203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="11.875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.875" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="5.75" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="48.08203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.58203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="20.08203125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="48.125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="20.125" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.58203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="13.58203125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="9.625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="13.625" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24316,7 +24316,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>191</v>
       </c>
@@ -24342,7 +24342,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>648</v>
       </c>
@@ -24368,7 +24368,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1174</v>
       </c>
@@ -24394,7 +24394,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1182</v>
       </c>
@@ -24420,7 +24420,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>649</v>
       </c>
@@ -24446,7 +24446,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>1176</v>
       </c>
@@ -24472,7 +24472,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1186</v>
       </c>
@@ -24498,7 +24498,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>1981</v>
       </c>
@@ -24524,7 +24524,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>2289</v>
       </c>
@@ -24550,7 +24550,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>650</v>
       </c>
@@ -24576,7 +24576,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>949</v>
       </c>
@@ -24602,7 +24602,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>995</v>
       </c>
@@ -24628,7 +24628,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>1241700000</v>
       </c>
@@ -24667,19 +24667,19 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F28B83C-EC15-4DE5-B23D-95C2173BD368}">
   <dimension ref="A1:J36"/>
-  <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="13" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="20" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="101.83203125" customWidth="1"/>
+    <col min="4" max="4" width="101.875" customWidth="1"/>
     <col min="5" max="5" width="17.5" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="24.5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.875" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="21.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -24711,7 +24711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A2" s="2" t="s">
         <v>88</v>
       </c>
@@ -24737,7 +24737,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A3" s="2" t="s">
         <v>119</v>
       </c>
@@ -24763,7 +24763,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A4" s="2" t="s">
         <v>1493</v>
       </c>
@@ -24789,7 +24789,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A5" s="2" t="s">
         <v>1551</v>
       </c>
@@ -24815,7 +24815,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A6" s="2" t="s">
         <v>1570</v>
       </c>
@@ -24841,7 +24841,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A7" s="2" t="s">
         <v>769</v>
       </c>
@@ -24867,7 +24867,7 @@
         <v>763</v>
       </c>
     </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A8" s="2" t="s">
         <v>1953</v>
       </c>
@@ -24893,7 +24893,7 @@
         <v>1947</v>
       </c>
     </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A9" s="2" t="s">
         <v>533</v>
       </c>
@@ -24922,7 +24922,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A10" s="2" t="s">
         <v>743</v>
       </c>
@@ -24948,7 +24948,7 @@
         <v>615</v>
       </c>
     </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A11" s="2" t="s">
         <v>742</v>
       </c>
@@ -24974,7 +24974,7 @@
         <v>746</v>
       </c>
     </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A12" s="2" t="s">
         <v>750</v>
       </c>
@@ -25000,7 +25000,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A13" s="2" t="s">
         <v>751</v>
       </c>
@@ -25026,7 +25026,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A14" s="2" t="s">
         <v>755</v>
       </c>
@@ -25052,7 +25052,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A15" s="2" t="s">
         <v>1344</v>
       </c>
@@ -25078,7 +25078,7 @@
         <v>1349</v>
       </c>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.2">
       <c r="A16" s="2" t="s">
         <v>1366</v>
       </c>
@@ -25104,7 +25104,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="17" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A17" s="2" t="s">
         <v>1367</v>
       </c>
@@ -25130,7 +25130,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="18" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A18" s="2" t="s">
         <v>1372</v>
       </c>
@@ -25156,7 +25156,7 @@
         <v>531</v>
       </c>
     </row>
-    <row r="19" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A19" s="2" t="s">
         <v>1499</v>
       </c>
@@ -25182,7 +25182,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A20" s="2" t="s">
         <v>1941</v>
       </c>
@@ -25208,7 +25208,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A21" s="2" t="s">
         <v>2416</v>
       </c>
@@ -25234,7 +25234,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A22" s="2" t="s">
         <v>2424</v>
       </c>
@@ -25254,7 +25254,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A23" s="2" t="s">
         <v>2425</v>
       </c>
@@ -25274,7 +25274,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A24" s="2" t="s">
         <v>2426</v>
       </c>
@@ -25294,7 +25294,7 @@
         <v>741</v>
       </c>
     </row>
-    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A25" s="2" t="s">
         <v>212</v>
       </c>
@@ -25320,7 +25320,7 @@
         <v>206</v>
       </c>
     </row>
-    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A26" s="2" t="s">
         <v>216</v>
       </c>
@@ -25346,7 +25346,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="27" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A27" s="2" t="s">
         <v>599</v>
       </c>
@@ -25372,7 +25372,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="28" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A28" s="2" t="s">
         <v>770</v>
       </c>
@@ -25398,7 +25398,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="29" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A29" s="2" t="s">
         <v>846</v>
       </c>
@@ -25424,7 +25424,7 @@
         <v>604</v>
       </c>
     </row>
-    <row r="30" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A30" s="2" t="s">
         <v>850</v>
       </c>
@@ -25450,7 +25450,7 @@
         <v>851</v>
       </c>
     </row>
-    <row r="31" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A31" s="2" t="s">
         <v>1060</v>
       </c>
@@ -25476,7 +25476,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="32" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A32" s="2" t="s">
         <v>1412</v>
       </c>
@@ -25502,7 +25502,7 @@
         <v>1414</v>
       </c>
     </row>
-    <row r="33" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A33" s="2" t="s">
         <v>1694</v>
       </c>
@@ -25528,7 +25528,7 @@
         <v>1697</v>
       </c>
     </row>
-    <row r="34" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A34" s="2" t="s">
         <v>1714</v>
       </c>
@@ -25554,7 +25554,7 @@
         <v>1061</v>
       </c>
     </row>
-    <row r="35" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A35" s="2" t="s">
         <v>2293</v>
       </c>
@@ -25580,27 +25580,27 @@
         <v>604</v>
       </c>
     </row>
-    <row r="36" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" x14ac:dyDescent="0.2">
       <c r="A36" s="2" t="s">
-        <v>2453</v>
+        <v>2452</v>
       </c>
       <c r="B36" t="s">
         <v>207</v>
       </c>
       <c r="C36" t="s">
-        <v>2452</v>
+        <v>2451</v>
       </c>
       <c r="D36" t="s">
+        <v>2453</v>
+      </c>
+      <c r="E36" t="s">
+        <v>2455</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2451</v>
+      </c>
+      <c r="G36" t="s">
         <v>2454</v>
-      </c>
-      <c r="E36" t="s">
-        <v>2456</v>
-      </c>
-      <c r="F36" t="s">
-        <v>2452</v>
-      </c>
-      <c r="G36" t="s">
-        <v>2455</v>
       </c>
       <c r="I36" t="s">
         <v>206</v>

--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B22F9FC1-03B5-4F17-96ED-3F0C41E4B4C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713A11F7-5C34-4EFB-9BE5-30F72B946BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">贴片电容!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">贴片电阻!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">贴片结构料!$A$1:$J$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11">振荡晶体!$A$1:$J$17</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11">振荡晶体!$A$1:$J$19</definedName>
     <definedName name="TMPPRTS">TMPPRTS!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4607" uniqueCount="2603">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="2619">
   <si>
     <t>Part Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9609,10 +9609,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>µPD720201K8-701-BAC-A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>瑞萨</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -10103,6 +10099,73 @@
   </si>
   <si>
     <t>金瑞电子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>31.6K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111316200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;31.6KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0731K6L</t>
+  </si>
+  <si>
+    <t>2041025004</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HC-49S-SMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>X49SM25MSD2SC</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystal;25MHZ;20pF;+/-10PPM;HC-49S-SMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CRYSTAL-2PIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041024002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystal;24MHZ;12pF;+/-10PPM;HC-49S-SMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6611600021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>强赛鑫电子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09.03.12.002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>uPD720201K8-701-BAC-A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCI-E 3.0 To USB 3.0; supports up to four USB3.0 SuperSpeed ports; QFN-68-8x8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RTL8153B</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10606,7 +10669,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J156"/>
+  <dimension ref="A1:J157"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" style="2" bestFit="1" customWidth="1"/>
@@ -10996,7 +11059,7 @@
         <v>892</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2515</v>
+        <v>2514</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>891</v>
@@ -11452,22 +11515,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>2590</v>
+        <v>2589</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2589</v>
+        <v>2588</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2588</v>
+        <v>2587</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2587</v>
+        <v>2586</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>19</v>
@@ -11478,25 +11541,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>2518</v>
+        <v>2517</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
-        <v>2517</v>
+        <v>2516</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>2519</v>
+        <v>2518</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
+        <v>2519</v>
+      </c>
+      <c r="G34" s="1" t="s">
         <v>2520</v>
-      </c>
-      <c r="G34" s="1" t="s">
-        <v>2521</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>339</v>
@@ -11894,22 +11957,22 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>2503</v>
+        <v>2502</v>
       </c>
       <c r="B50" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C50" s="1" t="s">
+        <v>2503</v>
+      </c>
+      <c r="D50" s="1" t="s">
         <v>2504</v>
-      </c>
-      <c r="D50" s="1" t="s">
-        <v>2505</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F50" s="1" t="s">
-        <v>2502</v>
+        <v>2501</v>
       </c>
       <c r="G50" t="s">
         <v>91</v>
@@ -11920,22 +11983,22 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>2509</v>
+        <v>2508</v>
       </c>
       <c r="B51" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C51" s="1" t="s">
+        <v>2506</v>
+      </c>
+      <c r="D51" s="1" t="s">
         <v>2507</v>
-      </c>
-      <c r="D51" s="1" t="s">
-        <v>2508</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F51" s="1" t="s">
-        <v>2506</v>
+        <v>2505</v>
       </c>
       <c r="G51" t="s">
         <v>91</v>
@@ -12284,22 +12347,22 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>2550</v>
+        <v>2549</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="1" t="s">
-        <v>2549</v>
+        <v>2548</v>
       </c>
       <c r="D65" s="1" t="s">
-        <v>2551</v>
+        <v>2550</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>2552</v>
+        <v>2551</v>
       </c>
       <c r="G65" t="s">
         <v>91</v>
@@ -12830,22 +12893,22 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>2542</v>
+        <v>2541</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="1" t="s">
-        <v>2541</v>
+        <v>2540</v>
       </c>
       <c r="D86" s="1" t="s">
-        <v>2543</v>
+        <v>2542</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>2544</v>
+        <v>2543</v>
       </c>
       <c r="G86" t="s">
         <v>19</v>
@@ -12882,22 +12945,22 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>1691</v>
+        <v>2603</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="1" t="s">
-        <v>1382</v>
+        <v>2602</v>
       </c>
       <c r="D88" s="1" t="s">
-        <v>1383</v>
+        <v>2604</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>1384</v>
+        <v>2605</v>
       </c>
       <c r="G88" t="s">
         <v>19</v>
@@ -12908,22 +12971,22 @@
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A89" s="2" t="s">
-        <v>789</v>
+        <v>1691</v>
       </c>
       <c r="B89" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C89" s="1" t="s">
-        <v>787</v>
+        <v>1382</v>
       </c>
       <c r="D89" s="1" t="s">
-        <v>788</v>
+        <v>1383</v>
       </c>
       <c r="E89" s="1" t="s">
-        <v>777</v>
+        <v>12</v>
       </c>
       <c r="F89" s="1" t="s">
-        <v>786</v>
+        <v>1384</v>
       </c>
       <c r="G89" t="s">
         <v>19</v>
@@ -12934,7 +12997,7 @@
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A90" s="2" t="s">
-        <v>1932</v>
+        <v>789</v>
       </c>
       <c r="B90" s="1" t="s">
         <v>10</v>
@@ -12943,16 +13006,16 @@
         <v>787</v>
       </c>
       <c r="D90" s="1" t="s">
-        <v>1931</v>
+        <v>788</v>
       </c>
       <c r="E90" s="1" t="s">
-        <v>12</v>
+        <v>777</v>
       </c>
       <c r="F90" s="1" t="s">
-        <v>1930</v>
+        <v>786</v>
       </c>
       <c r="G90" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I90" s="1" t="s">
         <v>339</v>
@@ -12960,24 +13023,24 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>1892</v>
+        <v>1932</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>1890</v>
+        <v>787</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>1893</v>
+        <v>1931</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>1891</v>
-      </c>
-      <c r="G91" s="1" t="s">
+        <v>1930</v>
+      </c>
+      <c r="G91" t="s">
         <v>332</v>
       </c>
       <c r="I91" s="1" t="s">
@@ -12986,7 +13049,7 @@
     </row>
     <row r="92" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A92" s="2" t="s">
-        <v>1927</v>
+        <v>1892</v>
       </c>
       <c r="B92" s="1" t="s">
         <v>10</v>
@@ -12995,16 +13058,16 @@
         <v>1890</v>
       </c>
       <c r="D92" s="1" t="s">
-        <v>1928</v>
+        <v>1893</v>
       </c>
       <c r="E92" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F92" s="1" t="s">
-        <v>1929</v>
+        <v>1891</v>
       </c>
       <c r="G92" s="1" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I92" s="1" t="s">
         <v>339</v>
@@ -13012,22 +13075,22 @@
     </row>
     <row r="93" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A93" s="2" t="s">
-        <v>2581</v>
+        <v>1927</v>
       </c>
       <c r="B93" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C93" s="1" t="s">
-        <v>2580</v>
+        <v>1890</v>
       </c>
       <c r="D93" s="1" t="s">
-        <v>2582</v>
+        <v>1928</v>
       </c>
       <c r="E93" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F93" s="1" t="s">
-        <v>2583</v>
+        <v>1929</v>
       </c>
       <c r="G93" s="1" t="s">
         <v>19</v>
@@ -13038,24 +13101,24 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>1709</v>
+        <v>2580</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>1707</v>
+        <v>2579</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>1708</v>
+        <v>2581</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>1710</v>
-      </c>
-      <c r="G94" t="s">
+        <v>2582</v>
+      </c>
+      <c r="G94" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I94" s="1" t="s">
@@ -13064,25 +13127,25 @@
     </row>
     <row r="95" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A95" s="2" t="s">
-        <v>1521</v>
+        <v>1709</v>
       </c>
       <c r="B95" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C95" s="1" t="s">
-        <v>1520</v>
+        <v>1707</v>
       </c>
       <c r="D95" s="1" t="s">
-        <v>1522</v>
+        <v>1708</v>
       </c>
       <c r="E95" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F95" s="1" t="s">
-        <v>1519</v>
+        <v>1710</v>
       </c>
       <c r="G95" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I95" s="1" t="s">
         <v>339</v>
@@ -13090,25 +13153,25 @@
     </row>
     <row r="96" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A96" s="2" t="s">
-        <v>130</v>
+        <v>1521</v>
       </c>
       <c r="B96" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C96" s="1" t="s">
-        <v>272</v>
+        <v>1520</v>
       </c>
       <c r="D96" s="1" t="s">
-        <v>832</v>
+        <v>1522</v>
       </c>
       <c r="E96" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F96" s="1" t="s">
-        <v>699</v>
+        <v>1519</v>
       </c>
       <c r="G96" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I96" s="1" t="s">
         <v>339</v>
@@ -13116,7 +13179,7 @@
     </row>
     <row r="97" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A97" s="2" t="s">
-        <v>697</v>
+        <v>130</v>
       </c>
       <c r="B97" s="1" t="s">
         <v>10</v>
@@ -13125,16 +13188,16 @@
         <v>272</v>
       </c>
       <c r="D97" s="1" t="s">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="E97" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F97" s="1" t="s">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="G97" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I97" s="1" t="s">
         <v>339</v>
@@ -13142,25 +13205,25 @@
     </row>
     <row r="98" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A98" s="2" t="s">
-        <v>1076</v>
+        <v>697</v>
       </c>
       <c r="B98" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C98" s="1" t="s">
-        <v>1077</v>
+        <v>272</v>
       </c>
       <c r="D98" s="1" t="s">
-        <v>1171</v>
+        <v>833</v>
       </c>
       <c r="E98" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F98" s="1" t="s">
-        <v>1078</v>
+        <v>698</v>
       </c>
       <c r="G98" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I98" s="1" t="s">
         <v>339</v>
@@ -13168,22 +13231,22 @@
     </row>
     <row r="99" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A99" s="2" t="s">
-        <v>1526</v>
+        <v>1076</v>
       </c>
       <c r="B99" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C99" s="1" t="s">
-        <v>1525</v>
+        <v>1077</v>
       </c>
       <c r="D99" s="1" t="s">
-        <v>1527</v>
+        <v>1171</v>
       </c>
       <c r="E99" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F99" s="1" t="s">
-        <v>1528</v>
+        <v>1078</v>
       </c>
       <c r="G99" t="s">
         <v>19</v>
@@ -13194,22 +13257,22 @@
     </row>
     <row r="100" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A100" s="2" t="s">
-        <v>2545</v>
+        <v>1526</v>
       </c>
       <c r="B100" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C100" s="1" t="s">
-        <v>2546</v>
+        <v>1525</v>
       </c>
       <c r="D100" s="1" t="s">
-        <v>2547</v>
+        <v>1527</v>
       </c>
       <c r="E100" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F100" s="1" t="s">
-        <v>2548</v>
+        <v>1528</v>
       </c>
       <c r="G100" t="s">
         <v>19</v>
@@ -13220,22 +13283,22 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>1170</v>
+        <v>2544</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>1169</v>
+        <v>2545</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>1172</v>
+        <v>2546</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>1173</v>
+        <v>2547</v>
       </c>
       <c r="G101" t="s">
         <v>19</v>
@@ -13246,22 +13309,22 @@
     </row>
     <row r="102" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A102" s="2" t="s">
-        <v>1054</v>
+        <v>1170</v>
       </c>
       <c r="B102" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C102" s="1" t="s">
-        <v>1050</v>
+        <v>1169</v>
       </c>
       <c r="D102" s="1" t="s">
-        <v>1051</v>
+        <v>1172</v>
       </c>
       <c r="E102" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F102" s="1" t="s">
-        <v>1052</v>
+        <v>1173</v>
       </c>
       <c r="G102" t="s">
         <v>19</v>
@@ -13272,22 +13335,22 @@
     </row>
     <row r="103" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A103" s="2" t="s">
-        <v>1542</v>
+        <v>1054</v>
       </c>
       <c r="B103" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C103" s="1" t="s">
-        <v>1541</v>
+        <v>1050</v>
       </c>
       <c r="D103" s="1" t="s">
-        <v>1543</v>
+        <v>1051</v>
       </c>
       <c r="E103" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F103" s="1" t="s">
-        <v>1544</v>
+        <v>1052</v>
       </c>
       <c r="G103" t="s">
         <v>19</v>
@@ -13298,25 +13361,25 @@
     </row>
     <row r="104" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A104" s="2" t="s">
-        <v>408</v>
+        <v>1542</v>
       </c>
       <c r="B104" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C104" s="1" t="s">
-        <v>404</v>
+        <v>1541</v>
       </c>
       <c r="D104" s="1" t="s">
-        <v>406</v>
+        <v>1543</v>
       </c>
       <c r="E104" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F104" s="1" t="s">
-        <v>410</v>
+        <v>1544</v>
       </c>
       <c r="G104" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I104" s="1" t="s">
         <v>339</v>
@@ -13324,22 +13387,22 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>470</v>
+        <v>408</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>468</v>
+        <v>404</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>469</v>
+        <v>406</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>467</v>
+        <v>410</v>
       </c>
       <c r="G105" t="s">
         <v>332</v>
@@ -13350,7 +13413,7 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>482</v>
+        <v>470</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>10</v>
@@ -13359,16 +13422,16 @@
         <v>468</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>484</v>
+        <v>469</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>483</v>
+        <v>467</v>
       </c>
       <c r="G106" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I106" s="1" t="s">
         <v>339</v>
@@ -13376,25 +13439,25 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>428</v>
+        <v>482</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>430</v>
+        <v>468</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>431</v>
+        <v>484</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>432</v>
+        <v>483</v>
       </c>
       <c r="G107" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I107" s="1" t="s">
         <v>339</v>
@@ -13402,25 +13465,25 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>2594</v>
+        <v>428</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>2591</v>
+        <v>430</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>2592</v>
+        <v>431</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>2593</v>
+        <v>432</v>
       </c>
       <c r="G108" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I108" s="1" t="s">
         <v>339</v>
@@ -13428,22 +13491,22 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>1087</v>
+        <v>2593</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>1088</v>
+        <v>2590</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>1089</v>
+        <v>2591</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>1090</v>
+        <v>2592</v>
       </c>
       <c r="G109" t="s">
         <v>19</v>
@@ -13454,22 +13517,22 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>1439</v>
+        <v>1087</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C110" s="1" t="s">
-        <v>1437</v>
+        <v>1088</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1440</v>
+        <v>1089</v>
       </c>
       <c r="E110" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1438</v>
+        <v>1090</v>
       </c>
       <c r="G110" t="s">
         <v>19</v>
@@ -13480,22 +13543,22 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>163</v>
+        <v>1439</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>273</v>
+        <v>1437</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>2176</v>
+        <v>1440</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>162</v>
+        <v>1438</v>
       </c>
       <c r="G111" t="s">
         <v>19</v>
@@ -13506,22 +13569,22 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>367</v>
+        <v>163</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C112" s="1" t="s">
-        <v>364</v>
+        <v>273</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>372</v>
+        <v>2176</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>363</v>
+        <v>162</v>
       </c>
       <c r="G112" t="s">
         <v>19</v>
@@ -13532,7 +13595,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>10</v>
@@ -13541,16 +13604,16 @@
         <v>364</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>365</v>
+        <v>372</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>366</v>
-      </c>
-      <c r="G113" s="1" t="s">
-        <v>332</v>
+        <v>363</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>339</v>
@@ -13558,7 +13621,7 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>1096</v>
+        <v>368</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>10</v>
@@ -13567,16 +13630,16 @@
         <v>364</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>1097</v>
+        <v>365</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>1098</v>
-      </c>
-      <c r="G114" t="s">
-        <v>19</v>
+        <v>366</v>
+      </c>
+      <c r="G114" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>339</v>
@@ -13584,22 +13647,22 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>153</v>
+        <v>1096</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C115" s="1" t="s">
-        <v>274</v>
+        <v>364</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>154</v>
+        <v>1097</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>152</v>
+        <v>1098</v>
       </c>
       <c r="G115" t="s">
         <v>19</v>
@@ -13610,22 +13673,22 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>157</v>
+        <v>153</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="G116" t="s">
         <v>19</v>
@@ -13636,7 +13699,7 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>450</v>
+        <v>157</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>10</v>
@@ -13645,16 +13708,16 @@
         <v>275</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>451</v>
+        <v>156</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>452</v>
+        <v>155</v>
       </c>
       <c r="G117" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>339</v>
@@ -13662,25 +13725,25 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>1030</v>
+        <v>450</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>1029</v>
+        <v>275</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>1044</v>
+        <v>451</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>1031</v>
+        <v>452</v>
       </c>
       <c r="G118" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>339</v>
@@ -13688,7 +13751,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>1453</v>
+        <v>1030</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>10</v>
@@ -13697,16 +13760,16 @@
         <v>1029</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>1454</v>
+        <v>1044</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>1455</v>
+        <v>1031</v>
       </c>
       <c r="G119" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>339</v>
@@ -13714,25 +13777,25 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>1042</v>
+        <v>1453</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>1041</v>
+        <v>1029</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>1043</v>
+        <v>1454</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1040</v>
+        <v>1455</v>
       </c>
       <c r="G120" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>339</v>
@@ -13740,7 +13803,7 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>1456</v>
+        <v>1042</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>10</v>
@@ -13749,16 +13812,16 @@
         <v>1041</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>1457</v>
+        <v>1043</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>1458</v>
+        <v>1040</v>
       </c>
       <c r="G121" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I121" s="1" t="s">
         <v>339</v>
@@ -13766,22 +13829,22 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>944</v>
+        <v>1456</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C122" s="1" t="s">
-        <v>945</v>
+        <v>1041</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>946</v>
+        <v>1457</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>947</v>
+        <v>1458</v>
       </c>
       <c r="G122" t="s">
         <v>332</v>
@@ -13792,25 +13855,25 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>1287</v>
+        <v>944</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>1288</v>
+        <v>945</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>1289</v>
+        <v>946</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1582</v>
-      </c>
-      <c r="G123" s="1" t="s">
-        <v>19</v>
+        <v>947</v>
+      </c>
+      <c r="G123" t="s">
+        <v>332</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>339</v>
@@ -13818,24 +13881,24 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>1158</v>
+        <v>1287</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>1157</v>
+        <v>1288</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>1160</v>
+        <v>1289</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>1159</v>
-      </c>
-      <c r="G124" t="s">
+        <v>1582</v>
+      </c>
+      <c r="G124" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I124" s="1" t="s">
@@ -13844,22 +13907,22 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>1575</v>
+        <v>1158</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1576</v>
+        <v>1157</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>1577</v>
+        <v>1160</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1578</v>
+        <v>1159</v>
       </c>
       <c r="G125" t="s">
         <v>19</v>
@@ -13870,22 +13933,22 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>1681</v>
+        <v>1575</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1682</v>
+        <v>1576</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>1683</v>
+        <v>1577</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1684</v>
+        <v>1578</v>
       </c>
       <c r="G126" t="s">
         <v>19</v>
@@ -13896,22 +13959,22 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>2235</v>
+        <v>1681</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>2236</v>
+        <v>1682</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>2237</v>
+        <v>1683</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>2238</v>
+        <v>1684</v>
       </c>
       <c r="G127" t="s">
         <v>19</v>
@@ -13922,22 +13985,22 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>1475</v>
+        <v>2235</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>1474</v>
+        <v>2236</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>1476</v>
+        <v>2237</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1477</v>
+        <v>2238</v>
       </c>
       <c r="G128" t="s">
         <v>19</v>
@@ -13948,25 +14011,25 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>679</v>
+        <v>1475</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>678</v>
+        <v>1474</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>677</v>
+        <v>1476</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>676</v>
+        <v>1477</v>
       </c>
       <c r="G129" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>339</v>
@@ -13974,22 +14037,22 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>687</v>
+        <v>679</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>686</v>
+        <v>678</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>685</v>
+        <v>677</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>696</v>
+        <v>676</v>
       </c>
       <c r="G130" t="s">
         <v>332</v>
@@ -14000,25 +14063,25 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>606</v>
+        <v>687</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C131" s="1" t="s">
-        <v>607</v>
+        <v>686</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>608</v>
+        <v>685</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>609</v>
+        <v>696</v>
       </c>
       <c r="G131" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>339</v>
@@ -14026,25 +14089,25 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>400</v>
+        <v>606</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>399</v>
+        <v>607</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>402</v>
+        <v>608</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>401</v>
+        <v>609</v>
       </c>
       <c r="G132" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>339</v>
@@ -14052,24 +14115,24 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>331</v>
+        <v>400</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>330</v>
+        <v>399</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>329</v>
+        <v>402</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G133" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="G133" t="s">
         <v>332</v>
       </c>
       <c r="I133" s="1" t="s">
@@ -14078,7 +14141,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>10</v>
@@ -14087,16 +14150,16 @@
         <v>330</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G134" t="s">
-        <v>19</v>
+        <v>328</v>
+      </c>
+      <c r="G134" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>339</v>
@@ -14104,22 +14167,22 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>1154</v>
+        <v>338</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>1153</v>
+        <v>330</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>1156</v>
+        <v>337</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1155</v>
+        <v>1082</v>
       </c>
       <c r="G135" t="s">
         <v>19</v>
@@ -14130,22 +14193,22 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>1703</v>
+        <v>1154</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1704</v>
+        <v>1153</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1705</v>
+        <v>1156</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1706</v>
+        <v>1155</v>
       </c>
       <c r="G136" t="s">
         <v>19</v>
@@ -14156,25 +14219,25 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>1816</v>
+        <v>1703</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1815</v>
+        <v>1704</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>1817</v>
+        <v>1705</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1818</v>
-      </c>
-      <c r="G137" s="1" t="s">
-        <v>332</v>
+        <v>1706</v>
+      </c>
+      <c r="G137" t="s">
+        <v>19</v>
       </c>
       <c r="I137" s="1" t="s">
         <v>339</v>
@@ -14182,25 +14245,25 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>1079</v>
+        <v>1816</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1080</v>
+        <v>1815</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>1081</v>
+        <v>1817</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G138" t="s">
-        <v>19</v>
+        <v>1818</v>
+      </c>
+      <c r="G138" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>339</v>
@@ -14208,13 +14271,13 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>1675</v>
+        <v>1079</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>1674</v>
+        <v>1080</v>
       </c>
       <c r="D139" s="1" t="s">
         <v>1081</v>
@@ -14223,7 +14286,7 @@
         <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1676</v>
+        <v>1083</v>
       </c>
       <c r="G139" t="s">
         <v>19</v>
@@ -14234,25 +14297,25 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>1883</v>
+        <v>1675</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1882</v>
+        <v>1674</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>1884</v>
+        <v>1081</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1885</v>
-      </c>
-      <c r="G140" s="1" t="s">
-        <v>332</v>
+        <v>1676</v>
+      </c>
+      <c r="G140" t="s">
+        <v>19</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>339</v>
@@ -14260,25 +14323,25 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>1272</v>
+        <v>1883</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1271</v>
+        <v>1882</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1273</v>
+        <v>1884</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G141" t="s">
-        <v>19</v>
+        <v>1885</v>
+      </c>
+      <c r="G141" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>339</v>
@@ -14286,22 +14349,22 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>1103</v>
+        <v>1272</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>1104</v>
+        <v>1271</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>1105</v>
+        <v>1273</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1106</v>
+        <v>1274</v>
       </c>
       <c r="G142" t="s">
         <v>19</v>
@@ -14312,22 +14375,22 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>828</v>
+        <v>1103</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>827</v>
+        <v>1104</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>829</v>
+        <v>1105</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>826</v>
+        <v>1106</v>
       </c>
       <c r="G143" t="s">
         <v>19</v>
@@ -14338,22 +14401,22 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>1919</v>
+        <v>828</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>1918</v>
+        <v>827</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>1920</v>
+        <v>829</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>1921</v>
+        <v>826</v>
       </c>
       <c r="G144" t="s">
         <v>19</v>
@@ -14364,22 +14427,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>1303</v>
+        <v>1919</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>1302</v>
+        <v>1918</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>1304</v>
+        <v>1920</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1305</v>
+        <v>1921</v>
       </c>
       <c r="G145" t="s">
         <v>19</v>
@@ -14390,7 +14453,7 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>2340</v>
+        <v>1303</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>10</v>
@@ -14399,16 +14462,16 @@
         <v>1302</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>2341</v>
+        <v>1304</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>2342</v>
-      </c>
-      <c r="G146" s="1" t="s">
-        <v>332</v>
+        <v>1305</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>339</v>
@@ -14416,22 +14479,22 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>2315</v>
+        <v>2340</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C147" s="1" t="s">
-        <v>2316</v>
+        <v>1302</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>2317</v>
+        <v>2341</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>2318</v>
+        <v>2342</v>
       </c>
       <c r="G147" s="1" t="s">
         <v>332</v>
@@ -14442,25 +14505,25 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>622</v>
+        <v>2315</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>621</v>
+        <v>2316</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>620</v>
+        <v>2317</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="G148" t="s">
-        <v>19</v>
+        <v>2318</v>
+      </c>
+      <c r="G148" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>339</v>
@@ -14468,22 +14531,22 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>1388</v>
+        <v>622</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>1387</v>
+        <v>621</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>1389</v>
+        <v>620</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1390</v>
+        <v>619</v>
       </c>
       <c r="G149" t="s">
         <v>19</v>
@@ -14494,22 +14557,22 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>134</v>
+        <v>1388</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>271</v>
+        <v>1387</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>133</v>
+        <v>1389</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>131</v>
+        <v>1390</v>
       </c>
       <c r="G150" t="s">
         <v>19</v>
@@ -14520,22 +14583,22 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>1538</v>
+        <v>134</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1537</v>
+        <v>271</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>1539</v>
+        <v>133</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1540</v>
+        <v>131</v>
       </c>
       <c r="G151" t="s">
         <v>19</v>
@@ -14546,25 +14609,25 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>690</v>
+        <v>1538</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>689</v>
+        <v>1537</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>688</v>
+        <v>1539</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>695</v>
+        <v>1540</v>
       </c>
       <c r="G152" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I152" s="1" t="s">
         <v>339</v>
@@ -14572,25 +14635,25 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>1053</v>
+        <v>690</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1055</v>
+        <v>689</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>1056</v>
+        <v>688</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1057</v>
+        <v>695</v>
       </c>
       <c r="G153" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>339</v>
@@ -14598,25 +14661,25 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>398</v>
+        <v>1053</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>397</v>
+        <v>1055</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>403</v>
+        <v>1056</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>401</v>
+        <v>1057</v>
       </c>
       <c r="G154" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>339</v>
@@ -14624,22 +14687,22 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>694</v>
+        <v>398</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>693</v>
+        <v>397</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>692</v>
+        <v>403</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>691</v>
+        <v>401</v>
       </c>
       <c r="G155" t="s">
         <v>332</v>
@@ -14650,27 +14713,53 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B156" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C156" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D156" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E156" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F156" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="G156" t="s">
+        <v>332</v>
+      </c>
+      <c r="I156" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="157" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A157" s="2" t="s">
         <v>1649</v>
       </c>
-      <c r="B156" s="1" t="s">
+      <c r="B157" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="C156" s="1" t="s">
+      <c r="C157" s="1" t="s">
         <v>1648</v>
       </c>
-      <c r="D156" s="1" t="s">
+      <c r="D157" s="1" t="s">
         <v>1650</v>
       </c>
-      <c r="E156" s="1" t="s">
+      <c r="E157" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F156" s="1" t="s">
+      <c r="F157" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="G156" s="1" t="s">
+      <c r="G157" s="1" t="s">
         <v>1652</v>
       </c>
-      <c r="I156" s="1" t="s">
+      <c r="I157" s="1" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -15671,30 +15760,30 @@
         <v>2469</v>
       </c>
       <c r="G37" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="I37" t="s">
-        <v>2516</v>
+        <v>2515</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>2528</v>
+        <v>2527</v>
       </c>
       <c r="B38" t="s">
         <v>388</v>
       </c>
       <c r="C38" t="s">
+        <v>2528</v>
+      </c>
+      <c r="D38" t="s">
         <v>2529</v>
-      </c>
-      <c r="D38" t="s">
-        <v>2530</v>
       </c>
       <c r="E38" t="s">
         <v>2186</v>
       </c>
       <c r="F38" t="s">
-        <v>2531</v>
+        <v>2530</v>
       </c>
       <c r="G38" t="s">
         <v>2230</v>
@@ -15705,28 +15794,28 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>2571</v>
+        <v>2570</v>
       </c>
       <c r="B39" t="s">
         <v>388</v>
       </c>
       <c r="C39" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
       <c r="D39" t="s">
-        <v>2572</v>
+        <v>2571</v>
       </c>
       <c r="E39" t="s">
         <v>2186</v>
       </c>
       <c r="F39" t="s">
-        <v>2574</v>
+        <v>2573</v>
       </c>
       <c r="G39" t="s">
         <v>2465</v>
       </c>
       <c r="I39" t="s">
-        <v>2573</v>
+        <v>2572</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -15783,28 +15872,28 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>2494</v>
+        <v>2493</v>
       </c>
       <c r="B42" t="s">
         <v>716</v>
       </c>
       <c r="C42" t="s">
+        <v>2494</v>
+      </c>
+      <c r="D42" t="s">
         <v>2495</v>
-      </c>
-      <c r="D42" t="s">
-        <v>2496</v>
       </c>
       <c r="E42" t="s">
         <v>513</v>
       </c>
       <c r="F42" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
       <c r="G42" t="s">
-        <v>2569</v>
+        <v>2568</v>
       </c>
       <c r="I42" t="s">
-        <v>2497</v>
+        <v>2496</v>
       </c>
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
@@ -16184,22 +16273,22 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>2532</v>
+        <v>2531</v>
       </c>
       <c r="B10" t="s">
         <v>1594</v>
       </c>
       <c r="C10" t="s">
+        <v>2532</v>
+      </c>
+      <c r="D10" t="s">
+        <v>2534</v>
+      </c>
+      <c r="E10" t="s">
         <v>2533</v>
       </c>
-      <c r="D10" t="s">
+      <c r="F10" t="s">
         <v>2535</v>
-      </c>
-      <c r="E10" t="s">
-        <v>2534</v>
-      </c>
-      <c r="F10" t="s">
-        <v>2536</v>
       </c>
       <c r="G10" t="s">
         <v>129</v>
@@ -16210,22 +16299,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="B11" t="s">
         <v>1594</v>
       </c>
       <c r="C11" t="s">
+        <v>2599</v>
+      </c>
+      <c r="D11" t="s">
         <v>2600</v>
       </c>
-      <c r="D11" t="s">
+      <c r="E11" t="s">
         <v>2601</v>
       </c>
-      <c r="E11" t="s">
-        <v>2602</v>
-      </c>
       <c r="F11" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="G11" t="s">
         <v>1597</v>
@@ -16245,7 +16334,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
-  <dimension ref="A1:J19"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" bestFit="1" customWidth="1"/>
@@ -16496,51 +16585,45 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1508</v>
+        <v>2611</v>
       </c>
       <c r="B9" t="s">
         <v>375</v>
       </c>
       <c r="C9" t="s">
-        <v>343</v>
+        <v>1315</v>
       </c>
       <c r="D9" t="s">
-        <v>1509</v>
+        <v>2612</v>
       </c>
       <c r="E9" t="s">
         <v>1217</v>
       </c>
-      <c r="F9" t="s">
-        <v>1620</v>
-      </c>
       <c r="G9" t="s">
-        <v>1219</v>
-      </c>
-      <c r="H9" t="s">
-        <v>1221</v>
+        <v>2607</v>
       </c>
       <c r="I9" t="s">
-        <v>346</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1748</v>
+        <v>1508</v>
       </c>
       <c r="B10" t="s">
         <v>375</v>
       </c>
       <c r="C10" t="s">
-        <v>1749</v>
+        <v>343</v>
       </c>
       <c r="D10" t="s">
-        <v>1750</v>
+        <v>1509</v>
       </c>
       <c r="E10" t="s">
-        <v>1751</v>
+        <v>1217</v>
       </c>
       <c r="F10" t="s">
-        <v>1752</v>
+        <v>1620</v>
       </c>
       <c r="G10" t="s">
         <v>1219</v>
@@ -16554,51 +16637,48 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1984</v>
+        <v>2606</v>
       </c>
       <c r="B11" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C11" t="s">
-        <v>1215</v>
+        <v>343</v>
       </c>
       <c r="D11" t="s">
-        <v>2195</v>
+        <v>2609</v>
       </c>
       <c r="E11" t="s">
-        <v>1217</v>
+        <v>2204</v>
       </c>
       <c r="F11" t="s">
-        <v>1622</v>
+        <v>2608</v>
       </c>
       <c r="G11" t="s">
-        <v>1219</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1221</v>
+        <v>2607</v>
       </c>
       <c r="I11" t="s">
-        <v>380</v>
+        <v>2610</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1961</v>
+        <v>1748</v>
       </c>
       <c r="B12" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C12" t="s">
-        <v>1547</v>
+        <v>1749</v>
       </c>
       <c r="D12" t="s">
-        <v>2194</v>
+        <v>1750</v>
       </c>
       <c r="E12" t="s">
-        <v>1217</v>
+        <v>1751</v>
       </c>
       <c r="F12" t="s">
-        <v>1623</v>
+        <v>1752</v>
       </c>
       <c r="G12" t="s">
         <v>1219</v>
@@ -16607,27 +16687,27 @@
         <v>1221</v>
       </c>
       <c r="I12" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1963</v>
+        <v>1984</v>
       </c>
       <c r="B13" t="s">
         <v>376</v>
       </c>
       <c r="C13" t="s">
-        <v>1545</v>
+        <v>1215</v>
       </c>
       <c r="D13" t="s">
-        <v>2196</v>
+        <v>2195</v>
       </c>
       <c r="E13" t="s">
         <v>1217</v>
       </c>
       <c r="F13" t="s">
-        <v>1962</v>
+        <v>1622</v>
       </c>
       <c r="G13" t="s">
         <v>1219</v>
@@ -16641,51 +16721,51 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1744</v>
+        <v>1961</v>
       </c>
       <c r="B14" t="s">
         <v>376</v>
       </c>
       <c r="C14" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="D14" t="s">
-        <v>2197</v>
+        <v>2194</v>
       </c>
       <c r="E14" t="s">
         <v>1217</v>
       </c>
       <c r="F14" t="s">
-        <v>1625</v>
+        <v>1623</v>
       </c>
       <c r="G14" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H14" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="I14" t="s">
-        <v>1222</v>
+        <v>380</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1745</v>
+        <v>1963</v>
       </c>
       <c r="B15" t="s">
         <v>376</v>
       </c>
       <c r="C15" t="s">
-        <v>1214</v>
+        <v>1545</v>
       </c>
       <c r="D15" t="s">
-        <v>2198</v>
+        <v>2196</v>
       </c>
       <c r="E15" t="s">
         <v>1217</v>
       </c>
       <c r="F15" t="s">
-        <v>1624</v>
+        <v>1962</v>
       </c>
       <c r="G15" t="s">
         <v>1219</v>
@@ -16699,22 +16779,22 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1746</v>
+        <v>1744</v>
       </c>
       <c r="B16" t="s">
         <v>376</v>
       </c>
       <c r="C16" t="s">
-        <v>1213</v>
+        <v>1545</v>
       </c>
       <c r="D16" t="s">
-        <v>2199</v>
+        <v>2197</v>
       </c>
       <c r="E16" t="s">
         <v>1217</v>
       </c>
       <c r="F16" t="s">
-        <v>1626</v>
+        <v>1625</v>
       </c>
       <c r="G16" t="s">
         <v>1218</v>
@@ -16728,91 +16808,149 @@
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1747</v>
+        <v>1745</v>
       </c>
       <c r="B17" t="s">
         <v>376</v>
       </c>
       <c r="C17" t="s">
-        <v>1546</v>
+        <v>1214</v>
       </c>
       <c r="D17" t="s">
-        <v>2200</v>
+        <v>2198</v>
       </c>
       <c r="E17" t="s">
         <v>1217</v>
       </c>
       <c r="F17" t="s">
-        <v>1627</v>
+        <v>1624</v>
       </c>
       <c r="G17" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H17" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="I17" t="s">
-        <v>1222</v>
+        <v>380</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>2177</v>
+        <v>1746</v>
       </c>
       <c r="B18" t="s">
         <v>376</v>
       </c>
       <c r="C18" t="s">
-        <v>2178</v>
+        <v>1213</v>
       </c>
       <c r="D18" t="s">
-        <v>2201</v>
+        <v>2199</v>
       </c>
       <c r="E18" t="s">
-        <v>2179</v>
+        <v>1217</v>
       </c>
       <c r="F18" t="s">
-        <v>2181</v>
+        <v>1626</v>
       </c>
       <c r="G18" t="s">
-        <v>2182</v>
+        <v>1218</v>
       </c>
       <c r="H18" t="s">
-        <v>2180</v>
+        <v>1220</v>
       </c>
       <c r="I18" t="s">
-        <v>380</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>2193</v>
+        <v>1747</v>
       </c>
       <c r="B19" t="s">
         <v>376</v>
       </c>
       <c r="C19" t="s">
+        <v>1546</v>
+      </c>
+      <c r="D19" t="s">
+        <v>2200</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1217</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1627</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1218</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1220</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1222</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
+        <v>2177</v>
+      </c>
+      <c r="B20" t="s">
+        <v>376</v>
+      </c>
+      <c r="C20" t="s">
+        <v>2178</v>
+      </c>
+      <c r="D20" t="s">
+        <v>2201</v>
+      </c>
+      <c r="E20" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F20" t="s">
+        <v>2181</v>
+      </c>
+      <c r="G20" t="s">
+        <v>2182</v>
+      </c>
+      <c r="H20" t="s">
+        <v>2180</v>
+      </c>
+      <c r="I20" t="s">
+        <v>380</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A21" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B21" t="s">
+        <v>376</v>
+      </c>
+      <c r="C21" t="s">
         <v>2192</v>
       </c>
-      <c r="D19" t="s">
+      <c r="D21" t="s">
         <v>2203</v>
       </c>
-      <c r="E19" t="s">
+      <c r="E21" t="s">
         <v>2204</v>
       </c>
-      <c r="F19" t="s">
+      <c r="F21" t="s">
         <v>2205</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G21" t="s">
         <v>2206</v>
       </c>
-      <c r="I19" t="s">
+      <c r="I21" t="s">
         <v>380</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:J17" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J17">
+  <autoFilter ref="A1:J19" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
       <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
@@ -16922,7 +17060,7 @@
         <v>387</v>
       </c>
       <c r="I3" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -17187,28 +17325,28 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>2522</v>
+        <v>2521</v>
       </c>
       <c r="B14" t="s">
         <v>382</v>
       </c>
       <c r="C14" t="s">
+        <v>2522</v>
+      </c>
+      <c r="D14" t="s">
         <v>2523</v>
       </c>
-      <c r="D14" t="s">
+      <c r="E14" t="s">
         <v>2524</v>
       </c>
-      <c r="E14" t="s">
+      <c r="F14" t="s">
         <v>2525</v>
-      </c>
-      <c r="F14" t="s">
-        <v>2526</v>
       </c>
       <c r="G14" t="s">
         <v>989</v>
       </c>
       <c r="I14" t="s">
-        <v>2527</v>
+        <v>2526</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -17343,28 +17481,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>2560</v>
+        <v>2559</v>
       </c>
       <c r="B20" t="s">
         <v>433</v>
       </c>
       <c r="C20" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2564</v>
+        <v>2563</v>
       </c>
       <c r="E20" t="s">
         <v>844</v>
       </c>
       <c r="F20" t="s">
+        <v>2561</v>
+      </c>
+      <c r="G20" t="s">
         <v>2562</v>
       </c>
-      <c r="G20" t="s">
-        <v>2563</v>
-      </c>
       <c r="I20" t="s">
-        <v>2561</v>
+        <v>2560</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -18549,7 +18687,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>2586</v>
+        <v>2585</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -18558,13 +18696,13 @@
         <v>198</v>
       </c>
       <c r="D21" t="s">
-        <v>2585</v>
+        <v>2584</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>2584</v>
+        <v>2583</v>
       </c>
       <c r="G21" t="s">
         <v>18</v>
@@ -18705,25 +18843,25 @@
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>2490</v>
+        <v>2489</v>
       </c>
       <c r="B27" t="s">
         <v>17</v>
       </c>
       <c r="C27" t="s">
-        <v>2489</v>
+        <v>2488</v>
       </c>
       <c r="D27" t="s">
-        <v>2493</v>
+        <v>2492</v>
       </c>
       <c r="E27" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F27" t="s">
+        <v>2490</v>
+      </c>
+      <c r="G27" t="s">
         <v>2491</v>
-      </c>
-      <c r="G27" t="s">
-        <v>2492</v>
       </c>
       <c r="I27" t="s">
         <v>20</v>
@@ -20206,22 +20344,25 @@
         <v>305</v>
       </c>
       <c r="C6" t="s">
-        <v>2482</v>
+        <v>2481</v>
+      </c>
+      <c r="D6" t="s">
+        <v>2617</v>
       </c>
       <c r="E6" t="s">
+        <v>2478</v>
+      </c>
+      <c r="F6" t="s">
+        <v>2616</v>
+      </c>
+      <c r="G6" t="s">
         <v>2479</v>
       </c>
-      <c r="F6" t="s">
-        <v>2478</v>
-      </c>
-      <c r="G6" t="s">
+      <c r="H6" t="s">
         <v>2480</v>
       </c>
-      <c r="H6" t="s">
+      <c r="I6" t="s">
         <v>2481</v>
-      </c>
-      <c r="I6" t="s">
-        <v>2482</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -20484,25 +20625,28 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="B16" t="s">
         <v>1223</v>
       </c>
+      <c r="C16" t="s">
+        <v>2618</v>
+      </c>
       <c r="D16" t="s">
-        <v>2513</v>
+        <v>2512</v>
       </c>
       <c r="E16" t="s">
         <v>1966</v>
       </c>
       <c r="F16" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="G16" t="s">
-        <v>2514</v>
+        <v>2513</v>
       </c>
       <c r="I16" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -21374,31 +21518,31 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>2554</v>
+        <v>2553</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>2556</v>
+        <v>2555</v>
       </c>
       <c r="D19" t="s">
-        <v>2555</v>
+        <v>2554</v>
       </c>
       <c r="E19" t="s">
         <v>864</v>
       </c>
       <c r="F19" t="s">
+        <v>2555</v>
+      </c>
+      <c r="G19" t="s">
         <v>2556</v>
       </c>
-      <c r="G19" t="s">
+      <c r="H19" t="s">
         <v>2557</v>
       </c>
-      <c r="H19" t="s">
+      <c r="I19" t="s">
         <v>2558</v>
-      </c>
-      <c r="I19" t="s">
-        <v>2559</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -22244,31 +22388,31 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>2483</v>
+        <v>2482</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>284</v>
       </c>
       <c r="C49" t="s">
+        <v>2483</v>
+      </c>
+      <c r="D49" t="s">
         <v>2484</v>
       </c>
-      <c r="D49" t="s">
+      <c r="E49" t="s">
         <v>2485</v>
       </c>
-      <c r="E49" t="s">
+      <c r="F49" t="s">
+        <v>2483</v>
+      </c>
+      <c r="G49" t="s">
+        <v>2552</v>
+      </c>
+      <c r="H49" t="s">
         <v>2486</v>
       </c>
-      <c r="F49" t="s">
-        <v>2484</v>
-      </c>
-      <c r="G49" t="s">
-        <v>2553</v>
-      </c>
-      <c r="H49" t="s">
+      <c r="I49" t="s">
         <v>2487</v>
-      </c>
-      <c r="I49" t="s">
-        <v>2488</v>
       </c>
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
@@ -22830,7 +22974,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61606E71-114A-4060-B4DA-26AC2BA8C44E}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.08203125" style="2" bestFit="1" customWidth="1"/>
@@ -23390,22 +23534,22 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>2498</v>
+        <v>2497</v>
       </c>
       <c r="B20" t="s">
         <v>2079</v>
       </c>
       <c r="C20" t="s">
+        <v>2498</v>
+      </c>
+      <c r="D20" s="6" t="s">
+        <v>2500</v>
+      </c>
+      <c r="E20" t="s">
         <v>2499</v>
       </c>
-      <c r="D20" s="6" t="s">
-        <v>2501</v>
-      </c>
-      <c r="E20" t="s">
-        <v>2500</v>
-      </c>
       <c r="F20" t="s">
-        <v>2499</v>
+        <v>2498</v>
       </c>
       <c r="G20" t="s">
         <v>2411</v>
@@ -23416,25 +23560,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>2565</v>
+        <v>2564</v>
       </c>
       <c r="B21" t="s">
         <v>2079</v>
       </c>
       <c r="C21" t="s">
-        <v>2568</v>
+        <v>2567</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2566</v>
+        <v>2565</v>
       </c>
       <c r="E21" t="s">
         <v>2410</v>
       </c>
       <c r="F21" t="s">
+        <v>2566</v>
+      </c>
+      <c r="G21" t="s">
         <v>2567</v>
-      </c>
-      <c r="G21" t="s">
-        <v>2568</v>
       </c>
       <c r="I21" t="s">
         <v>2083</v>
@@ -23442,27 +23586,53 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>2613</v>
+      </c>
+      <c r="B22" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2615</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>2565</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2614</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2615</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2567</v>
+      </c>
+      <c r="I22" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>2111</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>2110</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>2112</v>
       </c>
-      <c r="D22" s="6" t="s">
+      <c r="D23" s="6" t="s">
         <v>2113</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" t="s">
         <v>2114</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F23" t="s">
         <v>2112</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G23" t="s">
         <v>2112</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I23" t="s">
         <v>2115</v>
       </c>
     </row>
@@ -23533,7 +23703,7 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>2575</v>
+        <v>2574</v>
       </c>
       <c r="D2" t="s">
         <v>396</v>
@@ -23553,7 +23723,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>2577</v>
+        <v>2576</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>78</v>
@@ -23562,16 +23732,16 @@
         <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>2576</v>
+        <v>2575</v>
       </c>
       <c r="E3" t="s">
         <v>79</v>
       </c>
       <c r="F3" t="s">
+        <v>2577</v>
+      </c>
+      <c r="G3" t="s">
         <v>2578</v>
-      </c>
-      <c r="G3" t="s">
-        <v>2579</v>
       </c>
       <c r="I3" t="s">
         <v>76</v>
@@ -23579,7 +23749,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2595</v>
+        <v>2594</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>78</v>
@@ -23588,16 +23758,16 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
+        <v>2596</v>
+      </c>
+      <c r="G4" t="s">
         <v>2597</v>
-      </c>
-      <c r="G4" t="s">
-        <v>2598</v>
       </c>
       <c r="I4" t="s">
         <v>76</v>
@@ -24047,7 +24217,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>2537</v>
+        <v>2536</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>78</v>
@@ -24056,13 +24226,13 @@
         <v>821</v>
       </c>
       <c r="D22" t="s">
-        <v>2538</v>
+        <v>2537</v>
       </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>2540</v>
+        <v>2539</v>
       </c>
       <c r="G22" t="s">
         <v>1433</v>
@@ -24244,7 +24414,7 @@
         <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>2539</v>
+        <v>2538</v>
       </c>
       <c r="G29" t="s">
         <v>1433</v>
@@ -24585,7 +24755,7 @@
         <v>2450</v>
       </c>
       <c r="G42" t="s">
-        <v>2570</v>
+        <v>2569</v>
       </c>
       <c r="I42" t="s">
         <v>2448</v>

--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{713A11F7-5C34-4EFB-9BE5-30F72B946BB8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647804E1-485E-4B5B-82C7-6EDD00D54CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
     <definedName name="_xlnm._FilterDatabase" localSheetId="1">贴片电容!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0">贴片电阻!$A$1:$J$1</definedName>
     <definedName name="_xlnm._FilterDatabase" localSheetId="4">贴片结构料!$A$1:$J$55</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="11">振荡晶体!$A$1:$J$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="11">振荡晶体!$A$1:$J$20</definedName>
     <definedName name="TMPPRTS">TMPPRTS!$A$1:$B$1</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4640" uniqueCount="2619">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4670" uniqueCount="2632">
   <si>
     <t>Part Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -9732,10 +9732,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>RTL8153</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>RTL8153B-VB-CG</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -9748,10 +9744,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>QFN-40</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>YAGEO(国巨)</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -10166,6 +10158,65 @@
   </si>
   <si>
     <t>RTL8153B</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CL10A226MP8NUNE</t>
+  </si>
+  <si>
+    <t>1311226005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SATA供电座</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6611600022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RSM-C0XX-B15L1-X</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t xml:space="preserve">SATA 15P 单臂公座 90度 DIP型 </t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SATA-POWER</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SATA-15PIN-POWER-DIP</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6611600023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>09.03.12.003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HC-USB3_0-L257-P</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qfn40-5x5-EP3_6</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>晶立兴</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2041025005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Crystal;25MHZ;12pF;+/-10PPM;HC-49S-SMD</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11059,7 +11110,7 @@
         <v>892</v>
       </c>
       <c r="E15" s="1" t="s">
-        <v>2514</v>
+        <v>2512</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>891</v>
@@ -11515,22 +11566,22 @@
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>2589</v>
+        <v>2587</v>
       </c>
       <c r="B33" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C33" s="1" t="s">
-        <v>2588</v>
+        <v>2586</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>2587</v>
+        <v>2585</v>
       </c>
       <c r="E33" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F33" s="1" t="s">
-        <v>2586</v>
+        <v>2584</v>
       </c>
       <c r="G33" s="1" t="s">
         <v>19</v>
@@ -11541,25 +11592,25 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>2517</v>
+        <v>2515</v>
       </c>
       <c r="B34" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C34" s="1" t="s">
+        <v>2514</v>
+      </c>
+      <c r="D34" s="1" t="s">
         <v>2516</v>
-      </c>
-      <c r="D34" s="1" t="s">
-        <v>2518</v>
       </c>
       <c r="E34" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F34" s="1" t="s">
-        <v>2519</v>
+        <v>2517</v>
       </c>
       <c r="G34" s="1" t="s">
-        <v>2520</v>
+        <v>2518</v>
       </c>
       <c r="I34" s="1" t="s">
         <v>339</v>
@@ -12347,22 +12398,22 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>2549</v>
+        <v>2547</v>
       </c>
       <c r="B65" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C65" s="1" t="s">
+        <v>2546</v>
+      </c>
+      <c r="D65" s="1" t="s">
         <v>2548</v>
-      </c>
-      <c r="D65" s="1" t="s">
-        <v>2550</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F65" s="1" t="s">
-        <v>2551</v>
+        <v>2549</v>
       </c>
       <c r="G65" t="s">
         <v>91</v>
@@ -12893,22 +12944,22 @@
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A86" s="2" t="s">
-        <v>2541</v>
+        <v>2539</v>
       </c>
       <c r="B86" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C86" s="1" t="s">
+        <v>2538</v>
+      </c>
+      <c r="D86" s="1" t="s">
         <v>2540</v>
-      </c>
-      <c r="D86" s="1" t="s">
-        <v>2542</v>
       </c>
       <c r="E86" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F86" s="1" t="s">
-        <v>2543</v>
+        <v>2541</v>
       </c>
       <c r="G86" t="s">
         <v>19</v>
@@ -12945,22 +12996,22 @@
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A88" s="2" t="s">
-        <v>2603</v>
+        <v>2601</v>
       </c>
       <c r="B88" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C88" s="1" t="s">
+        <v>2600</v>
+      </c>
+      <c r="D88" s="1" t="s">
         <v>2602</v>
-      </c>
-      <c r="D88" s="1" t="s">
-        <v>2604</v>
       </c>
       <c r="E88" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F88" s="1" t="s">
-        <v>2605</v>
+        <v>2603</v>
       </c>
       <c r="G88" t="s">
         <v>19</v>
@@ -13101,22 +13152,22 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>2580</v>
+        <v>2578</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C94" s="1" t="s">
+        <v>2577</v>
+      </c>
+      <c r="D94" s="1" t="s">
         <v>2579</v>
-      </c>
-      <c r="D94" s="1" t="s">
-        <v>2581</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>2582</v>
+        <v>2580</v>
       </c>
       <c r="G94" s="1" t="s">
         <v>19</v>
@@ -13283,22 +13334,22 @@
     </row>
     <row r="101" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A101" s="2" t="s">
-        <v>2544</v>
+        <v>2542</v>
       </c>
       <c r="B101" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C101" s="1" t="s">
-        <v>2545</v>
+        <v>2543</v>
       </c>
       <c r="D101" s="1" t="s">
-        <v>2546</v>
+        <v>2544</v>
       </c>
       <c r="E101" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F101" s="1" t="s">
-        <v>2547</v>
+        <v>2545</v>
       </c>
       <c r="G101" t="s">
         <v>19</v>
@@ -13491,22 +13542,22 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>2593</v>
+        <v>2591</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>2590</v>
+        <v>2588</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>2591</v>
+        <v>2589</v>
       </c>
       <c r="E109" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>2592</v>
+        <v>2590</v>
       </c>
       <c r="G109" t="s">
         <v>19</v>
@@ -15760,30 +15811,30 @@
         <v>2469</v>
       </c>
       <c r="G37" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="I37" t="s">
-        <v>2515</v>
+        <v>2513</v>
       </c>
     </row>
     <row r="38" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A38" s="2" t="s">
-        <v>2527</v>
+        <v>2525</v>
       </c>
       <c r="B38" t="s">
         <v>388</v>
       </c>
       <c r="C38" t="s">
-        <v>2528</v>
+        <v>2526</v>
       </c>
       <c r="D38" t="s">
-        <v>2529</v>
+        <v>2527</v>
       </c>
       <c r="E38" t="s">
         <v>2186</v>
       </c>
       <c r="F38" t="s">
-        <v>2530</v>
+        <v>2528</v>
       </c>
       <c r="G38" t="s">
         <v>2230</v>
@@ -15794,28 +15845,28 @@
     </row>
     <row r="39" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A39" s="2" t="s">
-        <v>2570</v>
+        <v>2568</v>
       </c>
       <c r="B39" t="s">
         <v>388</v>
       </c>
       <c r="C39" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
       <c r="D39" t="s">
-        <v>2571</v>
+        <v>2569</v>
       </c>
       <c r="E39" t="s">
         <v>2186</v>
       </c>
       <c r="F39" t="s">
-        <v>2573</v>
+        <v>2571</v>
       </c>
       <c r="G39" t="s">
         <v>2465</v>
       </c>
       <c r="I39" t="s">
-        <v>2572</v>
+        <v>2570</v>
       </c>
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
@@ -15890,7 +15941,7 @@
         <v>2496</v>
       </c>
       <c r="G42" t="s">
-        <v>2568</v>
+        <v>2566</v>
       </c>
       <c r="I42" t="s">
         <v>2496</v>
@@ -16273,22 +16324,22 @@
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>2531</v>
+        <v>2529</v>
       </c>
       <c r="B10" t="s">
         <v>1594</v>
       </c>
       <c r="C10" t="s">
+        <v>2530</v>
+      </c>
+      <c r="D10" t="s">
         <v>2532</v>
       </c>
-      <c r="D10" t="s">
-        <v>2534</v>
-      </c>
       <c r="E10" t="s">
+        <v>2531</v>
+      </c>
+      <c r="F10" t="s">
         <v>2533</v>
-      </c>
-      <c r="F10" t="s">
-        <v>2535</v>
       </c>
       <c r="G10" t="s">
         <v>129</v>
@@ -16299,22 +16350,22 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>2598</v>
+        <v>2596</v>
       </c>
       <c r="B11" t="s">
         <v>1594</v>
       </c>
       <c r="C11" t="s">
+        <v>2597</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2598</v>
+      </c>
+      <c r="E11" t="s">
         <v>2599</v>
       </c>
-      <c r="D11" t="s">
-        <v>2600</v>
-      </c>
-      <c r="E11" t="s">
-        <v>2601</v>
-      </c>
       <c r="F11" t="s">
-        <v>2599</v>
+        <v>2597</v>
       </c>
       <c r="G11" t="s">
         <v>1597</v>
@@ -16334,7 +16385,7 @@
 
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
-  <dimension ref="A1:J21"/>
+  <dimension ref="A1:J22"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.25" style="2" bestFit="1" customWidth="1"/>
@@ -16585,7 +16636,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>2611</v>
+        <v>2609</v>
       </c>
       <c r="B9" t="s">
         <v>375</v>
@@ -16594,50 +16645,44 @@
         <v>1315</v>
       </c>
       <c r="D9" t="s">
-        <v>2612</v>
+        <v>2610</v>
       </c>
       <c r="E9" t="s">
         <v>1217</v>
       </c>
       <c r="G9" t="s">
-        <v>2607</v>
+        <v>2605</v>
       </c>
       <c r="I9" t="s">
-        <v>2610</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1508</v>
+        <v>2630</v>
       </c>
       <c r="B10" t="s">
         <v>375</v>
       </c>
       <c r="C10" t="s">
-        <v>343</v>
+        <v>1215</v>
       </c>
       <c r="D10" t="s">
-        <v>1509</v>
+        <v>2631</v>
       </c>
       <c r="E10" t="s">
         <v>1217</v>
       </c>
-      <c r="F10" t="s">
-        <v>1620</v>
-      </c>
       <c r="G10" t="s">
-        <v>1219</v>
-      </c>
-      <c r="H10" t="s">
-        <v>1221</v>
+        <v>2605</v>
       </c>
       <c r="I10" t="s">
-        <v>346</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>2606</v>
+        <v>1508</v>
       </c>
       <c r="B11" t="s">
         <v>375</v>
@@ -16646,68 +16691,68 @@
         <v>343</v>
       </c>
       <c r="D11" t="s">
-        <v>2609</v>
+        <v>1509</v>
       </c>
       <c r="E11" t="s">
-        <v>2204</v>
+        <v>2629</v>
       </c>
       <c r="F11" t="s">
-        <v>2608</v>
+        <v>1620</v>
       </c>
       <c r="G11" t="s">
-        <v>2607</v>
+        <v>1219</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1221</v>
       </c>
       <c r="I11" t="s">
-        <v>2610</v>
+        <v>346</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1748</v>
+        <v>2604</v>
       </c>
       <c r="B12" t="s">
         <v>375</v>
       </c>
       <c r="C12" t="s">
-        <v>1749</v>
+        <v>343</v>
       </c>
       <c r="D12" t="s">
-        <v>1750</v>
+        <v>2607</v>
       </c>
       <c r="E12" t="s">
-        <v>1751</v>
+        <v>2204</v>
       </c>
       <c r="F12" t="s">
-        <v>1752</v>
+        <v>2606</v>
       </c>
       <c r="G12" t="s">
-        <v>1219</v>
-      </c>
-      <c r="H12" t="s">
-        <v>1221</v>
+        <v>2605</v>
       </c>
       <c r="I12" t="s">
-        <v>346</v>
+        <v>2608</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1984</v>
+        <v>1748</v>
       </c>
       <c r="B13" t="s">
-        <v>376</v>
+        <v>375</v>
       </c>
       <c r="C13" t="s">
-        <v>1215</v>
+        <v>1749</v>
       </c>
       <c r="D13" t="s">
-        <v>2195</v>
+        <v>1750</v>
       </c>
       <c r="E13" t="s">
-        <v>1217</v>
+        <v>1751</v>
       </c>
       <c r="F13" t="s">
-        <v>1622</v>
+        <v>1752</v>
       </c>
       <c r="G13" t="s">
         <v>1219</v>
@@ -16716,27 +16761,27 @@
         <v>1221</v>
       </c>
       <c r="I13" t="s">
-        <v>380</v>
+        <v>346</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1961</v>
+        <v>1984</v>
       </c>
       <c r="B14" t="s">
         <v>376</v>
       </c>
       <c r="C14" t="s">
-        <v>1547</v>
+        <v>1215</v>
       </c>
       <c r="D14" t="s">
-        <v>2194</v>
+        <v>2195</v>
       </c>
       <c r="E14" t="s">
         <v>1217</v>
       </c>
       <c r="F14" t="s">
-        <v>1623</v>
+        <v>1622</v>
       </c>
       <c r="G14" t="s">
         <v>1219</v>
@@ -16750,22 +16795,22 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1963</v>
+        <v>1961</v>
       </c>
       <c r="B15" t="s">
         <v>376</v>
       </c>
       <c r="C15" t="s">
-        <v>1545</v>
+        <v>1547</v>
       </c>
       <c r="D15" t="s">
-        <v>2196</v>
+        <v>2194</v>
       </c>
       <c r="E15" t="s">
         <v>1217</v>
       </c>
       <c r="F15" t="s">
-        <v>1962</v>
+        <v>1623</v>
       </c>
       <c r="G15" t="s">
         <v>1219</v>
@@ -16779,7 +16824,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1744</v>
+        <v>1963</v>
       </c>
       <c r="B16" t="s">
         <v>376</v>
@@ -16788,100 +16833,100 @@
         <v>1545</v>
       </c>
       <c r="D16" t="s">
-        <v>2197</v>
+        <v>2196</v>
       </c>
       <c r="E16" t="s">
         <v>1217</v>
       </c>
       <c r="F16" t="s">
-        <v>1625</v>
+        <v>1962</v>
       </c>
       <c r="G16" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H16" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="I16" t="s">
-        <v>1222</v>
+        <v>380</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1745</v>
+        <v>1744</v>
       </c>
       <c r="B17" t="s">
         <v>376</v>
       </c>
       <c r="C17" t="s">
-        <v>1214</v>
+        <v>1545</v>
       </c>
       <c r="D17" t="s">
-        <v>2198</v>
+        <v>2197</v>
       </c>
       <c r="E17" t="s">
         <v>1217</v>
       </c>
       <c r="F17" t="s">
-        <v>1624</v>
+        <v>1625</v>
       </c>
       <c r="G17" t="s">
-        <v>1219</v>
+        <v>1218</v>
       </c>
       <c r="H17" t="s">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="I17" t="s">
-        <v>380</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1746</v>
+        <v>1745</v>
       </c>
       <c r="B18" t="s">
         <v>376</v>
       </c>
       <c r="C18" t="s">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="D18" t="s">
-        <v>2199</v>
+        <v>2198</v>
       </c>
       <c r="E18" t="s">
         <v>1217</v>
       </c>
       <c r="F18" t="s">
-        <v>1626</v>
+        <v>1624</v>
       </c>
       <c r="G18" t="s">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="H18" t="s">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="I18" t="s">
-        <v>1222</v>
+        <v>380</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1747</v>
+        <v>1746</v>
       </c>
       <c r="B19" t="s">
         <v>376</v>
       </c>
       <c r="C19" t="s">
-        <v>1546</v>
+        <v>1213</v>
       </c>
       <c r="D19" t="s">
-        <v>2200</v>
+        <v>2199</v>
       </c>
       <c r="E19" t="s">
         <v>1217</v>
       </c>
       <c r="F19" t="s">
-        <v>1627</v>
+        <v>1626</v>
       </c>
       <c r="G19" t="s">
         <v>1218</v>
@@ -16895,62 +16940,91 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>2177</v>
+        <v>1747</v>
       </c>
       <c r="B20" t="s">
         <v>376</v>
       </c>
       <c r="C20" t="s">
-        <v>2178</v>
+        <v>1546</v>
       </c>
       <c r="D20" t="s">
-        <v>2201</v>
+        <v>2200</v>
       </c>
       <c r="E20" t="s">
-        <v>2179</v>
+        <v>1217</v>
       </c>
       <c r="F20" t="s">
-        <v>2181</v>
+        <v>1627</v>
       </c>
       <c r="G20" t="s">
-        <v>2182</v>
+        <v>1218</v>
       </c>
       <c r="H20" t="s">
-        <v>2180</v>
+        <v>1220</v>
       </c>
       <c r="I20" t="s">
-        <v>380</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>2193</v>
+        <v>2177</v>
       </c>
       <c r="B21" t="s">
         <v>376</v>
       </c>
       <c r="C21" t="s">
-        <v>2192</v>
+        <v>2178</v>
       </c>
       <c r="D21" t="s">
-        <v>2203</v>
+        <v>2201</v>
       </c>
       <c r="E21" t="s">
-        <v>2204</v>
+        <v>2179</v>
       </c>
       <c r="F21" t="s">
-        <v>2205</v>
+        <v>2181</v>
       </c>
       <c r="G21" t="s">
-        <v>2206</v>
+        <v>2182</v>
+      </c>
+      <c r="H21" t="s">
+        <v>2180</v>
       </c>
       <c r="I21" t="s">
         <v>380</v>
       </c>
     </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A22" s="2" t="s">
+        <v>2193</v>
+      </c>
+      <c r="B22" t="s">
+        <v>376</v>
+      </c>
+      <c r="C22" t="s">
+        <v>2192</v>
+      </c>
+      <c r="D22" t="s">
+        <v>2203</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2204</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2205</v>
+      </c>
+      <c r="G22" t="s">
+        <v>2206</v>
+      </c>
+      <c r="I22" t="s">
+        <v>380</v>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:J19" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
-    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J19">
+  <autoFilter ref="A1:J20" xr:uid="{15246D15-200D-4616-89B7-7BD049663799}">
+    <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J20">
       <sortCondition ref="E1"/>
     </sortState>
   </autoFilter>
@@ -17060,7 +17134,7 @@
         <v>387</v>
       </c>
       <c r="I3" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -17325,28 +17399,28 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>2521</v>
+        <v>2519</v>
       </c>
       <c r="B14" t="s">
         <v>382</v>
       </c>
       <c r="C14" t="s">
+        <v>2520</v>
+      </c>
+      <c r="D14" t="s">
+        <v>2521</v>
+      </c>
+      <c r="E14" t="s">
         <v>2522</v>
       </c>
-      <c r="D14" t="s">
+      <c r="F14" t="s">
         <v>2523</v>
-      </c>
-      <c r="E14" t="s">
-        <v>2524</v>
-      </c>
-      <c r="F14" t="s">
-        <v>2525</v>
       </c>
       <c r="G14" t="s">
         <v>989</v>
       </c>
       <c r="I14" t="s">
-        <v>2526</v>
+        <v>2524</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
@@ -17481,28 +17555,28 @@
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>2559</v>
+        <v>2557</v>
       </c>
       <c r="B20" t="s">
         <v>433</v>
       </c>
       <c r="C20" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2563</v>
+        <v>2561</v>
       </c>
       <c r="E20" t="s">
         <v>844</v>
       </c>
       <c r="F20" t="s">
-        <v>2561</v>
+        <v>2559</v>
       </c>
       <c r="G20" t="s">
-        <v>2562</v>
+        <v>2560</v>
       </c>
       <c r="I20" t="s">
-        <v>2560</v>
+        <v>2558</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
@@ -18145,7 +18219,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CB78C2-2208-4DF0-8ABB-0CE48BD26296}">
-  <dimension ref="A1:J77"/>
+  <dimension ref="A1:J78"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
@@ -18687,7 +18761,7 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>2585</v>
+        <v>2583</v>
       </c>
       <c r="B21" t="s">
         <v>17</v>
@@ -18696,13 +18770,13 @@
         <v>198</v>
       </c>
       <c r="D21" t="s">
-        <v>2584</v>
+        <v>2582</v>
       </c>
       <c r="E21" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F21" t="s">
-        <v>2583</v>
+        <v>2581</v>
       </c>
       <c r="G21" t="s">
         <v>18</v>
@@ -19788,36 +19862,33 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>1149</v>
+        <v>2618</v>
       </c>
       <c r="B63" t="s">
-        <v>1112</v>
+        <v>17</v>
       </c>
       <c r="C63" t="s">
-        <v>1148</v>
+        <v>281</v>
       </c>
       <c r="D63" t="s">
-        <v>1150</v>
+        <v>540</v>
       </c>
       <c r="E63" s="1" t="s">
-        <v>1151</v>
+        <v>70</v>
       </c>
       <c r="F63" t="s">
-        <v>1152</v>
+        <v>2617</v>
       </c>
       <c r="G63" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H63" t="s">
-        <v>1114</v>
+        <v>120</v>
       </c>
       <c r="I63" t="s">
-        <v>818</v>
+        <v>20</v>
       </c>
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>2023</v>
+        <v>1149</v>
       </c>
       <c r="B64" t="s">
         <v>1112</v>
@@ -19826,16 +19897,19 @@
         <v>1148</v>
       </c>
       <c r="D64" t="s">
-        <v>2024</v>
+        <v>1150</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>1151</v>
       </c>
       <c r="F64" t="s">
-        <v>2025</v>
+        <v>1152</v>
       </c>
       <c r="G64" t="s">
-        <v>2026</v>
+        <v>1116</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1114</v>
       </c>
       <c r="I64" t="s">
         <v>818</v>
@@ -19843,28 +19917,25 @@
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>2031</v>
+        <v>2023</v>
       </c>
       <c r="B65" t="s">
-        <v>812</v>
+        <v>1112</v>
       </c>
       <c r="C65" t="s">
         <v>1148</v>
       </c>
       <c r="D65" t="s">
-        <v>2032</v>
-      </c>
-      <c r="E65" t="s">
-        <v>814</v>
+        <v>2024</v>
+      </c>
+      <c r="E65" s="1" t="s">
+        <v>1151</v>
       </c>
       <c r="F65" t="s">
-        <v>2033</v>
+        <v>2025</v>
       </c>
       <c r="G65" t="s">
-        <v>2030</v>
-      </c>
-      <c r="H65" t="s">
-        <v>2034</v>
+        <v>2026</v>
       </c>
       <c r="I65" t="s">
         <v>818</v>
@@ -19872,51 +19943,54 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>161</v>
+        <v>2031</v>
       </c>
       <c r="B66" t="s">
-        <v>17</v>
+        <v>812</v>
       </c>
       <c r="C66" t="s">
-        <v>160</v>
+        <v>1148</v>
       </c>
       <c r="D66" t="s">
-        <v>159</v>
-      </c>
-      <c r="E66" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F66" s="1" t="s">
-        <v>158</v>
+        <v>2032</v>
+      </c>
+      <c r="E66" t="s">
+        <v>814</v>
+      </c>
+      <c r="F66" t="s">
+        <v>2033</v>
       </c>
       <c r="G66" t="s">
-        <v>18</v>
+        <v>2030</v>
+      </c>
+      <c r="H66" t="s">
+        <v>2034</v>
       </c>
       <c r="I66" t="s">
-        <v>20</v>
+        <v>818</v>
       </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>979</v>
+        <v>161</v>
       </c>
       <c r="B67" t="s">
         <v>17</v>
       </c>
       <c r="C67" t="s">
-        <v>980</v>
+        <v>160</v>
       </c>
       <c r="D67" t="s">
-        <v>981</v>
+        <v>159</v>
       </c>
       <c r="E67" s="1" t="s">
-        <v>982</v>
+        <v>12</v>
       </c>
       <c r="F67" s="1" t="s">
-        <v>983</v>
+        <v>158</v>
       </c>
       <c r="G67" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="I67" t="s">
         <v>20</v>
@@ -19924,7 +19998,7 @@
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>2239</v>
+        <v>979</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
@@ -19933,16 +20007,16 @@
         <v>980</v>
       </c>
       <c r="D68" t="s">
-        <v>2240</v>
+        <v>981</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>1009</v>
+        <v>982</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>2241</v>
+        <v>983</v>
       </c>
       <c r="G68" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="I68" t="s">
         <v>20</v>
@@ -19950,62 +20024,62 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>1144</v>
+        <v>2239</v>
       </c>
       <c r="B69" t="s">
-        <v>1112</v>
+        <v>17</v>
       </c>
       <c r="C69" t="s">
-        <v>1145</v>
+        <v>980</v>
       </c>
       <c r="D69" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E69" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F69" t="s">
-        <v>1147</v>
+        <v>2240</v>
+      </c>
+      <c r="E69" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F69" s="1" t="s">
+        <v>2241</v>
       </c>
       <c r="G69" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H69" t="s">
-        <v>1114</v>
+        <v>18</v>
       </c>
       <c r="I69" t="s">
-        <v>818</v>
+        <v>20</v>
       </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>58</v>
+        <v>1144</v>
       </c>
       <c r="B70" t="s">
-        <v>17</v>
+        <v>1112</v>
       </c>
       <c r="C70" t="s">
-        <v>282</v>
+        <v>1145</v>
       </c>
       <c r="D70" t="s">
-        <v>59</v>
-      </c>
-      <c r="E70" s="1" t="s">
-        <v>12</v>
+        <v>1146</v>
+      </c>
+      <c r="E70" t="s">
+        <v>1115</v>
       </c>
       <c r="F70" t="s">
-        <v>60</v>
+        <v>1147</v>
       </c>
       <c r="G70" t="s">
-        <v>18</v>
+        <v>1116</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1114</v>
       </c>
       <c r="I70" t="s">
-        <v>20</v>
+        <v>818</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -20014,16 +20088,16 @@
         <v>282</v>
       </c>
       <c r="D71" t="s">
-        <v>68</v>
-      </c>
-      <c r="E71" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="E71" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F71" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G71" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="I71" t="s">
         <v>20</v>
@@ -20031,7 +20105,7 @@
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>1452</v>
+        <v>67</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -20040,16 +20114,16 @@
         <v>282</v>
       </c>
       <c r="D72" t="s">
-        <v>1450</v>
-      </c>
-      <c r="E72" s="1" t="s">
-        <v>188</v>
+        <v>68</v>
+      </c>
+      <c r="E72" t="s">
+        <v>70</v>
       </c>
       <c r="F72" t="s">
-        <v>1451</v>
+        <v>69</v>
       </c>
       <c r="G72" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
       <c r="I72" t="s">
         <v>20</v>
@@ -20057,25 +20131,25 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>548</v>
+        <v>1452</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
       </c>
       <c r="C73" t="s">
-        <v>547</v>
+        <v>282</v>
       </c>
       <c r="D73" t="s">
-        <v>551</v>
+        <v>1450</v>
       </c>
       <c r="E73" s="1" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="F73" t="s">
-        <v>550</v>
+        <v>1451</v>
       </c>
       <c r="G73" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="I73" t="s">
         <v>20</v>
@@ -20083,7 +20157,7 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>2325</v>
+        <v>548</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
@@ -20092,16 +20166,16 @@
         <v>547</v>
       </c>
       <c r="D74" t="s">
-        <v>2326</v>
+        <v>551</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>188</v>
+        <v>12</v>
       </c>
       <c r="F74" t="s">
-        <v>2327</v>
+        <v>550</v>
       </c>
       <c r="G74" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="I74" t="s">
         <v>20</v>
@@ -20109,46 +20183,57 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B75" t="s">
+        <v>17</v>
+      </c>
+      <c r="C75" t="s">
+        <v>547</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E75" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F75" t="s">
+        <v>2327</v>
+      </c>
+      <c r="G75" t="s">
+        <v>120</v>
+      </c>
+      <c r="I75" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A76" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B75" t="s">
+      <c r="B76" t="s">
         <v>1112</v>
       </c>
-      <c r="C75" t="s">
+      <c r="C76" t="s">
         <v>1108</v>
       </c>
-      <c r="D75" t="s">
+      <c r="D76" t="s">
         <v>1111</v>
       </c>
-      <c r="E75" t="s">
+      <c r="E76" t="s">
         <v>1115</v>
       </c>
-      <c r="F75" t="s">
+      <c r="F76" t="s">
         <v>1113</v>
       </c>
-      <c r="G75" t="s">
+      <c r="G76" t="s">
         <v>1116</v>
       </c>
-      <c r="H75" t="s">
+      <c r="H76" t="s">
         <v>1114</v>
       </c>
-      <c r="I75" t="s">
+      <c r="I76" t="s">
         <v>818</v>
-      </c>
-    </row>
-    <row r="76" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B76" t="s">
-        <v>17</v>
-      </c>
-      <c r="C76" t="s">
-        <v>90</v>
-      </c>
-      <c r="E76" s="1"/>
-      <c r="G76" t="s">
-        <v>18</v>
-      </c>
-      <c r="I76" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
@@ -20158,10 +20243,25 @@
       <c r="C77" t="s">
         <v>90</v>
       </c>
+      <c r="E77" s="1"/>
       <c r="G77" t="s">
+        <v>18</v>
+      </c>
+      <c r="I77" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="78" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B78" t="s">
+        <v>17</v>
+      </c>
+      <c r="C78" t="s">
+        <v>90</v>
+      </c>
+      <c r="G78" t="s">
         <v>325</v>
       </c>
-      <c r="I77" t="s">
+      <c r="I78" t="s">
         <v>20</v>
       </c>
     </row>
@@ -20347,13 +20447,13 @@
         <v>2481</v>
       </c>
       <c r="D6" t="s">
-        <v>2617</v>
+        <v>2615</v>
       </c>
       <c r="E6" t="s">
         <v>2478</v>
       </c>
       <c r="F6" t="s">
-        <v>2616</v>
+        <v>2614</v>
       </c>
       <c r="G6" t="s">
         <v>2479</v>
@@ -20625,28 +20725,28 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>2511</v>
+        <v>2510</v>
       </c>
       <c r="B16" t="s">
         <v>1223</v>
       </c>
       <c r="C16" t="s">
-        <v>2618</v>
+        <v>2616</v>
       </c>
       <c r="D16" t="s">
-        <v>2512</v>
+        <v>2511</v>
       </c>
       <c r="E16" t="s">
         <v>1966</v>
       </c>
       <c r="F16" t="s">
-        <v>2510</v>
+        <v>2509</v>
       </c>
       <c r="G16" t="s">
-        <v>2513</v>
+        <v>2628</v>
       </c>
       <c r="I16" t="s">
-        <v>2509</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
@@ -21518,31 +21618,31 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>2553</v>
+        <v>2551</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>33</v>
       </c>
       <c r="C19" t="s">
-        <v>2555</v>
+        <v>2553</v>
       </c>
       <c r="D19" t="s">
-        <v>2554</v>
+        <v>2552</v>
       </c>
       <c r="E19" t="s">
         <v>864</v>
       </c>
       <c r="F19" t="s">
+        <v>2553</v>
+      </c>
+      <c r="G19" t="s">
+        <v>2554</v>
+      </c>
+      <c r="H19" t="s">
         <v>2555</v>
       </c>
-      <c r="G19" t="s">
+      <c r="I19" t="s">
         <v>2556</v>
-      </c>
-      <c r="H19" t="s">
-        <v>2557</v>
-      </c>
-      <c r="I19" t="s">
-        <v>2558</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
@@ -22406,7 +22506,7 @@
         <v>2483</v>
       </c>
       <c r="G49" t="s">
-        <v>2552</v>
+        <v>2550</v>
       </c>
       <c r="H49" t="s">
         <v>2486</v>
@@ -22974,10 +23074,11 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61606E71-114A-4060-B4DA-26AC2BA8C44E}">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:J25"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.08203125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="10.9140625" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.5" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
@@ -23560,25 +23661,25 @@
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>2564</v>
+        <v>2562</v>
       </c>
       <c r="B21" t="s">
         <v>2079</v>
       </c>
       <c r="C21" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2565</v>
+        <v>2563</v>
       </c>
       <c r="E21" t="s">
         <v>2410</v>
       </c>
       <c r="F21" t="s">
-        <v>2566</v>
+        <v>2564</v>
       </c>
       <c r="G21" t="s">
-        <v>2567</v>
+        <v>2565</v>
       </c>
       <c r="I21" t="s">
         <v>2083</v>
@@ -23586,54 +23687,103 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>2613</v>
+        <v>2625</v>
       </c>
       <c r="B22" t="s">
         <v>2079</v>
       </c>
       <c r="C22" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2565</v>
+        <v>2500</v>
       </c>
       <c r="E22" t="s">
-        <v>2614</v>
+        <v>2612</v>
       </c>
       <c r="F22" t="s">
-        <v>2615</v>
+        <v>2613</v>
       </c>
       <c r="G22" t="s">
-        <v>2567</v>
+        <v>2627</v>
       </c>
       <c r="I22" t="s">
-        <v>2083</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
+        <v>2611</v>
+      </c>
+      <c r="B23" t="s">
+        <v>2079</v>
+      </c>
+      <c r="C23" t="s">
+        <v>2626</v>
+      </c>
+      <c r="D23" s="6" t="s">
+        <v>2563</v>
+      </c>
+      <c r="E23" t="s">
+        <v>2612</v>
+      </c>
+      <c r="F23" t="s">
+        <v>2626</v>
+      </c>
+      <c r="G23" t="s">
+        <v>2565</v>
+      </c>
+      <c r="I23" t="s">
+        <v>2083</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
         <v>2111</v>
       </c>
-      <c r="B23" t="s">
+      <c r="B24" t="s">
         <v>2110</v>
       </c>
-      <c r="C23" t="s">
+      <c r="C24" t="s">
         <v>2112</v>
       </c>
-      <c r="D23" s="6" t="s">
+      <c r="D24" s="6" t="s">
         <v>2113</v>
       </c>
-      <c r="E23" t="s">
+      <c r="E24" t="s">
         <v>2114</v>
       </c>
-      <c r="F23" t="s">
+      <c r="F24" t="s">
         <v>2112</v>
       </c>
-      <c r="G23" t="s">
+      <c r="G24" t="s">
         <v>2112</v>
       </c>
-      <c r="I23" t="s">
+      <c r="I24" t="s">
         <v>2115</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>2620</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2619</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2621</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>2622</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2621</v>
+      </c>
+      <c r="G25" t="s">
+        <v>2624</v>
+      </c>
+      <c r="I25" t="s">
+        <v>2623</v>
       </c>
     </row>
   </sheetData>
@@ -23703,7 +23853,7 @@
         <v>78</v>
       </c>
       <c r="C2" t="s">
-        <v>2574</v>
+        <v>2572</v>
       </c>
       <c r="D2" t="s">
         <v>396</v>
@@ -23723,7 +23873,7 @@
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="2" t="s">
-        <v>2576</v>
+        <v>2574</v>
       </c>
       <c r="B3" s="2" t="s">
         <v>78</v>
@@ -23732,16 +23882,16 @@
         <v>77</v>
       </c>
       <c r="D3" t="s">
-        <v>2575</v>
+        <v>2573</v>
       </c>
       <c r="E3" t="s">
         <v>79</v>
       </c>
       <c r="F3" t="s">
-        <v>2577</v>
+        <v>2575</v>
       </c>
       <c r="G3" t="s">
-        <v>2578</v>
+        <v>2576</v>
       </c>
       <c r="I3" t="s">
         <v>76</v>
@@ -23749,7 +23899,7 @@
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="2" t="s">
-        <v>2594</v>
+        <v>2592</v>
       </c>
       <c r="B4" s="2" t="s">
         <v>78</v>
@@ -23758,16 +23908,16 @@
         <v>77</v>
       </c>
       <c r="D4" t="s">
-        <v>2595</v>
+        <v>2593</v>
       </c>
       <c r="E4" t="s">
         <v>79</v>
       </c>
       <c r="F4" t="s">
-        <v>2596</v>
+        <v>2594</v>
       </c>
       <c r="G4" t="s">
-        <v>2597</v>
+        <v>2595</v>
       </c>
       <c r="I4" t="s">
         <v>76</v>
@@ -24217,7 +24367,7 @@
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>2536</v>
+        <v>2534</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>78</v>
@@ -24226,13 +24376,13 @@
         <v>821</v>
       </c>
       <c r="D22" t="s">
-        <v>2537</v>
+        <v>2535</v>
       </c>
       <c r="E22" t="s">
         <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>2539</v>
+        <v>2537</v>
       </c>
       <c r="G22" t="s">
         <v>1433</v>
@@ -24414,7 +24564,7 @@
         <v>79</v>
       </c>
       <c r="F29" t="s">
-        <v>2538</v>
+        <v>2536</v>
       </c>
       <c r="G29" t="s">
         <v>1433</v>
@@ -24755,7 +24905,7 @@
         <v>2450</v>
       </c>
       <c r="G42" t="s">
-        <v>2569</v>
+        <v>2567</v>
       </c>
       <c r="I42" t="s">
         <v>2448</v>

--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{647804E1-485E-4B5B-82C7-6EDD00D54CC5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E64ABD45-7AB3-499F-ABE8-1A85F9C11C4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="11" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4670" uniqueCount="2632">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4721" uniqueCount="2660">
   <si>
     <t>Part Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -10217,6 +10217,116 @@
   </si>
   <si>
     <t>Crystal;25MHZ;12pF;+/-10PPM;HC-49S-SMD</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6611600024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>XWRJ-1108C1016-12</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>讯旺电子科技</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RJ45_TFx1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RJ45+TFx1-1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1511100007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMAJ5.0A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TVS二极管;Vrwm=5V;Vbr= 6.40~7.00;Vc=9.2;Ipp=43.5;DFN1610-2L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MDD(辰达半导体)</t>
+  </si>
+  <si>
+    <t>SMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1411100005</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SS34</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>肖特基二极管;VR=40V;VF=0.55V;IF=3A;SMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SMA</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311107003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RST100UF25V004</t>
+  </si>
+  <si>
+    <t>6.3x5.4mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAP ELE;100uF;+/-20%;25V;88mA@120Hz;6.3x5.4mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-07560RL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>560R</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111561000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;560KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051000021</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AX99100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AX99100A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>亚信电子(ASIX)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCIe to Multi I/O Controller;Dual or Quad UARTs;Supports RS-232/RS-422/RS-485 multiprotocol</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qfn-68-8x8-ep43</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -10720,7 +10830,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J157"/>
+  <dimension ref="A1:J158"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" style="2" bestFit="1" customWidth="1"/>
@@ -14140,22 +14250,22 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>606</v>
+        <v>2652</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>607</v>
+        <v>2651</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>608</v>
+        <v>2653</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>609</v>
+        <v>2650</v>
       </c>
       <c r="G132" t="s">
         <v>19</v>
@@ -14166,25 +14276,25 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>400</v>
+        <v>606</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>399</v>
+        <v>607</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>402</v>
+        <v>608</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>401</v>
+        <v>609</v>
       </c>
       <c r="G133" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>339</v>
@@ -14192,24 +14302,24 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>331</v>
+        <v>400</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C134" s="1" t="s">
-        <v>330</v>
+        <v>399</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>329</v>
+        <v>402</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>328</v>
-      </c>
-      <c r="G134" s="1" t="s">
+        <v>401</v>
+      </c>
+      <c r="G134" t="s">
         <v>332</v>
       </c>
       <c r="I134" s="1" t="s">
@@ -14218,7 +14328,7 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>338</v>
+        <v>331</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>10</v>
@@ -14227,16 +14337,16 @@
         <v>330</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>337</v>
+        <v>329</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1082</v>
-      </c>
-      <c r="G135" t="s">
-        <v>19</v>
+        <v>328</v>
+      </c>
+      <c r="G135" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>339</v>
@@ -14244,22 +14354,22 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>1154</v>
+        <v>338</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1153</v>
+        <v>330</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1156</v>
+        <v>337</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1155</v>
+        <v>1082</v>
       </c>
       <c r="G136" t="s">
         <v>19</v>
@@ -14270,22 +14380,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>1703</v>
+        <v>1154</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>1704</v>
+        <v>1153</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>1705</v>
+        <v>1156</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>1706</v>
+        <v>1155</v>
       </c>
       <c r="G137" t="s">
         <v>19</v>
@@ -14296,25 +14406,25 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>1816</v>
+        <v>1703</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>1815</v>
+        <v>1704</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>1817</v>
+        <v>1705</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>1818</v>
-      </c>
-      <c r="G138" s="1" t="s">
-        <v>332</v>
+        <v>1706</v>
+      </c>
+      <c r="G138" t="s">
+        <v>19</v>
       </c>
       <c r="I138" s="1" t="s">
         <v>339</v>
@@ -14322,25 +14432,25 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>1079</v>
+        <v>1816</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>1080</v>
+        <v>1815</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>1081</v>
+        <v>1817</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>1083</v>
-      </c>
-      <c r="G139" t="s">
-        <v>19</v>
+        <v>1818</v>
+      </c>
+      <c r="G139" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>339</v>
@@ -14348,13 +14458,13 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>1675</v>
+        <v>1079</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C140" s="1" t="s">
-        <v>1674</v>
+        <v>1080</v>
       </c>
       <c r="D140" s="1" t="s">
         <v>1081</v>
@@ -14363,7 +14473,7 @@
         <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1676</v>
+        <v>1083</v>
       </c>
       <c r="G140" t="s">
         <v>19</v>
@@ -14374,25 +14484,25 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>1883</v>
+        <v>1675</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C141" s="1" t="s">
-        <v>1882</v>
+        <v>1674</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>1884</v>
+        <v>1081</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>1885</v>
-      </c>
-      <c r="G141" s="1" t="s">
-        <v>332</v>
+        <v>1676</v>
+      </c>
+      <c r="G141" t="s">
+        <v>19</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>339</v>
@@ -14400,25 +14510,25 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>1272</v>
+        <v>1883</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>1271</v>
+        <v>1882</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>1273</v>
+        <v>1884</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>1274</v>
-      </c>
-      <c r="G142" t="s">
-        <v>19</v>
+        <v>1885</v>
+      </c>
+      <c r="G142" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>339</v>
@@ -14426,22 +14536,22 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>1103</v>
+        <v>1272</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>1104</v>
+        <v>1271</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>1105</v>
+        <v>1273</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>1106</v>
+        <v>1274</v>
       </c>
       <c r="G143" t="s">
         <v>19</v>
@@ -14452,22 +14562,22 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>828</v>
+        <v>1103</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>827</v>
+        <v>1104</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>829</v>
+        <v>1105</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>826</v>
+        <v>1106</v>
       </c>
       <c r="G144" t="s">
         <v>19</v>
@@ -14478,22 +14588,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>1919</v>
+        <v>828</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C145" s="1" t="s">
-        <v>1918</v>
+        <v>827</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>1920</v>
+        <v>829</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>1921</v>
+        <v>826</v>
       </c>
       <c r="G145" t="s">
         <v>19</v>
@@ -14504,22 +14614,22 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>1303</v>
+        <v>1919</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>1302</v>
+        <v>1918</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>1304</v>
+        <v>1920</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1305</v>
+        <v>1921</v>
       </c>
       <c r="G146" t="s">
         <v>19</v>
@@ -14530,7 +14640,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>2340</v>
+        <v>1303</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>10</v>
@@ -14539,16 +14649,16 @@
         <v>1302</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>2341</v>
+        <v>1304</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>2342</v>
-      </c>
-      <c r="G147" s="1" t="s">
-        <v>332</v>
+        <v>1305</v>
+      </c>
+      <c r="G147" t="s">
+        <v>19</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>339</v>
@@ -14556,22 +14666,22 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>2315</v>
+        <v>2340</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>2316</v>
+        <v>1302</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>2317</v>
+        <v>2341</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>2318</v>
+        <v>2342</v>
       </c>
       <c r="G148" s="1" t="s">
         <v>332</v>
@@ -14582,25 +14692,25 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>622</v>
+        <v>2315</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C149" s="1" t="s">
-        <v>621</v>
+        <v>2316</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>620</v>
+        <v>2317</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>619</v>
-      </c>
-      <c r="G149" t="s">
-        <v>19</v>
+        <v>2318</v>
+      </c>
+      <c r="G149" s="1" t="s">
+        <v>332</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>339</v>
@@ -14608,22 +14718,22 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>1388</v>
+        <v>622</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>1387</v>
+        <v>621</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>1389</v>
+        <v>620</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>1390</v>
+        <v>619</v>
       </c>
       <c r="G150" t="s">
         <v>19</v>
@@ -14634,22 +14744,22 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>134</v>
+        <v>1388</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>271</v>
+        <v>1387</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>133</v>
+        <v>1389</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>131</v>
+        <v>1390</v>
       </c>
       <c r="G151" t="s">
         <v>19</v>
@@ -14660,22 +14770,22 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>1538</v>
+        <v>134</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>1537</v>
+        <v>271</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>1539</v>
+        <v>133</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1540</v>
+        <v>131</v>
       </c>
       <c r="G152" t="s">
         <v>19</v>
@@ -14686,25 +14796,25 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>690</v>
+        <v>1538</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>689</v>
+        <v>1537</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>688</v>
+        <v>1539</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>695</v>
+        <v>1540</v>
       </c>
       <c r="G153" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I153" s="1" t="s">
         <v>339</v>
@@ -14712,25 +14822,25 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>1053</v>
+        <v>690</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>1055</v>
+        <v>689</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>1056</v>
+        <v>688</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1057</v>
+        <v>695</v>
       </c>
       <c r="G154" t="s">
-        <v>19</v>
+        <v>332</v>
       </c>
       <c r="I154" s="1" t="s">
         <v>339</v>
@@ -14738,25 +14848,25 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>398</v>
+        <v>1053</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>397</v>
+        <v>1055</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>403</v>
+        <v>1056</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>401</v>
+        <v>1057</v>
       </c>
       <c r="G155" t="s">
-        <v>332</v>
+        <v>19</v>
       </c>
       <c r="I155" s="1" t="s">
         <v>339</v>
@@ -14764,22 +14874,22 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>694</v>
+        <v>398</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>693</v>
+        <v>397</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>692</v>
+        <v>403</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>691</v>
+        <v>401</v>
       </c>
       <c r="G156" t="s">
         <v>332</v>
@@ -14790,27 +14900,53 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
+        <v>694</v>
+      </c>
+      <c r="B157" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C157" s="1" t="s">
+        <v>693</v>
+      </c>
+      <c r="D157" s="1" t="s">
+        <v>692</v>
+      </c>
+      <c r="E157" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F157" s="1" t="s">
+        <v>691</v>
+      </c>
+      <c r="G157" t="s">
+        <v>332</v>
+      </c>
+      <c r="I157" s="1" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="158" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A158" s="2" t="s">
         <v>1649</v>
       </c>
-      <c r="B157" s="1" t="s">
+      <c r="B158" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="C157" s="1" t="s">
+      <c r="C158" s="1" t="s">
         <v>1648</v>
       </c>
-      <c r="D157" s="1" t="s">
+      <c r="D158" s="1" t="s">
         <v>1650</v>
       </c>
-      <c r="E157" s="1" t="s">
+      <c r="E158" s="1" t="s">
         <v>188</v>
       </c>
-      <c r="F157" s="1" t="s">
+      <c r="F158" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="G157" s="1" t="s">
+      <c r="G158" s="1" t="s">
         <v>1652</v>
       </c>
-      <c r="I157" s="1" t="s">
+      <c r="I158" s="1" t="s">
         <v>1653</v>
       </c>
     </row>
@@ -16068,14 +16204,14 @@
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{013733C5-3D86-4F9A-8E9B-0FC55B649E0F}">
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="13.33203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="91.33203125" customWidth="1"/>
-    <col min="5" max="5" width="11.83203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.83203125" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="18.75" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="12.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="9.83203125" bestFit="1" customWidth="1"/>
@@ -16194,48 +16330,48 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>125</v>
+        <v>2637</v>
       </c>
       <c r="B5" t="s">
-        <v>1259</v>
+        <v>107</v>
       </c>
       <c r="C5" t="s">
-        <v>126</v>
+        <v>2638</v>
       </c>
       <c r="D5" t="s">
-        <v>151</v>
+        <v>2639</v>
       </c>
       <c r="E5" t="s">
-        <v>56</v>
+        <v>2640</v>
       </c>
       <c r="F5" t="s">
-        <v>122</v>
+        <v>2638</v>
       </c>
       <c r="G5" t="s">
-        <v>123</v>
+        <v>2641</v>
       </c>
       <c r="I5" t="s">
-        <v>1260</v>
+        <v>2388</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" s="2" t="s">
-        <v>1355</v>
+        <v>125</v>
       </c>
       <c r="B6" t="s">
         <v>1259</v>
       </c>
       <c r="C6" t="s">
-        <v>855</v>
+        <v>126</v>
       </c>
       <c r="D6" t="s">
-        <v>1353</v>
+        <v>151</v>
       </c>
       <c r="E6" t="s">
         <v>56</v>
       </c>
       <c r="F6" t="s">
-        <v>856</v>
+        <v>122</v>
       </c>
       <c r="G6" t="s">
         <v>123</v>
@@ -16246,103 +16382,103 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="B7" t="s">
         <v>1259</v>
       </c>
       <c r="C7" t="s">
-        <v>1352</v>
+        <v>855</v>
       </c>
       <c r="D7" t="s">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="E7" t="s">
         <v>56</v>
       </c>
       <c r="F7" t="s">
-        <v>1351</v>
+        <v>856</v>
       </c>
       <c r="G7" t="s">
-        <v>1357</v>
+        <v>123</v>
       </c>
       <c r="I7" t="s">
-        <v>1358</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>2019</v>
+        <v>1356</v>
       </c>
       <c r="B8" t="s">
         <v>1259</v>
       </c>
       <c r="C8" t="s">
-        <v>2020</v>
+        <v>1352</v>
       </c>
       <c r="D8" t="s">
-        <v>2021</v>
+        <v>1354</v>
       </c>
       <c r="E8" t="s">
         <v>56</v>
       </c>
       <c r="F8" t="s">
-        <v>2022</v>
+        <v>1351</v>
       </c>
       <c r="G8" t="s">
-        <v>123</v>
+        <v>1357</v>
       </c>
       <c r="I8" t="s">
-        <v>1260</v>
+        <v>1358</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1600</v>
+        <v>2019</v>
       </c>
       <c r="B9" t="s">
-        <v>1594</v>
+        <v>1259</v>
       </c>
       <c r="C9" t="s">
-        <v>1595</v>
+        <v>2020</v>
       </c>
       <c r="D9" t="s">
-        <v>1599</v>
+        <v>2021</v>
       </c>
       <c r="E9" t="s">
-        <v>1596</v>
+        <v>56</v>
       </c>
       <c r="F9" t="s">
-        <v>1595</v>
+        <v>2022</v>
       </c>
       <c r="G9" t="s">
-        <v>1597</v>
+        <v>123</v>
       </c>
       <c r="I9" t="s">
-        <v>1598</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>2529</v>
+        <v>1600</v>
       </c>
       <c r="B10" t="s">
         <v>1594</v>
       </c>
       <c r="C10" t="s">
-        <v>2530</v>
+        <v>1595</v>
       </c>
       <c r="D10" t="s">
-        <v>2532</v>
+        <v>1599</v>
       </c>
       <c r="E10" t="s">
-        <v>2531</v>
+        <v>1596</v>
       </c>
       <c r="F10" t="s">
-        <v>2533</v>
+        <v>1595</v>
       </c>
       <c r="G10" t="s">
-        <v>129</v>
+        <v>1597</v>
       </c>
       <c r="I10" t="s">
         <v>1598</v>
@@ -16350,27 +16486,53 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>2596</v>
+        <v>2529</v>
       </c>
       <c r="B11" t="s">
         <v>1594</v>
       </c>
       <c r="C11" t="s">
+        <v>2530</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2532</v>
+      </c>
+      <c r="E11" t="s">
+        <v>2531</v>
+      </c>
+      <c r="F11" t="s">
+        <v>2533</v>
+      </c>
+      <c r="G11" t="s">
+        <v>129</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1598</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
+        <v>2596</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1594</v>
+      </c>
+      <c r="C12" t="s">
         <v>2597</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D12" t="s">
         <v>2598</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E12" t="s">
         <v>2599</v>
       </c>
-      <c r="F11" t="s">
+      <c r="F12" t="s">
         <v>2597</v>
       </c>
-      <c r="G11" t="s">
+      <c r="G12" t="s">
         <v>1597</v>
       </c>
-      <c r="I11" t="s">
+      <c r="I12" t="s">
         <v>1598</v>
       </c>
     </row>
@@ -18219,7 +18381,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CB78C2-2208-4DF0-8ABB-0CE48BD26296}">
-  <dimension ref="A1:J78"/>
+  <dimension ref="A1:J79"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
@@ -19310,28 +19472,28 @@
     </row>
     <row r="42" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>1120</v>
+        <v>2646</v>
       </c>
       <c r="B42" t="s">
-        <v>1112</v>
+        <v>812</v>
       </c>
       <c r="C42" t="s">
         <v>816</v>
       </c>
       <c r="D42" t="s">
-        <v>1121</v>
+        <v>2649</v>
       </c>
       <c r="E42" t="s">
-        <v>1122</v>
+        <v>814</v>
       </c>
       <c r="F42" t="s">
-        <v>1123</v>
+        <v>2647</v>
       </c>
       <c r="G42" t="s">
-        <v>1116</v>
+        <v>817</v>
       </c>
       <c r="H42" t="s">
-        <v>1114</v>
+        <v>2648</v>
       </c>
       <c r="I42" t="s">
         <v>818</v>
@@ -19339,28 +19501,28 @@
     </row>
     <row r="43" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A43" s="2" t="s">
-        <v>2027</v>
+        <v>1120</v>
       </c>
       <c r="B43" t="s">
-        <v>812</v>
+        <v>1112</v>
       </c>
       <c r="C43" t="s">
         <v>816</v>
       </c>
       <c r="D43" t="s">
-        <v>2029</v>
+        <v>1121</v>
       </c>
       <c r="E43" t="s">
-        <v>814</v>
+        <v>1122</v>
       </c>
       <c r="F43" t="s">
-        <v>2028</v>
+        <v>1123</v>
       </c>
       <c r="G43" t="s">
-        <v>2030</v>
+        <v>1116</v>
       </c>
       <c r="H43" t="s">
-        <v>2034</v>
+        <v>1114</v>
       </c>
       <c r="I43" t="s">
         <v>818</v>
@@ -19368,48 +19530,51 @@
     </row>
     <row r="44" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A44" s="2" t="s">
-        <v>1250</v>
+        <v>2027</v>
       </c>
       <c r="B44" t="s">
-        <v>17</v>
+        <v>812</v>
       </c>
       <c r="C44" t="s">
-        <v>1249</v>
+        <v>816</v>
       </c>
       <c r="D44" t="s">
-        <v>1252</v>
-      </c>
-      <c r="E44" s="1" t="s">
-        <v>12</v>
+        <v>2029</v>
+      </c>
+      <c r="E44" t="s">
+        <v>814</v>
       </c>
       <c r="F44" t="s">
-        <v>1251</v>
+        <v>2028</v>
       </c>
       <c r="G44" t="s">
-        <v>18</v>
+        <v>2030</v>
+      </c>
+      <c r="H44" t="s">
+        <v>2034</v>
       </c>
       <c r="I44" t="s">
-        <v>20</v>
+        <v>818</v>
       </c>
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>349</v>
+        <v>1250</v>
       </c>
       <c r="B45" t="s">
         <v>17</v>
       </c>
       <c r="C45" t="s">
-        <v>348</v>
+        <v>1249</v>
       </c>
       <c r="D45" t="s">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="E45" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F45" t="s">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="G45" t="s">
         <v>18</v>
@@ -19420,22 +19585,22 @@
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
-        <v>2038</v>
+        <v>349</v>
       </c>
       <c r="B46" t="s">
         <v>17</v>
       </c>
       <c r="C46" t="s">
-        <v>2037</v>
+        <v>348</v>
       </c>
       <c r="D46" t="s">
-        <v>2036</v>
+        <v>1254</v>
       </c>
       <c r="E46" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F46" t="s">
-        <v>2035</v>
+        <v>1253</v>
       </c>
       <c r="G46" t="s">
         <v>18</v>
@@ -19446,25 +19611,25 @@
     </row>
     <row r="47" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A47" s="2" t="s">
-        <v>417</v>
+        <v>2038</v>
       </c>
       <c r="B47" t="s">
         <v>17</v>
       </c>
       <c r="C47" t="s">
-        <v>416</v>
+        <v>2037</v>
       </c>
       <c r="D47" t="s">
-        <v>1256</v>
+        <v>2036</v>
       </c>
       <c r="E47" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F47" t="s">
-        <v>1255</v>
+        <v>2035</v>
       </c>
       <c r="G47" t="s">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="I47" t="s">
         <v>20</v>
@@ -19472,7 +19637,7 @@
     </row>
     <row r="48" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A48" s="2" t="s">
-        <v>887</v>
+        <v>417</v>
       </c>
       <c r="B48" t="s">
         <v>17</v>
@@ -19481,16 +19646,16 @@
         <v>416</v>
       </c>
       <c r="D48" t="s">
-        <v>1441</v>
+        <v>1256</v>
       </c>
       <c r="E48" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F48" t="s">
-        <v>888</v>
+        <v>1255</v>
       </c>
       <c r="G48" t="s">
-        <v>18</v>
+        <v>325</v>
       </c>
       <c r="I48" t="s">
         <v>20</v>
@@ -19498,22 +19663,22 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>197</v>
+        <v>887</v>
       </c>
       <c r="B49" t="s">
         <v>17</v>
       </c>
       <c r="C49" t="s">
-        <v>198</v>
+        <v>416</v>
       </c>
       <c r="D49" t="s">
-        <v>196</v>
+        <v>1441</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F49" t="s">
-        <v>195</v>
+        <v>888</v>
       </c>
       <c r="G49" t="s">
         <v>18</v>
@@ -19524,22 +19689,22 @@
     </row>
     <row r="50" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A50" s="2" t="s">
-        <v>1091</v>
+        <v>197</v>
       </c>
       <c r="B50" t="s">
         <v>17</v>
       </c>
       <c r="C50" t="s">
-        <v>1092</v>
+        <v>198</v>
       </c>
       <c r="D50" t="s">
-        <v>1442</v>
+        <v>196</v>
       </c>
       <c r="E50" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F50" t="s">
-        <v>1093</v>
+        <v>195</v>
       </c>
       <c r="G50" t="s">
         <v>18</v>
@@ -19550,22 +19715,22 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>167</v>
+        <v>1091</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>166</v>
+        <v>1092</v>
       </c>
       <c r="D51" t="s">
-        <v>165</v>
+        <v>1442</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>164</v>
+        <v>1093</v>
       </c>
       <c r="G51" t="s">
         <v>18</v>
@@ -19576,7 +19741,7 @@
     </row>
     <row r="52" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A52" s="2" t="s">
-        <v>1487</v>
+        <v>167</v>
       </c>
       <c r="B52" t="s">
         <v>17</v>
@@ -19585,16 +19750,16 @@
         <v>166</v>
       </c>
       <c r="D52" t="s">
-        <v>1488</v>
+        <v>165</v>
       </c>
       <c r="E52" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F52" t="s">
-        <v>1489</v>
+        <v>164</v>
       </c>
       <c r="G52" t="s">
-        <v>325</v>
+        <v>18</v>
       </c>
       <c r="I52" t="s">
         <v>20</v>
@@ -19602,25 +19767,25 @@
     </row>
     <row r="53" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A53" s="2" t="s">
-        <v>1130</v>
+        <v>1487</v>
       </c>
       <c r="B53" t="s">
         <v>17</v>
       </c>
       <c r="C53" t="s">
-        <v>1131</v>
+        <v>166</v>
       </c>
       <c r="D53" t="s">
-        <v>1581</v>
+        <v>1488</v>
       </c>
       <c r="E53" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F53" t="s">
-        <v>1580</v>
+        <v>1489</v>
       </c>
       <c r="G53" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="I53" t="s">
         <v>20</v>
@@ -19628,7 +19793,7 @@
     </row>
     <row r="54" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A54" s="2" t="s">
-        <v>1385</v>
+        <v>1130</v>
       </c>
       <c r="B54" t="s">
         <v>17</v>
@@ -19637,16 +19802,16 @@
         <v>1131</v>
       </c>
       <c r="D54" t="s">
-        <v>1386</v>
+        <v>1581</v>
       </c>
       <c r="E54" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F54" t="s">
-        <v>1579</v>
+        <v>1580</v>
       </c>
       <c r="G54" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="I54" t="s">
         <v>20</v>
@@ -19654,22 +19819,22 @@
     </row>
     <row r="55" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A55" s="2" t="s">
-        <v>170</v>
+        <v>1385</v>
       </c>
       <c r="B55" t="s">
         <v>17</v>
       </c>
       <c r="C55" t="s">
-        <v>280</v>
+        <v>1131</v>
       </c>
       <c r="D55" t="s">
-        <v>169</v>
+        <v>1386</v>
       </c>
       <c r="E55" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F55" t="s">
-        <v>168</v>
+        <v>1579</v>
       </c>
       <c r="G55" t="s">
         <v>18</v>
@@ -19680,7 +19845,7 @@
     </row>
     <row r="56" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A56" s="2" t="s">
-        <v>1591</v>
+        <v>170</v>
       </c>
       <c r="B56" t="s">
         <v>17</v>
@@ -19689,16 +19854,16 @@
         <v>280</v>
       </c>
       <c r="D56" t="s">
-        <v>1593</v>
+        <v>169</v>
       </c>
       <c r="E56" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F56" t="s">
-        <v>1592</v>
+        <v>168</v>
       </c>
       <c r="G56" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="I56" t="s">
         <v>20</v>
@@ -19706,7 +19871,7 @@
     </row>
     <row r="57" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A57" s="2" t="s">
-        <v>1905</v>
+        <v>1591</v>
       </c>
       <c r="B57" t="s">
         <v>17</v>
@@ -19715,16 +19880,16 @@
         <v>280</v>
       </c>
       <c r="D57" t="s">
-        <v>1906</v>
+        <v>1593</v>
       </c>
       <c r="E57" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F57" t="s">
-        <v>1907</v>
+        <v>1592</v>
       </c>
       <c r="G57" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
       <c r="I57" t="s">
         <v>20</v>
@@ -19732,25 +19897,25 @@
     </row>
     <row r="58" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A58" s="2" t="s">
-        <v>121</v>
+        <v>1905</v>
       </c>
       <c r="B58" t="s">
         <v>17</v>
       </c>
       <c r="C58" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D58" t="s">
-        <v>540</v>
+        <v>1906</v>
       </c>
       <c r="E58" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F58" t="s">
-        <v>549</v>
+        <v>1907</v>
       </c>
       <c r="G58" t="s">
-        <v>120</v>
+        <v>325</v>
       </c>
       <c r="I58" t="s">
         <v>20</v>
@@ -19758,7 +19923,7 @@
     </row>
     <row r="59" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A59" s="2" t="s">
-        <v>1117</v>
+        <v>121</v>
       </c>
       <c r="B59" t="s">
         <v>17</v>
@@ -19767,16 +19932,16 @@
         <v>281</v>
       </c>
       <c r="D59" t="s">
-        <v>1118</v>
+        <v>540</v>
       </c>
       <c r="E59" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F59" t="s">
-        <v>1119</v>
+        <v>549</v>
       </c>
       <c r="G59" t="s">
-        <v>71</v>
+        <v>120</v>
       </c>
       <c r="I59" t="s">
         <v>20</v>
@@ -19784,7 +19949,7 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>1434</v>
+        <v>1117</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
@@ -19793,16 +19958,16 @@
         <v>281</v>
       </c>
       <c r="D60" t="s">
-        <v>1436</v>
+        <v>1118</v>
       </c>
       <c r="E60" s="1" t="s">
-        <v>188</v>
+        <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>1435</v>
+        <v>1119</v>
       </c>
       <c r="G60" t="s">
-        <v>18</v>
+        <v>71</v>
       </c>
       <c r="I60" t="s">
         <v>20</v>
@@ -19810,7 +19975,7 @@
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="2" t="s">
-        <v>2219</v>
+        <v>1434</v>
       </c>
       <c r="B61" t="s">
         <v>17</v>
@@ -19819,16 +19984,16 @@
         <v>281</v>
       </c>
       <c r="D61" t="s">
-        <v>1118</v>
+        <v>1436</v>
       </c>
       <c r="E61" s="1" t="s">
-        <v>70</v>
+        <v>188</v>
       </c>
       <c r="F61" t="s">
-        <v>2218</v>
+        <v>1435</v>
       </c>
       <c r="G61" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="I61" t="s">
         <v>20</v>
@@ -19836,7 +20001,7 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>2223</v>
+        <v>2219</v>
       </c>
       <c r="B62" t="s">
         <v>17</v>
@@ -19845,16 +20010,16 @@
         <v>281</v>
       </c>
       <c r="D62" t="s">
-        <v>2224</v>
+        <v>1118</v>
       </c>
       <c r="E62" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F62" t="s">
-        <v>2225</v>
+        <v>2218</v>
       </c>
       <c r="G62" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="I62" t="s">
         <v>20</v>
@@ -19862,7 +20027,7 @@
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>2618</v>
+        <v>2223</v>
       </c>
       <c r="B63" t="s">
         <v>17</v>
@@ -19871,13 +20036,13 @@
         <v>281</v>
       </c>
       <c r="D63" t="s">
-        <v>540</v>
+        <v>2224</v>
       </c>
       <c r="E63" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F63" t="s">
-        <v>2617</v>
+        <v>2225</v>
       </c>
       <c r="G63" t="s">
         <v>120</v>
@@ -19888,36 +20053,33 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>1149</v>
+        <v>2618</v>
       </c>
       <c r="B64" t="s">
-        <v>1112</v>
+        <v>17</v>
       </c>
       <c r="C64" t="s">
-        <v>1148</v>
+        <v>281</v>
       </c>
       <c r="D64" t="s">
-        <v>1150</v>
+        <v>540</v>
       </c>
       <c r="E64" s="1" t="s">
-        <v>1151</v>
+        <v>70</v>
       </c>
       <c r="F64" t="s">
-        <v>1152</v>
+        <v>2617</v>
       </c>
       <c r="G64" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H64" t="s">
-        <v>1114</v>
+        <v>120</v>
       </c>
       <c r="I64" t="s">
-        <v>818</v>
+        <v>20</v>
       </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="2" t="s">
-        <v>2023</v>
+        <v>1149</v>
       </c>
       <c r="B65" t="s">
         <v>1112</v>
@@ -19926,16 +20088,19 @@
         <v>1148</v>
       </c>
       <c r="D65" t="s">
-        <v>2024</v>
+        <v>1150</v>
       </c>
       <c r="E65" s="1" t="s">
         <v>1151</v>
       </c>
       <c r="F65" t="s">
-        <v>2025</v>
+        <v>1152</v>
       </c>
       <c r="G65" t="s">
-        <v>2026</v>
+        <v>1116</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1114</v>
       </c>
       <c r="I65" t="s">
         <v>818</v>
@@ -19943,28 +20108,25 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>2031</v>
+        <v>2023</v>
       </c>
       <c r="B66" t="s">
-        <v>812</v>
+        <v>1112</v>
       </c>
       <c r="C66" t="s">
         <v>1148</v>
       </c>
       <c r="D66" t="s">
-        <v>2032</v>
-      </c>
-      <c r="E66" t="s">
-        <v>814</v>
+        <v>2024</v>
+      </c>
+      <c r="E66" s="1" t="s">
+        <v>1151</v>
       </c>
       <c r="F66" t="s">
-        <v>2033</v>
+        <v>2025</v>
       </c>
       <c r="G66" t="s">
-        <v>2030</v>
-      </c>
-      <c r="H66" t="s">
-        <v>2034</v>
+        <v>2026</v>
       </c>
       <c r="I66" t="s">
         <v>818</v>
@@ -19972,51 +20134,54 @@
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="2" t="s">
-        <v>161</v>
+        <v>2031</v>
       </c>
       <c r="B67" t="s">
-        <v>17</v>
+        <v>812</v>
       </c>
       <c r="C67" t="s">
-        <v>160</v>
+        <v>1148</v>
       </c>
       <c r="D67" t="s">
-        <v>159</v>
-      </c>
-      <c r="E67" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F67" s="1" t="s">
-        <v>158</v>
+        <v>2032</v>
+      </c>
+      <c r="E67" t="s">
+        <v>814</v>
+      </c>
+      <c r="F67" t="s">
+        <v>2033</v>
       </c>
       <c r="G67" t="s">
-        <v>18</v>
+        <v>2030</v>
+      </c>
+      <c r="H67" t="s">
+        <v>2034</v>
       </c>
       <c r="I67" t="s">
-        <v>20</v>
+        <v>818</v>
       </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="2" t="s">
-        <v>979</v>
+        <v>161</v>
       </c>
       <c r="B68" t="s">
         <v>17</v>
       </c>
       <c r="C68" t="s">
-        <v>980</v>
+        <v>160</v>
       </c>
       <c r="D68" t="s">
-        <v>981</v>
+        <v>159</v>
       </c>
       <c r="E68" s="1" t="s">
-        <v>982</v>
+        <v>12</v>
       </c>
       <c r="F68" s="1" t="s">
-        <v>983</v>
+        <v>158</v>
       </c>
       <c r="G68" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="I68" t="s">
         <v>20</v>
@@ -20024,7 +20189,7 @@
     </row>
     <row r="69" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A69" s="2" t="s">
-        <v>2239</v>
+        <v>979</v>
       </c>
       <c r="B69" t="s">
         <v>17</v>
@@ -20033,16 +20198,16 @@
         <v>980</v>
       </c>
       <c r="D69" t="s">
-        <v>2240</v>
+        <v>981</v>
       </c>
       <c r="E69" s="1" t="s">
-        <v>1009</v>
+        <v>982</v>
       </c>
       <c r="F69" s="1" t="s">
-        <v>2241</v>
+        <v>983</v>
       </c>
       <c r="G69" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="I69" t="s">
         <v>20</v>
@@ -20050,62 +20215,62 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>1144</v>
+        <v>2239</v>
       </c>
       <c r="B70" t="s">
-        <v>1112</v>
+        <v>17</v>
       </c>
       <c r="C70" t="s">
-        <v>1145</v>
+        <v>980</v>
       </c>
       <c r="D70" t="s">
-        <v>1146</v>
-      </c>
-      <c r="E70" t="s">
-        <v>1115</v>
-      </c>
-      <c r="F70" t="s">
-        <v>1147</v>
+        <v>2240</v>
+      </c>
+      <c r="E70" s="1" t="s">
+        <v>1009</v>
+      </c>
+      <c r="F70" s="1" t="s">
+        <v>2241</v>
       </c>
       <c r="G70" t="s">
-        <v>1116</v>
-      </c>
-      <c r="H70" t="s">
-        <v>1114</v>
+        <v>18</v>
       </c>
       <c r="I70" t="s">
-        <v>818</v>
+        <v>20</v>
       </c>
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>58</v>
+        <v>1144</v>
       </c>
       <c r="B71" t="s">
-        <v>17</v>
+        <v>1112</v>
       </c>
       <c r="C71" t="s">
-        <v>282</v>
+        <v>1145</v>
       </c>
       <c r="D71" t="s">
-        <v>59</v>
-      </c>
-      <c r="E71" s="1" t="s">
-        <v>12</v>
+        <v>1146</v>
+      </c>
+      <c r="E71" t="s">
+        <v>1115</v>
       </c>
       <c r="F71" t="s">
-        <v>60</v>
+        <v>1147</v>
       </c>
       <c r="G71" t="s">
-        <v>18</v>
+        <v>1116</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1114</v>
       </c>
       <c r="I71" t="s">
-        <v>20</v>
+        <v>818</v>
       </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B72" t="s">
         <v>17</v>
@@ -20114,16 +20279,16 @@
         <v>282</v>
       </c>
       <c r="D72" t="s">
-        <v>68</v>
-      </c>
-      <c r="E72" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="E72" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F72" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G72" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="I72" t="s">
         <v>20</v>
@@ -20131,7 +20296,7 @@
     </row>
     <row r="73" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A73" s="2" t="s">
-        <v>1452</v>
+        <v>67</v>
       </c>
       <c r="B73" t="s">
         <v>17</v>
@@ -20140,16 +20305,16 @@
         <v>282</v>
       </c>
       <c r="D73" t="s">
-        <v>1450</v>
-      </c>
-      <c r="E73" s="1" t="s">
-        <v>188</v>
+        <v>68</v>
+      </c>
+      <c r="E73" t="s">
+        <v>70</v>
       </c>
       <c r="F73" t="s">
-        <v>1451</v>
+        <v>69</v>
       </c>
       <c r="G73" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
       <c r="I73" t="s">
         <v>20</v>
@@ -20157,25 +20322,25 @@
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="2" t="s">
-        <v>548</v>
+        <v>1452</v>
       </c>
       <c r="B74" t="s">
         <v>17</v>
       </c>
       <c r="C74" t="s">
-        <v>547</v>
+        <v>282</v>
       </c>
       <c r="D74" t="s">
-        <v>551</v>
+        <v>1450</v>
       </c>
       <c r="E74" s="1" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="F74" t="s">
-        <v>550</v>
+        <v>1451</v>
       </c>
       <c r="G74" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="I74" t="s">
         <v>20</v>
@@ -20183,7 +20348,7 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>2325</v>
+        <v>548</v>
       </c>
       <c r="B75" t="s">
         <v>17</v>
@@ -20192,16 +20357,16 @@
         <v>547</v>
       </c>
       <c r="D75" t="s">
-        <v>2326</v>
+        <v>551</v>
       </c>
       <c r="E75" s="1" t="s">
-        <v>188</v>
+        <v>12</v>
       </c>
       <c r="F75" t="s">
-        <v>2327</v>
+        <v>550</v>
       </c>
       <c r="G75" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="I75" t="s">
         <v>20</v>
@@ -20209,46 +20374,57 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
+        <v>2325</v>
+      </c>
+      <c r="B76" t="s">
+        <v>17</v>
+      </c>
+      <c r="C76" t="s">
+        <v>547</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2326</v>
+      </c>
+      <c r="E76" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F76" t="s">
+        <v>2327</v>
+      </c>
+      <c r="G76" t="s">
+        <v>120</v>
+      </c>
+      <c r="I76" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A77" s="2" t="s">
         <v>1110</v>
       </c>
-      <c r="B76" t="s">
+      <c r="B77" t="s">
         <v>1112</v>
       </c>
-      <c r="C76" t="s">
+      <c r="C77" t="s">
         <v>1108</v>
       </c>
-      <c r="D76" t="s">
+      <c r="D77" t="s">
         <v>1111</v>
       </c>
-      <c r="E76" t="s">
+      <c r="E77" t="s">
         <v>1115</v>
       </c>
-      <c r="F76" t="s">
+      <c r="F77" t="s">
         <v>1113</v>
       </c>
-      <c r="G76" t="s">
+      <c r="G77" t="s">
         <v>1116</v>
       </c>
-      <c r="H76" t="s">
+      <c r="H77" t="s">
         <v>1114</v>
       </c>
-      <c r="I76" t="s">
+      <c r="I77" t="s">
         <v>818</v>
-      </c>
-    </row>
-    <row r="77" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B77" t="s">
-        <v>17</v>
-      </c>
-      <c r="C77" t="s">
-        <v>90</v>
-      </c>
-      <c r="E77" s="1"/>
-      <c r="G77" t="s">
-        <v>18</v>
-      </c>
-      <c r="I77" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
@@ -20258,10 +20434,25 @@
       <c r="C78" t="s">
         <v>90</v>
       </c>
+      <c r="E78" s="1"/>
       <c r="G78" t="s">
+        <v>18</v>
+      </c>
+      <c r="I78" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="79" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B79" t="s">
+        <v>17</v>
+      </c>
+      <c r="C79" t="s">
+        <v>90</v>
+      </c>
+      <c r="G79" t="s">
         <v>325</v>
       </c>
-      <c r="I78" t="s">
+      <c r="I79" t="s">
         <v>20</v>
       </c>
     </row>
@@ -20282,7 +20473,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C302E28E-61B5-45F2-9EED-9E658F066E8B}">
-  <dimension ref="A1:J22"/>
+  <dimension ref="A1:J23"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
@@ -20467,441 +20658,470 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>869</v>
+        <v>2654</v>
       </c>
       <c r="B7" t="s">
-        <v>29</v>
+        <v>305</v>
       </c>
       <c r="C7" t="s">
-        <v>870</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>871</v>
+        <v>2656</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2658</v>
       </c>
       <c r="E7" t="s">
-        <v>873</v>
+        <v>2657</v>
       </c>
       <c r="F7" t="s">
-        <v>874</v>
+        <v>2656</v>
       </c>
       <c r="G7" t="s">
-        <v>875</v>
+        <v>2659</v>
       </c>
       <c r="H7" t="s">
-        <v>872</v>
+        <v>2480</v>
       </c>
       <c r="I7" t="s">
-        <v>870</v>
+        <v>2655</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1010</v>
+        <v>869</v>
       </c>
       <c r="B8" t="s">
-        <v>1011</v>
+        <v>29</v>
       </c>
       <c r="C8" t="s">
-        <v>1012</v>
-      </c>
-      <c r="D8" t="s">
-        <v>1016</v>
+        <v>870</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>871</v>
       </c>
       <c r="E8" t="s">
-        <v>1013</v>
+        <v>873</v>
       </c>
       <c r="F8" t="s">
-        <v>1012</v>
+        <v>874</v>
       </c>
       <c r="G8" t="s">
-        <v>1018</v>
+        <v>875</v>
       </c>
       <c r="H8" t="s">
-        <v>1015</v>
+        <v>872</v>
       </c>
       <c r="I8" t="s">
-        <v>1014</v>
+        <v>870</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>1019</v>
+        <v>1010</v>
       </c>
       <c r="B9" t="s">
         <v>1011</v>
       </c>
       <c r="C9" t="s">
-        <v>1021</v>
+        <v>1012</v>
       </c>
       <c r="D9" t="s">
-        <v>1022</v>
+        <v>1016</v>
       </c>
       <c r="E9" t="s">
         <v>1013</v>
       </c>
       <c r="F9" t="s">
-        <v>1020</v>
+        <v>1012</v>
       </c>
       <c r="G9" t="s">
-        <v>1023</v>
+        <v>1018</v>
       </c>
       <c r="H9" t="s">
-        <v>1024</v>
+        <v>1015</v>
       </c>
       <c r="I9" t="s">
-        <v>1025</v>
+        <v>1014</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>1067</v>
+        <v>1019</v>
       </c>
       <c r="B10" t="s">
-        <v>1066</v>
+        <v>1011</v>
       </c>
       <c r="C10" t="s">
-        <v>1069</v>
+        <v>1021</v>
       </c>
       <c r="D10" t="s">
-        <v>1070</v>
+        <v>1022</v>
       </c>
       <c r="E10" t="s">
-        <v>1062</v>
+        <v>1013</v>
       </c>
       <c r="F10" t="s">
-        <v>1069</v>
+        <v>1020</v>
       </c>
       <c r="G10" t="s">
-        <v>1071</v>
+        <v>1023</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1024</v>
       </c>
       <c r="I10" t="s">
-        <v>1068</v>
+        <v>1025</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>1192</v>
+        <v>1067</v>
       </c>
       <c r="B11" t="s">
-        <v>29</v>
+        <v>1066</v>
       </c>
       <c r="C11" t="s">
-        <v>1193</v>
+        <v>1069</v>
       </c>
       <c r="D11" t="s">
-        <v>1194</v>
+        <v>1070</v>
       </c>
       <c r="E11" t="s">
-        <v>1195</v>
+        <v>1062</v>
       </c>
       <c r="F11" t="s">
-        <v>1193</v>
+        <v>1069</v>
       </c>
       <c r="G11" t="s">
-        <v>1196</v>
-      </c>
-      <c r="H11" t="s">
-        <v>1197</v>
+        <v>1071</v>
       </c>
       <c r="I11" t="s">
-        <v>1193</v>
+        <v>1068</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>1225</v>
+        <v>1192</v>
       </c>
       <c r="B12" t="s">
-        <v>1223</v>
+        <v>29</v>
       </c>
       <c r="C12" t="s">
-        <v>1224</v>
+        <v>1193</v>
       </c>
       <c r="D12" t="s">
-        <v>1230</v>
+        <v>1194</v>
       </c>
       <c r="E12" t="s">
-        <v>1226</v>
+        <v>1195</v>
       </c>
       <c r="F12" t="s">
-        <v>1227</v>
+        <v>1193</v>
       </c>
       <c r="G12" t="s">
-        <v>1228</v>
+        <v>1196</v>
       </c>
       <c r="H12" t="s">
-        <v>1229</v>
+        <v>1197</v>
       </c>
       <c r="I12" t="s">
-        <v>1224</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>1964</v>
+        <v>1225</v>
       </c>
       <c r="B13" t="s">
         <v>1223</v>
       </c>
       <c r="C13" t="s">
-        <v>1234</v>
+        <v>1224</v>
       </c>
       <c r="D13" t="s">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="E13" t="s">
         <v>1226</v>
       </c>
       <c r="F13" t="s">
-        <v>1232</v>
+        <v>1227</v>
       </c>
       <c r="G13" t="s">
-        <v>1233</v>
+        <v>1228</v>
       </c>
       <c r="H13" t="s">
-        <v>1197</v>
+        <v>1229</v>
       </c>
       <c r="I13" t="s">
-        <v>1234</v>
+        <v>1224</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>1970</v>
+        <v>1964</v>
       </c>
       <c r="B14" t="s">
         <v>1223</v>
       </c>
       <c r="C14" t="s">
-        <v>1965</v>
+        <v>1234</v>
       </c>
       <c r="D14" t="s">
-        <v>1969</v>
+        <v>1231</v>
       </c>
       <c r="E14" t="s">
-        <v>1966</v>
+        <v>1226</v>
       </c>
       <c r="F14" t="s">
-        <v>1967</v>
+        <v>1232</v>
       </c>
       <c r="G14" t="s">
-        <v>1968</v>
+        <v>1233</v>
       </c>
       <c r="H14" t="s">
         <v>1197</v>
       </c>
       <c r="I14" t="s">
-        <v>2064</v>
+        <v>1234</v>
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1971</v>
+        <v>1970</v>
       </c>
       <c r="B15" t="s">
         <v>1223</v>
       </c>
       <c r="C15" t="s">
-        <v>1972</v>
+        <v>1965</v>
       </c>
       <c r="D15" t="s">
-        <v>1973</v>
+        <v>1969</v>
       </c>
       <c r="E15" t="s">
-        <v>1722</v>
+        <v>1966</v>
       </c>
       <c r="F15" t="s">
-        <v>1972</v>
+        <v>1967</v>
       </c>
       <c r="G15" t="s">
-        <v>1976</v>
+        <v>1968</v>
       </c>
       <c r="H15" t="s">
-        <v>1975</v>
+        <v>1197</v>
       </c>
       <c r="I15" t="s">
-        <v>1974</v>
+        <v>2064</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>2510</v>
+        <v>1971</v>
       </c>
       <c r="B16" t="s">
         <v>1223</v>
       </c>
       <c r="C16" t="s">
-        <v>2616</v>
+        <v>1972</v>
       </c>
       <c r="D16" t="s">
-        <v>2511</v>
+        <v>1973</v>
       </c>
       <c r="E16" t="s">
-        <v>1966</v>
+        <v>1722</v>
       </c>
       <c r="F16" t="s">
-        <v>2509</v>
+        <v>1972</v>
       </c>
       <c r="G16" t="s">
-        <v>2628</v>
+        <v>1976</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1975</v>
       </c>
       <c r="I16" t="s">
-        <v>2616</v>
+        <v>1974</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1238</v>
+        <v>2510</v>
       </c>
       <c r="B17" t="s">
-        <v>1235</v>
+        <v>1223</v>
       </c>
       <c r="C17" t="s">
-        <v>1237</v>
+        <v>2616</v>
       </c>
       <c r="D17" t="s">
-        <v>1236</v>
+        <v>2511</v>
       </c>
       <c r="E17" t="s">
-        <v>1239</v>
+        <v>1966</v>
       </c>
       <c r="F17" t="s">
-        <v>1240</v>
+        <v>2509</v>
       </c>
       <c r="G17" t="s">
-        <v>1295</v>
+        <v>2628</v>
       </c>
       <c r="I17" t="s">
-        <v>1294</v>
+        <v>2616</v>
       </c>
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1465</v>
+        <v>1238</v>
       </c>
       <c r="B18" t="s">
-        <v>1066</v>
+        <v>1235</v>
       </c>
       <c r="C18" t="s">
-        <v>1466</v>
+        <v>1237</v>
       </c>
       <c r="D18" t="s">
-        <v>1467</v>
+        <v>1236</v>
       </c>
       <c r="E18" t="s">
-        <v>1468</v>
+        <v>1239</v>
       </c>
       <c r="F18" t="s">
-        <v>1469</v>
+        <v>1240</v>
       </c>
       <c r="G18" t="s">
-        <v>1228</v>
+        <v>1295</v>
       </c>
       <c r="I18" t="s">
-        <v>1470</v>
+        <v>1294</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1717</v>
+        <v>1465</v>
       </c>
       <c r="B19" t="s">
-        <v>29</v>
+        <v>1066</v>
       </c>
       <c r="C19" t="s">
-        <v>1718</v>
+        <v>1466</v>
       </c>
       <c r="D19" t="s">
-        <v>1730</v>
+        <v>1467</v>
       </c>
       <c r="E19" t="s">
-        <v>1722</v>
+        <v>1468</v>
       </c>
       <c r="F19" t="s">
-        <v>1718</v>
+        <v>1469</v>
       </c>
       <c r="G19" t="s">
-        <v>1741</v>
+        <v>1228</v>
       </c>
       <c r="I19" t="s">
-        <v>1723</v>
+        <v>1470</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>1720</v>
+        <v>1717</v>
       </c>
       <c r="B20" t="s">
-        <v>1719</v>
+        <v>29</v>
       </c>
       <c r="C20" t="s">
-        <v>1724</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>1728</v>
+        <v>1718</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1730</v>
       </c>
       <c r="E20" t="s">
         <v>1722</v>
       </c>
       <c r="F20" t="s">
-        <v>1724</v>
+        <v>1718</v>
       </c>
       <c r="G20" t="s">
-        <v>1736</v>
+        <v>1741</v>
       </c>
       <c r="I20" t="s">
-        <v>1725</v>
+        <v>1723</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>1721</v>
+        <v>1720</v>
       </c>
       <c r="B21" t="s">
         <v>1719</v>
       </c>
       <c r="C21" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>1729</v>
+        <v>1728</v>
       </c>
       <c r="E21" t="s">
         <v>1722</v>
       </c>
       <c r="F21" t="s">
-        <v>1727</v>
+        <v>1724</v>
       </c>
       <c r="G21" t="s">
         <v>1736</v>
       </c>
       <c r="I21" t="s">
-        <v>1726</v>
+        <v>1725</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
+        <v>1721</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1719</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1727</v>
+      </c>
+      <c r="D22" s="6" t="s">
+        <v>1729</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1722</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1727</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1736</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1726</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A23" s="2" t="s">
         <v>2320</v>
       </c>
-      <c r="B22" t="s">
+      <c r="B23" t="s">
         <v>29</v>
       </c>
-      <c r="C22" t="s">
+      <c r="C23" t="s">
         <v>2319</v>
       </c>
-      <c r="D22" t="s">
+      <c r="D23" t="s">
         <v>2322</v>
       </c>
-      <c r="E22" t="s">
+      <c r="E23" t="s">
         <v>1195</v>
       </c>
-      <c r="F22" t="s">
+      <c r="F23" t="s">
         <v>2321</v>
       </c>
-      <c r="G22" t="s">
+      <c r="G23" t="s">
         <v>2323</v>
       </c>
-      <c r="I22" t="s">
+      <c r="I23" t="s">
         <v>2324</v>
       </c>
     </row>
@@ -23074,15 +23294,16 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{61606E71-114A-4060-B4DA-26AC2BA8C44E}">
-  <dimension ref="A1:J25"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.08203125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="10.9140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="17.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="19.25" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="75.5" customWidth="1"/>
     <col min="5" max="5" width="17.33203125" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="19.25" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="16.83203125" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="14.08203125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="17.83203125" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="9.5" bestFit="1" customWidth="1"/>
@@ -23583,206 +23804,235 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>2080</v>
+        <v>2632</v>
       </c>
       <c r="B18" t="s">
-        <v>2079</v>
+        <v>1275</v>
       </c>
       <c r="C18" t="s">
-        <v>2090</v>
+        <v>2633</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>2082</v>
+        <v>2393</v>
       </c>
       <c r="E18" t="s">
-        <v>1991</v>
+        <v>2634</v>
       </c>
       <c r="F18" t="s">
-        <v>2081</v>
+        <v>2633</v>
       </c>
       <c r="G18" t="s">
-        <v>2081</v>
+        <v>2635</v>
+      </c>
+      <c r="H18" t="s">
+        <v>2395</v>
       </c>
       <c r="I18" t="s">
-        <v>2083</v>
+        <v>2636</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>2084</v>
+        <v>2080</v>
       </c>
       <c r="B19" t="s">
         <v>2079</v>
       </c>
       <c r="C19" t="s">
-        <v>2089</v>
+        <v>2090</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>2085</v>
+        <v>2082</v>
       </c>
       <c r="E19" t="s">
-        <v>2086</v>
+        <v>1991</v>
       </c>
       <c r="F19" t="s">
-        <v>2088</v>
+        <v>2081</v>
       </c>
       <c r="G19" t="s">
-        <v>2089</v>
+        <v>2081</v>
       </c>
       <c r="I19" t="s">
-        <v>2087</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>2497</v>
+        <v>2084</v>
       </c>
       <c r="B20" t="s">
         <v>2079</v>
       </c>
       <c r="C20" t="s">
-        <v>2498</v>
+        <v>2089</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>2500</v>
+        <v>2085</v>
       </c>
       <c r="E20" t="s">
-        <v>2499</v>
+        <v>2086</v>
       </c>
       <c r="F20" t="s">
-        <v>2498</v>
+        <v>2088</v>
       </c>
       <c r="G20" t="s">
-        <v>2411</v>
+        <v>2089</v>
       </c>
       <c r="I20" t="s">
-        <v>2096</v>
+        <v>2087</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>2562</v>
+        <v>2497</v>
       </c>
       <c r="B21" t="s">
         <v>2079</v>
       </c>
       <c r="C21" t="s">
-        <v>2565</v>
+        <v>2498</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>2563</v>
+        <v>2500</v>
       </c>
       <c r="E21" t="s">
-        <v>2410</v>
+        <v>2499</v>
       </c>
       <c r="F21" t="s">
-        <v>2564</v>
+        <v>2498</v>
       </c>
       <c r="G21" t="s">
-        <v>2565</v>
+        <v>2411</v>
       </c>
       <c r="I21" t="s">
-        <v>2083</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>2625</v>
+        <v>2562</v>
       </c>
       <c r="B22" t="s">
         <v>2079</v>
       </c>
       <c r="C22" t="s">
-        <v>2613</v>
+        <v>2565</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>2500</v>
+        <v>2563</v>
       </c>
       <c r="E22" t="s">
-        <v>2612</v>
+        <v>2410</v>
       </c>
       <c r="F22" t="s">
-        <v>2613</v>
+        <v>2564</v>
       </c>
       <c r="G22" t="s">
-        <v>2627</v>
+        <v>2565</v>
       </c>
       <c r="I22" t="s">
-        <v>2096</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>2611</v>
+        <v>2625</v>
       </c>
       <c r="B23" t="s">
         <v>2079</v>
       </c>
       <c r="C23" t="s">
-        <v>2626</v>
+        <v>2613</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>2563</v>
+        <v>2500</v>
       </c>
       <c r="E23" t="s">
         <v>2612</v>
       </c>
       <c r="F23" t="s">
-        <v>2626</v>
+        <v>2613</v>
       </c>
       <c r="G23" t="s">
-        <v>2565</v>
+        <v>2627</v>
       </c>
       <c r="I23" t="s">
-        <v>2083</v>
+        <v>2096</v>
       </c>
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>2111</v>
+        <v>2611</v>
       </c>
       <c r="B24" t="s">
-        <v>2110</v>
+        <v>2079</v>
       </c>
       <c r="C24" t="s">
-        <v>2112</v>
+        <v>2626</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>2113</v>
+        <v>2563</v>
       </c>
       <c r="E24" t="s">
-        <v>2114</v>
+        <v>2612</v>
       </c>
       <c r="F24" t="s">
-        <v>2112</v>
+        <v>2626</v>
       </c>
       <c r="G24" t="s">
-        <v>2112</v>
+        <v>2565</v>
       </c>
       <c r="I24" t="s">
-        <v>2115</v>
+        <v>2083</v>
       </c>
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
+        <v>2111</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2110</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2112</v>
+      </c>
+      <c r="D25" s="6" t="s">
+        <v>2113</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2114</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2112</v>
+      </c>
+      <c r="G25" t="s">
+        <v>2112</v>
+      </c>
+      <c r="I25" t="s">
+        <v>2115</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
         <v>2620</v>
       </c>
-      <c r="B25" t="s">
+      <c r="B26" t="s">
         <v>2619</v>
       </c>
-      <c r="C25" t="s">
+      <c r="C26" t="s">
         <v>2621</v>
       </c>
-      <c r="D25" s="6" t="s">
+      <c r="D26" s="6" t="s">
         <v>2622</v>
       </c>
-      <c r="F25" t="s">
+      <c r="F26" t="s">
         <v>2621</v>
       </c>
-      <c r="G25" t="s">
+      <c r="G26" t="s">
         <v>2624</v>
       </c>
-      <c r="I25" t="s">
+      <c r="I26" t="s">
         <v>2623</v>
       </c>
     </row>
@@ -25320,7 +25570,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8F28B83C-EC15-4DE5-B23D-95C2173BD368}">
-  <dimension ref="A1:J36"/>
+  <dimension ref="A1:J37"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
@@ -25497,181 +25747,181 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>769</v>
+        <v>2642</v>
       </c>
       <c r="B7" t="s">
-        <v>763</v>
+        <v>87</v>
       </c>
       <c r="C7" t="s">
-        <v>768</v>
+        <v>2643</v>
       </c>
       <c r="D7" t="s">
-        <v>764</v>
+        <v>2644</v>
       </c>
       <c r="E7" t="s">
-        <v>767</v>
+        <v>2640</v>
       </c>
       <c r="F7" t="s">
-        <v>768</v>
+        <v>2643</v>
       </c>
       <c r="G7" t="s">
-        <v>766</v>
+        <v>2645</v>
       </c>
       <c r="I7" t="s">
-        <v>763</v>
+        <v>89</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>1953</v>
+        <v>769</v>
       </c>
       <c r="B8" t="s">
         <v>763</v>
       </c>
       <c r="C8" t="s">
-        <v>1948</v>
+        <v>768</v>
       </c>
       <c r="D8" t="s">
-        <v>1952</v>
+        <v>764</v>
       </c>
       <c r="E8" t="s">
-        <v>1951</v>
+        <v>767</v>
       </c>
       <c r="F8" t="s">
-        <v>1949</v>
+        <v>768</v>
       </c>
       <c r="G8" t="s">
-        <v>1950</v>
+        <v>766</v>
       </c>
       <c r="I8" t="s">
-        <v>1947</v>
+        <v>763</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>533</v>
+        <v>1953</v>
       </c>
       <c r="B9" t="s">
-        <v>531</v>
+        <v>763</v>
       </c>
       <c r="C9" t="s">
-        <v>534</v>
+        <v>1948</v>
       </c>
       <c r="D9" t="s">
-        <v>538</v>
+        <v>1952</v>
       </c>
       <c r="E9" t="s">
-        <v>535</v>
+        <v>1951</v>
       </c>
       <c r="F9" t="s">
-        <v>536</v>
+        <v>1949</v>
       </c>
       <c r="G9" t="s">
-        <v>537</v>
-      </c>
-      <c r="H9" t="s">
-        <v>539</v>
+        <v>1950</v>
       </c>
       <c r="I9" t="s">
-        <v>532</v>
+        <v>1947</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>743</v>
+        <v>533</v>
       </c>
       <c r="B10" t="s">
         <v>531</v>
       </c>
       <c r="C10" t="s">
-        <v>614</v>
+        <v>534</v>
       </c>
       <c r="D10" t="s">
-        <v>618</v>
+        <v>538</v>
       </c>
       <c r="E10" t="s">
-        <v>617</v>
+        <v>535</v>
       </c>
       <c r="F10" t="s">
-        <v>616</v>
+        <v>536</v>
       </c>
       <c r="G10" t="s">
-        <v>614</v>
+        <v>537</v>
+      </c>
+      <c r="H10" t="s">
+        <v>539</v>
       </c>
       <c r="I10" t="s">
-        <v>615</v>
+        <v>532</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="B11" t="s">
-        <v>741</v>
+        <v>531</v>
       </c>
       <c r="C11" t="s">
-        <v>744</v>
+        <v>614</v>
       </c>
       <c r="D11" t="s">
-        <v>745</v>
+        <v>618</v>
       </c>
       <c r="E11" t="s">
-        <v>740</v>
+        <v>617</v>
       </c>
       <c r="F11" t="s">
-        <v>744</v>
+        <v>616</v>
       </c>
       <c r="G11" t="s">
-        <v>746</v>
+        <v>614</v>
       </c>
       <c r="I11" t="s">
-        <v>746</v>
+        <v>615</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>750</v>
+        <v>742</v>
       </c>
       <c r="B12" t="s">
         <v>741</v>
       </c>
       <c r="C12" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="D12" t="s">
-        <v>748</v>
+        <v>745</v>
       </c>
       <c r="E12" t="s">
         <v>740</v>
       </c>
       <c r="F12" t="s">
-        <v>747</v>
+        <v>744</v>
       </c>
       <c r="G12" t="s">
-        <v>749</v>
+        <v>746</v>
       </c>
       <c r="I12" t="s">
-        <v>531</v>
+        <v>746</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A13" s="2" t="s">
-        <v>751</v>
+        <v>750</v>
       </c>
       <c r="B13" t="s">
         <v>741</v>
       </c>
       <c r="C13" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="D13" t="s">
-        <v>753</v>
+        <v>748</v>
       </c>
       <c r="E13" t="s">
         <v>740</v>
       </c>
       <c r="F13" t="s">
-        <v>752</v>
+        <v>747</v>
       </c>
       <c r="G13" t="s">
         <v>749</v>
@@ -25682,22 +25932,22 @@
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A14" s="2" t="s">
-        <v>755</v>
+        <v>751</v>
       </c>
       <c r="B14" t="s">
         <v>741</v>
       </c>
       <c r="C14" t="s">
-        <v>756</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>754</v>
+        <v>752</v>
+      </c>
+      <c r="D14" t="s">
+        <v>753</v>
       </c>
       <c r="E14" t="s">
         <v>740</v>
       </c>
       <c r="F14" t="s">
-        <v>756</v>
+        <v>752</v>
       </c>
       <c r="G14" t="s">
         <v>749</v>
@@ -25708,74 +25958,74 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>1344</v>
+        <v>755</v>
       </c>
       <c r="B15" t="s">
+        <v>741</v>
+      </c>
+      <c r="C15" t="s">
+        <v>756</v>
+      </c>
+      <c r="D15" s="6" t="s">
+        <v>754</v>
+      </c>
+      <c r="E15" t="s">
+        <v>740</v>
+      </c>
+      <c r="F15" t="s">
+        <v>756</v>
+      </c>
+      <c r="G15" t="s">
+        <v>749</v>
+      </c>
+      <c r="I15" t="s">
         <v>531</v>
-      </c>
-      <c r="C15" t="s">
-        <v>1345</v>
-      </c>
-      <c r="D15" s="6" t="s">
-        <v>1346</v>
-      </c>
-      <c r="E15" t="s">
-        <v>1348</v>
-      </c>
-      <c r="F15" t="s">
-        <v>1347</v>
-      </c>
-      <c r="G15" t="s">
-        <v>1350</v>
-      </c>
-      <c r="I15" t="s">
-        <v>1349</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>1366</v>
+        <v>1344</v>
       </c>
       <c r="B16" t="s">
         <v>531</v>
       </c>
       <c r="C16" t="s">
-        <v>1368</v>
-      </c>
-      <c r="D16" t="s">
-        <v>1370</v>
+        <v>1345</v>
+      </c>
+      <c r="D16" s="6" t="s">
+        <v>1346</v>
       </c>
       <c r="E16" t="s">
         <v>1348</v>
       </c>
       <c r="F16" t="s">
-        <v>1374</v>
+        <v>1347</v>
       </c>
       <c r="G16" t="s">
-        <v>749</v>
+        <v>1350</v>
       </c>
       <c r="I16" t="s">
-        <v>531</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="17" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A17" s="2" t="s">
-        <v>1367</v>
+        <v>1366</v>
       </c>
       <c r="B17" t="s">
         <v>531</v>
       </c>
       <c r="C17" t="s">
-        <v>1369</v>
+        <v>1368</v>
       </c>
       <c r="D17" t="s">
-        <v>1371</v>
+        <v>1370</v>
       </c>
       <c r="E17" t="s">
         <v>1348</v>
       </c>
       <c r="F17" t="s">
-        <v>1375</v>
+        <v>1374</v>
       </c>
       <c r="G17" t="s">
         <v>749</v>
@@ -25786,22 +26036,22 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>1372</v>
+        <v>1367</v>
       </c>
       <c r="B18" t="s">
         <v>531</v>
       </c>
       <c r="C18" t="s">
-        <v>1373</v>
+        <v>1369</v>
       </c>
       <c r="D18" t="s">
-        <v>748</v>
+        <v>1371</v>
       </c>
       <c r="E18" t="s">
         <v>1348</v>
       </c>
       <c r="F18" t="s">
-        <v>1376</v>
+        <v>1375</v>
       </c>
       <c r="G18" t="s">
         <v>749</v>
@@ -25812,94 +26062,100 @@
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A19" s="2" t="s">
-        <v>1499</v>
+        <v>1372</v>
       </c>
       <c r="B19" t="s">
         <v>531</v>
       </c>
       <c r="C19" t="s">
-        <v>1496</v>
-      </c>
-      <c r="D19" s="6" t="s">
-        <v>1346</v>
+        <v>1373</v>
+      </c>
+      <c r="D19" t="s">
+        <v>748</v>
       </c>
       <c r="E19" t="s">
         <v>1348</v>
       </c>
       <c r="F19" t="s">
-        <v>1495</v>
+        <v>1376</v>
       </c>
       <c r="G19" t="s">
-        <v>1497</v>
+        <v>749</v>
       </c>
       <c r="I19" t="s">
-        <v>1498</v>
+        <v>531</v>
       </c>
     </row>
     <row r="20" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A20" s="2" t="s">
-        <v>1941</v>
+        <v>1499</v>
       </c>
       <c r="B20" t="s">
         <v>531</v>
       </c>
       <c r="C20" t="s">
-        <v>532</v>
+        <v>1496</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>1945</v>
+        <v>1346</v>
       </c>
       <c r="E20" t="s">
-        <v>1942</v>
+        <v>1348</v>
       </c>
       <c r="F20" t="s">
-        <v>1943</v>
+        <v>1495</v>
       </c>
       <c r="G20" t="s">
-        <v>1944</v>
+        <v>1497</v>
       </c>
       <c r="I20" t="s">
-        <v>1946</v>
+        <v>1498</v>
       </c>
     </row>
     <row r="21" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A21" s="2" t="s">
-        <v>2416</v>
+        <v>1941</v>
       </c>
       <c r="B21" t="s">
         <v>531</v>
       </c>
       <c r="C21" t="s">
-        <v>1373</v>
-      </c>
-      <c r="D21" t="s">
-        <v>2420</v>
+        <v>532</v>
+      </c>
+      <c r="D21" s="6" t="s">
+        <v>1945</v>
       </c>
       <c r="E21" t="s">
-        <v>2419</v>
+        <v>1942</v>
       </c>
       <c r="F21" t="s">
-        <v>2418</v>
+        <v>1943</v>
       </c>
       <c r="G21" t="s">
-        <v>2417</v>
+        <v>1944</v>
       </c>
       <c r="I21" t="s">
-        <v>741</v>
+        <v>1946</v>
       </c>
     </row>
     <row r="22" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>2424</v>
+        <v>2416</v>
       </c>
       <c r="B22" t="s">
         <v>531</v>
       </c>
       <c r="C22" t="s">
-        <v>1369</v>
+        <v>1373</v>
       </c>
       <c r="D22" t="s">
-        <v>2421</v>
+        <v>2420</v>
+      </c>
+      <c r="E22" t="s">
+        <v>2419</v>
+      </c>
+      <c r="F22" t="s">
+        <v>2418</v>
       </c>
       <c r="G22" t="s">
         <v>2417</v>
@@ -25910,16 +26166,16 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>2425</v>
+        <v>2424</v>
       </c>
       <c r="B23" t="s">
         <v>531</v>
       </c>
       <c r="C23" t="s">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="D23" t="s">
-        <v>2422</v>
+        <v>2421</v>
       </c>
       <c r="G23" t="s">
         <v>2417</v>
@@ -25930,16 +26186,16 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>2426</v>
+        <v>2425</v>
       </c>
       <c r="B24" t="s">
         <v>531</v>
       </c>
       <c r="C24" t="s">
-        <v>2423</v>
+        <v>1368</v>
       </c>
       <c r="D24" t="s">
-        <v>2427</v>
+        <v>2422</v>
       </c>
       <c r="G24" t="s">
         <v>2417</v>
@@ -25950,103 +26206,97 @@
     </row>
     <row r="25" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A25" s="2" t="s">
-        <v>212</v>
+        <v>2426</v>
       </c>
       <c r="B25" t="s">
-        <v>207</v>
+        <v>531</v>
       </c>
       <c r="C25" t="s">
-        <v>208</v>
+        <v>2423</v>
       </c>
       <c r="D25" t="s">
-        <v>211</v>
-      </c>
-      <c r="E25" t="s">
-        <v>56</v>
-      </c>
-      <c r="F25" t="s">
-        <v>209</v>
+        <v>2427</v>
       </c>
       <c r="G25" t="s">
-        <v>210</v>
+        <v>2417</v>
       </c>
       <c r="I25" t="s">
-        <v>206</v>
+        <v>741</v>
       </c>
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
-        <v>216</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="C26" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="D26" t="s">
-        <v>601</v>
+        <v>211</v>
       </c>
       <c r="E26" t="s">
         <v>56</v>
       </c>
       <c r="F26" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="G26" t="s">
-        <v>217</v>
+        <v>210</v>
       </c>
       <c r="I26" t="s">
-        <v>218</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A27" s="2" t="s">
-        <v>599</v>
+        <v>216</v>
       </c>
       <c r="B27" t="s">
         <v>213</v>
       </c>
       <c r="C27" t="s">
-        <v>600</v>
+        <v>214</v>
       </c>
       <c r="D27" t="s">
-        <v>602</v>
+        <v>601</v>
       </c>
       <c r="E27" t="s">
         <v>56</v>
       </c>
       <c r="F27" t="s">
-        <v>603</v>
+        <v>215</v>
       </c>
       <c r="G27" t="s">
-        <v>210</v>
+        <v>217</v>
       </c>
       <c r="I27" t="s">
-        <v>604</v>
+        <v>218</v>
       </c>
     </row>
     <row r="28" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A28" s="2" t="s">
-        <v>770</v>
+        <v>599</v>
       </c>
       <c r="B28" t="s">
         <v>213</v>
       </c>
       <c r="C28" t="s">
-        <v>771</v>
+        <v>600</v>
       </c>
       <c r="D28" t="s">
-        <v>772</v>
+        <v>602</v>
       </c>
       <c r="E28" t="s">
         <v>56</v>
       </c>
       <c r="F28" t="s">
-        <v>773</v>
+        <v>603</v>
       </c>
       <c r="G28" t="s">
-        <v>765</v>
+        <v>210</v>
       </c>
       <c r="I28" t="s">
         <v>604</v>
@@ -26054,25 +26304,25 @@
     </row>
     <row r="29" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A29" s="2" t="s">
-        <v>846</v>
+        <v>770</v>
       </c>
       <c r="B29" t="s">
         <v>213</v>
       </c>
       <c r="C29" t="s">
-        <v>847</v>
+        <v>771</v>
       </c>
       <c r="D29" t="s">
-        <v>848</v>
+        <v>772</v>
       </c>
       <c r="E29" t="s">
-        <v>767</v>
+        <v>56</v>
       </c>
       <c r="F29" t="s">
-        <v>847</v>
+        <v>773</v>
       </c>
       <c r="G29" t="s">
-        <v>849</v>
+        <v>765</v>
       </c>
       <c r="I29" t="s">
         <v>604</v>
@@ -26080,183 +26330,209 @@
     </row>
     <row r="30" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A30" s="2" t="s">
-        <v>850</v>
+        <v>846</v>
       </c>
       <c r="B30" t="s">
         <v>213</v>
       </c>
       <c r="C30" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="D30" t="s">
-        <v>852</v>
+        <v>848</v>
       </c>
       <c r="E30" t="s">
-        <v>853</v>
+        <v>767</v>
       </c>
       <c r="F30" t="s">
-        <v>851</v>
+        <v>847</v>
       </c>
       <c r="G30" t="s">
-        <v>854</v>
+        <v>849</v>
       </c>
       <c r="I30" t="s">
-        <v>851</v>
+        <v>604</v>
       </c>
     </row>
     <row r="31" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A31" s="2" t="s">
-        <v>1060</v>
+        <v>850</v>
       </c>
       <c r="B31" t="s">
-        <v>1059</v>
+        <v>213</v>
       </c>
       <c r="C31" t="s">
-        <v>1063</v>
+        <v>851</v>
       </c>
       <c r="D31" t="s">
-        <v>1065</v>
+        <v>852</v>
       </c>
       <c r="E31" t="s">
-        <v>1062</v>
+        <v>853</v>
       </c>
       <c r="F31" t="s">
-        <v>1061</v>
+        <v>851</v>
       </c>
       <c r="G31" t="s">
-        <v>1064</v>
+        <v>854</v>
       </c>
       <c r="I31" t="s">
-        <v>1061</v>
+        <v>851</v>
       </c>
     </row>
     <row r="32" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A32" s="2" t="s">
-        <v>1412</v>
+        <v>1060</v>
       </c>
       <c r="B32" t="s">
-        <v>213</v>
+        <v>1059</v>
       </c>
       <c r="C32" t="s">
-        <v>1583</v>
+        <v>1063</v>
       </c>
       <c r="D32" t="s">
-        <v>1584</v>
+        <v>1065</v>
       </c>
       <c r="E32" t="s">
-        <v>767</v>
+        <v>1062</v>
       </c>
       <c r="F32" t="s">
-        <v>1413</v>
+        <v>1061</v>
       </c>
       <c r="G32" t="s">
-        <v>1415</v>
+        <v>1064</v>
       </c>
       <c r="I32" t="s">
-        <v>1414</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="33" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A33" s="2" t="s">
-        <v>1694</v>
+        <v>1412</v>
       </c>
       <c r="B33" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="C33" t="s">
-        <v>1695</v>
+        <v>1583</v>
       </c>
       <c r="D33" t="s">
-        <v>1698</v>
+        <v>1584</v>
       </c>
       <c r="E33" t="s">
-        <v>1696</v>
+        <v>767</v>
       </c>
       <c r="F33" t="s">
-        <v>1695</v>
+        <v>1413</v>
       </c>
       <c r="G33" t="s">
         <v>1415</v>
       </c>
       <c r="I33" t="s">
-        <v>1697</v>
+        <v>1414</v>
       </c>
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>1714</v>
+        <v>1694</v>
       </c>
       <c r="B34" t="s">
-        <v>1059</v>
+        <v>207</v>
       </c>
       <c r="C34" t="s">
-        <v>1716</v>
+        <v>1695</v>
       </c>
       <c r="D34" t="s">
-        <v>1065</v>
+        <v>1698</v>
       </c>
       <c r="E34" t="s">
-        <v>1715</v>
+        <v>1696</v>
       </c>
       <c r="F34" t="s">
-        <v>1716</v>
+        <v>1695</v>
       </c>
       <c r="G34" t="s">
-        <v>1064</v>
+        <v>1415</v>
       </c>
       <c r="I34" t="s">
-        <v>1061</v>
+        <v>1697</v>
       </c>
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>2293</v>
+        <v>1714</v>
       </c>
       <c r="B35" t="s">
-        <v>213</v>
+        <v>1059</v>
       </c>
       <c r="C35" t="s">
-        <v>2294</v>
+        <v>1716</v>
       </c>
       <c r="D35" t="s">
-        <v>2295</v>
+        <v>1065</v>
       </c>
       <c r="E35" t="s">
-        <v>853</v>
+        <v>1715</v>
       </c>
       <c r="F35" t="s">
-        <v>2294</v>
+        <v>1716</v>
       </c>
       <c r="G35" t="s">
-        <v>765</v>
+        <v>1064</v>
       </c>
       <c r="I35" t="s">
-        <v>604</v>
+        <v>1061</v>
       </c>
     </row>
     <row r="36" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A36" s="2" t="s">
+        <v>2293</v>
+      </c>
+      <c r="B36" t="s">
+        <v>213</v>
+      </c>
+      <c r="C36" t="s">
+        <v>2294</v>
+      </c>
+      <c r="D36" t="s">
+        <v>2295</v>
+      </c>
+      <c r="E36" t="s">
+        <v>853</v>
+      </c>
+      <c r="F36" t="s">
+        <v>2294</v>
+      </c>
+      <c r="G36" t="s">
+        <v>765</v>
+      </c>
+      <c r="I36" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A37" s="2" t="s">
         <v>2452</v>
       </c>
-      <c r="B36" t="s">
+      <c r="B37" t="s">
         <v>207</v>
       </c>
-      <c r="C36" t="s">
+      <c r="C37" t="s">
         <v>2451</v>
       </c>
-      <c r="D36" t="s">
+      <c r="D37" t="s">
         <v>2453</v>
       </c>
-      <c r="E36" t="s">
+      <c r="E37" t="s">
         <v>2455</v>
       </c>
-      <c r="F36" t="s">
+      <c r="F37" t="s">
         <v>2451</v>
       </c>
-      <c r="G36" t="s">
+      <c r="G37" t="s">
         <v>2454</v>
       </c>
-      <c r="I36" t="s">
+      <c r="I37" t="s">
         <v>206</v>
       </c>
     </row>

--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28827"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{250F2ECA-5A36-4605-A0DC-156C7B1628D2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E6A53D37-1CB2-4CAC-85C2-5B0A311F6547}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" activeTab="9" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4963" uniqueCount="2800">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4986" uniqueCount="2812">
   <si>
     <t>Part Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -10071,10 +10071,6 @@
     <t>JK-mSMD150</t>
   </si>
   <si>
-    <t>自恢复保险丝;Vmax 8V; Imax 100A; Ihold 1.5A; Itrip 3A; Maximun Time To Tirp Current 8A,Time 0.5Sec;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>金瑞电子</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -10355,509 +10351,558 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
+    <t>SOIC-8</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SP3485EN-L/TR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MaxLinear(迈凌)</t>
+  </si>
+  <si>
+    <t>SP3485</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDH连接器</t>
+  </si>
+  <si>
+    <t>SHD-2x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SDH 连接器线对板针座;立式;20pin; 13x5.4x4.75</t>
+  </si>
+  <si>
+    <t>3015200000</t>
+  </si>
+  <si>
+    <t>HC-SHD-2*10PLT-G-04</t>
+  </si>
+  <si>
+    <t>13x5.4x4.75</t>
+  </si>
+  <si>
+    <t>SHD-20PIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1411200002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMBT3904M</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MMBT3904</t>
+  </si>
+  <si>
+    <t>NPN三极管;VCEO = 40V;VCBO = 60V; Ic = 0.1A;P = 200mW;SOT-23</t>
+  </si>
+  <si>
+    <t>onsemi(安森美)</t>
+  </si>
+  <si>
+    <t>MMBT3904LT1G</t>
+  </si>
+  <si>
+    <t>SOT-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2082400012</t>
+  </si>
+  <si>
+    <t>24C02</t>
+  </si>
+  <si>
+    <t>I2C flash;2K bits EEPROMFLASH; SOT23-5</t>
+  </si>
+  <si>
+    <t>XBLW(芯伯乐)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>24C02S(XBLW)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>SOT23_5</t>
+  </si>
+  <si>
+    <t>EEPROM-Sot23-5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311104002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAP CER X7R;100nF;+/-10%;500V;1206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CGA1206X7R104K501NT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HRE(芯声)</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>100nF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311104003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAP CER X7R;100nF;+/-10%;50V;0603</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC0603KRX7R9BB104</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C0603</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC0603KRX5R8BB225</t>
+  </si>
+  <si>
+    <t>2.2uF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311225003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAP CER X5R;2.2μF;+/-10%;25V;0603</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;0Ω;+/-1%;1/8W;0805</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0805FR-070RL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>6.65K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-076K65L</t>
+  </si>
+  <si>
+    <t>RES FILM;6.65KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111665100</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>14.7K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0714K7L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;14.7KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111147200</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1511300012</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2N7002K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOS管N-FET;VDS=60V;2.5ohm;0.3A;0.3W;SOT-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AOS</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AO3401A</t>
+  </si>
+  <si>
+    <t>1511300013</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MOS管N-FET;VDS=30V;50mohm;4A;1.4W;SOT-23</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AO3401A</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1231105006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>MWTC201610S1R0MT</t>
+  </si>
+  <si>
+    <t>IND POWER Coil;1.0uH;+/-20%;DRC=50mΩ;3.4A;2*1.6*1mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311200000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>20pF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CAP CER NPO;20pF;+/-5%;50V;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC0402JRNPO9BN200</t>
+  </si>
+  <si>
+    <t>CL31A226KAHNNNE</t>
+  </si>
+  <si>
+    <t>CAP CER X5R;22μF;+/-10%;25V;1206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>C1206</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311226006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311471001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC0402JRNPO9BN471</t>
+  </si>
+  <si>
+    <t>CAP CER NP0;470pF;+/-5%;50V;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>12.1K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;12.1KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0712K1L</t>
+  </si>
+  <si>
+    <t>1111121300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>18K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0718KL</t>
+  </si>
+  <si>
+    <t>RES FILM;18KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111183000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-072K2L</t>
+  </si>
+  <si>
+    <t>RES FILM;2.2KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2.2K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111222000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>75K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111753000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;75KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0775KL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1411100006</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RB551V-30</t>
+  </si>
+  <si>
+    <t>宏嘉诚</t>
+  </si>
+  <si>
+    <t>肖特基二极管;VR=30V;VF=0.47V;IF=0.5A;SOT-323</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3015180007</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPEC-505DDW</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPEC-505DDW-ACP24</t>
+  </si>
+  <si>
+    <t>USB-C连接器;24pin;pitch 0.5mm;半插半贴片;11.15*9.90*高5.18mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>11.15*9.90*高5.18mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3015180008</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HC-USB3.0-L168-ZJ</t>
+  </si>
+  <si>
+    <t>USB-A连接器;9pin;pitch 2.mm;插件;弯插;14.2*13.1*7mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HC-USB3.0-L168-ZJ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051000022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM3242</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASMedia</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>10x10</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PCI Express至1端口USB3.2 20Gbps xHCI 1.1主机控制器，支持多个IN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2031200022</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>HR3420</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DC-DC降压;输入2.5-6v;开关频率=1.5MHz;PFM;SOT23-5;</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>鸿润电子</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>DCDC5PIN</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111274300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>27.4K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;27.4KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0727K4L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>36.5K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111365300</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;36.5KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0736K5L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>78.7K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;78.7KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111787400</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-0778K7L</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qfn-88-10x10-ep635</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>typec-505ddw-acp24</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>TYPE-C_24PIN_1</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>220nF</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311224002</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>CC0402KRX7R8BB224</t>
+  </si>
+  <si>
+    <t>CAP CER X7R;220nF;+/-10%;25V;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111204000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1111204001</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;200KΩ;+/-1%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402FR-07200KL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
     <t>2083700002</t>
-  </si>
-  <si>
-    <t>SOIC-8</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SP3485EN-L/TR</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MaxLinear(迈凌)</t>
-  </si>
-  <si>
-    <t>SP3485</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SDH连接器</t>
-  </si>
-  <si>
-    <t>SHD-2x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SDH 连接器线对板针座;立式;20pin; 13x5.4x4.75</t>
-  </si>
-  <si>
-    <t>3015200000</t>
-  </si>
-  <si>
-    <t>HC-SHD-2*10PLT-G-04</t>
-  </si>
-  <si>
-    <t>13x5.4x4.75</t>
-  </si>
-  <si>
-    <t>SHD-20PIN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1411200002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MMBT3904M</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MMBT3904</t>
-  </si>
-  <si>
-    <t>NPN三极管;VCEO = 40V;VCBO = 60V; Ic = 0.1A;P = 200mW;SOT-23</t>
-  </si>
-  <si>
-    <t>onsemi(安森美)</t>
-  </si>
-  <si>
-    <t>MMBT3904LT1G</t>
-  </si>
-  <si>
-    <t>SOT-23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2082400012</t>
-  </si>
-  <si>
-    <t>24C02</t>
-  </si>
-  <si>
-    <t>I2C flash;2K bits EEPROMFLASH; SOT23-5</t>
-  </si>
-  <si>
-    <t>XBLW(芯伯乐)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>24C02S(XBLW)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>SOT23_5</t>
-  </si>
-  <si>
-    <t>EEPROM-Sot23-5</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1311104002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAP CER X7R;100nF;+/-10%;500V;1206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CGA1206X7R104K501NT</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HRE(芯声)</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C1206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>100nF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1311104003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAP CER X7R;100nF;+/-10%;50V;0603</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CC0603KRX7R9BB104</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C0603</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CC0603KRX5R8BB225</t>
-  </si>
-  <si>
-    <t>2.2uF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1311225003</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAP CER X5R;2.2μF;+/-10%;25V;0603</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;0Ω;+/-1%;1/8W;0805</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0805FR-070RL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>6.65K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-076K65L</t>
-  </si>
-  <si>
-    <t>RES FILM;6.65KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111665100</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>14.7K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-0714K7L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;14.7KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111147200</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1511300012</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2N7002K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MOS管N-FET;VDS=60V;2.5ohm;0.3A;0.3W;SOT-23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AOS</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AO3401A</t>
-  </si>
-  <si>
-    <t>1511300013</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MOS管N-FET;VDS=30V;50mohm;4A;1.4W;SOT-23</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>AO3401A</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1231105006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>MWTC201610S1R0MT</t>
-  </si>
-  <si>
-    <t>IND POWER Coil;1.0uH;+/-20%;DRC=50mΩ;3.4A;2*1.6*1mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1311200000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>20pF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CAP CER NPO;20pF;+/-5%;50V;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CC0402JRNPO9BN200</t>
-  </si>
-  <si>
-    <t>CL31A226KAHNNNE</t>
-  </si>
-  <si>
-    <t>CAP CER X5R;22μF;+/-10%;25V;1206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>C1206</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1311226006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1311471001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CC0402JRNPO9BN471</t>
-  </si>
-  <si>
-    <t>CAP CER NP0;470pF;+/-5%;50V;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>12.1K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;12.1KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-0712K1L</t>
-  </si>
-  <si>
-    <t>1111121300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>18K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-0718KL</t>
-  </si>
-  <si>
-    <t>RES FILM;18KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111183000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-072K2L</t>
-  </si>
-  <si>
-    <t>RES FILM;2.2KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2.2K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111222000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>75K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111753000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;75KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-0775KL</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1411100006</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RB551V-30</t>
-  </si>
-  <si>
-    <t>宏嘉诚</t>
-  </si>
-  <si>
-    <t>肖特基二极管;VR=30V;VF=0.47V;IF=0.5A;SOT-323</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3015180007</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TYPEC-505DDW</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TYPEC-505DDW-ACP24</t>
-  </si>
-  <si>
-    <t>USB-C连接器;24pin;pitch 0.5mm;半插半贴片;11.15*9.90*高5.18mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>11.15*9.90*高5.18mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>3015180008</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC-USB3.0-L168-ZJ</t>
-  </si>
-  <si>
-    <t>USB-A连接器;9pin;pitch 2.mm;插件;弯插;14.2*13.1*7mm</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HC-USB3.0-L168-ZJ</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2051000022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>ASM3242</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>Typec-cc逻辑芯片</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>2051000023</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM1543</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM1543 is a one Four to two differential channels mux switch with integrated Type-C Configuration Channel Logic Circuitry, using for USB3.1 type-C mux and CC detection application.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>qfn32-4x4_asm1543</t>
+  </si>
+  <si>
+    <t>2051000024</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ASM1541</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>dfn12-118x118</t>
   </si>
   <si>
     <t>ASMedia</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>10x10</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>PCI Express至1端口USB3.2 20Gbps xHCI 1.1主机控制器，支持多个IN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>2031200022</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>HR3420</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DC-DC降压;输入2.5-6v;开关频率=1.5MHz;PFM;SOT23-5;</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>鸿润电子</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>DCDC5PIN</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111274300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>27.4K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;27.4KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-0727K4L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>36.5K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111365300</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;36.5KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-0736K5L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>78.7K</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;78.7KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111787400</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-0778K7L</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>qfn-88-10x10-ep635</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>typec-505ddw-acp24</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>TYPE-C_24PIN_1</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>220nF</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1311224002</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>CC0402KRX7R8BB224</t>
-  </si>
-  <si>
-    <t>CAP CER X7R;220nF;+/-10%;25V;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111204000</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>1111204001</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RES FILM;200KΩ;+/-1%;1/16W;0402</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>RC0402FR-07200KL</t>
+  </si>
+  <si>
+    <t>ASM1541 is a one integrated Type-C Configuration Channel Logic Circuitry, using for USB3.1 type-C CC detection application.</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311227003</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RVT220UF16V67RV0015</t>
+  </si>
+  <si>
+    <t>自恢复保险丝;Vmax 8V; Imax 100A; Ihold 2.5A; Itrip 3A; Maximun Time To Tirp Current 8A,Time 2.5Sec;</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -11488,13 +11533,13 @@
         <v>269</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>2706</v>
+        <v>2704</v>
       </c>
       <c r="E5" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F5" s="1" t="s">
-        <v>2707</v>
+        <v>2705</v>
       </c>
       <c r="G5" s="1" t="s">
         <v>129</v>
@@ -12441,22 +12486,22 @@
     </row>
     <row r="42" spans="1:9" ht="13.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A42" s="2" t="s">
-        <v>2741</v>
+        <v>2739</v>
       </c>
       <c r="B42" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C42" s="1" t="s">
-        <v>2738</v>
+        <v>2736</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>2739</v>
+        <v>2737</v>
       </c>
       <c r="E42" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F42" s="1" t="s">
-        <v>2740</v>
+        <v>2738</v>
       </c>
       <c r="G42" t="s">
         <v>19</v>
@@ -12623,22 +12668,22 @@
     </row>
     <row r="49" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A49" s="2" t="s">
-        <v>2715</v>
+        <v>2713</v>
       </c>
       <c r="B49" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C49" s="1" t="s">
+        <v>2710</v>
+      </c>
+      <c r="D49" s="1" t="s">
         <v>2712</v>
-      </c>
-      <c r="D49" s="1" t="s">
-        <v>2714</v>
       </c>
       <c r="E49" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F49" s="1" t="s">
-        <v>2713</v>
+        <v>2711</v>
       </c>
       <c r="G49" t="s">
         <v>19</v>
@@ -12909,22 +12954,22 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>2745</v>
+        <v>2743</v>
       </c>
       <c r="B60" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C60" s="1" t="s">
+        <v>2740</v>
+      </c>
+      <c r="D60" s="1" t="s">
         <v>2742</v>
-      </c>
-      <c r="D60" s="1" t="s">
-        <v>2744</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F60" s="1" t="s">
-        <v>2743</v>
+        <v>2741</v>
       </c>
       <c r="G60" t="s">
         <v>91</v>
@@ -13065,22 +13110,22 @@
     </row>
     <row r="66" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A66" s="2" t="s">
-        <v>2749</v>
+        <v>2747</v>
       </c>
       <c r="B66" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C66" s="1" t="s">
-        <v>2748</v>
+        <v>2746</v>
       </c>
       <c r="D66" s="1" t="s">
-        <v>2747</v>
+        <v>2745</v>
       </c>
       <c r="E66" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F66" s="1" t="s">
-        <v>2746</v>
+        <v>2744</v>
       </c>
       <c r="G66" t="s">
         <v>91</v>
@@ -13325,7 +13370,7 @@
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>2796</v>
+        <v>2794</v>
       </c>
       <c r="B76" s="1" t="s">
         <v>10</v>
@@ -13351,7 +13396,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>2797</v>
+        <v>2795</v>
       </c>
       <c r="B77" s="1" t="s">
         <v>10</v>
@@ -13360,13 +13405,13 @@
         <v>2293</v>
       </c>
       <c r="D77" s="1" t="s">
-        <v>2798</v>
+        <v>2796</v>
       </c>
       <c r="E77" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>2799</v>
+        <v>2797</v>
       </c>
       <c r="G77" t="s">
         <v>19</v>
@@ -13715,22 +13760,22 @@
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A91" s="2" t="s">
-        <v>2777</v>
+        <v>2775</v>
       </c>
       <c r="B91" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C91" s="1" t="s">
-        <v>2778</v>
+        <v>2776</v>
       </c>
       <c r="D91" s="1" t="s">
-        <v>2779</v>
+        <v>2777</v>
       </c>
       <c r="E91" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F91" s="1" t="s">
-        <v>2780</v>
+        <v>2778</v>
       </c>
       <c r="G91" t="s">
         <v>19</v>
@@ -13793,22 +13838,22 @@
     </row>
     <row r="94" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A94" s="2" t="s">
-        <v>2597</v>
+        <v>2596</v>
       </c>
       <c r="B94" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C94" s="1" t="s">
-        <v>2596</v>
+        <v>2595</v>
       </c>
       <c r="D94" s="1" t="s">
-        <v>2598</v>
+        <v>2597</v>
       </c>
       <c r="E94" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F94" s="1" t="s">
-        <v>2599</v>
+        <v>2598</v>
       </c>
       <c r="G94" t="s">
         <v>19</v>
@@ -14105,22 +14150,22 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>2782</v>
+        <v>2780</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C106" s="1" t="s">
+        <v>2779</v>
+      </c>
+      <c r="D106" s="1" t="s">
         <v>2781</v>
-      </c>
-      <c r="D106" s="1" t="s">
-        <v>2783</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>2784</v>
+        <v>2782</v>
       </c>
       <c r="G106" t="s">
         <v>19</v>
@@ -14963,22 +15008,22 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>2648</v>
+        <v>2647</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C139" s="1" t="s">
-        <v>2647</v>
+        <v>2646</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>2649</v>
+        <v>2648</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>2646</v>
+        <v>2645</v>
       </c>
       <c r="G139" t="s">
         <v>19</v>
@@ -15119,22 +15164,22 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>2711</v>
+        <v>2709</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C145" s="1" t="s">
+        <v>2706</v>
+      </c>
+      <c r="D145" s="1" t="s">
         <v>2708</v>
-      </c>
-      <c r="D145" s="1" t="s">
-        <v>2710</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>2709</v>
+        <v>2707</v>
       </c>
       <c r="G145" t="s">
         <v>19</v>
@@ -15327,22 +15372,22 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>2751</v>
+        <v>2749</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C153" s="1" t="s">
+        <v>2748</v>
+      </c>
+      <c r="D153" s="1" t="s">
         <v>2750</v>
-      </c>
-      <c r="D153" s="1" t="s">
-        <v>2752</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>2753</v>
+        <v>2751</v>
       </c>
       <c r="G153" t="s">
         <v>19</v>
@@ -15405,22 +15450,22 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>2787</v>
+        <v>2785</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>2785</v>
+        <v>2783</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>2786</v>
+        <v>2784</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>2788</v>
+        <v>2786</v>
       </c>
       <c r="G156" t="s">
         <v>19</v>
@@ -16798,28 +16843,28 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>2772</v>
+        <v>2770</v>
       </c>
       <c r="B40" t="s">
         <v>388</v>
       </c>
       <c r="C40" t="s">
+        <v>2771</v>
+      </c>
+      <c r="D40" t="s">
+        <v>2772</v>
+      </c>
+      <c r="E40" t="s">
         <v>2773</v>
       </c>
-      <c r="D40" t="s">
-        <v>2774</v>
-      </c>
-      <c r="E40" t="s">
-        <v>2775</v>
-      </c>
       <c r="F40" t="s">
-        <v>2773</v>
+        <v>2771</v>
       </c>
       <c r="G40" t="s">
         <v>1583</v>
       </c>
       <c r="I40" t="s">
-        <v>2776</v>
+        <v>2774</v>
       </c>
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
@@ -17147,25 +17192,25 @@
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A5" s="2" t="s">
-        <v>2633</v>
+        <v>2632</v>
       </c>
       <c r="B5" t="s">
         <v>107</v>
       </c>
       <c r="C5" t="s">
+        <v>2633</v>
+      </c>
+      <c r="D5" t="s">
         <v>2634</v>
       </c>
-      <c r="D5" t="s">
+      <c r="E5" t="s">
         <v>2635</v>
       </c>
-      <c r="E5" t="s">
+      <c r="F5" t="s">
+        <v>2633</v>
+      </c>
+      <c r="G5" t="s">
         <v>2636</v>
-      </c>
-      <c r="F5" t="s">
-        <v>2634</v>
-      </c>
-      <c r="G5" t="s">
-        <v>2637</v>
       </c>
       <c r="I5" t="s">
         <v>2384</v>
@@ -17338,10 +17383,10 @@
         <v>2593</v>
       </c>
       <c r="D12" t="s">
+        <v>2811</v>
+      </c>
+      <c r="E12" t="s">
         <v>2594</v>
-      </c>
-      <c r="E12" t="s">
-        <v>2595</v>
       </c>
       <c r="F12" t="s">
         <v>2593</v>
@@ -17615,7 +17660,7 @@
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A9" s="2" t="s">
-        <v>2605</v>
+        <v>2604</v>
       </c>
       <c r="B9" t="s">
         <v>375</v>
@@ -17624,21 +17669,21 @@
         <v>1313</v>
       </c>
       <c r="D9" t="s">
-        <v>2606</v>
+        <v>2605</v>
       </c>
       <c r="E9" t="s">
         <v>1215</v>
       </c>
       <c r="G9" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="I9" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A10" s="2" t="s">
-        <v>2626</v>
+        <v>2625</v>
       </c>
       <c r="B10" t="s">
         <v>375</v>
@@ -17647,16 +17692,16 @@
         <v>1213</v>
       </c>
       <c r="D10" t="s">
-        <v>2627</v>
+        <v>2626</v>
       </c>
       <c r="E10" t="s">
         <v>1215</v>
       </c>
       <c r="G10" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="I10" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -17673,7 +17718,7 @@
         <v>1507</v>
       </c>
       <c r="E11" t="s">
-        <v>2625</v>
+        <v>2624</v>
       </c>
       <c r="F11" t="s">
         <v>1618</v>
@@ -17690,7 +17735,7 @@
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
-        <v>2600</v>
+        <v>2599</v>
       </c>
       <c r="B12" t="s">
         <v>375</v>
@@ -17699,19 +17744,19 @@
         <v>343</v>
       </c>
       <c r="D12" t="s">
-        <v>2603</v>
+        <v>2602</v>
       </c>
       <c r="E12" t="s">
         <v>2201</v>
       </c>
       <c r="F12" t="s">
-        <v>2602</v>
+        <v>2601</v>
       </c>
       <c r="G12" t="s">
-        <v>2601</v>
+        <v>2600</v>
       </c>
       <c r="I12" t="s">
-        <v>2604</v>
+        <v>2603</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -18404,28 +18449,28 @@
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="2" t="s">
-        <v>2685</v>
+        <v>2683</v>
       </c>
       <c r="B15" t="s">
         <v>382</v>
       </c>
       <c r="C15" t="s">
+        <v>2684</v>
+      </c>
+      <c r="D15" t="s">
+        <v>2685</v>
+      </c>
+      <c r="E15" t="s">
         <v>2686</v>
       </c>
-      <c r="D15" t="s">
+      <c r="F15" t="s">
         <v>2687</v>
       </c>
-      <c r="E15" t="s">
+      <c r="G15" t="s">
         <v>2688</v>
       </c>
-      <c r="F15" t="s">
+      <c r="I15" t="s">
         <v>2689</v>
-      </c>
-      <c r="G15" t="s">
-        <v>2690</v>
-      </c>
-      <c r="I15" t="s">
-        <v>2691</v>
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
@@ -19190,54 +19235,54 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
+        <v>2656</v>
+      </c>
+      <c r="B45" t="s">
+        <v>2655</v>
+      </c>
+      <c r="C45" t="s">
+        <v>2658</v>
+      </c>
+      <c r="D45" t="s">
+        <v>2662</v>
+      </c>
+      <c r="E45" t="s">
+        <v>2659</v>
+      </c>
+      <c r="F45" t="s">
+        <v>2660</v>
+      </c>
+      <c r="G45" t="s">
         <v>2657</v>
       </c>
-      <c r="B45" t="s">
-        <v>2656</v>
-      </c>
-      <c r="C45" t="s">
-        <v>2659</v>
-      </c>
-      <c r="D45" t="s">
-        <v>2663</v>
-      </c>
-      <c r="E45" t="s">
-        <v>2660</v>
-      </c>
-      <c r="F45" t="s">
+      <c r="I45" t="s">
         <v>2661</v>
-      </c>
-      <c r="G45" t="s">
-        <v>2658</v>
-      </c>
-      <c r="I45" t="s">
-        <v>2662</v>
       </c>
     </row>
     <row r="46" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A46" s="2" t="s">
+        <v>2798</v>
+      </c>
+      <c r="B46" t="s">
+        <v>2655</v>
+      </c>
+      <c r="C46" t="s">
+        <v>2668</v>
+      </c>
+      <c r="D46" t="s">
+        <v>2663</v>
+      </c>
+      <c r="E46" t="s">
+        <v>2667</v>
+      </c>
+      <c r="F46" t="s">
         <v>2666</v>
       </c>
-      <c r="B46" t="s">
-        <v>2656</v>
-      </c>
-      <c r="C46" t="s">
-        <v>2670</v>
-      </c>
-      <c r="D46" t="s">
+      <c r="G46" t="s">
+        <v>2665</v>
+      </c>
+      <c r="I46" t="s">
         <v>2664</v>
-      </c>
-      <c r="E46" t="s">
-        <v>2669</v>
-      </c>
-      <c r="F46" t="s">
-        <v>2668</v>
-      </c>
-      <c r="G46" t="s">
-        <v>2667</v>
-      </c>
-      <c r="I46" t="s">
-        <v>2665</v>
       </c>
     </row>
   </sheetData>
@@ -19276,7 +19321,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{22CB78C2-2208-4DF0-8ABB-0CE48BD26296}">
-  <dimension ref="A1:J86"/>
+  <dimension ref="A1:J87"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
@@ -19870,7 +19915,7 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>2735</v>
+        <v>2733</v>
       </c>
       <c r="B23" t="s">
         <v>17</v>
@@ -19879,13 +19924,13 @@
         <v>2328</v>
       </c>
       <c r="D23" t="s">
-        <v>2737</v>
+        <v>2735</v>
       </c>
       <c r="E23" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F23" t="s">
-        <v>2736</v>
+        <v>2734</v>
       </c>
       <c r="G23" t="s">
         <v>18</v>
@@ -20156,7 +20201,7 @@
     </row>
     <row r="34" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A34" s="2" t="s">
-        <v>2692</v>
+        <v>2690</v>
       </c>
       <c r="B34" t="s">
         <v>17</v>
@@ -20165,16 +20210,16 @@
         <v>73</v>
       </c>
       <c r="D34" t="s">
+        <v>2691</v>
+      </c>
+      <c r="E34" s="1" t="s">
         <v>2693</v>
       </c>
-      <c r="E34" s="1" t="s">
-        <v>2695</v>
-      </c>
       <c r="F34" t="s">
+        <v>2692</v>
+      </c>
+      <c r="G34" t="s">
         <v>2694</v>
-      </c>
-      <c r="G34" t="s">
-        <v>2696</v>
       </c>
       <c r="I34" t="s">
         <v>20</v>
@@ -20182,25 +20227,25 @@
     </row>
     <row r="35" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A35" s="2" t="s">
-        <v>2698</v>
+        <v>2696</v>
       </c>
       <c r="B35" t="s">
         <v>17</v>
       </c>
       <c r="C35" t="s">
+        <v>2695</v>
+      </c>
+      <c r="D35" t="s">
         <v>2697</v>
-      </c>
-      <c r="D35" t="s">
-        <v>2699</v>
       </c>
       <c r="E35" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F35" t="s">
-        <v>2700</v>
+        <v>2698</v>
       </c>
       <c r="G35" t="s">
-        <v>2701</v>
+        <v>2699</v>
       </c>
       <c r="I35" t="s">
         <v>20</v>
@@ -20445,7 +20490,7 @@
     </row>
     <row r="45" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A45" s="2" t="s">
-        <v>2642</v>
+        <v>2641</v>
       </c>
       <c r="B45" t="s">
         <v>810</v>
@@ -20454,19 +20499,19 @@
         <v>814</v>
       </c>
       <c r="D45" t="s">
-        <v>2645</v>
+        <v>2644</v>
       </c>
       <c r="E45" t="s">
         <v>812</v>
       </c>
       <c r="F45" t="s">
-        <v>2643</v>
+        <v>2642</v>
       </c>
       <c r="G45" t="s">
         <v>815</v>
       </c>
       <c r="H45" t="s">
-        <v>2644</v>
+        <v>2643</v>
       </c>
       <c r="I45" t="s">
         <v>816</v>
@@ -20610,22 +20655,22 @@
     </row>
     <row r="51" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A51" s="2" t="s">
-        <v>2727</v>
+        <v>2725</v>
       </c>
       <c r="B51" t="s">
         <v>17</v>
       </c>
       <c r="C51" t="s">
-        <v>2728</v>
+        <v>2726</v>
       </c>
       <c r="D51" t="s">
-        <v>2729</v>
+        <v>2727</v>
       </c>
       <c r="E51" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F51" t="s">
-        <v>2730</v>
+        <v>2728</v>
       </c>
       <c r="G51" t="s">
         <v>18</v>
@@ -20844,22 +20889,22 @@
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A60" s="2" t="s">
-        <v>2793</v>
+        <v>2791</v>
       </c>
       <c r="B60" t="s">
         <v>17</v>
       </c>
       <c r="C60" t="s">
-        <v>2792</v>
+        <v>2790</v>
       </c>
       <c r="D60" t="s">
-        <v>2795</v>
+        <v>2793</v>
       </c>
       <c r="E60" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F60" t="s">
-        <v>2794</v>
+        <v>2792</v>
       </c>
       <c r="G60" t="s">
         <v>18</v>
@@ -20948,22 +20993,22 @@
     </row>
     <row r="64" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A64" s="2" t="s">
-        <v>2704</v>
+        <v>2702</v>
       </c>
       <c r="B64" t="s">
         <v>17</v>
       </c>
       <c r="C64" t="s">
+        <v>2701</v>
+      </c>
+      <c r="D64" t="s">
         <v>2703</v>
-      </c>
-      <c r="D64" t="s">
-        <v>2705</v>
       </c>
       <c r="E64" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F64" t="s">
-        <v>2702</v>
+        <v>2700</v>
       </c>
       <c r="G64" t="s">
         <v>120</v>
@@ -21104,7 +21149,7 @@
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="2" t="s">
-        <v>2614</v>
+        <v>2613</v>
       </c>
       <c r="B70" t="s">
         <v>17</v>
@@ -21119,7 +21164,7 @@
         <v>70</v>
       </c>
       <c r="F70" t="s">
-        <v>2613</v>
+        <v>2612</v>
       </c>
       <c r="G70" t="s">
         <v>120</v>
@@ -21130,7 +21175,7 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>2734</v>
+        <v>2732</v>
       </c>
       <c r="B71" t="s">
         <v>17</v>
@@ -21139,16 +21184,16 @@
         <v>281</v>
       </c>
       <c r="D71" t="s">
-        <v>2732</v>
+        <v>2730</v>
       </c>
       <c r="E71" s="1" t="s">
         <v>70</v>
       </c>
       <c r="F71" t="s">
+        <v>2729</v>
+      </c>
+      <c r="G71" t="s">
         <v>2731</v>
-      </c>
-      <c r="G71" t="s">
-        <v>2733</v>
       </c>
       <c r="I71" t="s">
         <v>20</v>
@@ -21240,51 +21285,51 @@
     </row>
     <row r="75" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A75" s="2" t="s">
-        <v>161</v>
+        <v>2809</v>
       </c>
       <c r="B75" t="s">
-        <v>17</v>
+        <v>810</v>
       </c>
       <c r="C75" t="s">
-        <v>160</v>
+        <v>1146</v>
       </c>
       <c r="D75" t="s">
-        <v>159</v>
-      </c>
-      <c r="E75" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="F75" s="1" t="s">
-        <v>158</v>
+        <v>2029</v>
+      </c>
+      <c r="E75" t="s">
+        <v>812</v>
+      </c>
+      <c r="F75" t="s">
+        <v>2810</v>
       </c>
       <c r="G75" t="s">
-        <v>18</v>
+        <v>815</v>
       </c>
       <c r="I75" t="s">
-        <v>20</v>
+        <v>816</v>
       </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="2" t="s">
-        <v>977</v>
+        <v>161</v>
       </c>
       <c r="B76" t="s">
         <v>17</v>
       </c>
       <c r="C76" t="s">
-        <v>978</v>
+        <v>160</v>
       </c>
       <c r="D76" t="s">
-        <v>979</v>
+        <v>159</v>
       </c>
       <c r="E76" s="1" t="s">
-        <v>980</v>
+        <v>12</v>
       </c>
       <c r="F76" s="1" t="s">
-        <v>981</v>
+        <v>158</v>
       </c>
       <c r="G76" t="s">
-        <v>120</v>
+        <v>18</v>
       </c>
       <c r="I76" t="s">
         <v>20</v>
@@ -21292,7 +21337,7 @@
     </row>
     <row r="77" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A77" s="2" t="s">
-        <v>2236</v>
+        <v>977</v>
       </c>
       <c r="B77" t="s">
         <v>17</v>
@@ -21301,16 +21346,16 @@
         <v>978</v>
       </c>
       <c r="D77" t="s">
-        <v>2237</v>
+        <v>979</v>
       </c>
       <c r="E77" s="1" t="s">
-        <v>1007</v>
+        <v>980</v>
       </c>
       <c r="F77" s="1" t="s">
-        <v>2238</v>
+        <v>981</v>
       </c>
       <c r="G77" t="s">
-        <v>18</v>
+        <v>120</v>
       </c>
       <c r="I77" t="s">
         <v>20</v>
@@ -21318,62 +21363,62 @@
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="2" t="s">
-        <v>1142</v>
+        <v>2236</v>
       </c>
       <c r="B78" t="s">
-        <v>1110</v>
+        <v>17</v>
       </c>
       <c r="C78" t="s">
-        <v>1143</v>
+        <v>978</v>
       </c>
       <c r="D78" t="s">
-        <v>1144</v>
-      </c>
-      <c r="E78" t="s">
-        <v>1113</v>
-      </c>
-      <c r="F78" t="s">
-        <v>1145</v>
+        <v>2237</v>
+      </c>
+      <c r="E78" s="1" t="s">
+        <v>1007</v>
+      </c>
+      <c r="F78" s="1" t="s">
+        <v>2238</v>
       </c>
       <c r="G78" t="s">
-        <v>1114</v>
-      </c>
-      <c r="H78" t="s">
-        <v>1112</v>
+        <v>18</v>
       </c>
       <c r="I78" t="s">
-        <v>816</v>
+        <v>20</v>
       </c>
     </row>
     <row r="79" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A79" s="2" t="s">
-        <v>58</v>
+        <v>1142</v>
       </c>
       <c r="B79" t="s">
-        <v>17</v>
+        <v>1110</v>
       </c>
       <c r="C79" t="s">
-        <v>282</v>
+        <v>1143</v>
       </c>
       <c r="D79" t="s">
-        <v>59</v>
-      </c>
-      <c r="E79" s="1" t="s">
-        <v>12</v>
+        <v>1144</v>
+      </c>
+      <c r="E79" t="s">
+        <v>1113</v>
       </c>
       <c r="F79" t="s">
-        <v>60</v>
+        <v>1145</v>
       </c>
       <c r="G79" t="s">
-        <v>18</v>
+        <v>1114</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1112</v>
       </c>
       <c r="I79" t="s">
-        <v>20</v>
+        <v>816</v>
       </c>
     </row>
     <row r="80" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A80" s="2" t="s">
-        <v>67</v>
+        <v>58</v>
       </c>
       <c r="B80" t="s">
         <v>17</v>
@@ -21382,16 +21427,16 @@
         <v>282</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
-      </c>
-      <c r="E80" t="s">
-        <v>70</v>
+        <v>59</v>
+      </c>
+      <c r="E80" s="1" t="s">
+        <v>12</v>
       </c>
       <c r="F80" t="s">
-        <v>69</v>
+        <v>60</v>
       </c>
       <c r="G80" t="s">
-        <v>71</v>
+        <v>18</v>
       </c>
       <c r="I80" t="s">
         <v>20</v>
@@ -21399,7 +21444,7 @@
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="2" t="s">
-        <v>1450</v>
+        <v>67</v>
       </c>
       <c r="B81" t="s">
         <v>17</v>
@@ -21408,16 +21453,16 @@
         <v>282</v>
       </c>
       <c r="D81" t="s">
-        <v>1448</v>
-      </c>
-      <c r="E81" s="1" t="s">
-        <v>188</v>
+        <v>68</v>
+      </c>
+      <c r="E81" t="s">
+        <v>70</v>
       </c>
       <c r="F81" t="s">
-        <v>1449</v>
+        <v>69</v>
       </c>
       <c r="G81" t="s">
-        <v>325</v>
+        <v>71</v>
       </c>
       <c r="I81" t="s">
         <v>20</v>
@@ -21425,25 +21470,25 @@
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A82" s="2" t="s">
-        <v>548</v>
+        <v>1450</v>
       </c>
       <c r="B82" t="s">
         <v>17</v>
       </c>
       <c r="C82" t="s">
-        <v>547</v>
+        <v>282</v>
       </c>
       <c r="D82" t="s">
-        <v>551</v>
+        <v>1448</v>
       </c>
       <c r="E82" s="1" t="s">
-        <v>12</v>
+        <v>188</v>
       </c>
       <c r="F82" t="s">
-        <v>550</v>
+        <v>1449</v>
       </c>
       <c r="G82" t="s">
-        <v>71</v>
+        <v>325</v>
       </c>
       <c r="I82" t="s">
         <v>20</v>
@@ -21451,7 +21496,7 @@
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A83" s="2" t="s">
-        <v>2321</v>
+        <v>548</v>
       </c>
       <c r="B83" t="s">
         <v>17</v>
@@ -21460,16 +21505,16 @@
         <v>547</v>
       </c>
       <c r="D83" t="s">
-        <v>2322</v>
+        <v>551</v>
       </c>
       <c r="E83" s="1" t="s">
-        <v>188</v>
+        <v>12</v>
       </c>
       <c r="F83" t="s">
-        <v>2323</v>
+        <v>550</v>
       </c>
       <c r="G83" t="s">
-        <v>120</v>
+        <v>71</v>
       </c>
       <c r="I83" t="s">
         <v>20</v>
@@ -21477,46 +21522,57 @@
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A84" s="2" t="s">
+        <v>2321</v>
+      </c>
+      <c r="B84" t="s">
+        <v>17</v>
+      </c>
+      <c r="C84" t="s">
+        <v>547</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2322</v>
+      </c>
+      <c r="E84" s="1" t="s">
+        <v>188</v>
+      </c>
+      <c r="F84" t="s">
+        <v>2323</v>
+      </c>
+      <c r="G84" t="s">
+        <v>120</v>
+      </c>
+      <c r="I84" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A85" s="2" t="s">
         <v>1108</v>
       </c>
-      <c r="B84" t="s">
+      <c r="B85" t="s">
         <v>1110</v>
       </c>
-      <c r="C84" t="s">
+      <c r="C85" t="s">
         <v>1106</v>
       </c>
-      <c r="D84" t="s">
+      <c r="D85" t="s">
         <v>1109</v>
       </c>
-      <c r="E84" t="s">
+      <c r="E85" t="s">
         <v>1113</v>
       </c>
-      <c r="F84" t="s">
+      <c r="F85" t="s">
         <v>1111</v>
       </c>
-      <c r="G84" t="s">
+      <c r="G85" t="s">
         <v>1114</v>
       </c>
-      <c r="H84" t="s">
+      <c r="H85" t="s">
         <v>1112</v>
       </c>
-      <c r="I84" t="s">
+      <c r="I85" t="s">
         <v>816</v>
-      </c>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B85" t="s">
-        <v>17</v>
-      </c>
-      <c r="C85" t="s">
-        <v>90</v>
-      </c>
-      <c r="E85" s="1"/>
-      <c r="G85" t="s">
-        <v>18</v>
-      </c>
-      <c r="I85" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
@@ -21526,10 +21582,25 @@
       <c r="C86" t="s">
         <v>90</v>
       </c>
+      <c r="E86" s="1"/>
       <c r="G86" t="s">
+        <v>18</v>
+      </c>
+      <c r="I86" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B87" t="s">
+        <v>17</v>
+      </c>
+      <c r="C87" t="s">
+        <v>90</v>
+      </c>
+      <c r="G87" t="s">
         <v>325</v>
       </c>
-      <c r="I86" t="s">
+      <c r="I87" t="s">
         <v>20</v>
       </c>
     </row>
@@ -21550,11 +21621,11 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C302E28E-61B5-45F2-9EED-9E658F066E8B}">
-  <dimension ref="A1:J24"/>
+  <dimension ref="A1:J26"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.58203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="16.08203125" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="21.08203125" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="133.08203125" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="20.08203125" bestFit="1" customWidth="1"/>
@@ -21715,13 +21786,13 @@
         <v>2477</v>
       </c>
       <c r="D6" t="s">
-        <v>2611</v>
+        <v>2610</v>
       </c>
       <c r="E6" t="s">
         <v>2474</v>
       </c>
       <c r="F6" t="s">
-        <v>2610</v>
+        <v>2609</v>
       </c>
       <c r="G6" t="s">
         <v>2475</v>
@@ -21735,60 +21806,60 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>2650</v>
+        <v>2649</v>
       </c>
       <c r="B7" t="s">
         <v>305</v>
       </c>
       <c r="C7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="D7" t="s">
+        <v>2653</v>
+      </c>
+      <c r="E7" t="s">
         <v>2652</v>
       </c>
-      <c r="D7" t="s">
+      <c r="F7" t="s">
+        <v>2651</v>
+      </c>
+      <c r="G7" t="s">
         <v>2654</v>
-      </c>
-      <c r="E7" t="s">
-        <v>2653</v>
-      </c>
-      <c r="F7" t="s">
-        <v>2652</v>
-      </c>
-      <c r="G7" t="s">
-        <v>2655</v>
       </c>
       <c r="H7" t="s">
         <v>2476</v>
       </c>
       <c r="I7" t="s">
-        <v>2651</v>
+        <v>2650</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>2767</v>
+        <v>2765</v>
       </c>
       <c r="B8" t="s">
         <v>305</v>
       </c>
       <c r="C8" t="s">
+        <v>2766</v>
+      </c>
+      <c r="D8" t="s">
+        <v>2769</v>
+      </c>
+      <c r="E8" t="s">
+        <v>2767</v>
+      </c>
+      <c r="F8" t="s">
+        <v>2766</v>
+      </c>
+      <c r="G8" t="s">
+        <v>2787</v>
+      </c>
+      <c r="H8" t="s">
         <v>2768</v>
       </c>
-      <c r="D8" t="s">
-        <v>2771</v>
-      </c>
-      <c r="E8" t="s">
-        <v>2769</v>
-      </c>
-      <c r="F8" t="s">
-        <v>2768</v>
-      </c>
-      <c r="G8" t="s">
-        <v>2789</v>
-      </c>
-      <c r="H8" t="s">
-        <v>2770</v>
-      </c>
       <c r="I8" t="s">
-        <v>2768</v>
+        <v>2766</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -22057,7 +22128,7 @@
         <v>1221</v>
       </c>
       <c r="C18" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
       <c r="D18" t="s">
         <v>2507</v>
@@ -22069,10 +22140,10 @@
         <v>2505</v>
       </c>
       <c r="G18" t="s">
-        <v>2624</v>
+        <v>2623</v>
       </c>
       <c r="I18" t="s">
-        <v>2612</v>
+        <v>2611</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -22229,6 +22300,55 @@
       </c>
       <c r="I24" t="s">
         <v>2320</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A25" s="2" t="s">
+        <v>2800</v>
+      </c>
+      <c r="B25" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C25" t="s">
+        <v>2801</v>
+      </c>
+      <c r="D25" t="s">
+        <v>2802</v>
+      </c>
+      <c r="E25" t="s">
+        <v>2767</v>
+      </c>
+      <c r="F25" t="s">
+        <v>2801</v>
+      </c>
+      <c r="G25" t="s">
+        <v>2803</v>
+      </c>
+      <c r="I25" t="s">
+        <v>2801</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A26" s="2" t="s">
+        <v>2804</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2799</v>
+      </c>
+      <c r="C26" t="s">
+        <v>2805</v>
+      </c>
+      <c r="D26" t="s">
+        <v>2808</v>
+      </c>
+      <c r="E26" t="s">
+        <v>2807</v>
+      </c>
+      <c r="G26" t="s">
+        <v>2806</v>
+      </c>
+      <c r="I26" t="s">
+        <v>2805</v>
       </c>
     </row>
   </sheetData>
@@ -24185,51 +24305,51 @@
     </row>
     <row r="62" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A62" s="2" t="s">
-        <v>2758</v>
+        <v>2756</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C62" t="s">
+        <v>2757</v>
+      </c>
+      <c r="D62" t="s">
         <v>2759</v>
-      </c>
-      <c r="D62" t="s">
-        <v>2761</v>
       </c>
       <c r="E62" t="s">
         <v>936</v>
       </c>
       <c r="F62" t="s">
+        <v>2758</v>
+      </c>
+      <c r="G62" t="s">
+        <v>2788</v>
+      </c>
+      <c r="H62" t="s">
         <v>2760</v>
       </c>
-      <c r="G62" t="s">
-        <v>2790</v>
-      </c>
-      <c r="H62" t="s">
-        <v>2762</v>
-      </c>
       <c r="I62" t="s">
-        <v>2791</v>
+        <v>2789</v>
       </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="2" t="s">
-        <v>2763</v>
+        <v>2761</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>219</v>
       </c>
       <c r="C63" t="s">
-        <v>2764</v>
+        <v>2762</v>
       </c>
       <c r="D63" t="s">
-        <v>2765</v>
+        <v>2763</v>
       </c>
       <c r="E63" t="s">
         <v>2092</v>
       </c>
       <c r="F63" t="s">
-        <v>2766</v>
+        <v>2764</v>
       </c>
       <c r="I63" t="s">
         <v>2080</v>
@@ -24437,31 +24557,31 @@
     </row>
     <row r="71" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A71" s="2" t="s">
-        <v>2674</v>
+        <v>2672</v>
       </c>
       <c r="B71" t="s">
+        <v>2669</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2673</v>
+      </c>
+      <c r="D71" t="s">
         <v>2671</v>
-      </c>
-      <c r="C71" t="s">
-        <v>2675</v>
-      </c>
-      <c r="D71" t="s">
-        <v>2673</v>
       </c>
       <c r="E71" t="s">
         <v>1988</v>
       </c>
       <c r="F71" t="s">
+        <v>2673</v>
+      </c>
+      <c r="G71" t="s">
+        <v>2670</v>
+      </c>
+      <c r="H71" t="s">
+        <v>2674</v>
+      </c>
+      <c r="I71" t="s">
         <v>2675</v>
-      </c>
-      <c r="G71" t="s">
-        <v>2672</v>
-      </c>
-      <c r="H71" t="s">
-        <v>2676</v>
-      </c>
-      <c r="I71" t="s">
-        <v>2677</v>
       </c>
     </row>
   </sheetData>
@@ -24991,31 +25111,31 @@
     </row>
     <row r="18" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A18" s="2" t="s">
-        <v>2628</v>
+        <v>2627</v>
       </c>
       <c r="B18" t="s">
         <v>1273</v>
       </c>
       <c r="C18" t="s">
-        <v>2629</v>
+        <v>2628</v>
       </c>
       <c r="D18" s="6" t="s">
         <v>2389</v>
       </c>
       <c r="E18" t="s">
+        <v>2629</v>
+      </c>
+      <c r="F18" t="s">
+        <v>2628</v>
+      </c>
+      <c r="G18" t="s">
         <v>2630</v>
-      </c>
-      <c r="F18" t="s">
-        <v>2629</v>
-      </c>
-      <c r="G18" t="s">
-        <v>2631</v>
       </c>
       <c r="H18" t="s">
         <v>2391</v>
       </c>
       <c r="I18" t="s">
-        <v>2632</v>
+        <v>2631</v>
       </c>
     </row>
     <row r="19" spans="1:9" x14ac:dyDescent="0.3">
@@ -25124,25 +25244,25 @@
     </row>
     <row r="23" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A23" s="2" t="s">
-        <v>2621</v>
+        <v>2620</v>
       </c>
       <c r="B23" t="s">
         <v>2076</v>
       </c>
       <c r="C23" t="s">
-        <v>2609</v>
+        <v>2608</v>
       </c>
       <c r="D23" s="6" t="s">
         <v>2496</v>
       </c>
       <c r="E23" t="s">
+        <v>2607</v>
+      </c>
+      <c r="F23" t="s">
         <v>2608</v>
       </c>
-      <c r="F23" t="s">
-        <v>2609</v>
-      </c>
       <c r="G23" t="s">
-        <v>2623</v>
+        <v>2622</v>
       </c>
       <c r="I23" t="s">
         <v>2093</v>
@@ -25150,22 +25270,22 @@
     </row>
     <row r="24" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A24" s="2" t="s">
-        <v>2607</v>
+        <v>2606</v>
       </c>
       <c r="B24" t="s">
         <v>2076</v>
       </c>
       <c r="C24" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="D24" s="6" t="s">
         <v>2559</v>
       </c>
       <c r="E24" t="s">
-        <v>2608</v>
+        <v>2607</v>
       </c>
       <c r="F24" t="s">
-        <v>2622</v>
+        <v>2621</v>
       </c>
       <c r="G24" t="s">
         <v>2561</v>
@@ -25202,25 +25322,25 @@
     </row>
     <row r="26" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A26" s="2" t="s">
+        <v>2615</v>
+      </c>
+      <c r="B26" t="s">
+        <v>2614</v>
+      </c>
+      <c r="C26" t="s">
         <v>2616</v>
       </c>
-      <c r="B26" t="s">
-        <v>2615</v>
-      </c>
-      <c r="C26" t="s">
+      <c r="D26" s="6" t="s">
         <v>2617</v>
       </c>
-      <c r="D26" s="6" t="s">
+      <c r="F26" t="s">
+        <v>2616</v>
+      </c>
+      <c r="G26" t="s">
+        <v>2619</v>
+      </c>
+      <c r="I26" t="s">
         <v>2618</v>
-      </c>
-      <c r="F26" t="s">
-        <v>2617</v>
-      </c>
-      <c r="G26" t="s">
-        <v>2620</v>
-      </c>
-      <c r="I26" t="s">
-        <v>2619</v>
       </c>
     </row>
   </sheetData>
@@ -25648,7 +25768,7 @@
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="2" t="s">
-        <v>2724</v>
+        <v>2722</v>
       </c>
       <c r="B16" s="2" t="s">
         <v>78</v>
@@ -25657,13 +25777,13 @@
         <v>466</v>
       </c>
       <c r="D16" t="s">
-        <v>2726</v>
+        <v>2724</v>
       </c>
       <c r="E16" t="s">
         <v>79</v>
       </c>
       <c r="F16" t="s">
-        <v>2725</v>
+        <v>2723</v>
       </c>
       <c r="G16" t="s">
         <v>394</v>
@@ -26960,25 +27080,25 @@
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" s="2" t="s">
-        <v>2638</v>
+        <v>2637</v>
       </c>
       <c r="B7" t="s">
         <v>87</v>
       </c>
       <c r="C7" t="s">
+        <v>2638</v>
+      </c>
+      <c r="D7" t="s">
         <v>2639</v>
       </c>
-      <c r="D7" t="s">
+      <c r="E7" t="s">
+        <v>2635</v>
+      </c>
+      <c r="F7" t="s">
+        <v>2638</v>
+      </c>
+      <c r="G7" t="s">
         <v>2640</v>
-      </c>
-      <c r="E7" t="s">
-        <v>2636</v>
-      </c>
-      <c r="F7" t="s">
-        <v>2639</v>
-      </c>
-      <c r="G7" t="s">
-        <v>2641</v>
       </c>
       <c r="I7" t="s">
         <v>89</v>
@@ -26986,22 +27106,22 @@
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A8" s="2" t="s">
-        <v>2754</v>
+        <v>2752</v>
       </c>
       <c r="B8" t="s">
         <v>87</v>
       </c>
       <c r="C8" t="s">
+        <v>2753</v>
+      </c>
+      <c r="D8" t="s">
         <v>2755</v>
       </c>
-      <c r="D8" t="s">
-        <v>2757</v>
-      </c>
       <c r="E8" t="s">
-        <v>2756</v>
+        <v>2754</v>
       </c>
       <c r="F8" t="s">
-        <v>2755</v>
+        <v>2753</v>
       </c>
       <c r="G8" t="s">
         <v>115</v>
@@ -27044,7 +27164,7 @@
         <v>762</v>
       </c>
       <c r="C10" t="s">
-        <v>2679</v>
+        <v>2677</v>
       </c>
       <c r="D10" t="s">
         <v>1949</v>
@@ -27064,25 +27184,25 @@
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A11" s="2" t="s">
-        <v>2678</v>
+        <v>2676</v>
       </c>
       <c r="B11" t="s">
         <v>762</v>
       </c>
       <c r="C11" t="s">
+        <v>2678</v>
+      </c>
+      <c r="D11" t="s">
+        <v>2679</v>
+      </c>
+      <c r="E11" t="s">
         <v>2680</v>
       </c>
-      <c r="D11" t="s">
+      <c r="F11" t="s">
         <v>2681</v>
       </c>
-      <c r="E11" t="s">
+      <c r="G11" t="s">
         <v>2682</v>
-      </c>
-      <c r="F11" t="s">
-        <v>2683</v>
-      </c>
-      <c r="G11" t="s">
-        <v>2684</v>
       </c>
       <c r="I11" t="s">
         <v>1945</v>
@@ -27803,22 +27923,22 @@
     </row>
     <row r="40" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A40" s="2" t="s">
-        <v>2716</v>
+        <v>2714</v>
       </c>
       <c r="B40" t="s">
         <v>207</v>
       </c>
       <c r="C40" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="D40" t="s">
-        <v>2718</v>
+        <v>2716</v>
       </c>
       <c r="E40" t="s">
-        <v>2636</v>
+        <v>2635</v>
       </c>
       <c r="F40" t="s">
-        <v>2717</v>
+        <v>2715</v>
       </c>
       <c r="G40" t="s">
         <v>847</v>
@@ -27829,22 +27949,22 @@
     </row>
     <row r="41" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A41" s="2" t="s">
-        <v>2721</v>
+        <v>2719</v>
       </c>
       <c r="B41" t="s">
         <v>213</v>
       </c>
       <c r="C41" t="s">
-        <v>2723</v>
+        <v>2721</v>
       </c>
       <c r="D41" t="s">
-        <v>2722</v>
+        <v>2720</v>
       </c>
       <c r="E41" t="s">
-        <v>2719</v>
+        <v>2717</v>
       </c>
       <c r="F41" t="s">
-        <v>2720</v>
+        <v>2718</v>
       </c>
       <c r="G41" t="s">
         <v>847</v>

--- a/WyyComponentDatabase.xlsx
+++ b/WyyComponentDatabase.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Cadence\SPB_Data\Lib\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1344B7AE-EEC4-4988-B6AC-C2DB818EE38A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A2232258-CF01-43C4-B6F0-3B1E9CF10A78}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="38620" windowHeight="21100" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3190" yWindow="3120" windowWidth="28300" windowHeight="14840" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="贴片电阻" sheetId="1" r:id="rId1"/>
@@ -48,7 +48,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5723" uniqueCount="3177">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5750" uniqueCount="3202">
   <si>
     <t>Part Number</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -12347,6 +12347,102 @@
     <t>RC0402FR-07123KL</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
+  <si>
+    <t>1111283000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>28K</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RES FILM;28KΩ;+/-5%;1/16W;0402</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>RC0402JR-0728KL</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屏蔽夹</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3015230000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICT</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>ICSRC52128SFR</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>pbz</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>5.2x1x1.28mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>屏蔽罩夹子5.2x1x1.28mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>PBZ</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>1311100007</t>
+  </si>
+  <si>
+    <t>法拉电容</t>
+  </si>
+  <si>
+    <t>10F</t>
+  </si>
+  <si>
+    <t>cap26_27_13</t>
+  </si>
+  <si>
+    <t>螺柱</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>3015240000</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2x3x3.5</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>贴片螺母盲孔;直径3.5MM;高3mm;M2螺丝孔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>某宝</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>https://item.taobao.com/item.htm?abbucket=20&amp;id=893193932244&amp;mi_id=0000_KECX4mtebUkdFVmasN8hajObYcROfSPAPEx6Kh5hgo&amp;ns=1&amp;skuId=5907526874006&amp;spm=a21n57.1.hoverItem.7&amp;utparam=%7B%22aplus_abtest%22%3A%22df6f7110ae7be6d236cb91d20cf1f603%22%7D&amp;xxc=taobaoSearch</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>M2*3*∅3.5盲孔</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>tp-3_5mm</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>hole</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
 </sst>
 </file>
 
@@ -12355,7 +12451,7 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="0.00_);[Red]\(0.00\)"/>
   </numFmts>
-  <fonts count="5" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -12392,6 +12488,14 @@
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
+      <name val="等线"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -12410,10 +12514,11 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -12425,9 +12530,11 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="超链接" xfId="1" builtinId="8"/>
   </cellStyles>
   <dxfs count="14">
     <dxf>
@@ -12846,7 +12953,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:J198"/>
+  <dimension ref="A1:J199"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="13.75" style="2" bestFit="1" customWidth="1"/>
@@ -15555,22 +15662,22 @@
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A105" s="2" t="s">
-        <v>2527</v>
+        <v>3177</v>
       </c>
       <c r="B105" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C105" s="1" t="s">
-        <v>2526</v>
+        <v>3178</v>
       </c>
       <c r="D105" s="1" t="s">
-        <v>2528</v>
+        <v>3179</v>
       </c>
       <c r="E105" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F105" s="1" t="s">
-        <v>2529</v>
+        <v>3180</v>
       </c>
       <c r="G105" t="s">
         <v>19</v>
@@ -15581,22 +15688,22 @@
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A106" s="2" t="s">
-        <v>1685</v>
+        <v>2527</v>
       </c>
       <c r="B106" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C106" s="1" t="s">
-        <v>1684</v>
+        <v>2526</v>
       </c>
       <c r="D106" s="1" t="s">
-        <v>1687</v>
+        <v>2528</v>
       </c>
       <c r="E106" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F106" s="1" t="s">
-        <v>1688</v>
+        <v>2529</v>
       </c>
       <c r="G106" t="s">
         <v>19</v>
@@ -15607,22 +15714,22 @@
     </row>
     <row r="107" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A107" s="2" t="s">
-        <v>2588</v>
+        <v>1685</v>
       </c>
       <c r="B107" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C107" s="1" t="s">
-        <v>2587</v>
+        <v>1684</v>
       </c>
       <c r="D107" s="1" t="s">
-        <v>2589</v>
+        <v>1687</v>
       </c>
       <c r="E107" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F107" s="1" t="s">
-        <v>2590</v>
+        <v>1688</v>
       </c>
       <c r="G107" t="s">
         <v>19</v>
@@ -15633,22 +15740,22 @@
     </row>
     <row r="108" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A108" s="2" t="s">
-        <v>1686</v>
+        <v>2588</v>
       </c>
       <c r="B108" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C108" s="1" t="s">
-        <v>1377</v>
+        <v>2587</v>
       </c>
       <c r="D108" s="1" t="s">
-        <v>1378</v>
+        <v>2589</v>
       </c>
       <c r="E108" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F108" s="1" t="s">
-        <v>1379</v>
+        <v>2590</v>
       </c>
       <c r="G108" t="s">
         <v>19</v>
@@ -15659,22 +15766,22 @@
     </row>
     <row r="109" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A109" s="2" t="s">
-        <v>786</v>
+        <v>1686</v>
       </c>
       <c r="B109" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C109" s="1" t="s">
-        <v>784</v>
+        <v>1377</v>
       </c>
       <c r="D109" s="1" t="s">
-        <v>785</v>
+        <v>1378</v>
       </c>
       <c r="E109" s="1" t="s">
-        <v>774</v>
+        <v>12</v>
       </c>
       <c r="F109" s="1" t="s">
-        <v>783</v>
+        <v>1379</v>
       </c>
       <c r="G109" t="s">
         <v>19</v>
@@ -15685,7 +15792,7 @@
     </row>
     <row r="110" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A110" s="2" t="s">
-        <v>1925</v>
+        <v>786</v>
       </c>
       <c r="B110" s="1" t="s">
         <v>10</v>
@@ -15694,16 +15801,16 @@
         <v>784</v>
       </c>
       <c r="D110" s="1" t="s">
-        <v>1924</v>
+        <v>785</v>
       </c>
       <c r="E110" s="1" t="s">
-        <v>12</v>
+        <v>774</v>
       </c>
       <c r="F110" s="1" t="s">
-        <v>1923</v>
+        <v>783</v>
       </c>
       <c r="G110" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I110" s="1" t="s">
         <v>337</v>
@@ -15711,24 +15818,24 @@
     </row>
     <row r="111" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A111" s="2" t="s">
-        <v>1885</v>
+        <v>1925</v>
       </c>
       <c r="B111" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C111" s="1" t="s">
-        <v>1883</v>
+        <v>784</v>
       </c>
       <c r="D111" s="1" t="s">
-        <v>1886</v>
+        <v>1924</v>
       </c>
       <c r="E111" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F111" s="1" t="s">
-        <v>1884</v>
-      </c>
-      <c r="G111" s="1" t="s">
+        <v>1923</v>
+      </c>
+      <c r="G111" t="s">
         <v>330</v>
       </c>
       <c r="I111" s="1" t="s">
@@ -15737,7 +15844,7 @@
     </row>
     <row r="112" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A112" s="2" t="s">
-        <v>1920</v>
+        <v>1885</v>
       </c>
       <c r="B112" s="1" t="s">
         <v>10</v>
@@ -15746,16 +15853,16 @@
         <v>1883</v>
       </c>
       <c r="D112" s="1" t="s">
-        <v>1921</v>
+        <v>1886</v>
       </c>
       <c r="E112" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F112" s="1" t="s">
-        <v>1922</v>
+        <v>1884</v>
       </c>
       <c r="G112" s="1" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I112" s="1" t="s">
         <v>337</v>
@@ -15763,7 +15870,7 @@
     </row>
     <row r="113" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A113" s="2" t="s">
-        <v>2827</v>
+        <v>1920</v>
       </c>
       <c r="B113" s="1" t="s">
         <v>10</v>
@@ -15772,16 +15879,16 @@
         <v>1883</v>
       </c>
       <c r="D113" s="1" t="s">
-        <v>2828</v>
+        <v>1921</v>
       </c>
       <c r="E113" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F113" s="1" t="s">
-        <v>2829</v>
+        <v>1922</v>
       </c>
       <c r="G113" s="1" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I113" s="1" t="s">
         <v>337</v>
@@ -15789,25 +15896,25 @@
     </row>
     <row r="114" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A114" s="2" t="s">
-        <v>2566</v>
+        <v>2827</v>
       </c>
       <c r="B114" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C114" s="1" t="s">
-        <v>2565</v>
+        <v>1883</v>
       </c>
       <c r="D114" s="1" t="s">
-        <v>2567</v>
+        <v>2828</v>
       </c>
       <c r="E114" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F114" s="1" t="s">
-        <v>2568</v>
+        <v>2829</v>
       </c>
       <c r="G114" s="1" t="s">
-        <v>19</v>
+        <v>776</v>
       </c>
       <c r="I114" s="1" t="s">
         <v>337</v>
@@ -15815,7 +15922,7 @@
     </row>
     <row r="115" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A115" s="2" t="s">
-        <v>2856</v>
+        <v>2566</v>
       </c>
       <c r="B115" s="1" t="s">
         <v>10</v>
@@ -15824,16 +15931,16 @@
         <v>2565</v>
       </c>
       <c r="D115" s="1" t="s">
-        <v>2857</v>
+        <v>2567</v>
       </c>
       <c r="E115" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F115" s="1" t="s">
-        <v>2858</v>
+        <v>2568</v>
       </c>
       <c r="G115" s="1" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I115" s="1" t="s">
         <v>337</v>
@@ -15841,25 +15948,25 @@
     </row>
     <row r="116" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A116" s="2" t="s">
-        <v>1704</v>
+        <v>2856</v>
       </c>
       <c r="B116" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C116" s="1" t="s">
-        <v>1702</v>
+        <v>2565</v>
       </c>
       <c r="D116" s="1" t="s">
-        <v>1703</v>
+        <v>2857</v>
       </c>
       <c r="E116" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F116" s="1" t="s">
-        <v>1705</v>
-      </c>
-      <c r="G116" t="s">
-        <v>19</v>
+        <v>2858</v>
+      </c>
+      <c r="G116" s="1" t="s">
+        <v>776</v>
       </c>
       <c r="I116" s="1" t="s">
         <v>337</v>
@@ -15867,25 +15974,25 @@
     </row>
     <row r="117" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A117" s="2" t="s">
-        <v>1516</v>
+        <v>1704</v>
       </c>
       <c r="B117" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C117" s="1" t="s">
-        <v>1515</v>
+        <v>1702</v>
       </c>
       <c r="D117" s="1" t="s">
-        <v>1517</v>
+        <v>1703</v>
       </c>
       <c r="E117" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F117" s="1" t="s">
-        <v>1514</v>
+        <v>1705</v>
       </c>
       <c r="G117" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I117" s="1" t="s">
         <v>337</v>
@@ -15893,25 +16000,25 @@
     </row>
     <row r="118" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A118" s="2" t="s">
-        <v>130</v>
+        <v>1516</v>
       </c>
       <c r="B118" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C118" s="1" t="s">
-        <v>270</v>
+        <v>1515</v>
       </c>
       <c r="D118" s="1" t="s">
-        <v>828</v>
+        <v>1517</v>
       </c>
       <c r="E118" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F118" s="1" t="s">
-        <v>696</v>
+        <v>1514</v>
       </c>
       <c r="G118" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I118" s="1" t="s">
         <v>337</v>
@@ -15919,7 +16026,7 @@
     </row>
     <row r="119" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A119" s="2" t="s">
-        <v>694</v>
+        <v>130</v>
       </c>
       <c r="B119" s="1" t="s">
         <v>10</v>
@@ -15928,16 +16035,16 @@
         <v>270</v>
       </c>
       <c r="D119" s="1" t="s">
-        <v>829</v>
+        <v>828</v>
       </c>
       <c r="E119" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F119" s="1" t="s">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="G119" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I119" s="1" t="s">
         <v>337</v>
@@ -15945,25 +16052,25 @@
     </row>
     <row r="120" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A120" s="2" t="s">
-        <v>1072</v>
+        <v>694</v>
       </c>
       <c r="B120" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C120" s="1" t="s">
-        <v>1073</v>
+        <v>270</v>
       </c>
       <c r="D120" s="1" t="s">
-        <v>1167</v>
+        <v>829</v>
       </c>
       <c r="E120" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F120" s="1" t="s">
-        <v>1074</v>
+        <v>695</v>
       </c>
       <c r="G120" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I120" s="1" t="s">
         <v>337</v>
@@ -15971,22 +16078,22 @@
     </row>
     <row r="121" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A121" s="2" t="s">
-        <v>2767</v>
+        <v>1072</v>
       </c>
       <c r="B121" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C121" s="1" t="s">
-        <v>2766</v>
+        <v>1073</v>
       </c>
       <c r="D121" s="1" t="s">
-        <v>2768</v>
+        <v>1167</v>
       </c>
       <c r="E121" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F121" s="1" t="s">
-        <v>2769</v>
+        <v>1074</v>
       </c>
       <c r="G121" t="s">
         <v>19</v>
@@ -15997,7 +16104,7 @@
     </row>
     <row r="122" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A122" s="2" t="s">
-        <v>2838</v>
+        <v>2767</v>
       </c>
       <c r="B122" s="1" t="s">
         <v>10</v>
@@ -16006,16 +16113,16 @@
         <v>2766</v>
       </c>
       <c r="D122" s="1" t="s">
-        <v>2839</v>
+        <v>2768</v>
       </c>
       <c r="E122" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F122" s="1" t="s">
-        <v>2840</v>
+        <v>2769</v>
       </c>
       <c r="G122" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I122" s="1" t="s">
         <v>337</v>
@@ -16023,25 +16130,25 @@
     </row>
     <row r="123" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A123" s="2" t="s">
-        <v>1521</v>
+        <v>2838</v>
       </c>
       <c r="B123" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C123" s="1" t="s">
-        <v>1520</v>
+        <v>2766</v>
       </c>
       <c r="D123" s="1" t="s">
-        <v>1522</v>
+        <v>2839</v>
       </c>
       <c r="E123" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F123" s="1" t="s">
-        <v>1523</v>
+        <v>2840</v>
       </c>
       <c r="G123" t="s">
-        <v>19</v>
+        <v>776</v>
       </c>
       <c r="I123" s="1" t="s">
         <v>337</v>
@@ -16049,22 +16156,22 @@
     </row>
     <row r="124" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A124" s="2" t="s">
-        <v>2530</v>
+        <v>1521</v>
       </c>
       <c r="B124" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C124" s="1" t="s">
-        <v>2531</v>
+        <v>1520</v>
       </c>
       <c r="D124" s="1" t="s">
-        <v>2532</v>
+        <v>1522</v>
       </c>
       <c r="E124" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F124" s="1" t="s">
-        <v>2533</v>
+        <v>1523</v>
       </c>
       <c r="G124" t="s">
         <v>19</v>
@@ -16075,22 +16182,22 @@
     </row>
     <row r="125" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A125" s="2" t="s">
-        <v>1166</v>
+        <v>2530</v>
       </c>
       <c r="B125" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C125" s="1" t="s">
-        <v>1165</v>
+        <v>2531</v>
       </c>
       <c r="D125" s="1" t="s">
-        <v>1168</v>
+        <v>2532</v>
       </c>
       <c r="E125" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F125" s="1" t="s">
-        <v>1169</v>
+        <v>2533</v>
       </c>
       <c r="G125" t="s">
         <v>19</v>
@@ -16101,22 +16208,22 @@
     </row>
     <row r="126" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A126" s="2" t="s">
-        <v>1050</v>
+        <v>1166</v>
       </c>
       <c r="B126" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C126" s="1" t="s">
-        <v>1046</v>
+        <v>1165</v>
       </c>
       <c r="D126" s="1" t="s">
-        <v>1047</v>
+        <v>1168</v>
       </c>
       <c r="E126" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F126" s="1" t="s">
-        <v>1048</v>
+        <v>1169</v>
       </c>
       <c r="G126" t="s">
         <v>19</v>
@@ -16127,25 +16234,25 @@
     </row>
     <row r="127" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A127" s="2" t="s">
-        <v>2831</v>
+        <v>1050</v>
       </c>
       <c r="B127" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C127" s="1" t="s">
-        <v>2830</v>
+        <v>1046</v>
       </c>
       <c r="D127" s="1" t="s">
-        <v>2832</v>
+        <v>1047</v>
       </c>
       <c r="E127" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F127" s="1" t="s">
-        <v>2833</v>
-      </c>
-      <c r="G127" s="1" t="s">
-        <v>2834</v>
+        <v>1048</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
       </c>
       <c r="I127" s="1" t="s">
         <v>337</v>
@@ -16153,25 +16260,25 @@
     </row>
     <row r="128" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A128" s="2" t="s">
-        <v>1537</v>
+        <v>2831</v>
       </c>
       <c r="B128" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C128" s="1" t="s">
-        <v>1536</v>
+        <v>2830</v>
       </c>
       <c r="D128" s="1" t="s">
-        <v>1538</v>
+        <v>2832</v>
       </c>
       <c r="E128" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F128" s="1" t="s">
-        <v>1539</v>
-      </c>
-      <c r="G128" t="s">
-        <v>19</v>
+        <v>2833</v>
+      </c>
+      <c r="G128" s="1" t="s">
+        <v>2834</v>
       </c>
       <c r="I128" s="1" t="s">
         <v>337</v>
@@ -16179,25 +16286,25 @@
     </row>
     <row r="129" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A129" s="2" t="s">
-        <v>406</v>
+        <v>1537</v>
       </c>
       <c r="B129" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C129" s="1" t="s">
-        <v>402</v>
+        <v>1536</v>
       </c>
       <c r="D129" s="1" t="s">
-        <v>404</v>
+        <v>1538</v>
       </c>
       <c r="E129" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F129" s="1" t="s">
-        <v>408</v>
+        <v>1539</v>
       </c>
       <c r="G129" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I129" s="1" t="s">
         <v>337</v>
@@ -16205,22 +16312,22 @@
     </row>
     <row r="130" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A130" s="2" t="s">
-        <v>468</v>
+        <v>406</v>
       </c>
       <c r="B130" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C130" s="1" t="s">
-        <v>466</v>
+        <v>402</v>
       </c>
       <c r="D130" s="1" t="s">
-        <v>467</v>
+        <v>404</v>
       </c>
       <c r="E130" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F130" s="1" t="s">
-        <v>465</v>
+        <v>408</v>
       </c>
       <c r="G130" t="s">
         <v>330</v>
@@ -16231,7 +16338,7 @@
     </row>
     <row r="131" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A131" s="2" t="s">
-        <v>480</v>
+        <v>468</v>
       </c>
       <c r="B131" s="1" t="s">
         <v>10</v>
@@ -16240,16 +16347,16 @@
         <v>466</v>
       </c>
       <c r="D131" s="1" t="s">
-        <v>482</v>
+        <v>467</v>
       </c>
       <c r="E131" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F131" s="1" t="s">
-        <v>481</v>
+        <v>465</v>
       </c>
       <c r="G131" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I131" s="1" t="s">
         <v>337</v>
@@ -16257,25 +16364,25 @@
     </row>
     <row r="132" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A132" s="2" t="s">
-        <v>426</v>
+        <v>480</v>
       </c>
       <c r="B132" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C132" s="1" t="s">
-        <v>428</v>
+        <v>466</v>
       </c>
       <c r="D132" s="1" t="s">
-        <v>429</v>
+        <v>482</v>
       </c>
       <c r="E132" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F132" s="1" t="s">
-        <v>430</v>
+        <v>481</v>
       </c>
       <c r="G132" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I132" s="1" t="s">
         <v>337</v>
@@ -16283,25 +16390,25 @@
     </row>
     <row r="133" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A133" s="2" t="s">
-        <v>2579</v>
+        <v>426</v>
       </c>
       <c r="B133" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C133" s="1" t="s">
-        <v>2576</v>
+        <v>428</v>
       </c>
       <c r="D133" s="1" t="s">
-        <v>2577</v>
+        <v>429</v>
       </c>
       <c r="E133" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F133" s="1" t="s">
-        <v>2578</v>
+        <v>430</v>
       </c>
       <c r="G133" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I133" s="1" t="s">
         <v>337</v>
@@ -16309,7 +16416,7 @@
     </row>
     <row r="134" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A134" s="2" t="s">
-        <v>2847</v>
+        <v>2579</v>
       </c>
       <c r="B134" s="1" t="s">
         <v>10</v>
@@ -16318,16 +16425,16 @@
         <v>2576</v>
       </c>
       <c r="D134" s="1" t="s">
-        <v>2848</v>
+        <v>2577</v>
       </c>
       <c r="E134" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F134" s="1" t="s">
-        <v>2849</v>
+        <v>2578</v>
       </c>
       <c r="G134" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I134" s="1" t="s">
         <v>337</v>
@@ -16335,25 +16442,25 @@
     </row>
     <row r="135" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A135" s="2" t="s">
-        <v>1083</v>
+        <v>2847</v>
       </c>
       <c r="B135" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C135" s="1" t="s">
-        <v>1084</v>
+        <v>2576</v>
       </c>
       <c r="D135" s="1" t="s">
-        <v>1085</v>
+        <v>2848</v>
       </c>
       <c r="E135" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F135" s="1" t="s">
-        <v>1086</v>
+        <v>2849</v>
       </c>
       <c r="G135" t="s">
-        <v>19</v>
+        <v>776</v>
       </c>
       <c r="I135" s="1" t="s">
         <v>337</v>
@@ -16361,22 +16468,22 @@
     </row>
     <row r="136" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A136" s="2" t="s">
-        <v>1434</v>
+        <v>1083</v>
       </c>
       <c r="B136" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C136" s="1" t="s">
-        <v>1432</v>
+        <v>1084</v>
       </c>
       <c r="D136" s="1" t="s">
-        <v>1435</v>
+        <v>1085</v>
       </c>
       <c r="E136" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F136" s="1" t="s">
-        <v>1433</v>
+        <v>1086</v>
       </c>
       <c r="G136" t="s">
         <v>19</v>
@@ -16387,22 +16494,22 @@
     </row>
     <row r="137" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A137" s="2" t="s">
-        <v>161</v>
+        <v>1434</v>
       </c>
       <c r="B137" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C137" s="1" t="s">
-        <v>271</v>
+        <v>1432</v>
       </c>
       <c r="D137" s="1" t="s">
-        <v>2167</v>
+        <v>1435</v>
       </c>
       <c r="E137" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F137" s="1" t="s">
-        <v>160</v>
+        <v>1433</v>
       </c>
       <c r="G137" t="s">
         <v>19</v>
@@ -16413,22 +16520,22 @@
     </row>
     <row r="138" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A138" s="2" t="s">
-        <v>365</v>
+        <v>161</v>
       </c>
       <c r="B138" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C138" s="1" t="s">
-        <v>362</v>
+        <v>271</v>
       </c>
       <c r="D138" s="1" t="s">
-        <v>370</v>
+        <v>2167</v>
       </c>
       <c r="E138" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F138" s="1" t="s">
-        <v>361</v>
+        <v>160</v>
       </c>
       <c r="G138" t="s">
         <v>19</v>
@@ -16439,7 +16546,7 @@
     </row>
     <row r="139" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A139" s="2" t="s">
-        <v>366</v>
+        <v>365</v>
       </c>
       <c r="B139" s="1" t="s">
         <v>10</v>
@@ -16448,16 +16555,16 @@
         <v>362</v>
       </c>
       <c r="D139" s="1" t="s">
-        <v>363</v>
+        <v>370</v>
       </c>
       <c r="E139" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F139" s="1" t="s">
-        <v>364</v>
-      </c>
-      <c r="G139" s="1" t="s">
-        <v>330</v>
+        <v>361</v>
+      </c>
+      <c r="G139" t="s">
+        <v>19</v>
       </c>
       <c r="I139" s="1" t="s">
         <v>337</v>
@@ -16465,7 +16572,7 @@
     </row>
     <row r="140" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A140" s="2" t="s">
-        <v>1092</v>
+        <v>366</v>
       </c>
       <c r="B140" s="1" t="s">
         <v>10</v>
@@ -16474,16 +16581,16 @@
         <v>362</v>
       </c>
       <c r="D140" s="1" t="s">
-        <v>1093</v>
+        <v>363</v>
       </c>
       <c r="E140" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F140" s="1" t="s">
-        <v>1094</v>
-      </c>
-      <c r="G140" t="s">
-        <v>19</v>
+        <v>364</v>
+      </c>
+      <c r="G140" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="I140" s="1" t="s">
         <v>337</v>
@@ -16491,7 +16598,7 @@
     </row>
     <row r="141" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A141" s="2" t="s">
-        <v>2811</v>
+        <v>1092</v>
       </c>
       <c r="B141" s="1" t="s">
         <v>10</v>
@@ -16500,16 +16607,16 @@
         <v>362</v>
       </c>
       <c r="D141" s="1" t="s">
-        <v>2812</v>
+        <v>1093</v>
       </c>
       <c r="E141" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F141" s="1" t="s">
-        <v>2813</v>
+        <v>1094</v>
       </c>
       <c r="G141" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I141" s="1" t="s">
         <v>337</v>
@@ -16517,25 +16624,25 @@
     </row>
     <row r="142" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A142" s="2" t="s">
-        <v>152</v>
+        <v>2811</v>
       </c>
       <c r="B142" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C142" s="1" t="s">
-        <v>272</v>
+        <v>362</v>
       </c>
       <c r="D142" s="1" t="s">
-        <v>3161</v>
+        <v>2812</v>
       </c>
       <c r="E142" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F142" s="1" t="s">
-        <v>3162</v>
+        <v>2813</v>
       </c>
       <c r="G142" t="s">
-        <v>19</v>
+        <v>776</v>
       </c>
       <c r="I142" s="1" t="s">
         <v>337</v>
@@ -16543,25 +16650,25 @@
     </row>
     <row r="143" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A143" s="2" t="s">
-        <v>2860</v>
+        <v>152</v>
       </c>
       <c r="B143" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C143" s="1" t="s">
-        <v>2859</v>
+        <v>272</v>
       </c>
       <c r="D143" s="1" t="s">
-        <v>2861</v>
+        <v>3161</v>
       </c>
       <c r="E143" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F143" s="1" t="s">
-        <v>2862</v>
+        <v>3162</v>
       </c>
       <c r="G143" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I143" s="1" t="s">
         <v>337</v>
@@ -16569,25 +16676,25 @@
     </row>
     <row r="144" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A144" s="2" t="s">
-        <v>155</v>
+        <v>2860</v>
       </c>
       <c r="B144" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C144" s="1" t="s">
-        <v>273</v>
+        <v>2859</v>
       </c>
       <c r="D144" s="1" t="s">
-        <v>154</v>
+        <v>2861</v>
       </c>
       <c r="E144" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F144" s="1" t="s">
-        <v>153</v>
+        <v>2862</v>
       </c>
       <c r="G144" t="s">
-        <v>19</v>
+        <v>776</v>
       </c>
       <c r="I144" s="1" t="s">
         <v>337</v>
@@ -16595,7 +16702,7 @@
     </row>
     <row r="145" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A145" s="2" t="s">
-        <v>448</v>
+        <v>155</v>
       </c>
       <c r="B145" s="1" t="s">
         <v>10</v>
@@ -16604,16 +16711,16 @@
         <v>273</v>
       </c>
       <c r="D145" s="1" t="s">
-        <v>449</v>
+        <v>154</v>
       </c>
       <c r="E145" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F145" s="1" t="s">
-        <v>450</v>
+        <v>153</v>
       </c>
       <c r="G145" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I145" s="1" t="s">
         <v>337</v>
@@ -16621,25 +16728,25 @@
     </row>
     <row r="146" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A146" s="2" t="s">
-        <v>1026</v>
+        <v>448</v>
       </c>
       <c r="B146" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C146" s="1" t="s">
-        <v>1025</v>
+        <v>273</v>
       </c>
       <c r="D146" s="1" t="s">
-        <v>1040</v>
+        <v>449</v>
       </c>
       <c r="E146" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F146" s="1" t="s">
-        <v>1027</v>
+        <v>450</v>
       </c>
       <c r="G146" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I146" s="1" t="s">
         <v>337</v>
@@ -16647,7 +16754,7 @@
     </row>
     <row r="147" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A147" s="2" t="s">
-        <v>1448</v>
+        <v>1026</v>
       </c>
       <c r="B147" s="1" t="s">
         <v>10</v>
@@ -16656,16 +16763,16 @@
         <v>1025</v>
       </c>
       <c r="D147" s="1" t="s">
-        <v>1449</v>
+        <v>1040</v>
       </c>
       <c r="E147" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F147" s="1" t="s">
-        <v>1450</v>
+        <v>1027</v>
       </c>
       <c r="G147" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I147" s="1" t="s">
         <v>337</v>
@@ -16673,25 +16780,25 @@
     </row>
     <row r="148" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A148" s="2" t="s">
-        <v>1038</v>
+        <v>1448</v>
       </c>
       <c r="B148" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C148" s="1" t="s">
-        <v>1037</v>
+        <v>1025</v>
       </c>
       <c r="D148" s="1" t="s">
-        <v>1039</v>
+        <v>1449</v>
       </c>
       <c r="E148" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F148" s="1" t="s">
-        <v>1036</v>
+        <v>1450</v>
       </c>
       <c r="G148" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I148" s="1" t="s">
         <v>337</v>
@@ -16699,7 +16806,7 @@
     </row>
     <row r="149" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A149" s="2" t="s">
-        <v>1451</v>
+        <v>1038</v>
       </c>
       <c r="B149" s="1" t="s">
         <v>10</v>
@@ -16708,16 +16815,16 @@
         <v>1037</v>
       </c>
       <c r="D149" s="1" t="s">
-        <v>1452</v>
+        <v>1039</v>
       </c>
       <c r="E149" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F149" s="1" t="s">
-        <v>1453</v>
+        <v>1036</v>
       </c>
       <c r="G149" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I149" s="1" t="s">
         <v>337</v>
@@ -16725,22 +16832,22 @@
     </row>
     <row r="150" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A150" s="2" t="s">
-        <v>940</v>
+        <v>1451</v>
       </c>
       <c r="B150" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C150" s="1" t="s">
-        <v>941</v>
+        <v>1037</v>
       </c>
       <c r="D150" s="1" t="s">
-        <v>942</v>
+        <v>1452</v>
       </c>
       <c r="E150" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F150" s="1" t="s">
-        <v>943</v>
+        <v>1453</v>
       </c>
       <c r="G150" t="s">
         <v>330</v>
@@ -16751,25 +16858,25 @@
     </row>
     <row r="151" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A151" s="2" t="s">
-        <v>1282</v>
+        <v>940</v>
       </c>
       <c r="B151" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C151" s="1" t="s">
-        <v>1283</v>
+        <v>941</v>
       </c>
       <c r="D151" s="1" t="s">
-        <v>1284</v>
+        <v>942</v>
       </c>
       <c r="E151" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F151" s="1" t="s">
-        <v>1577</v>
-      </c>
-      <c r="G151" s="1" t="s">
-        <v>19</v>
+        <v>943</v>
+      </c>
+      <c r="G151" t="s">
+        <v>330</v>
       </c>
       <c r="I151" s="1" t="s">
         <v>337</v>
@@ -16777,24 +16884,24 @@
     </row>
     <row r="152" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A152" s="2" t="s">
-        <v>1154</v>
+        <v>1282</v>
       </c>
       <c r="B152" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C152" s="1" t="s">
-        <v>1153</v>
+        <v>1283</v>
       </c>
       <c r="D152" s="1" t="s">
-        <v>1156</v>
+        <v>1284</v>
       </c>
       <c r="E152" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F152" s="1" t="s">
-        <v>1155</v>
-      </c>
-      <c r="G152" t="s">
+        <v>1577</v>
+      </c>
+      <c r="G152" s="1" t="s">
         <v>19</v>
       </c>
       <c r="I152" s="1" t="s">
@@ -16803,22 +16910,22 @@
     </row>
     <row r="153" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A153" s="2" t="s">
-        <v>1570</v>
+        <v>1154</v>
       </c>
       <c r="B153" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C153" s="1" t="s">
-        <v>1571</v>
+        <v>1153</v>
       </c>
       <c r="D153" s="1" t="s">
-        <v>1572</v>
+        <v>1156</v>
       </c>
       <c r="E153" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F153" s="1" t="s">
-        <v>1573</v>
+        <v>1155</v>
       </c>
       <c r="G153" t="s">
         <v>19</v>
@@ -16829,22 +16936,22 @@
     </row>
     <row r="154" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A154" s="2" t="s">
-        <v>1676</v>
+        <v>1570</v>
       </c>
       <c r="B154" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C154" s="1" t="s">
-        <v>1677</v>
+        <v>1571</v>
       </c>
       <c r="D154" s="1" t="s">
-        <v>1678</v>
+        <v>1572</v>
       </c>
       <c r="E154" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F154" s="1" t="s">
-        <v>1679</v>
+        <v>1573</v>
       </c>
       <c r="G154" t="s">
         <v>19</v>
@@ -16855,22 +16962,22 @@
     </row>
     <row r="155" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A155" s="2" t="s">
-        <v>2225</v>
+        <v>1676</v>
       </c>
       <c r="B155" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C155" s="1" t="s">
-        <v>2226</v>
+        <v>1677</v>
       </c>
       <c r="D155" s="1" t="s">
-        <v>2227</v>
+        <v>1678</v>
       </c>
       <c r="E155" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F155" s="1" t="s">
-        <v>2228</v>
+        <v>1679</v>
       </c>
       <c r="G155" t="s">
         <v>19</v>
@@ -16881,22 +16988,22 @@
     </row>
     <row r="156" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A156" s="2" t="s">
-        <v>1470</v>
+        <v>2225</v>
       </c>
       <c r="B156" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C156" s="1" t="s">
-        <v>1469</v>
+        <v>2226</v>
       </c>
       <c r="D156" s="1" t="s">
-        <v>1471</v>
+        <v>2227</v>
       </c>
       <c r="E156" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F156" s="1" t="s">
-        <v>1472</v>
+        <v>2228</v>
       </c>
       <c r="G156" t="s">
         <v>19</v>
@@ -16907,25 +17014,25 @@
     </row>
     <row r="157" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A157" s="2" t="s">
-        <v>676</v>
+        <v>1470</v>
       </c>
       <c r="B157" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C157" s="1" t="s">
-        <v>675</v>
+        <v>1469</v>
       </c>
       <c r="D157" s="1" t="s">
-        <v>674</v>
+        <v>1471</v>
       </c>
       <c r="E157" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F157" s="1" t="s">
-        <v>673</v>
+        <v>1472</v>
       </c>
       <c r="G157" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I157" s="1" t="s">
         <v>337</v>
@@ -16933,7 +17040,7 @@
     </row>
     <row r="158" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A158" s="2" t="s">
-        <v>3049</v>
+        <v>676</v>
       </c>
       <c r="B158" s="1" t="s">
         <v>10</v>
@@ -16942,16 +17049,16 @@
         <v>675</v>
       </c>
       <c r="D158" s="1" t="s">
-        <v>3050</v>
+        <v>674</v>
       </c>
       <c r="E158" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F158" s="1" t="s">
-        <v>3051</v>
+        <v>673</v>
       </c>
       <c r="G158" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I158" s="1" t="s">
         <v>337</v>
@@ -16959,25 +17066,25 @@
     </row>
     <row r="159" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A159" s="2" t="s">
-        <v>684</v>
+        <v>3049</v>
       </c>
       <c r="B159" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C159" s="1" t="s">
-        <v>683</v>
+        <v>675</v>
       </c>
       <c r="D159" s="1" t="s">
-        <v>682</v>
+        <v>3050</v>
       </c>
       <c r="E159" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F159" s="1" t="s">
-        <v>693</v>
+        <v>3051</v>
       </c>
       <c r="G159" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I159" s="1" t="s">
         <v>337</v>
@@ -16985,25 +17092,25 @@
     </row>
     <row r="160" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A160" s="2" t="s">
-        <v>2638</v>
+        <v>684</v>
       </c>
       <c r="B160" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C160" s="1" t="s">
-        <v>2637</v>
+        <v>683</v>
       </c>
       <c r="D160" s="1" t="s">
-        <v>2959</v>
+        <v>682</v>
       </c>
       <c r="E160" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F160" s="1" t="s">
-        <v>2636</v>
+        <v>693</v>
       </c>
       <c r="G160" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I160" s="1" t="s">
         <v>337</v>
@@ -17011,22 +17118,22 @@
     </row>
     <row r="161" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A161" s="2" t="s">
-        <v>2977</v>
+        <v>2638</v>
       </c>
       <c r="B161" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C161" s="1" t="s">
-        <v>2975</v>
+        <v>2637</v>
       </c>
       <c r="D161" s="1" t="s">
-        <v>2976</v>
+        <v>2959</v>
       </c>
       <c r="E161" s="1" t="s">
-        <v>774</v>
+        <v>12</v>
       </c>
       <c r="F161" s="1" t="s">
-        <v>2978</v>
+        <v>2636</v>
       </c>
       <c r="G161" t="s">
         <v>19</v>
@@ -17037,22 +17144,22 @@
     </row>
     <row r="162" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A162" s="2" t="s">
-        <v>2957</v>
+        <v>2977</v>
       </c>
       <c r="B162" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C162" s="1" t="s">
-        <v>2958</v>
+        <v>2975</v>
       </c>
       <c r="D162" s="1" t="s">
-        <v>2960</v>
+        <v>2976</v>
       </c>
       <c r="E162" s="1" t="s">
-        <v>12</v>
+        <v>774</v>
       </c>
       <c r="F162" s="1" t="s">
-        <v>2961</v>
+        <v>2978</v>
       </c>
       <c r="G162" t="s">
         <v>19</v>
@@ -17063,22 +17170,22 @@
     </row>
     <row r="163" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A163" s="2" t="s">
-        <v>3000</v>
+        <v>2957</v>
       </c>
       <c r="B163" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C163" s="1" t="s">
-        <v>2998</v>
+        <v>2958</v>
       </c>
       <c r="D163" s="1" t="s">
-        <v>2999</v>
+        <v>2960</v>
       </c>
       <c r="E163" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F163" s="1" t="s">
-        <v>3001</v>
+        <v>2961</v>
       </c>
       <c r="G163" t="s">
         <v>19</v>
@@ -17089,22 +17196,22 @@
     </row>
     <row r="164" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A164" s="2" t="s">
-        <v>603</v>
+        <v>3000</v>
       </c>
       <c r="B164" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C164" s="1" t="s">
-        <v>604</v>
+        <v>2998</v>
       </c>
       <c r="D164" s="1" t="s">
-        <v>605</v>
+        <v>2999</v>
       </c>
       <c r="E164" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F164" s="1" t="s">
-        <v>606</v>
+        <v>3001</v>
       </c>
       <c r="G164" t="s">
         <v>19</v>
@@ -17115,25 +17222,25 @@
     </row>
     <row r="165" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A165" s="2" t="s">
-        <v>398</v>
+        <v>603</v>
       </c>
       <c r="B165" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C165" s="1" t="s">
-        <v>397</v>
+        <v>604</v>
       </c>
       <c r="D165" s="1" t="s">
-        <v>400</v>
+        <v>605</v>
       </c>
       <c r="E165" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F165" s="1" t="s">
-        <v>399</v>
+        <v>606</v>
       </c>
       <c r="G165" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I165" s="1" t="s">
         <v>337</v>
@@ -17141,24 +17248,24 @@
     </row>
     <row r="166" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A166" s="2" t="s">
-        <v>329</v>
+        <v>398</v>
       </c>
       <c r="B166" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C166" s="1" t="s">
-        <v>328</v>
+        <v>397</v>
       </c>
       <c r="D166" s="1" t="s">
-        <v>327</v>
+        <v>400</v>
       </c>
       <c r="E166" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F166" s="1" t="s">
-        <v>326</v>
-      </c>
-      <c r="G166" s="1" t="s">
+        <v>399</v>
+      </c>
+      <c r="G166" t="s">
         <v>330</v>
       </c>
       <c r="I166" s="1" t="s">
@@ -17167,7 +17274,7 @@
     </row>
     <row r="167" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A167" s="2" t="s">
-        <v>336</v>
+        <v>329</v>
       </c>
       <c r="B167" s="1" t="s">
         <v>10</v>
@@ -17176,16 +17283,16 @@
         <v>328</v>
       </c>
       <c r="D167" s="1" t="s">
-        <v>335</v>
+        <v>327</v>
       </c>
       <c r="E167" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F167" s="1" t="s">
-        <v>1078</v>
-      </c>
-      <c r="G167" t="s">
-        <v>19</v>
+        <v>326</v>
+      </c>
+      <c r="G167" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="I167" s="1" t="s">
         <v>337</v>
@@ -17193,22 +17300,22 @@
     </row>
     <row r="168" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A168" s="2" t="s">
-        <v>1150</v>
+        <v>336</v>
       </c>
       <c r="B168" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C168" s="1" t="s">
-        <v>1149</v>
+        <v>328</v>
       </c>
       <c r="D168" s="1" t="s">
-        <v>1152</v>
+        <v>335</v>
       </c>
       <c r="E168" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F168" s="1" t="s">
-        <v>1151</v>
+        <v>1078</v>
       </c>
       <c r="G168" t="s">
         <v>19</v>
@@ -17219,22 +17326,22 @@
     </row>
     <row r="169" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A169" s="2" t="s">
-        <v>2698</v>
+        <v>1150</v>
       </c>
       <c r="B169" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C169" s="1" t="s">
-        <v>2695</v>
+        <v>1149</v>
       </c>
       <c r="D169" s="1" t="s">
-        <v>2697</v>
+        <v>1152</v>
       </c>
       <c r="E169" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F169" s="1" t="s">
-        <v>2696</v>
+        <v>1151</v>
       </c>
       <c r="G169" t="s">
         <v>19</v>
@@ -17245,22 +17352,22 @@
     </row>
     <row r="170" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A170" s="2" t="s">
-        <v>1698</v>
+        <v>2698</v>
       </c>
       <c r="B170" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C170" s="1" t="s">
-        <v>1699</v>
+        <v>2695</v>
       </c>
       <c r="D170" s="1" t="s">
-        <v>1700</v>
+        <v>2697</v>
       </c>
       <c r="E170" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F170" s="1" t="s">
-        <v>1701</v>
+        <v>2696</v>
       </c>
       <c r="G170" t="s">
         <v>19</v>
@@ -17271,25 +17378,25 @@
     </row>
     <row r="171" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A171" s="2" t="s">
-        <v>1809</v>
+        <v>1698</v>
       </c>
       <c r="B171" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C171" s="1" t="s">
-        <v>1808</v>
+        <v>1699</v>
       </c>
       <c r="D171" s="1" t="s">
-        <v>1810</v>
+        <v>1700</v>
       </c>
       <c r="E171" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F171" s="1" t="s">
-        <v>1811</v>
-      </c>
-      <c r="G171" s="1" t="s">
-        <v>330</v>
+        <v>1701</v>
+      </c>
+      <c r="G171" t="s">
+        <v>19</v>
       </c>
       <c r="I171" s="1" t="s">
         <v>337</v>
@@ -17297,25 +17404,25 @@
     </row>
     <row r="172" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A172" s="2" t="s">
-        <v>1075</v>
+        <v>1809</v>
       </c>
       <c r="B172" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C172" s="1" t="s">
-        <v>1076</v>
+        <v>1808</v>
       </c>
       <c r="D172" s="1" t="s">
-        <v>1077</v>
+        <v>1810</v>
       </c>
       <c r="E172" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F172" s="1" t="s">
-        <v>1079</v>
-      </c>
-      <c r="G172" t="s">
-        <v>19</v>
+        <v>1811</v>
+      </c>
+      <c r="G172" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="I172" s="1" t="s">
         <v>337</v>
@@ -17323,13 +17430,13 @@
     </row>
     <row r="173" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A173" s="2" t="s">
-        <v>1670</v>
+        <v>1075</v>
       </c>
       <c r="B173" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C173" s="1" t="s">
-        <v>1669</v>
+        <v>1076</v>
       </c>
       <c r="D173" s="1" t="s">
         <v>1077</v>
@@ -17338,7 +17445,7 @@
         <v>12</v>
       </c>
       <c r="F173" s="1" t="s">
-        <v>1671</v>
+        <v>1079</v>
       </c>
       <c r="G173" t="s">
         <v>19</v>
@@ -17349,25 +17456,25 @@
     </row>
     <row r="174" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A174" s="2" t="s">
-        <v>1876</v>
+        <v>1670</v>
       </c>
       <c r="B174" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C174" s="1" t="s">
-        <v>1875</v>
+        <v>1669</v>
       </c>
       <c r="D174" s="1" t="s">
-        <v>1877</v>
+        <v>1077</v>
       </c>
       <c r="E174" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F174" s="1" t="s">
-        <v>1878</v>
-      </c>
-      <c r="G174" s="1" t="s">
-        <v>330</v>
+        <v>1671</v>
+      </c>
+      <c r="G174" t="s">
+        <v>19</v>
       </c>
       <c r="I174" s="1" t="s">
         <v>337</v>
@@ -17375,25 +17482,25 @@
     </row>
     <row r="175" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A175" s="2" t="s">
-        <v>3074</v>
+        <v>1876</v>
       </c>
       <c r="B175" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C175" s="1" t="s">
-        <v>3072</v>
+        <v>1875</v>
       </c>
       <c r="D175" s="1" t="s">
-        <v>3075</v>
+        <v>1877</v>
       </c>
       <c r="E175" s="1" t="s">
-        <v>774</v>
+        <v>12</v>
       </c>
       <c r="F175" s="1" t="s">
-        <v>3073</v>
-      </c>
-      <c r="G175" t="s">
-        <v>19</v>
+        <v>1878</v>
+      </c>
+      <c r="G175" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="I175" s="1" t="s">
         <v>337</v>
@@ -17401,22 +17508,22 @@
     </row>
     <row r="176" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A176" s="2" t="s">
-        <v>3160</v>
+        <v>3074</v>
       </c>
       <c r="B176" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C176" s="1" t="s">
-        <v>3157</v>
+        <v>3072</v>
       </c>
       <c r="D176" s="1" t="s">
-        <v>3158</v>
+        <v>3075</v>
       </c>
       <c r="E176" s="1" t="s">
         <v>774</v>
       </c>
       <c r="F176" s="1" t="s">
-        <v>3159</v>
+        <v>3073</v>
       </c>
       <c r="G176" t="s">
         <v>19</v>
@@ -17427,22 +17534,22 @@
     </row>
     <row r="177" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A177" s="2" t="s">
-        <v>1267</v>
+        <v>3160</v>
       </c>
       <c r="B177" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C177" s="1" t="s">
-        <v>1266</v>
+        <v>3157</v>
       </c>
       <c r="D177" s="1" t="s">
-        <v>1268</v>
+        <v>3158</v>
       </c>
       <c r="E177" s="1" t="s">
-        <v>12</v>
+        <v>774</v>
       </c>
       <c r="F177" s="1" t="s">
-        <v>1269</v>
+        <v>3159</v>
       </c>
       <c r="G177" t="s">
         <v>19</v>
@@ -17453,22 +17560,22 @@
     </row>
     <row r="178" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A178" s="2" t="s">
-        <v>1099</v>
+        <v>1267</v>
       </c>
       <c r="B178" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C178" s="1" t="s">
-        <v>1100</v>
+        <v>1266</v>
       </c>
       <c r="D178" s="1" t="s">
-        <v>1101</v>
+        <v>1268</v>
       </c>
       <c r="E178" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F178" s="1" t="s">
-        <v>1102</v>
+        <v>1269</v>
       </c>
       <c r="G178" t="s">
         <v>19</v>
@@ -17479,7 +17586,7 @@
     </row>
     <row r="179" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A179" s="2" t="s">
-        <v>2824</v>
+        <v>1099</v>
       </c>
       <c r="B179" s="1" t="s">
         <v>10</v>
@@ -17488,16 +17595,16 @@
         <v>1100</v>
       </c>
       <c r="D179" s="1" t="s">
-        <v>2825</v>
+        <v>1101</v>
       </c>
       <c r="E179" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F179" s="1" t="s">
-        <v>2826</v>
+        <v>1102</v>
       </c>
       <c r="G179" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I179" s="1" t="s">
         <v>337</v>
@@ -17505,25 +17612,25 @@
     </row>
     <row r="180" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A180" s="2" t="s">
-        <v>2737</v>
+        <v>2824</v>
       </c>
       <c r="B180" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C180" s="1" t="s">
-        <v>2736</v>
+        <v>1100</v>
       </c>
       <c r="D180" s="1" t="s">
-        <v>2738</v>
+        <v>2825</v>
       </c>
       <c r="E180" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F180" s="1" t="s">
-        <v>2739</v>
+        <v>2826</v>
       </c>
       <c r="G180" t="s">
-        <v>19</v>
+        <v>776</v>
       </c>
       <c r="I180" s="1" t="s">
         <v>337</v>
@@ -17531,22 +17638,22 @@
     </row>
     <row r="181" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A181" s="2" t="s">
-        <v>824</v>
+        <v>2737</v>
       </c>
       <c r="B181" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C181" s="1" t="s">
-        <v>823</v>
+        <v>2736</v>
       </c>
       <c r="D181" s="1" t="s">
-        <v>825</v>
+        <v>2738</v>
       </c>
       <c r="E181" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F181" s="1" t="s">
-        <v>822</v>
+        <v>2739</v>
       </c>
       <c r="G181" t="s">
         <v>19</v>
@@ -17557,22 +17664,22 @@
     </row>
     <row r="182" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A182" s="2" t="s">
-        <v>1912</v>
+        <v>824</v>
       </c>
       <c r="B182" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C182" s="1" t="s">
-        <v>1911</v>
+        <v>823</v>
       </c>
       <c r="D182" s="1" t="s">
-        <v>1913</v>
+        <v>825</v>
       </c>
       <c r="E182" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F182" s="1" t="s">
-        <v>1914</v>
+        <v>822</v>
       </c>
       <c r="G182" t="s">
         <v>19</v>
@@ -17583,22 +17690,22 @@
     </row>
     <row r="183" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A183" s="2" t="s">
-        <v>2772</v>
+        <v>1912</v>
       </c>
       <c r="B183" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C183" s="1" t="s">
-        <v>2770</v>
+        <v>1911</v>
       </c>
       <c r="D183" s="1" t="s">
-        <v>2771</v>
+        <v>1913</v>
       </c>
       <c r="E183" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F183" s="1" t="s">
-        <v>2773</v>
+        <v>1914</v>
       </c>
       <c r="G183" t="s">
         <v>19</v>
@@ -17609,7 +17716,7 @@
     </row>
     <row r="184" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A184" s="2" t="s">
-        <v>2841</v>
+        <v>2772</v>
       </c>
       <c r="B184" s="1" t="s">
         <v>10</v>
@@ -17618,16 +17725,16 @@
         <v>2770</v>
       </c>
       <c r="D184" s="1" t="s">
-        <v>2842</v>
+        <v>2771</v>
       </c>
       <c r="E184" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F184" s="1" t="s">
-        <v>2843</v>
+        <v>2773</v>
       </c>
       <c r="G184" t="s">
-        <v>776</v>
+        <v>19</v>
       </c>
       <c r="I184" s="1" t="s">
         <v>337</v>
@@ -17635,25 +17742,25 @@
     </row>
     <row r="185" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A185" s="2" t="s">
-        <v>1298</v>
+        <v>2841</v>
       </c>
       <c r="B185" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C185" s="1" t="s">
-        <v>1297</v>
+        <v>2770</v>
       </c>
       <c r="D185" s="1" t="s">
-        <v>1299</v>
+        <v>2842</v>
       </c>
       <c r="E185" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F185" s="1" t="s">
-        <v>1300</v>
+        <v>2843</v>
       </c>
       <c r="G185" t="s">
-        <v>19</v>
+        <v>776</v>
       </c>
       <c r="I185" s="1" t="s">
         <v>337</v>
@@ -17661,7 +17768,7 @@
     </row>
     <row r="186" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A186" s="2" t="s">
-        <v>2329</v>
+        <v>1298</v>
       </c>
       <c r="B186" s="1" t="s">
         <v>10</v>
@@ -17670,16 +17777,16 @@
         <v>1297</v>
       </c>
       <c r="D186" s="1" t="s">
-        <v>2330</v>
+        <v>1299</v>
       </c>
       <c r="E186" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F186" s="1" t="s">
-        <v>2331</v>
-      </c>
-      <c r="G186" s="1" t="s">
-        <v>330</v>
+        <v>1300</v>
+      </c>
+      <c r="G186" t="s">
+        <v>19</v>
       </c>
       <c r="I186" s="1" t="s">
         <v>337</v>
@@ -17687,22 +17794,22 @@
     </row>
     <row r="187" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A187" s="2" t="s">
-        <v>2304</v>
+        <v>2329</v>
       </c>
       <c r="B187" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C187" s="1" t="s">
-        <v>2305</v>
+        <v>1297</v>
       </c>
       <c r="D187" s="1" t="s">
-        <v>2306</v>
+        <v>2330</v>
       </c>
       <c r="E187" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F187" s="1" t="s">
-        <v>2307</v>
+        <v>2331</v>
       </c>
       <c r="G187" s="1" t="s">
         <v>330</v>
@@ -17713,25 +17820,25 @@
     </row>
     <row r="188" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A188" s="2" t="s">
-        <v>619</v>
+        <v>2304</v>
       </c>
       <c r="B188" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C188" s="1" t="s">
-        <v>618</v>
+        <v>2305</v>
       </c>
       <c r="D188" s="1" t="s">
-        <v>617</v>
+        <v>2306</v>
       </c>
       <c r="E188" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F188" s="1" t="s">
-        <v>616</v>
-      </c>
-      <c r="G188" t="s">
-        <v>19</v>
+        <v>2307</v>
+      </c>
+      <c r="G188" s="1" t="s">
+        <v>330</v>
       </c>
       <c r="I188" s="1" t="s">
         <v>337</v>
@@ -17739,22 +17846,22 @@
     </row>
     <row r="189" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A189" s="2" t="s">
-        <v>1383</v>
+        <v>619</v>
       </c>
       <c r="B189" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C189" s="1" t="s">
-        <v>1382</v>
+        <v>618</v>
       </c>
       <c r="D189" s="1" t="s">
-        <v>1384</v>
+        <v>617</v>
       </c>
       <c r="E189" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F189" s="1" t="s">
-        <v>1385</v>
+        <v>616</v>
       </c>
       <c r="G189" t="s">
         <v>19</v>
@@ -17765,22 +17872,22 @@
     </row>
     <row r="190" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A190" s="2" t="s">
-        <v>134</v>
+        <v>1383</v>
       </c>
       <c r="B190" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C190" s="1" t="s">
-        <v>269</v>
+        <v>1382</v>
       </c>
       <c r="D190" s="1" t="s">
-        <v>133</v>
+        <v>1384</v>
       </c>
       <c r="E190" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F190" s="1" t="s">
-        <v>131</v>
+        <v>1385</v>
       </c>
       <c r="G190" t="s">
         <v>19</v>
@@ -17791,22 +17898,22 @@
     </row>
     <row r="191" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A191" s="2" t="s">
-        <v>1533</v>
+        <v>134</v>
       </c>
       <c r="B191" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C191" s="1" t="s">
-        <v>1532</v>
+        <v>269</v>
       </c>
       <c r="D191" s="1" t="s">
-        <v>1534</v>
+        <v>133</v>
       </c>
       <c r="E191" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F191" s="1" t="s">
-        <v>1535</v>
+        <v>131</v>
       </c>
       <c r="G191" t="s">
         <v>19</v>
@@ -17817,25 +17924,25 @@
     </row>
     <row r="192" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A192" s="2" t="s">
-        <v>687</v>
+        <v>1533</v>
       </c>
       <c r="B192" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C192" s="1" t="s">
-        <v>686</v>
+        <v>1532</v>
       </c>
       <c r="D192" s="1" t="s">
-        <v>685</v>
+        <v>1534</v>
       </c>
       <c r="E192" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F192" s="1" t="s">
-        <v>692</v>
+        <v>1535</v>
       </c>
       <c r="G192" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I192" s="1" t="s">
         <v>337</v>
@@ -17843,25 +17950,25 @@
     </row>
     <row r="193" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A193" s="2" t="s">
-        <v>1049</v>
+        <v>687</v>
       </c>
       <c r="B193" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C193" s="1" t="s">
-        <v>1051</v>
+        <v>686</v>
       </c>
       <c r="D193" s="1" t="s">
-        <v>1052</v>
+        <v>685</v>
       </c>
       <c r="E193" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F193" s="1" t="s">
-        <v>1053</v>
+        <v>692</v>
       </c>
       <c r="G193" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I193" s="1" t="s">
         <v>337</v>
@@ -17869,25 +17976,25 @@
     </row>
     <row r="194" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A194" s="2" t="s">
-        <v>396</v>
+        <v>1049</v>
       </c>
       <c r="B194" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C194" s="1" t="s">
-        <v>395</v>
+        <v>1051</v>
       </c>
       <c r="D194" s="1" t="s">
-        <v>401</v>
+        <v>1052</v>
       </c>
       <c r="E194" s="1" t="s">
         <v>12</v>
       </c>
       <c r="F194" s="1" t="s">
-        <v>399</v>
+        <v>1053</v>
       </c>
       <c r="G194" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I194" s="1" t="s">
         <v>337</v>
@@ -17895,25 +18002,25 @@
     </row>
     <row r="195" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A195" s="2" t="s">
-        <v>2956</v>
+        <v>396</v>
       </c>
       <c r="B195" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C195" s="1" t="s">
-        <v>2953</v>
+        <v>395</v>
       </c>
       <c r="D195" s="1" t="s">
-        <v>2955</v>
+        <v>401</v>
       </c>
       <c r="E195" s="1" t="s">
-        <v>774</v>
+        <v>12</v>
       </c>
       <c r="F195" s="1" t="s">
-        <v>2954</v>
+        <v>399</v>
       </c>
       <c r="G195" t="s">
-        <v>19</v>
+        <v>330</v>
       </c>
       <c r="I195" s="1" t="s">
         <v>337</v>
@@ -17921,22 +18028,22 @@
     </row>
     <row r="196" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A196" s="2" t="s">
-        <v>3055</v>
+        <v>2956</v>
       </c>
       <c r="B196" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C196" s="1" t="s">
-        <v>3054</v>
+        <v>2953</v>
       </c>
       <c r="D196" s="1" t="s">
-        <v>3053</v>
+        <v>2955</v>
       </c>
       <c r="E196" s="1" t="s">
         <v>774</v>
       </c>
       <c r="F196" s="1" t="s">
-        <v>3052</v>
+        <v>2954</v>
       </c>
       <c r="G196" t="s">
         <v>19</v>
@@ -17947,25 +18054,25 @@
     </row>
     <row r="197" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A197" s="2" t="s">
-        <v>691</v>
+        <v>3055</v>
       </c>
       <c r="B197" s="1" t="s">
         <v>10</v>
       </c>
       <c r="C197" s="1" t="s">
-        <v>690</v>
+        <v>3054</v>
       </c>
       <c r="D197" s="1" t="s">
-        <v>689</v>
+        <v>3053</v>
       </c>
       <c r="E197" s="1" t="s">
-        <v>12</v>
+        <v>774</v>
       </c>
       <c r="F197" s="1" t="s">
-        <v>688</v>
+        <v>3052</v>
       </c>
       <c r="G197" t="s">
-        <v>330</v>
+        <v>19</v>
       </c>
       <c r="I197" s="1" t="s">
         <v>337</v>
@@ -17973,27 +18080,53 @@
     </row>
     <row r="198" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A198" s="2" t="s">
+        <v>691</v>
+      </c>
+      <c r="B198" s="1" t="s">
+        <v>10</v>
+      </c>
+      <c r="C198" s="1" t="s">
+        <v>690</v>
+      </c>
+      <c r="D198" s="1" t="s">
+        <v>689</v>
+      </c>
+      <c r="E198" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="F198" s="1" t="s">
+        <v>688</v>
+      </c>
+      <c r="G198" t="s">
+        <v>330</v>
+      </c>
+      <c r="I198" s="1" t="s">
+        <v>337</v>
+      </c>
+    </row>
+    <row r="199" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A199" s="2" t="s">
         <v>1644</v>
       </c>
-      <c r="B198" s="1" t="s">
+      <c r="B199" s="1" t="s">
         <v>1642</v>
       </c>
-      <c r="C198" s="1" t="s">
+      <c r="C199" s="1" t="s">
         <v>1643</v>
       </c>
-      <c r="D198" s="1" t="s">
+      <c r="D199" s="1" t="s">
         <v>1645</v>
       </c>
-      <c r="E198" s="1" t="s">
+      <c r="E199" s="1" t="s">
         <v>186</v>
       </c>
-      <c r="F198" s="1" t="s">
+      <c r="F199" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="G198" s="1" t="s">
+      <c r="G199" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="I198" s="1" t="s">
+      <c r="I199" s="1" t="s">
         <v>1648</v>
       </c>
     </row>
@@ -24572,18 +24705,21 @@
       </c>
     </row>
     <row r="105" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A105" s="2" t="s">
+        <v>3189</v>
+      </c>
       <c r="B105" t="s">
-        <v>17</v>
+        <v>3190</v>
       </c>
       <c r="C105" t="s">
-        <v>90</v>
+        <v>3191</v>
       </c>
       <c r="E105" s="1"/>
       <c r="G105" t="s">
-        <v>18</v>
+        <v>3192</v>
       </c>
       <c r="I105" t="s">
-        <v>20</v>
+        <v>814</v>
       </c>
     </row>
     <row r="106" spans="1:9" x14ac:dyDescent="0.3">
@@ -25600,7 +25736,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F77DF9D1-733F-4622-A5B9-9F6937E4842B}">
-  <dimension ref="A1:J80"/>
+  <dimension ref="A1:J82"/>
   <sheetFormatPr defaultRowHeight="14" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.58203125" style="2" bestFit="1" customWidth="1"/>
@@ -27925,6 +28061,64 @@
         <v>2107</v>
       </c>
     </row>
+    <row r="81" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A81" s="2" t="s">
+        <v>3182</v>
+      </c>
+      <c r="B81" s="3" t="s">
+        <v>3181</v>
+      </c>
+      <c r="C81" t="s">
+        <v>3188</v>
+      </c>
+      <c r="D81" t="s">
+        <v>3187</v>
+      </c>
+      <c r="E81" t="s">
+        <v>3183</v>
+      </c>
+      <c r="F81" t="s">
+        <v>3184</v>
+      </c>
+      <c r="G81" t="s">
+        <v>3185</v>
+      </c>
+      <c r="H81" t="s">
+        <v>3186</v>
+      </c>
+      <c r="I81" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="82" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A82" s="2" t="s">
+        <v>3194</v>
+      </c>
+      <c r="B82" s="3" t="s">
+        <v>3193</v>
+      </c>
+      <c r="C82" t="s">
+        <v>3195</v>
+      </c>
+      <c r="D82" t="s">
+        <v>3196</v>
+      </c>
+      <c r="E82" t="s">
+        <v>3197</v>
+      </c>
+      <c r="F82" t="s">
+        <v>3199</v>
+      </c>
+      <c r="G82" t="s">
+        <v>3200</v>
+      </c>
+      <c r="I82" t="s">
+        <v>3201</v>
+      </c>
+      <c r="J82" s="7" t="s">
+        <v>3198</v>
+      </c>
+    </row>
   </sheetData>
   <autoFilter ref="A1:J59" xr:uid="{F77DF9D1-733F-4622-A5B9-9F6937E4842B}">
     <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:J59">
@@ -27935,8 +28129,11 @@
   <conditionalFormatting sqref="A1:A1048576">
     <cfRule type="duplicateValues" dxfId="9" priority="1"/>
   </conditionalFormatting>
+  <hyperlinks>
+    <hyperlink ref="J82" r:id="rId1" xr:uid="{A6B84562-817B-4A0C-9A5C-E32F469917D4}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId2"/>
 </worksheet>
 </file>
 
